--- a/exports/meal_database_architecture_v1.xlsx
+++ b/exports/meal_database_architecture_v1.xlsx
@@ -500,7 +500,7 @@
         <v>["breakfast"]</v>
       </c>
       <c r="P2" t="str">
-        <v>{"macros_p":22}</v>
+        <v>{"macros_p":22,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low"}</v>
       </c>
     </row>
     <row r="3">
@@ -550,7 +550,7 @@
         <v>["breakfast","grilled"]</v>
       </c>
       <c r="P3" t="str">
-        <v>{"macros_p":38}</v>
+        <v>{"macros_p":38,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="4">
@@ -600,7 +600,7 @@
         <v>["breakfast","grilled"]</v>
       </c>
       <c r="P4" t="str">
-        <v>{"macros_p":33}</v>
+        <v>{"macros_p":33,"protein_family":"fish","meal_weight_class":"light","carb_level":"low"}</v>
       </c>
     </row>
     <row r="5">
@@ -650,7 +650,7 @@
         <v>["breakfast","grilled","low-carb"]</v>
       </c>
       <c r="P5" t="str">
-        <v>{"macros_p":21}</v>
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="6">
@@ -700,7 +700,7 @@
         <v>["breakfast"]</v>
       </c>
       <c r="P6" t="str">
-        <v>{"macros_p":37}</v>
+        <v>{"macros_p":37,"protein_family":"chicken","meal_weight_class":"light","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="7">
@@ -750,7 +750,7 @@
         <v>["breakfast","low-carb"]</v>
       </c>
       <c r="P7" t="str">
-        <v>{"macros_p":19}</v>
+        <v>{"macros_p":19,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low"}</v>
       </c>
     </row>
     <row r="8">
@@ -800,7 +800,7 @@
         <v>["breakfast","grilled","low-carb"]</v>
       </c>
       <c r="P8" t="str">
-        <v>{"macros_p":28}</v>
+        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="9">
@@ -850,7 +850,7 @@
         <v>["breakfast"]</v>
       </c>
       <c r="P9" t="str">
-        <v>{"macros_p":18}</v>
+        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high"}</v>
       </c>
     </row>
     <row r="10">
@@ -900,7 +900,7 @@
         <v>["breakfast"]</v>
       </c>
       <c r="P10" t="str">
-        <v>{"macros_p":17}</v>
+        <v>{"macros_p":17,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high"}</v>
       </c>
     </row>
     <row r="11">
@@ -950,7 +950,7 @@
         <v>["lunch","dinner","curry","high-protein","indian"]</v>
       </c>
       <c r="P11" t="str">
-        <v>{"macros_p":55.5}</v>
+        <v>{"macros_p":55.5,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high"}</v>
       </c>
     </row>
     <row r="12">
@@ -1000,7 +1000,7 @@
         <v>["lunch","dinner","grilled","high-protein","western"]</v>
       </c>
       <c r="P12" t="str">
-        <v>{"macros_p":43.5}</v>
+        <v>{"macros_p":43.5,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="13">
@@ -1050,7 +1050,7 @@
         <v>["lunch","dinner","curry","indian"]</v>
       </c>
       <c r="P13" t="str">
-        <v>{"macros_p":19}</v>
+        <v>{"macros_p":19,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high"}</v>
       </c>
     </row>
     <row r="14">
@@ -1100,7 +1100,7 @@
         <v>["lunch","dinner","curry","indian"]</v>
       </c>
       <c r="P14" t="str">
-        <v>{"macros_p":24}</v>
+        <v>{"macros_p":24,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high"}</v>
       </c>
     </row>
     <row r="15">
@@ -1150,7 +1150,7 @@
         <v>["lunch","dinner","soup","high-protein","asian"]</v>
       </c>
       <c r="P15" t="str">
-        <v>{"macros_p":49.4}</v>
+        <v>{"macros_p":49.4,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="16">
@@ -1200,7 +1200,7 @@
         <v>["lunch","dinner","salad","grilled","low-carb","high-protein","western"]</v>
       </c>
       <c r="P16" t="str">
-        <v>{"macros_p":49}</v>
+        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low"}</v>
       </c>
     </row>
     <row r="17">
@@ -1250,7 +1250,7 @@
         <v>["lunch","dinner","high-protein","asian"]</v>
       </c>
       <c r="P17" t="str">
-        <v>{"macros_p":49.3}</v>
+        <v>{"macros_p":49.3,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="18">
@@ -1300,7 +1300,7 @@
         <v>["lunch","dinner","curry","indian"]</v>
       </c>
       <c r="P18" t="str">
-        <v>{"macros_p":33.9}</v>
+        <v>{"macros_p":33.9,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high"}</v>
       </c>
     </row>
     <row r="19">
@@ -1350,7 +1350,7 @@
         <v>["lunch","dinner","curry","indian"]</v>
       </c>
       <c r="P19" t="str">
-        <v>{"macros_p":35}</v>
+        <v>{"macros_p":35,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high"}</v>
       </c>
     </row>
     <row r="20">
@@ -1400,7 +1400,7 @@
         <v>["lunch","dinner","curry","high-protein","indian"]</v>
       </c>
       <c r="P20" t="str">
-        <v>{"macros_p":64}</v>
+        <v>{"macros_p":64,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high"}</v>
       </c>
     </row>
     <row r="21">
@@ -1450,7 +1450,7 @@
         <v>["lunch","dinner","salad","grilled","low-carb","western"]</v>
       </c>
       <c r="P21" t="str">
-        <v>{"macros_p":37}</v>
+        <v>{"macros_p":37,"protein_family":"fish","meal_weight_class":"light","carb_level":"low"}</v>
       </c>
     </row>
     <row r="22">
@@ -1500,7 +1500,7 @@
         <v>["lunch","dinner","grilled","high-protein","western"]</v>
       </c>
       <c r="P22" t="str">
-        <v>{"macros_p":42}</v>
+        <v>{"macros_p":42,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="23">
@@ -1550,7 +1550,7 @@
         <v>["lunch","dinner","salad","soup","low-carb","high-protein","western"]</v>
       </c>
       <c r="P23" t="str">
-        <v>{"macros_p":61}</v>
+        <v>{"macros_p":61,"protein_family":"mixed","meal_weight_class":"medium","carb_level":"low"}</v>
       </c>
     </row>
     <row r="24">
@@ -1600,7 +1600,7 @@
         <v>["lunch","dinner","curry","low-carb","indian"]</v>
       </c>
       <c r="P24" t="str">
-        <v>{"macros_p":30}</v>
+        <v>{"macros_p":30,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="25">
@@ -1650,7 +1650,7 @@
         <v>["lunch","dinner","salad","grilled","low-carb","high-protein","western"]</v>
       </c>
       <c r="P25" t="str">
-        <v>{"macros_p":44}</v>
+        <v>{"macros_p":44,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low"}</v>
       </c>
     </row>
     <row r="26">
@@ -1700,7 +1700,7 @@
         <v>["lunch","dinner","salad","grilled","low-carb","high-protein","western"]</v>
       </c>
       <c r="P26" t="str">
-        <v>{"macros_p":43}</v>
+        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low"}</v>
       </c>
     </row>
     <row r="27">
@@ -1750,7 +1750,7 @@
         <v>["lunch","dinner","salad","low-carb","high-protein","indian"]</v>
       </c>
       <c r="P27" t="str">
-        <v>{"macros_p":60.9}</v>
+        <v>{"macros_p":60.9,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low"}</v>
       </c>
     </row>
     <row r="28">
@@ -1800,7 +1800,7 @@
         <v>["lunch","dinner","soup","high-protein","western"]</v>
       </c>
       <c r="P28" t="str">
-        <v>{"macros_p":47}</v>
+        <v>{"macros_p":47,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="29">
@@ -1850,7 +1850,7 @@
         <v>["lunch","dinner","curry","indian"]</v>
       </c>
       <c r="P29" t="str">
-        <v>{"macros_p":36}</v>
+        <v>{"macros_p":36,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high"}</v>
       </c>
     </row>
     <row r="30">
@@ -1900,7 +1900,7 @@
         <v>["lunch","dinner","curry","indian"]</v>
       </c>
       <c r="P30" t="str">
-        <v>{"macros_p":33}</v>
+        <v>{"macros_p":33,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high"}</v>
       </c>
     </row>
     <row r="31">
@@ -1950,7 +1950,7 @@
         <v>["lunch","dinner","indian"]</v>
       </c>
       <c r="P31" t="str">
-        <v>{"macros_p":37}</v>
+        <v>{"macros_p":37,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high"}</v>
       </c>
     </row>
     <row r="32">
@@ -2000,7 +2000,7 @@
         <v>["lunch","dinner","curry","indian"]</v>
       </c>
       <c r="P32" t="str">
-        <v>{"macros_p":36}</v>
+        <v>{"macros_p":36,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="33">
@@ -2050,7 +2050,7 @@
         <v>["snack","global"]</v>
       </c>
       <c r="P33" t="str">
-        <v>{"macros_p":31}</v>
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low"}</v>
       </c>
     </row>
     <row r="34">
@@ -2100,7 +2100,7 @@
         <v>["snack","indian"]</v>
       </c>
       <c r="P34" t="str">
-        <v>{"macros_p":4}</v>
+        <v>{"macros_p":4,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="35">
@@ -2150,7 +2150,7 @@
         <v>["snack","indian"]</v>
       </c>
       <c r="P35" t="str">
-        <v>{"macros_p":10}</v>
+        <v>{"macros_p":10,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="36">
@@ -2200,7 +2200,7 @@
         <v>["snack","global"]</v>
       </c>
       <c r="P36" t="str">
-        <v>{"macros_p":16}</v>
+        <v>{"macros_p":16,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
       </c>
     </row>
   </sheetData>
@@ -3366,7 +3366,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3574,36 +3574,36 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>meal_template_components</v>
+        <v>meal_templates</v>
       </c>
       <c r="B13" t="str">
-        <v>meal_id</v>
+        <v>metadata</v>
       </c>
       <c r="C13" t="str">
-        <v>text (pk,fk)</v>
+        <v>jsonb</v>
       </c>
       <c r="D13" t="str">
         <v>yes</v>
       </c>
       <c r="E13" t="str">
-        <v>Links to template</v>
+        <v>Derived keys: macros_p, protein_family, meal_weight_class, carb_level</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>daily_meal_plan</v>
+        <v>meal_template_components</v>
       </c>
       <c r="B14" t="str">
-        <v>user_id + plan_date + meal_type</v>
+        <v>meal_id</v>
       </c>
       <c r="C14" t="str">
-        <v>unique</v>
+        <v>text (pk,fk)</v>
       </c>
       <c r="D14" t="str">
         <v>yes</v>
       </c>
       <c r="E14" t="str">
-        <v>One row per meal slot/day</v>
+        <v>Links to template</v>
       </c>
     </row>
     <row r="15">
@@ -3611,24 +3611,24 @@
         <v>daily_meal_plan</v>
       </c>
       <c r="B15" t="str">
-        <v>status</v>
+        <v>user_id + plan_date + meal_type</v>
       </c>
       <c r="C15" t="str">
-        <v>text</v>
+        <v>unique</v>
       </c>
       <c r="D15" t="str">
         <v>yes</v>
       </c>
       <c r="E15" t="str">
-        <v>planned/confirmed/skipped/custom</v>
+        <v>One row per meal slot/day</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>meal_events</v>
+        <v>daily_meal_plan</v>
       </c>
       <c r="B16" t="str">
-        <v>event_type</v>
+        <v>status</v>
       </c>
       <c r="C16" t="str">
         <v>text</v>
@@ -3637,7 +3637,7 @@
         <v>yes</v>
       </c>
       <c r="E16" t="str">
-        <v>generated/edited/confirmed/undone/etc.</v>
+        <v>planned/confirmed/skipped/custom</v>
       </c>
     </row>
     <row r="17">
@@ -3645,33 +3645,33 @@
         <v>meal_events</v>
       </c>
       <c r="B17" t="str">
-        <v>delta</v>
+        <v>event_type</v>
       </c>
       <c r="C17" t="str">
-        <v>jsonb</v>
+        <v>text</v>
       </c>
       <c r="D17" t="str">
         <v>yes</v>
       </c>
       <c r="E17" t="str">
-        <v>Payload of change details</v>
+        <v>generated/edited/confirmed/undone/etc.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>preference_scores</v>
+        <v>meal_events</v>
       </c>
       <c r="B18" t="str">
-        <v>accepts_score</v>
+        <v>delta</v>
       </c>
       <c r="C18" t="str">
-        <v>numeric</v>
+        <v>jsonb</v>
       </c>
       <c r="D18" t="str">
         <v>yes</v>
       </c>
       <c r="E18" t="str">
-        <v>Learning weight</v>
+        <v>Payload of change details</v>
       </c>
     </row>
     <row r="19">
@@ -3679,7 +3679,7 @@
         <v>preference_scores</v>
       </c>
       <c r="B19" t="str">
-        <v>avoids_score</v>
+        <v>accepts_score</v>
       </c>
       <c r="C19" t="str">
         <v>numeric</v>
@@ -3691,9 +3691,26 @@
         <v>Learning weight</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>preference_scores</v>
+      </c>
+      <c r="B20" t="str">
+        <v>avoids_score</v>
+      </c>
+      <c r="C20" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="D20" t="str">
+        <v>yes</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Learning weight</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E20"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/exports/meal_database_architecture_v1.xlsx
+++ b/exports/meal_database_architecture_v1.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2005,34 +2005,34 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B33" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C33" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="D33" t="str">
-        <v>Nuts + Seeds + Protein Shake</v>
+        <v>Sweet Potato Curry + Kaala Chanaa + Jowar Roti</v>
       </c>
       <c r="E33" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="F33" t="str">
-        <v>global</v>
+        <v>indian</v>
       </c>
       <c r="G33">
-        <v>320</v>
+        <v>590</v>
       </c>
       <c r="H33">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I33">
+        <v>102</v>
+      </c>
+      <c r="J33">
         <v>11</v>
-      </c>
-      <c r="J33">
-        <v>18</v>
       </c>
       <c r="K33" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2047,42 +2047,42 @@
         <v>1</v>
       </c>
       <c r="O33" t="str">
-        <v>["snack","global"]</v>
+        <v>["lunch","dinner","curry","indian"]</v>
       </c>
       <c r="P33" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low"}</v>
+        <v>{"macros_p":22,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high"}</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>lunch_dinner_chicken-red-curry-rice</v>
       </c>
       <c r="B34" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C34" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Chicken red curry + rice</v>
       </c>
       <c r="D34" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Chicken Red Curry + Rice</v>
       </c>
       <c r="E34" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Chicken red curry + rice</v>
       </c>
       <c r="F34" t="str">
-        <v>indian</v>
+        <v>asian</v>
       </c>
       <c r="G34">
-        <v>180</v>
+        <v>520</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="I34">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="J34">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K34" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2097,42 +2097,42 @@
         <v>1</v>
       </c>
       <c r="O34" t="str">
-        <v>["snack","indian"]</v>
+        <v>["lunch","dinner","curry","high-protein","asian"]</v>
       </c>
       <c r="P34" t="str">
-        <v>{"macros_p":4,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
+        <v>{"macros_p":47,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium"}</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>snack_nuts-seeds-protein-shake</v>
       </c>
       <c r="B35" t="str">
         <v>snack</v>
       </c>
       <c r="C35" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Nuts, seeds + protein shake</v>
       </c>
       <c r="D35" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Nuts + Seeds + Protein Shake</v>
       </c>
       <c r="E35" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Nuts, seeds + protein shake</v>
       </c>
       <c r="F35" t="str">
-        <v>indian</v>
+        <v>global</v>
       </c>
       <c r="G35">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="H35">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I35">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K35" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2147,42 +2147,42 @@
         <v>1</v>
       </c>
       <c r="O35" t="str">
-        <v>["snack","indian"]</v>
+        <v>["snack","global"]</v>
       </c>
       <c r="P35" t="str">
-        <v>{"macros_p":10,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low"}</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>snack_sweet-potato-chaat</v>
       </c>
       <c r="B36" t="str">
         <v>snack</v>
       </c>
       <c r="C36" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Sweet potato chaat</v>
       </c>
       <c r="D36" t="str">
-        <v>Avocado/Cheese Toast</v>
+        <v>Sweet potato chaat</v>
       </c>
       <c r="E36" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Sweet potato chaat</v>
       </c>
       <c r="F36" t="str">
-        <v>global</v>
+        <v>indian</v>
       </c>
       <c r="G36">
-        <v>327</v>
+        <v>180</v>
       </c>
       <c r="H36">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I36">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J36">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K36" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2197,22 +2197,122 @@
         <v>1</v>
       </c>
       <c r="O36" t="str">
+        <v>["snack","indian"]</v>
+      </c>
+      <c r="P36" t="str">
+        <v>{"macros_p":4,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B37" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="F37" t="str">
+        <v>indian</v>
+      </c>
+      <c r="G37">
+        <v>220</v>
+      </c>
+      <c r="H37">
+        <v>10</v>
+      </c>
+      <c r="I37">
+        <v>35</v>
+      </c>
+      <c r="J37">
+        <v>4</v>
+      </c>
+      <c r="K37" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L37" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M37" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" t="str">
+        <v>["snack","indian"]</v>
+      </c>
+      <c r="P37" t="str">
+        <v>{"macros_p":10,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B38" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Avocado/Cheese Toast</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="F38" t="str">
+        <v>global</v>
+      </c>
+      <c r="G38">
+        <v>327</v>
+      </c>
+      <c r="H38">
+        <v>16</v>
+      </c>
+      <c r="I38">
+        <v>21</v>
+      </c>
+      <c r="J38">
+        <v>20</v>
+      </c>
+      <c r="K38" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L38" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M38" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38" t="str">
         <v>["snack","global"]</v>
       </c>
-      <c r="P36" t="str">
+      <c r="P38" t="str">
         <v>{"macros_p":16,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P38"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3144,28 +3244,28 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B33" t="str">
-        <v/>
-      </c>
-      <c r="C33" t="str">
-        <v/>
+        <v>Kaala chanaa (black chickpeas)</v>
+      </c>
+      <c r="C33">
+        <v>160</v>
       </c>
       <c r="D33" t="str">
-        <v/>
-      </c>
-      <c r="E33" t="str">
-        <v/>
+        <v>Jowar roti (millet)</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v/>
-      </c>
-      <c r="G33" t="str">
-        <v/>
+        <v>Sweet potato curry</v>
+      </c>
+      <c r="G33">
+        <v>180</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>Curry style</v>
       </c>
       <c r="I33" t="str">
         <v>{}</v>
@@ -3173,28 +3273,28 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>lunch_dinner_chicken-red-curry-rice</v>
       </c>
       <c r="B34" t="str">
-        <v/>
-      </c>
-      <c r="C34" t="str">
-        <v/>
+        <v>Chicken breast</v>
+      </c>
+      <c r="C34">
+        <v>150</v>
       </c>
       <c r="D34" t="str">
-        <v/>
-      </c>
-      <c r="E34" t="str">
-        <v/>
+        <v>Cooked rice</v>
+      </c>
+      <c r="E34">
+        <v>80</v>
       </c>
       <c r="F34" t="str">
-        <v/>
-      </c>
-      <c r="G34" t="str">
-        <v/>
+        <v>Red curry vegetables</v>
+      </c>
+      <c r="G34">
+        <v>120</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>Curry style</v>
       </c>
       <c r="I34" t="str">
         <v>{}</v>
@@ -3202,7 +3302,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>snack_nuts-seeds-protein-shake</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -3231,7 +3331,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>snack_sweet-potato-chaat</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -3258,9 +3358,67 @@
         <v>{}</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>{}</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I38"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/exports/meal_database_architecture_v1.xlsx
+++ b/exports/meal_database_architecture_v1.xlsx
@@ -497,10 +497,10 @@
         <v>1</v>
       </c>
       <c r="O2" t="str">
-        <v>["breakfast"]</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"low","cuisine":"global","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P2" t="str">
-        <v>{"macros_p":22,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low"}</v>
+        <v>{"macros_p":22,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":242,"delta_kcal":10,"tolerance_kcal":50.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="3">
@@ -547,10 +547,10 @@
         <v>1</v>
       </c>
       <c r="O3" t="str">
-        <v>["breakfast","grilled"]</v>
+        <v>{"meal_type":"breakfast","protein_family":"red_meat","carb_level":"medium","cuisine":"global","format":"sandwich","effort":"low","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P3" t="str">
-        <v>{"macros_p":38,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"medium"}</v>
+        <v>{"macros_p":38,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"medium","format":"sandwich","effort":"low","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":379,"delta_kcal":11,"tolerance_kcal":78},"issues":[]}}</v>
       </c>
     </row>
     <row r="4">
@@ -597,10 +597,10 @@
         <v>1</v>
       </c>
       <c r="O4" t="str">
-        <v>["breakfast","grilled"]</v>
+        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"low","cuisine":"global","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P4" t="str">
-        <v>{"macros_p":33,"protein_family":"fish","meal_weight_class":"light","carb_level":"low"}</v>
+        <v>{"macros_p":33,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":343,"delta_kcal":2,"tolerance_kcal":69},"issues":[]}}</v>
       </c>
     </row>
     <row r="5">
@@ -647,10 +647,10 @@
         <v>1</v>
       </c>
       <c r="O5" t="str">
-        <v>["breakfast","grilled","low-carb"]</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"global","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P5" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":216,"delta_kcal":4,"tolerance_kcal":44},"issues":[]}}</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         <v>1</v>
       </c>
       <c r="O6" t="str">
-        <v>["breakfast"]</v>
+        <v>{"meal_type":"breakfast","protein_family":"chicken","carb_level":"medium","cuisine":"global","format":"plate","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P6" t="str">
-        <v>{"macros_p":37,"protein_family":"chicken","meal_weight_class":"light","carb_level":"medium"}</v>
+        <v>{"macros_p":37,"protein_family":"chicken","meal_weight_class":"light","carb_level":"medium","format":"plate","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":345,"delta_kcal":0,"tolerance_kcal":69},"issues":[]}}</v>
       </c>
     </row>
     <row r="7">
@@ -747,10 +747,10 @@
         <v>1</v>
       </c>
       <c r="O7" t="str">
-        <v>["breakfast","low-carb"]</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"low","cuisine":"global","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P7" t="str">
-        <v>{"macros_p":19,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low"}</v>
+        <v>{"macros_p":19,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":220,"delta_kcal":25,"tolerance_kcal":49},"issues":[]}}</v>
       </c>
     </row>
     <row r="8">
@@ -797,10 +797,10 @@
         <v>1</v>
       </c>
       <c r="O8" t="str">
-        <v>["breakfast","grilled","low-carb"]</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"global","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P8" t="str">
-        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
+        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":280,"delta_kcal":40,"tolerance_kcal":64},"issues":[]}}</v>
       </c>
     </row>
     <row r="9">
@@ -847,10 +847,10 @@
         <v>1</v>
       </c>
       <c r="O9" t="str">
-        <v>["breakfast"]</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"high","cuisine":"global","format":"plate","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P9" t="str">
-        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high"}</v>
+        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"plate","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":574,"delta_kcal":14,"tolerance_kcal":112},"issues":[]}}</v>
       </c>
     </row>
     <row r="10">
@@ -897,10 +897,10 @@
         <v>1</v>
       </c>
       <c r="O10" t="str">
-        <v>["breakfast"]</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"high","cuisine":"global","format":"plate","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P10" t="str">
-        <v>{"macros_p":17,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high"}</v>
+        <v>{"macros_p":17,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":607,"delta_kcal":13,"tolerance_kcal":124},"issues":[]}}</v>
       </c>
     </row>
     <row r="11">
@@ -947,10 +947,10 @@
         <v>1</v>
       </c>
       <c r="O11" t="str">
-        <v>["lunch","dinner","curry","high-protein","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P11" t="str">
-        <v>{"macros_p":55.5,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high"}</v>
+        <v>{"macros_p":55.5,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":626.2,"delta_kcal":37.8,"tolerance_kcal":132.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="12">
@@ -997,10 +997,10 @@
         <v>1</v>
       </c>
       <c r="O12" t="str">
-        <v>["lunch","dinner","grilled","high-protein","western"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"western","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P12" t="str">
-        <v>{"macros_p":43.5,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium"}</v>
+        <v>{"macros_p":43.5,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":582.2,"delta_kcal":5.2,"tolerance_kcal":115.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="13">
@@ -1047,10 +1047,10 @@
         <v>1</v>
       </c>
       <c r="O13" t="str">
-        <v>["lunch","dinner","curry","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P13" t="str">
-        <v>{"macros_p":19,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high"}</v>
+        <v>{"macros_p":19,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":407,"delta_kcal":3,"tolerance_kcal":82},"issues":[]}}</v>
       </c>
     </row>
     <row r="14">
@@ -1097,10 +1097,10 @@
         <v>1</v>
       </c>
       <c r="O14" t="str">
-        <v>["lunch","dinner","curry","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P14" t="str">
-        <v>{"macros_p":24,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high"}</v>
+        <v>{"macros_p":24,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":583,"delta_kcal":8,"tolerance_kcal":115},"issues":[]}}</v>
       </c>
     </row>
     <row r="15">
@@ -1147,10 +1147,10 @@
         <v>1</v>
       </c>
       <c r="O15" t="str">
-        <v>["lunch","dinner","soup","high-protein","asian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P15" t="str">
-        <v>{"macros_p":49.4,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium"}</v>
+        <v>{"macros_p":49.4,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":396.6,"delta_kcal":18.4,"tolerance_kcal":83},"issues":[]}}</v>
       </c>
     </row>
     <row r="16">
@@ -1197,10 +1197,10 @@
         <v>1</v>
       </c>
       <c r="O16" t="str">
-        <v>["lunch","dinner","salad","grilled","low-carb","high-protein","western"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"western","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P16" t="str">
-        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low"}</v>
+        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":477,"delta_kcal":3,"tolerance_kcal":96},"issues":[]}}</v>
       </c>
     </row>
     <row r="17">
@@ -1247,10 +1247,10 @@
         <v>1</v>
       </c>
       <c r="O17" t="str">
-        <v>["lunch","dinner","high-protein","asian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P17" t="str">
-        <v>{"macros_p":49.3,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium"}</v>
+        <v>{"macros_p":49.3,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":405.2,"delta_kcal":13.8,"tolerance_kcal":83.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="18">
@@ -1297,10 +1297,10 @@
         <v>1</v>
       </c>
       <c r="O18" t="str">
-        <v>["lunch","dinner","curry","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P18" t="str">
-        <v>{"macros_p":33.9,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high"}</v>
+        <v>{"macros_p":33.9,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":641.5,"delta_kcal":23.5,"tolerance_kcal":133},"issues":[]}}</v>
       </c>
     </row>
     <row r="19">
@@ -1347,10 +1347,10 @@
         <v>1</v>
       </c>
       <c r="O19" t="str">
-        <v>["lunch","dinner","curry","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P19" t="str">
-        <v>{"macros_p":35,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high"}</v>
+        <v>{"macros_p":35,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":715,"delta_kcal":15,"tolerance_kcal":146},"issues":[]}}</v>
       </c>
     </row>
     <row r="20">
@@ -1397,10 +1397,10 @@
         <v>1</v>
       </c>
       <c r="O20" t="str">
-        <v>["lunch","dinner","curry","high-protein","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P20" t="str">
-        <v>{"macros_p":64,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high"}</v>
+        <v>{"macros_p":64,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":745,"delta_kcal":40,"tolerance_kcal":157},"issues":[]}}</v>
       </c>
     </row>
     <row r="21">
@@ -1447,10 +1447,10 @@
         <v>1</v>
       </c>
       <c r="O21" t="str">
-        <v>["lunch","dinner","salad","grilled","low-carb","western"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"western","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P21" t="str">
-        <v>{"macros_p":37,"protein_family":"fish","meal_weight_class":"light","carb_level":"low"}</v>
+        <v>{"macros_p":37,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":276,"delta_kcal":3,"tolerance_kcal":55.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="22">
@@ -1497,10 +1497,10 @@
         <v>1</v>
       </c>
       <c r="O22" t="str">
-        <v>["lunch","dinner","grilled","high-protein","western"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"western","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P22" t="str">
-        <v>{"macros_p":42,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium"}</v>
+        <v>{"macros_p":42,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":543.4,"delta_kcal":1.4,"tolerance_kcal":108.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="23">
@@ -1547,10 +1547,10 @@
         <v>1</v>
       </c>
       <c r="O23" t="str">
-        <v>["lunch","dinner","salad","soup","low-carb","high-protein","western"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"low","cuisine":"western","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P23" t="str">
-        <v>{"macros_p":61,"protein_family":"mixed","meal_weight_class":"medium","carb_level":"low"}</v>
+        <v>{"macros_p":61,"protein_family":"mixed","meal_weight_class":"medium","carb_level":"low","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":412,"delta_kcal":35,"tolerance_kcal":89.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="24">
@@ -1597,10 +1597,10 @@
         <v>1</v>
       </c>
       <c r="O24" t="str">
-        <v>["lunch","dinner","curry","low-carb","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P24" t="str">
-        <v>{"macros_p":30,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium"}</v>
+        <v>{"macros_p":30,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":569,"delta_kcal":9,"tolerance_kcal":112},"issues":[]}}</v>
       </c>
     </row>
     <row r="25">
@@ -1647,10 +1647,10 @@
         <v>1</v>
       </c>
       <c r="O25" t="str">
-        <v>["lunch","dinner","salad","grilled","low-carb","high-protein","western"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"western","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P25" t="str">
-        <v>{"macros_p":44,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low"}</v>
+        <v>{"macros_p":44,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":520,"delta_kcal":13,"tolerance_kcal":106.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="26">
@@ -1697,10 +1697,10 @@
         <v>1</v>
       </c>
       <c r="O26" t="str">
-        <v>["lunch","dinner","salad","grilled","low-carb","high-protein","western"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"western","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P26" t="str">
-        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low"}</v>
+        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":435,"delta_kcal":12,"tolerance_kcal":89.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="27">
@@ -1747,10 +1747,10 @@
         <v>1</v>
       </c>
       <c r="O27" t="str">
-        <v>["lunch","dinner","salad","low-carb","high-protein","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P27" t="str">
-        <v>{"macros_p":60.9,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low"}</v>
+        <v>{"macros_p":60.9,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":446.5,"delta_kcal":19.5,"tolerance_kcal":93.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="28">
@@ -1797,10 +1797,10 @@
         <v>1</v>
       </c>
       <c r="O28" t="str">
-        <v>["lunch","dinner","soup","high-protein","western"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"western","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P28" t="str">
-        <v>{"macros_p":47,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium"}</v>
+        <v>{"macros_p":47,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":489,"delta_kcal":11,"tolerance_kcal":95.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="29">
@@ -1847,10 +1847,10 @@
         <v>1</v>
       </c>
       <c r="O29" t="str">
-        <v>["lunch","dinner","curry","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P29" t="str">
-        <v>{"macros_p":36,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high"}</v>
+        <v>{"macros_p":36,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":689,"delta_kcal":21,"tolerance_kcal":142},"issues":[]}}</v>
       </c>
     </row>
     <row r="30">
@@ -1897,10 +1897,10 @@
         <v>1</v>
       </c>
       <c r="O30" t="str">
-        <v>["lunch","dinner","curry","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P30" t="str">
-        <v>{"macros_p":33,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high"}</v>
+        <v>{"macros_p":33,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":704,"delta_kcal":20,"tolerance_kcal":144.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="31">
@@ -1947,10 +1947,10 @@
         <v>1</v>
       </c>
       <c r="O31" t="str">
-        <v>["lunch","dinner","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P31" t="str">
-        <v>{"macros_p":37,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high"}</v>
+        <v>{"macros_p":37,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":666,"delta_kcal":3,"tolerance_kcal":133.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="32">
@@ -1997,10 +1997,10 @@
         <v>1</v>
       </c>
       <c r="O32" t="str">
-        <v>["lunch","dinner","curry","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P32" t="str">
-        <v>{"macros_p":36,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium"}</v>
+        <v>{"macros_p":36,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":372,"delta_kcal":8,"tolerance_kcal":76},"issues":[]}}</v>
       </c>
     </row>
     <row r="33">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="O33" t="str">
-        <v>["lunch","dinner","curry","indian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P33" t="str">
-        <v>{"macros_p":22,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high"}</v>
+        <v>{"macros_p":22,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":595,"delta_kcal":5,"tolerance_kcal":118},"issues":[]}}</v>
       </c>
     </row>
     <row r="34">
@@ -2097,10 +2097,10 @@
         <v>1</v>
       </c>
       <c r="O34" t="str">
-        <v>["lunch","dinner","curry","high-protein","asian"]</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P34" t="str">
-        <v>{"macros_p":47,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium"}</v>
+        <v>{"macros_p":47,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":512,"delta_kcal":8,"tolerance_kcal":104},"issues":[]}}</v>
       </c>
     </row>
     <row r="35">
@@ -2147,10 +2147,10 @@
         <v>1</v>
       </c>
       <c r="O35" t="str">
-        <v>["snack","global"]</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"global","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P35" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low"}</v>
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":330,"delta_kcal":10,"tolerance_kcal":64},"issues":[]}}</v>
       </c>
     </row>
     <row r="36">
@@ -2197,10 +2197,10 @@
         <v>1</v>
       </c>
       <c r="O36" t="str">
-        <v>["snack","indian"]</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P36" t="str">
-        <v>{"macros_p":4,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
+        <v>{"macros_p":4,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":184,"delta_kcal":4,"tolerance_kcal":36},"issues":[]}}</v>
       </c>
     </row>
     <row r="37">
@@ -2247,10 +2247,10 @@
         <v>1</v>
       </c>
       <c r="O37" t="str">
-        <v>["snack","indian"]</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P37" t="str">
-        <v>{"macros_p":10,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
+        <v>{"macros_p":10,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":216,"delta_kcal":4,"tolerance_kcal":44},"issues":[]}}</v>
       </c>
     </row>
     <row r="38">
@@ -2297,10 +2297,10 @@
         <v>1</v>
       </c>
       <c r="O38" t="str">
-        <v>["snack","global"]</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"global","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P38" t="str">
-        <v>{"macros_p":16,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium"}</v>
+        <v>{"macros_p":16,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":328,"delta_kcal":1,"tolerance_kcal":65.4},"issues":[]}}</v>
       </c>
     </row>
   </sheetData>
@@ -3524,7 +3524,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3735,7 +3735,7 @@
         <v>meal_templates</v>
       </c>
       <c r="B13" t="str">
-        <v>metadata</v>
+        <v>tags</v>
       </c>
       <c r="C13" t="str">
         <v>jsonb</v>
@@ -3744,41 +3744,41 @@
         <v>yes</v>
       </c>
       <c r="E13" t="str">
-        <v>Derived keys: macros_p, protein_family, meal_weight_class, carb_level</v>
+        <v>Object keys: meal_type, protein_family, carb_level, cuisine, format, effort, goal_fit</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>meal_template_components</v>
+        <v>meal_templates</v>
       </c>
       <c r="B14" t="str">
-        <v>meal_id</v>
+        <v>metadata</v>
       </c>
       <c r="C14" t="str">
-        <v>text (pk,fk)</v>
+        <v>jsonb</v>
       </c>
       <c r="D14" t="str">
         <v>yes</v>
       </c>
       <c r="E14" t="str">
-        <v>Links to template</v>
+        <v>Derived keys: macros_p, source_type, source_url, confidence_score, needs_review, validation</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>daily_meal_plan</v>
+        <v>meal_template_components</v>
       </c>
       <c r="B15" t="str">
-        <v>user_id + plan_date + meal_type</v>
+        <v>meal_id</v>
       </c>
       <c r="C15" t="str">
-        <v>unique</v>
+        <v>text (pk,fk)</v>
       </c>
       <c r="D15" t="str">
         <v>yes</v>
       </c>
       <c r="E15" t="str">
-        <v>One row per meal slot/day</v>
+        <v>Links to template</v>
       </c>
     </row>
     <row r="16">
@@ -3786,24 +3786,24 @@
         <v>daily_meal_plan</v>
       </c>
       <c r="B16" t="str">
-        <v>status</v>
+        <v>user_id + plan_date + meal_type</v>
       </c>
       <c r="C16" t="str">
-        <v>text</v>
+        <v>unique</v>
       </c>
       <c r="D16" t="str">
         <v>yes</v>
       </c>
       <c r="E16" t="str">
-        <v>planned/confirmed/skipped/custom</v>
+        <v>One row per meal slot/day</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>meal_events</v>
+        <v>daily_meal_plan</v>
       </c>
       <c r="B17" t="str">
-        <v>event_type</v>
+        <v>status</v>
       </c>
       <c r="C17" t="str">
         <v>text</v>
@@ -3812,7 +3812,7 @@
         <v>yes</v>
       </c>
       <c r="E17" t="str">
-        <v>generated/edited/confirmed/undone/etc.</v>
+        <v>planned/confirmed/skipped/custom</v>
       </c>
     </row>
     <row r="18">
@@ -3820,33 +3820,33 @@
         <v>meal_events</v>
       </c>
       <c r="B18" t="str">
-        <v>delta</v>
+        <v>event_type</v>
       </c>
       <c r="C18" t="str">
-        <v>jsonb</v>
+        <v>text</v>
       </c>
       <c r="D18" t="str">
         <v>yes</v>
       </c>
       <c r="E18" t="str">
-        <v>Payload of change details</v>
+        <v>generated/edited/confirmed/undone/etc.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>preference_scores</v>
+        <v>meal_events</v>
       </c>
       <c r="B19" t="str">
-        <v>accepts_score</v>
+        <v>delta</v>
       </c>
       <c r="C19" t="str">
-        <v>numeric</v>
+        <v>jsonb</v>
       </c>
       <c r="D19" t="str">
         <v>yes</v>
       </c>
       <c r="E19" t="str">
-        <v>Learning weight</v>
+        <v>Payload of change details</v>
       </c>
     </row>
     <row r="20">
@@ -3854,7 +3854,7 @@
         <v>preference_scores</v>
       </c>
       <c r="B20" t="str">
-        <v>avoids_score</v>
+        <v>accepts_score</v>
       </c>
       <c r="C20" t="str">
         <v>numeric</v>
@@ -3866,9 +3866,26 @@
         <v>Learning weight</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>preference_scores</v>
+      </c>
+      <c r="B21" t="str">
+        <v>avoids_score</v>
+      </c>
+      <c r="C21" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="D21" t="str">
+        <v>yes</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Learning weight</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E21"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/exports/meal_database_architecture_v1.xlsx
+++ b/exports/meal_database_architecture_v1.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -470,19 +470,19 @@
         <v>Scrambled eggs + toast</v>
       </c>
       <c r="F2" t="str">
-        <v>global</v>
+        <v>Continental</v>
       </c>
       <c r="G2">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="H2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K2" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -497,10 +497,10 @@
         <v>1</v>
       </c>
       <c r="O2" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"low","cuisine":"global","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P2" t="str">
-        <v>{"macros_p":22,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":242,"delta_kcal":10,"tolerance_kcal":50.4},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":279,"delta_kcal":5,"tolerance_kcal":56.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="3">
@@ -520,19 +520,19 @@
         <v>Boiled eggs + ham sandwich</v>
       </c>
       <c r="F3" t="str">
-        <v>global</v>
+        <v>Continental</v>
       </c>
       <c r="G3">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="H3">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K3" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -547,10 +547,10 @@
         <v>1</v>
       </c>
       <c r="O3" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"red_meat","carb_level":"medium","cuisine":"global","format":"sandwich","effort":"low","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"red_meat","carb_level":"medium","cuisine":"continental","format":"sandwich","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P3" t="str">
-        <v>{"macros_p":38,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"medium","format":"sandwich","effort":"low","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":379,"delta_kcal":11,"tolerance_kcal":78},"issues":[]}}</v>
+        <v>{"macros_p":31,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"medium","format":"sandwich","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":382,"delta_kcal":11,"tolerance_kcal":78.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="4">
@@ -570,19 +570,19 @@
         <v>Smoked salmon + avocado on toast</v>
       </c>
       <c r="F4" t="str">
-        <v>global</v>
+        <v>Continental</v>
       </c>
       <c r="G4">
-        <v>345</v>
+        <v>285</v>
       </c>
       <c r="H4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K4" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -597,42 +597,42 @@
         <v>1</v>
       </c>
       <c r="O4" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"low","cuisine":"global","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P4" t="str">
-        <v>{"macros_p":33,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":343,"delta_kcal":2,"tolerance_kcal":69},"issues":[]}}</v>
+        <v>{"macros_p":31,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":279,"delta_kcal":6,"tolerance_kcal":57},"issues":[]}}</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>breakfast_greek-yogurt-berry-bowl</v>
+        <v>breakfast_poha-kabab-protein-shake</v>
       </c>
       <c r="B5" t="str">
         <v>breakfast</v>
       </c>
       <c r="C5" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Poha + kabab/protein shake</v>
       </c>
       <c r="D5" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Poha + Kabab/Protein Shake</v>
       </c>
       <c r="E5" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Poha + kabab/protein shake</v>
       </c>
       <c r="F5" t="str">
-        <v>global</v>
+        <v>Indian</v>
       </c>
       <c r="G5">
-        <v>220</v>
+        <v>345</v>
       </c>
       <c r="H5">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I5">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -647,42 +647,42 @@
         <v>1</v>
       </c>
       <c r="O5" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"global","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"plate","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P5" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":216,"delta_kcal":4,"tolerance_kcal":44},"issues":[]}}</v>
+        <v>{"macros_p":37,"protein_family":"chicken","meal_weight_class":"light","carb_level":"medium","format":"plate","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":345,"delta_kcal":0,"tolerance_kcal":69},"issues":[]}}</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>breakfast_poha-kabab-protein-shake</v>
+        <v>breakfast_egg-white-omelette-avocado</v>
       </c>
       <c r="B6" t="str">
         <v>breakfast</v>
       </c>
       <c r="C6" t="str">
-        <v>Poha + kabab/protein shake</v>
+        <v>Egg white omelette + avocado</v>
       </c>
       <c r="D6" t="str">
-        <v>Poha + Kabab/Protein Shake</v>
+        <v>Egg white omelette + avocado</v>
       </c>
       <c r="E6" t="str">
-        <v>Poha + kabab/protein shake</v>
+        <v>Egg white omelette + avocado</v>
       </c>
       <c r="F6" t="str">
-        <v>global</v>
+        <v>Continental</v>
       </c>
       <c r="G6">
-        <v>345</v>
+        <v>190</v>
       </c>
       <c r="H6">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K6" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -697,42 +697,42 @@
         <v>1</v>
       </c>
       <c r="O6" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"chicken","carb_level":"medium","cuisine":"global","format":"plate","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P6" t="str">
-        <v>{"macros_p":37,"protein_family":"chicken","meal_weight_class":"light","carb_level":"medium","format":"plate","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":345,"delta_kcal":0,"tolerance_kcal":69},"issues":[]}}</v>
+        <v>{"macros_p":22,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":189,"delta_kcal":1,"tolerance_kcal":38},"issues":[]}}</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>breakfast_egg-white-omelette-avocado</v>
+        <v>breakfast_aloo-paratha-curd</v>
       </c>
       <c r="B7" t="str">
         <v>breakfast</v>
       </c>
       <c r="C7" t="str">
-        <v>Egg white omelette + avocado</v>
+        <v>Aloo paratha + curd</v>
       </c>
       <c r="D7" t="str">
-        <v>Egg white omelette + avocado</v>
+        <v>Aloo paratha + curd</v>
       </c>
       <c r="E7" t="str">
-        <v>Egg white omelette + avocado</v>
+        <v>Aloo paratha + curd</v>
       </c>
       <c r="F7" t="str">
-        <v>global</v>
+        <v>Indian</v>
       </c>
       <c r="G7">
-        <v>245</v>
+        <v>685</v>
       </c>
       <c r="H7">
         <v>19</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K7" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -747,42 +747,42 @@
         <v>1</v>
       </c>
       <c r="O7" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"low","cuisine":"global","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":[]}</v>
       </c>
       <c r="P7" t="str">
-        <v>{"macros_p":19,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":220,"delta_kcal":25,"tolerance_kcal":49},"issues":[]}}</v>
+        <v>{"macros_p":19,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":685,"delta_kcal":0,"tolerance_kcal":137},"issues":[]}}</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>breakfast_carrot-halwa-sugar-free-protein-shake</v>
+        <v>breakfast_idli-mysore-masala-dosa-sambar-chutney</v>
       </c>
       <c r="B8" t="str">
         <v>breakfast</v>
       </c>
       <c r="C8" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Idli, Mysore masala dosa + sambar + chutney</v>
       </c>
       <c r="D8" t="str">
-        <v>Carrot Halwa + Protein Shake</v>
+        <v>Idli + Mysore Dosa + Sambar</v>
       </c>
       <c r="E8" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Idli, Mysore masala dosa + sambar + chutney</v>
       </c>
       <c r="F8" t="str">
-        <v>global</v>
+        <v>Indian</v>
       </c>
       <c r="G8">
-        <v>320</v>
+        <v>624</v>
       </c>
       <c r="H8">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I8">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K8" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -797,42 +797,42 @@
         <v>1</v>
       </c>
       <c r="O8" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"global","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"plate","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P8" t="str">
-        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":280,"delta_kcal":40,"tolerance_kcal":64},"issues":[]}}</v>
+        <v>{"macros_p":19,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":604,"delta_kcal":20,"tolerance_kcal":124.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>breakfast_aloo-paratha-curd</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti</v>
       </c>
       <c r="B9" t="str">
-        <v>breakfast</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C9" t="str">
-        <v>Aloo paratha + curd</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="D9" t="str">
-        <v>Aloo paratha + curd</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="E9" t="str">
-        <v>Aloo paratha + curd</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="F9" t="str">
-        <v>global</v>
+        <v>Indian</v>
       </c>
       <c r="G9">
-        <v>560</v>
+        <v>702</v>
       </c>
       <c r="H9">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I9">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="J9">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K9" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -847,42 +847,42 @@
         <v>1</v>
       </c>
       <c r="O9" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"high","cuisine":"global","format":"plate","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P9" t="str">
-        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"plate","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":574,"delta_kcal":14,"tolerance_kcal":112},"issues":[]}}</v>
+        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":676,"delta_kcal":26,"tolerance_kcal":140.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>breakfast_idli-mysore-masala-dosa-sambar-chutney</v>
+        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B10" t="str">
-        <v>breakfast</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C10" t="str">
-        <v>Idli, Mysore masala dosa + sambar + chutney</v>
+        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
       </c>
       <c r="D10" t="str">
-        <v>Idli + Mysore Dosa + Sambar</v>
+        <v>Salmon + Veg + Aglio Olio</v>
       </c>
       <c r="E10" t="str">
-        <v>Idli, Mysore masala dosa + sambar + chutney</v>
+        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
       </c>
       <c r="F10" t="str">
-        <v>global</v>
+        <v>Continental</v>
       </c>
       <c r="G10">
-        <v>620</v>
+        <v>669</v>
       </c>
       <c r="H10">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="I10">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="J10">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K10" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -897,42 +897,42 @@
         <v>1</v>
       </c>
       <c r="O10" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"high","cuisine":"global","format":"plate","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"continental","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P10" t="str">
-        <v>{"macros_p":17,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":607,"delta_kcal":13,"tolerance_kcal":124},"issues":[]}}</v>
+        <v>{"macros_p":46,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":688,"delta_kcal":19,"tolerance_kcal":133.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti</v>
+        <v>lunch_dinner_rajma-chawal-raita</v>
       </c>
       <c r="B11" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C11" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="D11" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="E11" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="F11" t="str">
-        <v>indian</v>
+        <v>Indian</v>
       </c>
       <c r="G11">
-        <v>664</v>
+        <v>482</v>
       </c>
       <c r="H11">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="I11">
-        <v>66.4</v>
+        <v>77</v>
       </c>
       <c r="J11">
-        <v>15.4</v>
+        <v>10</v>
       </c>
       <c r="K11" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -947,42 +947,42 @@
         <v>1</v>
       </c>
       <c r="O11" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P11" t="str">
-        <v>{"macros_p":55.5,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":626.2,"delta_kcal":37.8,"tolerance_kcal":132.8},"issues":[]}}</v>
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":482,"delta_kcal":0,"tolerance_kcal":96.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_chole-jowar-roti-raita</v>
       </c>
       <c r="B12" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C12" t="str">
-        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="D12" t="str">
-        <v>Salmon + Veg + Aglio Olio</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="E12" t="str">
-        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="F12" t="str">
-        <v>western</v>
+        <v>Indian</v>
       </c>
       <c r="G12">
-        <v>577</v>
+        <v>726</v>
       </c>
       <c r="H12">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="I12">
-        <v>39.5</v>
+        <v>113</v>
       </c>
       <c r="J12">
-        <v>27.8</v>
+        <v>18</v>
       </c>
       <c r="K12" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -997,42 +997,42 @@
         <v>1</v>
       </c>
       <c r="O12" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"western","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P12" t="str">
-        <v>{"macros_p":43.5,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":582.2,"delta_kcal":5.2,"tolerance_kcal":115.4},"issues":[]}}</v>
+        <v>{"macros_p":27,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":722,"delta_kcal":4,"tolerance_kcal":145.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>lunch_dinner_rajma-chawal-raita</v>
+        <v>lunch_dinner_vietnamese-chicken-pho</v>
       </c>
       <c r="B13" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C13" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="D13" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="E13" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="F13" t="str">
-        <v>indian</v>
+        <v>Asian</v>
       </c>
       <c r="G13">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="H13">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="I13">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K13" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1047,42 +1047,42 @@
         <v>1</v>
       </c>
       <c r="O13" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P13" t="str">
-        <v>{"macros_p":19,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":407,"delta_kcal":3,"tolerance_kcal":82},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":374,"delta_kcal":20,"tolerance_kcal":78.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>lunch_dinner_chole-jowar-roti-raita</v>
+        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
       </c>
       <c r="B14" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C14" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Grilled steak + mixed greens salad</v>
       </c>
       <c r="D14" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Steak + Mixed Greens</v>
       </c>
       <c r="E14" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Grilled steak + mixed greens salad</v>
       </c>
       <c r="F14" t="str">
-        <v>indian</v>
+        <v>Continental</v>
       </c>
       <c r="G14">
-        <v>575</v>
+        <v>480</v>
       </c>
       <c r="H14">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="I14">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K14" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1097,42 +1097,42 @@
         <v>1</v>
       </c>
       <c r="O14" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P14" t="str">
-        <v>{"macros_p":24,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":583,"delta_kcal":8,"tolerance_kcal":115},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":477,"delta_kcal":3,"tolerance_kcal":96},"issues":[]}}</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>lunch_dinner_vietnamese-chicken-pho</v>
+        <v>lunch_dinner_thai-pad-krapow-rice</v>
       </c>
       <c r="B15" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C15" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="D15" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="E15" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="F15" t="str">
-        <v>asian</v>
+        <v>Asian</v>
       </c>
       <c r="G15">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="H15">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I15">
-        <v>34.9</v>
+        <v>33</v>
       </c>
       <c r="J15">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="K15" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1147,42 +1147,42 @@
         <v>1</v>
       </c>
       <c r="O15" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P15" t="str">
-        <v>{"macros_p":49.4,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":396.6,"delta_kcal":18.4,"tolerance_kcal":83},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":422,"delta_kcal":16,"tolerance_kcal":87.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
+        <v>lunch_dinner_mutton-keema-jowar-roti</v>
       </c>
       <c r="B16" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C16" t="str">
-        <v>Grilled steak + mixed greens salad</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="D16" t="str">
-        <v>Steak + Mixed Greens</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="E16" t="str">
-        <v>Grilled steak + mixed greens salad</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="F16" t="str">
-        <v>western</v>
+        <v>Indian</v>
       </c>
       <c r="G16">
-        <v>480</v>
+        <v>670</v>
       </c>
       <c r="H16">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="J16">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K16" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1197,42 +1197,42 @@
         <v>1</v>
       </c>
       <c r="O16" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"western","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P16" t="str">
-        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":477,"delta_kcal":3,"tolerance_kcal":96},"issues":[]}}</v>
+        <v>{"macros_p":34,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":654,"delta_kcal":16,"tolerance_kcal":134},"issues":[]}}</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>lunch_dinner_thai-pad-krapow-rice</v>
+        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
       </c>
       <c r="B17" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C17" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Arhar dal + rice + matar paneer</v>
       </c>
       <c r="D17" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Arhar Dal + Rice + Matar Paneer</v>
       </c>
       <c r="E17" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Arhar dal + rice + matar paneer</v>
       </c>
       <c r="F17" t="str">
-        <v>asian</v>
+        <v>Indian</v>
       </c>
       <c r="G17">
-        <v>419</v>
+        <v>669</v>
       </c>
       <c r="H17">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="I17">
-        <v>27.7</v>
+        <v>67</v>
       </c>
       <c r="J17">
-        <v>10.8</v>
+        <v>30</v>
       </c>
       <c r="K17" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1247,42 +1247,42 @@
         <v>1</v>
       </c>
       <c r="O17" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P17" t="str">
-        <v>{"macros_p":49.3,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":405.2,"delta_kcal":13.8,"tolerance_kcal":83.8},"issues":[]}}</v>
+        <v>{"macros_p":32,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":666,"delta_kcal":3,"tolerance_kcal":133.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>lunch_dinner_mutton-keema-jowar-roti</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
       </c>
       <c r="B18" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C18" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Chicken curry + jowar roti + dal</v>
       </c>
       <c r="D18" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Chicken Curry + Roti + Dal</v>
       </c>
       <c r="E18" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Chicken curry + jowar roti + dal</v>
       </c>
       <c r="F18" t="str">
-        <v>indian</v>
+        <v>Indian</v>
       </c>
       <c r="G18">
-        <v>665</v>
+        <v>736</v>
       </c>
       <c r="H18">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="I18">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="J18">
-        <v>33.1</v>
+        <v>17</v>
       </c>
       <c r="K18" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1297,42 +1297,42 @@
         <v>1</v>
       </c>
       <c r="O18" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P18" t="str">
-        <v>{"macros_p":33.9,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":641.5,"delta_kcal":23.5,"tolerance_kcal":133},"issues":[]}}</v>
+        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":709,"delta_kcal":27,"tolerance_kcal":147.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
+        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
       </c>
       <c r="B19" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C19" t="str">
-        <v>Arhar dal + rice + matar paneer</v>
+        <v>Grilled fish + pumpkin salad</v>
       </c>
       <c r="D19" t="str">
-        <v>Arhar Dal + Rice + Matar Paneer</v>
+        <v>Grilled Fish + Pumpkin Salad</v>
       </c>
       <c r="E19" t="str">
-        <v>Arhar dal + rice + matar paneer</v>
+        <v>Grilled fish + pumpkin salad</v>
       </c>
       <c r="F19" t="str">
-        <v>indian</v>
+        <v>Continental</v>
       </c>
       <c r="G19">
-        <v>730</v>
+        <v>308</v>
       </c>
       <c r="H19">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I19">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="J19">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="K19" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1347,42 +1347,42 @@
         <v>1</v>
       </c>
       <c r="O19" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P19" t="str">
-        <v>{"macros_p":35,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":715,"delta_kcal":15,"tolerance_kcal":146},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":305,"delta_kcal":3,"tolerance_kcal":61.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
+        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
       </c>
       <c r="B20" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C20" t="str">
-        <v>Chicken curry + jowar roti + dal</v>
+        <v>Grilled salmon + sauteed veg + garlic rice</v>
       </c>
       <c r="D20" t="str">
-        <v>Chicken Curry + Roti + Dal</v>
+        <v>Salmon + Veg + Garlic Rice</v>
       </c>
       <c r="E20" t="str">
-        <v>Chicken curry + jowar roti + dal</v>
+        <v>Grilled salmon + sauteed veg + garlic rice</v>
       </c>
       <c r="F20" t="str">
-        <v>indian</v>
+        <v>Continental</v>
       </c>
       <c r="G20">
-        <v>785</v>
+        <v>514</v>
       </c>
       <c r="H20">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="I20">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="J20">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K20" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1397,39 +1397,39 @@
         <v>1</v>
       </c>
       <c r="O20" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P20" t="str">
-        <v>{"macros_p":64,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":745,"delta_kcal":40,"tolerance_kcal":157},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":11,"tolerance_kcal":102.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
+        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
       </c>
       <c r="B21" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C21" t="str">
-        <v>Grilled fish + pumpkin salad</v>
+        <v>Chicken soup + smoked salmon salad</v>
       </c>
       <c r="D21" t="str">
-        <v>Grilled Fish + Pumpkin Salad</v>
+        <v>Chicken Soup + Salmon Salad</v>
       </c>
       <c r="E21" t="str">
-        <v>Grilled fish + pumpkin salad</v>
+        <v>Chicken soup + smoked salmon salad</v>
       </c>
       <c r="F21" t="str">
-        <v>western</v>
+        <v>Continental</v>
       </c>
       <c r="G21">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="H21">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="I21">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J21">
         <v>8</v>
@@ -1447,42 +1447,42 @@
         <v>1</v>
       </c>
       <c r="O21" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"western","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"low","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P21" t="str">
-        <v>{"macros_p":37,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":276,"delta_kcal":3,"tolerance_kcal":55.8},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"mixed","meal_weight_class":"light","carb_level":"low","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":284,"delta_kcal":18,"tolerance_kcal":60.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
+        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
       </c>
       <c r="B22" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C22" t="str">
-        <v>Grilled salmon + sauteed veg + garlic rice</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="D22" t="str">
-        <v>Salmon + Veg + Garlic Rice</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="E22" t="str">
-        <v>Grilled salmon + sauteed veg + garlic rice</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="F22" t="str">
-        <v>western</v>
+        <v>Indian</v>
       </c>
       <c r="G22">
-        <v>542</v>
+        <v>628</v>
       </c>
       <c r="H22">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I22">
-        <v>38.5</v>
+        <v>43</v>
       </c>
       <c r="J22">
-        <v>24.6</v>
+        <v>35</v>
       </c>
       <c r="K22" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1497,42 +1497,42 @@
         <v>1</v>
       </c>
       <c r="O22" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"western","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P22" t="str">
-        <v>{"macros_p":42,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":543.4,"delta_kcal":1.4,"tolerance_kcal":108.4},"issues":[]}}</v>
+        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":631,"delta_kcal":3,"tolerance_kcal":125.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
+        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
       </c>
       <c r="B23" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C23" t="str">
-        <v>Chicken soup + smoked salmon salad</v>
+        <v>Pork chop + pumpkin salad</v>
       </c>
       <c r="D23" t="str">
-        <v>Chicken Soup + Salmon Salad</v>
+        <v>Pork Chop + Pumpkin Salad</v>
       </c>
       <c r="E23" t="str">
-        <v>Chicken soup + smoked salmon salad</v>
+        <v>Pork chop + pumpkin salad</v>
       </c>
       <c r="F23" t="str">
-        <v>western</v>
+        <v>Continental</v>
       </c>
       <c r="G23">
-        <v>447</v>
+        <v>562</v>
       </c>
       <c r="H23">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J23">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K23" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1547,42 +1547,42 @@
         <v>1</v>
       </c>
       <c r="O23" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"low","cuisine":"western","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P23" t="str">
-        <v>{"macros_p":61,"protein_family":"mixed","meal_weight_class":"medium","carb_level":"low","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":412,"delta_kcal":35,"tolerance_kcal":89.4},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":13,"tolerance_kcal":112.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
+        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
       </c>
       <c r="B24" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C24" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Pork chop + mixed greens salad</v>
       </c>
       <c r="D24" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Pork Chop + Mixed Greens</v>
       </c>
       <c r="E24" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Pork chop + mixed greens salad</v>
       </c>
       <c r="F24" t="str">
-        <v>indian</v>
+        <v>Continental</v>
       </c>
       <c r="G24">
-        <v>560</v>
+        <v>449</v>
       </c>
       <c r="H24">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="I24">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K24" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1597,42 +1597,42 @@
         <v>1</v>
       </c>
       <c r="O24" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P24" t="str">
-        <v>{"macros_p":30,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":569,"delta_kcal":9,"tolerance_kcal":112},"issues":[]}}</v>
+        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":435,"delta_kcal":14,"tolerance_kcal":89.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
+        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
       </c>
       <c r="B25" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C25" t="str">
-        <v>Pork chop + pumpkin salad</v>
+        <v>Tandoori chicken + smoked chicken + avocado salad</v>
       </c>
       <c r="D25" t="str">
-        <v>Pork Chop + Pumpkin Salad</v>
+        <v>Tandoori Chicken + Smoked Chicken Salad</v>
       </c>
       <c r="E25" t="str">
-        <v>Pork chop + pumpkin salad</v>
+        <v>Tandoori chicken + smoked chicken + avocado salad</v>
       </c>
       <c r="F25" t="str">
-        <v>western</v>
+        <v>Indian</v>
       </c>
       <c r="G25">
-        <v>533</v>
+        <v>366</v>
       </c>
       <c r="H25">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="I25">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="K25" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1647,42 +1647,42 @@
         <v>1</v>
       </c>
       <c r="O25" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"western","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P25" t="str">
-        <v>{"macros_p":44,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":520,"delta_kcal":13,"tolerance_kcal":106.6},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":347,"delta_kcal":19,"tolerance_kcal":73.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
+        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B26" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C26" t="str">
-        <v>Pork chop + mixed greens salad</v>
+        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
       </c>
       <c r="D26" t="str">
-        <v>Pork Chop + Mixed Greens</v>
+        <v>Broccoli Soup + Fish + Aglio Olio</v>
       </c>
       <c r="E26" t="str">
-        <v>Pork chop + mixed greens salad</v>
+        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
       </c>
       <c r="F26" t="str">
-        <v>western</v>
+        <v>Continental</v>
       </c>
       <c r="G26">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="H26">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="J26">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K26" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1697,42 +1697,42 @@
         <v>1</v>
       </c>
       <c r="O26" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"western","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P26" t="str">
-        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":435,"delta_kcal":12,"tolerance_kcal":89.4},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":448,"delta_kcal":15,"tolerance_kcal":86.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
+        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
       </c>
       <c r="B27" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C27" t="str">
-        <v>Tandoori chicken + smoked chicken + avocado salad</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="D27" t="str">
-        <v>Tandoori Chicken + Smoked Chicken Salad</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="E27" t="str">
-        <v>Tandoori chicken + smoked chicken + avocado salad</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="F27" t="str">
-        <v>indian</v>
+        <v>Indian</v>
       </c>
       <c r="G27">
-        <v>466</v>
+        <v>771</v>
       </c>
       <c r="H27">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I27">
-        <v>8.2</v>
+        <v>74</v>
       </c>
       <c r="J27">
-        <v>18.9</v>
+        <v>31</v>
       </c>
       <c r="K27" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1747,42 +1747,42 @@
         <v>1</v>
       </c>
       <c r="O27" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P27" t="str">
-        <v>{"macros_p":60.9,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":446.5,"delta_kcal":19.5,"tolerance_kcal":93.2},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":755,"delta_kcal":16,"tolerance_kcal":154.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_kofta-dal-jowar-roti</v>
       </c>
       <c r="B28" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C28" t="str">
-        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="D28" t="str">
-        <v>Broccoli Soup + Fish + Aglio Olio</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="E28" t="str">
-        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="F28" t="str">
-        <v>western</v>
+        <v>Indian</v>
       </c>
       <c r="G28">
-        <v>478</v>
+        <v>769</v>
       </c>
       <c r="H28">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="I28">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="J28">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K28" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1797,42 +1797,42 @@
         <v>1</v>
       </c>
       <c r="O28" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"western","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
       </c>
       <c r="P28" t="str">
-        <v>{"macros_p":47,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":489,"delta_kcal":11,"tolerance_kcal":95.6},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":746,"delta_kcal":23,"tolerance_kcal":153.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
+        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
       </c>
       <c r="B29" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C29" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Kababs + dal + gobi + jowar roti</v>
       </c>
       <c r="D29" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Kababs + Dal + Gobi + Roti</v>
       </c>
       <c r="E29" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Kababs + dal + gobi + jowar roti</v>
       </c>
       <c r="F29" t="str">
-        <v>indian</v>
+        <v>Indian</v>
       </c>
       <c r="G29">
-        <v>710</v>
+        <v>823</v>
       </c>
       <c r="H29">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I29">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J29">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K29" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1847,42 +1847,42 @@
         <v>1</v>
       </c>
       <c r="O29" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P29" t="str">
-        <v>{"macros_p":36,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":689,"delta_kcal":21,"tolerance_kcal":142},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":813,"delta_kcal":10,"tolerance_kcal":164.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>lunch_dinner_kofta-dal-jowar-roti</v>
+        <v>lunch_dinner_fish-curry-rice</v>
       </c>
       <c r="B30" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C30" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="D30" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="E30" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="F30" t="str">
-        <v>indian</v>
+        <v>Indian</v>
       </c>
       <c r="G30">
-        <v>724</v>
+        <v>446</v>
       </c>
       <c r="H30">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I30">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="J30">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K30" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1897,42 +1897,42 @@
         <v>1</v>
       </c>
       <c r="O30" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P30" t="str">
-        <v>{"macros_p":33,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":704,"delta_kcal":20,"tolerance_kcal":144.8},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":433,"delta_kcal":13,"tolerance_kcal":89.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B31" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C31" t="str">
-        <v>Kababs + dal + gobi + jowar roti</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="D31" t="str">
-        <v>Kababs + Dal + Gobi + Roti</v>
+        <v>Sweet Potato Curry + Kaala Chanaa + Jowar Roti</v>
       </c>
       <c r="E31" t="str">
-        <v>Kababs + dal + gobi + jowar roti</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="F31" t="str">
-        <v>indian</v>
+        <v>Indian</v>
       </c>
       <c r="G31">
-        <v>669</v>
+        <v>731</v>
       </c>
       <c r="H31">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I31">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="J31">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K31" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1947,42 +1947,42 @@
         <v>1</v>
       </c>
       <c r="O31" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
       </c>
       <c r="P31" t="str">
-        <v>{"macros_p":37,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":666,"delta_kcal":3,"tolerance_kcal":133.8},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":735,"delta_kcal":4,"tolerance_kcal":146.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lunch_dinner_fish-curry-rice</v>
+        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
       </c>
       <c r="B32" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C32" t="str">
-        <v>Fish curry + rice</v>
+        <v>Avocado and smoked salmon salad</v>
       </c>
       <c r="D32" t="str">
-        <v>Fish curry + rice</v>
+        <v>Avocado &amp; Smoked Salmon Salad</v>
       </c>
       <c r="E32" t="str">
-        <v>Fish curry + rice</v>
+        <v>Avocado and smoked salmon salad</v>
       </c>
       <c r="F32" t="str">
-        <v>indian</v>
+        <v>Continental</v>
       </c>
       <c r="G32">
-        <v>380</v>
+        <v>206</v>
       </c>
       <c r="H32">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I32">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K32" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1997,42 +1997,42 @@
         <v>1</v>
       </c>
       <c r="O32" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P32" t="str">
-        <v>{"macros_p":36,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":372,"delta_kcal":8,"tolerance_kcal":76},"issues":[]}}</v>
+        <v>{"macros_p":24,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":201,"delta_kcal":5,"tolerance_kcal":41.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
+        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
       </c>
       <c r="B33" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C33" t="str">
-        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
+        <v>Avocado and smoked chicken salad</v>
       </c>
       <c r="D33" t="str">
-        <v>Sweet Potato Curry + Kaala Chanaa + Jowar Roti</v>
+        <v>Avocado &amp; Smoked Chicken Salad</v>
       </c>
       <c r="E33" t="str">
-        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
+        <v>Avocado and smoked chicken salad</v>
       </c>
       <c r="F33" t="str">
-        <v>indian</v>
+        <v>Continental</v>
       </c>
       <c r="G33">
-        <v>590</v>
+        <v>244</v>
       </c>
       <c r="H33">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I33">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K33" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="O33" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P33" t="str">
-        <v>{"macros_p":22,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":595,"delta_kcal":5,"tolerance_kcal":118},"issues":[]}}</v>
+        <v>{"macros_p":33,"protein_family":"chicken","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":237,"delta_kcal":7,"tolerance_kcal":48.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="34">
@@ -2070,19 +2070,19 @@
         <v>Chicken red curry + rice</v>
       </c>
       <c r="F34" t="str">
-        <v>asian</v>
+        <v>Asian</v>
       </c>
       <c r="G34">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="H34">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I34">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J34">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K34" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2100,45 +2100,45 @@
         <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P34" t="str">
-        <v>{"macros_p":47,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":512,"delta_kcal":8,"tolerance_kcal":104},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":486,"delta_kcal":18,"tolerance_kcal":100.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>snack_fruit-almonds-plant-shake</v>
       </c>
       <c r="B35" t="str">
         <v>snack</v>
       </c>
       <c r="C35" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="D35" t="str">
-        <v>Nuts + Seeds + Protein Shake</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="E35" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="F35" t="str">
-        <v>global</v>
+        <v>General</v>
       </c>
       <c r="G35">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="H35">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I35">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J35">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K35" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+        <v>USDA + custom user specs</v>
       </c>
       <c r="L35" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>v1_custom</v>
       </c>
       <c r="M35" t="str">
         <v>seed_v1</v>
@@ -2147,48 +2147,48 @@
         <v>1</v>
       </c>
       <c r="O35" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"global","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P35" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":330,"delta_kcal":10,"tolerance_kcal":64},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>snack_chaat-bhel-protein-shake</v>
       </c>
       <c r="B36" t="str">
         <v>snack</v>
       </c>
       <c r="C36" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Chaat + Bhel + Protein Shake</v>
       </c>
       <c r="D36" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Chaat + Bhel + Protein Shake</v>
       </c>
       <c r="E36" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Chaat + Bhel + Protein Shake</v>
       </c>
       <c r="F36" t="str">
-        <v>indian</v>
+        <v>Indian</v>
       </c>
       <c r="G36">
-        <v>180</v>
+        <v>345</v>
       </c>
       <c r="H36">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K36" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+        <v>IFCT/USDA + custom user specs</v>
       </c>
       <c r="L36" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>v1_custom</v>
       </c>
       <c r="M36" t="str">
         <v>seed_v1</v>
@@ -2197,39 +2197,39 @@
         <v>1</v>
       </c>
       <c r="O36" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P36" t="str">
-        <v>{"macros_p":4,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":184,"delta_kcal":4,"tolerance_kcal":36},"issues":[]}}</v>
+        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>snack_greek-yogurt-berry-bowl</v>
       </c>
       <c r="B37" t="str">
         <v>snack</v>
       </c>
       <c r="C37" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Greek yogurt + berry bowl</v>
       </c>
       <c r="D37" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Greek yogurt + berry bowl</v>
       </c>
       <c r="E37" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Greek yogurt + berry bowl</v>
       </c>
       <c r="F37" t="str">
-        <v>indian</v>
+        <v>International</v>
       </c>
       <c r="G37">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="H37">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I37">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="J37">
         <v>4</v>
@@ -2247,42 +2247,42 @@
         <v>1</v>
       </c>
       <c r="O37" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P37" t="str">
-        <v>{"macros_p":10,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":216,"delta_kcal":4,"tolerance_kcal":44},"issues":[]}}</v>
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
       </c>
       <c r="B38" t="str">
         <v>snack</v>
       </c>
       <c r="C38" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Carrot halwa (sugar-free) + protein shake</v>
       </c>
       <c r="D38" t="str">
-        <v>Avocado/Cheese Toast</v>
+        <v>Carrot Halwa + Protein Shake</v>
       </c>
       <c r="E38" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Carrot halwa (sugar-free) + protein shake</v>
       </c>
       <c r="F38" t="str">
-        <v>global</v>
+        <v>Indian</v>
       </c>
       <c r="G38">
-        <v>327</v>
+        <v>220</v>
       </c>
       <c r="H38">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I38">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J38">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K38" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2297,22 +2297,222 @@
         <v>1</v>
       </c>
       <c r="O38" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"global","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P38" t="str">
-        <v>{"macros_p":16,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":328,"delta_kcal":1,"tolerance_kcal":65.4},"issues":[]}}</v>
+        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B39" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Nuts + Seeds + Protein Shake</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="F39" t="str">
+        <v>International</v>
+      </c>
+      <c r="G39">
+        <v>320</v>
+      </c>
+      <c r="H39">
+        <v>31</v>
+      </c>
+      <c r="I39">
+        <v>11</v>
+      </c>
+      <c r="J39">
+        <v>17</v>
+      </c>
+      <c r="K39" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L39" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M39" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P39" t="str">
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B40" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G40">
+        <v>135</v>
+      </c>
+      <c r="H40">
+        <v>3</v>
+      </c>
+      <c r="I40">
+        <v>32</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L40" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M40" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P40" t="str">
+        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B41" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G41">
+        <v>246</v>
+      </c>
+      <c r="H41">
+        <v>13</v>
+      </c>
+      <c r="I41">
+        <v>41</v>
+      </c>
+      <c r="J41">
+        <v>4</v>
+      </c>
+      <c r="K41" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L41" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M41" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+      </c>
+      <c r="P41" t="str">
+        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B42" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Avocado/Cheese Toast</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G42">
+        <v>193</v>
+      </c>
+      <c r="H42">
+        <v>9</v>
+      </c>
+      <c r="I42">
+        <v>14</v>
+      </c>
+      <c r="J42">
+        <v>12</v>
+      </c>
+      <c r="K42" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L42" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M42" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P42" t="str">
+        <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":200,"delta_kcal":7,"tolerance_kcal":38.6},"issues":[]}}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P42"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2432,19 +2632,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>breakfast_greek-yogurt-berry-bowl</v>
+        <v>breakfast_poha-kabab-protein-shake</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>Chicken breast</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5" t="str">
-        <v>No carb</v>
+        <v>Poha</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -2453,7 +2653,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I5" t="str">
         <v>{}</v>
@@ -2461,25 +2661,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>breakfast_poha-kabab-protein-shake</v>
+        <v>breakfast_egg-white-omelette-avocado</v>
       </c>
       <c r="B6" t="str">
-        <v>Chicken breast</v>
+        <v>Eggs (whole)</v>
       </c>
       <c r="C6">
+        <v>120</v>
+      </c>
+      <c r="D6" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Mixed salad</v>
+      </c>
+      <c r="G6">
         <v>100</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Poha</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
       </c>
       <c r="H6" t="str">
         <v>Pan-fried</v>
@@ -2490,25 +2690,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>breakfast_egg-white-omelette-avocado</v>
+        <v>breakfast_aloo-paratha-curd</v>
       </c>
       <c r="B7" t="str">
-        <v>Eggs (whole)</v>
+        <v>Paneer</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="D7" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>Mixed salad</v>
-      </c>
-      <c r="G7">
-        <v>100</v>
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
       </c>
       <c r="H7" t="str">
         <v>Pan-fried</v>
@@ -2519,7 +2719,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>breakfast_carrot-halwa-sugar-free-protein-shake</v>
+        <v>breakfast_idli-mysore-masala-dosa-sambar-chutney</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -2528,19 +2728,19 @@
         <v>0</v>
       </c>
       <c r="D8" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G8">
+        <v>120</v>
       </c>
       <c r="H8" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I8" t="str">
         <v>{}</v>
@@ -2548,13 +2748,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>breakfast_aloo-paratha-curd</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti</v>
       </c>
       <c r="B9" t="str">
-        <v>Paneer</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C9">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="D9" t="str">
         <v>Jowar roti (millet)</v>
@@ -2563,13 +2763,13 @@
         <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G9">
+        <v>120</v>
       </c>
       <c r="H9" t="str">
-        <v>Pan-fried</v>
+        <v>Curry style</v>
       </c>
       <c r="I9" t="str">
         <v>{}</v>
@@ -2577,28 +2777,28 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>breakfast_idli-mysore-masala-dosa-sambar-chutney</v>
+        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>Grilled salmon</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D10" t="str">
-        <v>Cooked rice</v>
+        <v>Spaghetti aglio e olio (small portion)</v>
       </c>
       <c r="E10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F10" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G10">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H10" t="str">
-        <v>Pan-fried</v>
+        <v>Grilled</v>
       </c>
       <c r="I10" t="str">
         <v>{}</v>
@@ -2606,25 +2806,25 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti</v>
+        <v>lunch_dinner_rajma-chawal-raita</v>
       </c>
       <c r="B11" t="str">
-        <v>Chicken breast</v>
+        <v/>
       </c>
       <c r="C11">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D11" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="F11" t="str">
         <v>Mixed veg sabzi</v>
       </c>
       <c r="G11">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H11" t="str">
         <v>Curry style</v>
@@ -2635,28 +2835,28 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_chole-jowar-roti-raita</v>
       </c>
       <c r="B12" t="str">
-        <v>Grilled salmon</v>
+        <v/>
       </c>
       <c r="C12">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D12" t="str">
-        <v>Spaghetti aglio e olio (small portion)</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F12" t="str">
-        <v>Sautéed broccoli</v>
-      </c>
-      <c r="G12">
-        <v>150</v>
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I12" t="str">
         <v>{}</v>
@@ -2664,28 +2864,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>lunch_dinner_rajma-chawal-raita</v>
+        <v>lunch_dinner_vietnamese-chicken-pho</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>Chicken breast</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D13" t="str">
-        <v>Cooked rice</v>
+        <v>Rice noodles</v>
       </c>
       <c r="E13">
+        <v>120</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Pho greens + side salad</v>
+      </c>
+      <c r="G13">
         <v>80</v>
       </c>
-      <c r="F13" t="str">
-        <v>Mixed veg sabzi</v>
-      </c>
-      <c r="G13">
-        <v>150</v>
-      </c>
       <c r="H13" t="str">
-        <v>Curry style</v>
+        <v>Soup style</v>
       </c>
       <c r="I13" t="str">
         <v>{}</v>
@@ -2693,28 +2893,28 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>lunch_dinner_chole-jowar-roti-raita</v>
+        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>Beef steak</v>
       </c>
       <c r="C14">
+        <v>180</v>
+      </c>
+      <c r="D14" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E14">
         <v>0</v>
       </c>
-      <c r="D14" t="str">
-        <v>Jowar roti (millet)</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
       <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
+        <v>Mixed greens salad</v>
+      </c>
+      <c r="G14">
+        <v>150</v>
       </c>
       <c r="H14" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I14" t="str">
         <v>{}</v>
@@ -2722,7 +2922,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>lunch_dinner_vietnamese-chicken-pho</v>
+        <v>lunch_dinner_thai-pad-krapow-rice</v>
       </c>
       <c r="B15" t="str">
         <v>Chicken breast</v>
@@ -2731,19 +2931,19 @@
         <v>150</v>
       </c>
       <c r="D15" t="str">
-        <v>Rice noodles</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E15">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F15" t="str">
-        <v>Mixed salad</v>
+        <v>Sautéed peppers + side salad</v>
       </c>
       <c r="G15">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H15" t="str">
-        <v>Soup style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I15" t="str">
         <v>{}</v>
@@ -2751,28 +2951,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
+        <v>lunch_dinner_mutton-keema-jowar-roti</v>
       </c>
       <c r="B16" t="str">
-        <v>Beef steak</v>
+        <v>Mutton keema</v>
       </c>
       <c r="C16">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D16" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>Mixed greens salad</v>
-      </c>
-      <c r="G16">
-        <v>150</v>
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I16" t="str">
         <v>{}</v>
@@ -2780,13 +2980,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>lunch_dinner_thai-pad-krapow-rice</v>
+        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
       </c>
       <c r="B17" t="str">
-        <v>Chicken breast</v>
+        <v>Paneer</v>
       </c>
       <c r="C17">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D17" t="str">
         <v>Cooked rice</v>
@@ -2795,13 +2995,13 @@
         <v>80</v>
       </c>
       <c r="F17" t="str">
-        <v>Sautéed peppers</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G17">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H17" t="str">
-        <v>Pan-fried</v>
+        <v>Curry style</v>
       </c>
       <c r="I17" t="str">
         <v>{}</v>
@@ -2809,10 +3009,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>lunch_dinner_mutton-keema-jowar-roti</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
       </c>
       <c r="B18" t="str">
-        <v>Mutton keema</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C18">
         <v>150</v>
@@ -2824,10 +3024,10 @@
         <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G18">
+        <v>100</v>
       </c>
       <c r="H18" t="str">
         <v>Curry style</v>
@@ -2838,28 +3038,28 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
+        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
       </c>
       <c r="B19" t="str">
-        <v>Paneer</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C19">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D19" t="str">
-        <v>Cooked rice</v>
+        <v>No carb</v>
       </c>
       <c r="E19">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F19" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Pumpkin salad</v>
       </c>
       <c r="G19">
         <v>120</v>
       </c>
       <c r="H19" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I19" t="str">
         <v>{}</v>
@@ -2867,28 +3067,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
+        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
       </c>
       <c r="B20" t="str">
-        <v>Chicken breast</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C20">
         <v>150</v>
       </c>
       <c r="D20" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Garlic rice (small portion)</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F20" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G20">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H20" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I20" t="str">
         <v>{}</v>
@@ -2896,10 +3096,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
+        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
       </c>
       <c r="B21" t="str">
-        <v>Fish fillet</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C21">
         <v>150</v>
@@ -2911,13 +3111,13 @@
         <v>0</v>
       </c>
       <c r="F21" t="str">
-        <v>Pumpkin salad</v>
+        <v>Smoked salmon salad</v>
       </c>
       <c r="G21">
         <v>120</v>
       </c>
       <c r="H21" t="str">
-        <v>Grilled</v>
+        <v>Soup style</v>
       </c>
       <c r="I21" t="str">
         <v>{}</v>
@@ -2925,28 +3125,28 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
+        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
       </c>
       <c r="B22" t="str">
-        <v>Grilled salmon</v>
+        <v>Paneer</v>
       </c>
       <c r="C22">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D22" t="str">
-        <v>Garlic rice (small portion)</v>
+        <v>No carb</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" t="str">
-        <v>Sautéed broccoli</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G22">
         <v>150</v>
       </c>
       <c r="H22" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I22" t="str">
         <v>{}</v>
@@ -2954,13 +3154,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
+        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
       </c>
       <c r="B23" t="str">
-        <v>Chicken breast</v>
+        <v>Pork chop</v>
       </c>
       <c r="C23">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D23" t="str">
         <v>No carb</v>
@@ -2969,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="F23" t="str">
-        <v>Smoked salmon salad</v>
+        <v>Pumpkin salad</v>
       </c>
       <c r="G23">
         <v>120</v>
       </c>
       <c r="H23" t="str">
-        <v>Soup style</v>
+        <v>Grilled</v>
       </c>
       <c r="I23" t="str">
         <v>{}</v>
@@ -2983,13 +3183,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
+        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
       </c>
       <c r="B24" t="str">
-        <v>Paneer</v>
+        <v>Pork chop</v>
       </c>
       <c r="C24">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="D24" t="str">
         <v>No carb</v>
@@ -2998,13 +3198,13 @@
         <v>0</v>
       </c>
       <c r="F24" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G24">
         <v>150</v>
       </c>
       <c r="H24" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I24" t="str">
         <v>{}</v>
@@ -3012,13 +3212,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
+        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
       </c>
       <c r="B25" t="str">
-        <v>Pork chop</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C25">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D25" t="str">
         <v>No carb</v>
@@ -3027,13 +3227,13 @@
         <v>0</v>
       </c>
       <c r="F25" t="str">
-        <v>Pumpkin salad</v>
+        <v>Smoked chicken + avocado salad</v>
       </c>
       <c r="G25">
         <v>120</v>
       </c>
       <c r="H25" t="str">
-        <v>Grilled</v>
+        <v>Tandoori</v>
       </c>
       <c r="I25" t="str">
         <v>{}</v>
@@ -3041,28 +3241,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
+        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B26" t="str">
-        <v>Pork chop</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C26">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D26" t="str">
-        <v>No carb</v>
+        <v>Spaghetti aglio e olio (small portion)</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26" t="str">
-        <v>Mixed greens salad</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G26">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H26" t="str">
-        <v>Grilled</v>
+        <v>Soup style</v>
       </c>
       <c r="I26" t="str">
         <v>{}</v>
@@ -3070,28 +3270,28 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
+        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
       </c>
       <c r="B27" t="str">
-        <v>Chicken breast</v>
+        <v>Lamb (seekh kabab)</v>
       </c>
       <c r="C27">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="D27" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" t="str">
-        <v>Smoked chicken + avocado salad</v>
+        <v>Sautéed spinach</v>
       </c>
       <c r="G27">
         <v>120</v>
       </c>
       <c r="H27" t="str">
-        <v>Tandoori</v>
+        <v>Curry style</v>
       </c>
       <c r="I27" t="str">
         <v>{}</v>
@@ -3099,28 +3299,28 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_kofta-dal-jowar-roti</v>
       </c>
       <c r="B28" t="str">
-        <v>Fish fillet</v>
+        <v>Veg kofta</v>
       </c>
       <c r="C28">
         <v>150</v>
       </c>
       <c r="D28" t="str">
-        <v>Spaghetti aglio e olio (small portion)</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>Sautéed broccoli</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G28">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H28" t="str">
-        <v>Soup style</v>
+        <v>Curry style</v>
       </c>
       <c r="I28" t="str">
         <v>{}</v>
@@ -3128,13 +3328,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
+        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
       </c>
       <c r="B29" t="str">
         <v>Lamb (seekh kabab)</v>
       </c>
       <c r="C29">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D29" t="str">
         <v>Jowar roti (millet)</v>
@@ -3143,13 +3343,13 @@
         <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>Sautéed spinach</v>
+        <v>Cauliflower</v>
       </c>
       <c r="G29">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H29" t="str">
-        <v>Curry style</v>
+        <v>Tandoori</v>
       </c>
       <c r="I29" t="str">
         <v>{}</v>
@@ -3157,25 +3357,25 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>lunch_dinner_kofta-dal-jowar-roti</v>
+        <v>lunch_dinner_fish-curry-rice</v>
       </c>
       <c r="B30" t="str">
-        <v>Lamb (seekh kabab)</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C30">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D30" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="F30" t="str">
-        <v>Mixed veg sabzi</v>
-      </c>
-      <c r="G30">
-        <v>120</v>
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
       </c>
       <c r="H30" t="str">
         <v>Curry style</v>
@@ -3186,13 +3386,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B31" t="str">
-        <v>Lamb (seekh kabab)</v>
+        <v>Kaala chanaa (black chickpeas)</v>
       </c>
       <c r="C31">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D31" t="str">
         <v>Jowar roti (millet)</v>
@@ -3201,13 +3401,13 @@
         <v>2</v>
       </c>
       <c r="F31" t="str">
-        <v>Cauliflower</v>
+        <v>Sweet potato curry</v>
       </c>
       <c r="G31">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="H31" t="str">
-        <v>Tandoori</v>
+        <v>Curry style</v>
       </c>
       <c r="I31" t="str">
         <v>{}</v>
@@ -3215,28 +3415,28 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lunch_dinner_fish-curry-rice</v>
+        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
       </c>
       <c r="B32" t="str">
-        <v>Fish fillet</v>
+        <v>Smoked salmon</v>
       </c>
       <c r="C32">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D32" t="str">
-        <v>Cooked rice</v>
+        <v>No carb</v>
       </c>
       <c r="E32">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F32" t="str">
-        <v/>
-      </c>
-      <c r="G32" t="str">
-        <v/>
+        <v>Avocado &amp; mixed greens</v>
+      </c>
+      <c r="G32">
+        <v>155</v>
       </c>
       <c r="H32" t="str">
-        <v>Curry style</v>
+        <v>Salad</v>
       </c>
       <c r="I32" t="str">
         <v>{}</v>
@@ -3244,28 +3444,28 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
+        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
       </c>
       <c r="B33" t="str">
-        <v>Kaala chanaa (black chickpeas)</v>
+        <v>Smoked chicken breast</v>
       </c>
       <c r="C33">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D33" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>No carb</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" t="str">
-        <v>Sweet potato curry</v>
+        <v>Avocado &amp; mixed greens</v>
       </c>
       <c r="G33">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="H33" t="str">
-        <v>Curry style</v>
+        <v>Salad</v>
       </c>
       <c r="I33" t="str">
         <v>{}</v>
@@ -3291,7 +3491,7 @@
         <v>Red curry vegetables</v>
       </c>
       <c r="G34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H34" t="str">
         <v>Curry style</v>
@@ -3302,28 +3502,28 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>snack_fruit-almonds-plant-shake</v>
       </c>
       <c r="B35" t="str">
-        <v/>
-      </c>
-      <c r="C35" t="str">
-        <v/>
+        <v>Plant Shake</v>
+      </c>
+      <c r="C35">
+        <v>25</v>
       </c>
       <c r="D35" t="str">
-        <v/>
-      </c>
-      <c r="E35" t="str">
-        <v/>
+        <v>Mixed Fruit</v>
+      </c>
+      <c r="E35">
+        <v>100</v>
       </c>
       <c r="F35" t="str">
-        <v/>
-      </c>
-      <c r="G35" t="str">
-        <v/>
+        <v>Almonds</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>Snack</v>
       </c>
       <c r="I35" t="str">
         <v>{}</v>
@@ -3331,19 +3531,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>snack_chaat-bhel-protein-shake</v>
       </c>
       <c r="B36" t="str">
-        <v/>
-      </c>
-      <c r="C36" t="str">
-        <v/>
+        <v>Plant Shake</v>
+      </c>
+      <c r="C36">
+        <v>25</v>
       </c>
       <c r="D36" t="str">
-        <v/>
-      </c>
-      <c r="E36" t="str">
-        <v/>
+        <v>Chaat &amp; Bhel</v>
+      </c>
+      <c r="E36">
+        <v>150</v>
       </c>
       <c r="F36" t="str">
         <v/>
@@ -3352,7 +3552,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>Street Food Twist</v>
       </c>
       <c r="I36" t="str">
         <v>{}</v>
@@ -3360,19 +3560,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>snack_greek-yogurt-berry-bowl</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
-      <c r="C37" t="str">
-        <v/>
+      <c r="C37">
+        <v>0</v>
       </c>
       <c r="D37" t="str">
-        <v/>
-      </c>
-      <c r="E37" t="str">
-        <v/>
+        <v>No carb</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
       </c>
       <c r="F37" t="str">
         <v/>
@@ -3381,7 +3581,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>Grilled</v>
       </c>
       <c r="I37" t="str">
         <v>{}</v>
@@ -3389,19 +3589,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
-      <c r="C38" t="str">
-        <v/>
+      <c r="C38">
+        <v>0</v>
       </c>
       <c r="D38" t="str">
-        <v/>
-      </c>
-      <c r="E38" t="str">
-        <v/>
+        <v>No carb</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
       </c>
       <c r="F38" t="str">
         <v/>
@@ -3410,15 +3610,131 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>Grilled</v>
       </c>
       <c r="I38" t="str">
         <v>{}</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Mixed nuts &amp; seeds</v>
+      </c>
+      <c r="C39">
+        <v>30</v>
+      </c>
+      <c r="D39" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="I39" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Sweet potato</v>
+      </c>
+      <c r="E40">
+        <v>150</v>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I40" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Kaala chana</v>
+      </c>
+      <c r="C41">
+        <v>150</v>
+      </c>
+      <c r="D41" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I41" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Whole wheat toast</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Avocado</v>
+      </c>
+      <c r="G42">
+        <v>50</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Toast</v>
+      </c>
+      <c r="I42" t="str">
+        <v>{}</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I42"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/exports/meal_database_architecture_v1.xlsx
+++ b/exports/meal_database_architecture_v1.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -805,40 +805,40 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti</v>
+        <v>breakfast_chicken-keema-bhurji-jowar-roti</v>
       </c>
       <c r="B9" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C9" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Chicken keema bhurji + jowar roti</v>
       </c>
       <c r="D9" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Chicken Keema Bhurji + Jowar Roti</v>
       </c>
       <c r="E9" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Chicken keema bhurji + jowar roti</v>
       </c>
       <c r="F9" t="str">
         <v>Indian</v>
       </c>
       <c r="G9">
-        <v>702</v>
+        <v>554</v>
       </c>
       <c r="H9">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I9">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K9" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L9" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M9" t="str">
         <v>seed_v1</v>
@@ -847,48 +847,48 @@
         <v>1</v>
       </c>
       <c r="O9" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"mixed","carb_level":"high","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P9" t="str">
-        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":676,"delta_kcal":26,"tolerance_kcal":140.4},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"mixed","meal_weight_class":"medium","carb_level":"high","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":542,"delta_kcal":12,"tolerance_kcal":110.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
+        <v>breakfast_moong-dal-chilla-paneer-hung-curd</v>
       </c>
       <c r="B10" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C10" t="str">
-        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
+        <v>Moong dal chilla + paneer + hung curd</v>
       </c>
       <c r="D10" t="str">
-        <v>Salmon + Veg + Aglio Olio</v>
+        <v>Moong Dal Chilla + Paneer</v>
       </c>
       <c r="E10" t="str">
-        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
+        <v>Moong dal chilla + paneer + hung curd</v>
       </c>
       <c r="F10" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G10">
-        <v>669</v>
+        <v>568</v>
       </c>
       <c r="H10">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I10">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K10" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L10" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M10" t="str">
         <v>seed_v1</v>
@@ -897,48 +897,48 @@
         <v>1</v>
       </c>
       <c r="O10" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"continental","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P10" t="str">
-        <v>{"macros_p":46,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":688,"delta_kcal":19,"tolerance_kcal":133.8},"issues":[]}}</v>
+        <v>{"macros_p":42,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":567,"delta_kcal":1,"tolerance_kcal":113.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>lunch_dinner_rajma-chawal-raita</v>
+        <v>breakfast_oats-whey-porridge-nuts</v>
       </c>
       <c r="B11" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C11" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Oats + whey porridge with nuts</v>
       </c>
       <c r="D11" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Oats + Whey Porridge</v>
       </c>
       <c r="E11" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Oats + whey porridge with nuts</v>
       </c>
       <c r="F11" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G11">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="H11">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="I11">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="J11">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K11" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L11" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M11" t="str">
         <v>seed_v1</v>
@@ -947,48 +947,48 @@
         <v>1</v>
       </c>
       <c r="O11" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P11" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":482,"delta_kcal":0,"tolerance_kcal":96.4},"issues":[]}}</v>
+        <v>{"macros_p":42,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":527,"delta_kcal":6,"tolerance_kcal":104.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>lunch_dinner_chole-jowar-roti-raita</v>
+        <v>breakfast_chicken-sausage-scrambled-eggs-toast</v>
       </c>
       <c r="B12" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C12" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Chicken sausage + scrambled eggs + toast</v>
       </c>
       <c r="D12" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Chicken Sausage + Eggs + Toast</v>
       </c>
       <c r="E12" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Chicken sausage + scrambled eggs + toast</v>
       </c>
       <c r="F12" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G12">
-        <v>726</v>
+        <v>541</v>
       </c>
       <c r="H12">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I12">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K12" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L12" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M12" t="str">
         <v>seed_v1</v>
@@ -997,48 +997,48 @@
         <v>1</v>
       </c>
       <c r="O12" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P12" t="str">
-        <v>{"macros_p":27,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":722,"delta_kcal":4,"tolerance_kcal":145.2},"issues":[]}}</v>
+        <v>{"macros_p":44,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":530,"delta_kcal":11,"tolerance_kcal":108.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>lunch_dinner_vietnamese-chicken-pho</v>
+        <v>breakfast_tofu-spinach-scramble-avocado-toast</v>
       </c>
       <c r="B13" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C13" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Tofu &amp; spinach scramble + avocado toast</v>
       </c>
       <c r="D13" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Tofu Scramble + Avocado Toast</v>
       </c>
       <c r="E13" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Tofu &amp; spinach scramble + avocado toast</v>
       </c>
       <c r="F13" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G13">
-        <v>394</v>
+        <v>516</v>
       </c>
       <c r="H13">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I13">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J13">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="K13" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L13" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M13" t="str">
         <v>seed_v1</v>
@@ -1047,48 +1047,48 @@
         <v>1</v>
       </c>
       <c r="O13" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"toast","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P13" t="str">
-        <v>{"macros_p":49,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":374,"delta_kcal":20,"tolerance_kcal":78.8},"issues":[]}}</v>
+        <v>{"macros_p":43,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":553,"delta_kcal":37,"tolerance_kcal":103.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
+        <v>breakfast_idli-sambar-masala-egg-bhurji</v>
       </c>
       <c r="B14" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C14" t="str">
-        <v>Grilled steak + mixed greens salad</v>
+        <v>Idli + sambar + masala egg bhurji</v>
       </c>
       <c r="D14" t="str">
-        <v>Steak + Mixed Greens</v>
+        <v>Idli + Sambar + Egg Bhurji</v>
       </c>
       <c r="E14" t="str">
-        <v>Grilled steak + mixed greens salad</v>
+        <v>Idli + sambar + masala egg bhurji</v>
       </c>
       <c r="F14" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G14">
-        <v>480</v>
+        <v>575</v>
       </c>
       <c r="H14">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="J14">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K14" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L14" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M14" t="str">
         <v>seed_v1</v>
@@ -1097,48 +1097,48 @@
         <v>1</v>
       </c>
       <c r="O14" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P14" t="str">
-        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":477,"delta_kcal":3,"tolerance_kcal":96},"issues":[]}}</v>
+        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":564,"delta_kcal":11,"tolerance_kcal":115},"issues":[]}}</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>lunch_dinner_thai-pad-krapow-rice</v>
+        <v>breakfast_paneer-paratha-curd</v>
       </c>
       <c r="B15" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C15" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Paneer paratha + curd</v>
       </c>
       <c r="D15" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Paneer paratha + curd</v>
       </c>
       <c r="E15" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Paneer paratha + curd</v>
       </c>
       <c r="F15" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G15">
-        <v>438</v>
+        <v>593</v>
       </c>
       <c r="H15">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="I15">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="J15">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="K15" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L15" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M15" t="str">
         <v>seed_v1</v>
@@ -1147,42 +1147,42 @@
         <v>1</v>
       </c>
       <c r="O15" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"plate","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P15" t="str">
-        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":422,"delta_kcal":16,"tolerance_kcal":87.6},"issues":[]}}</v>
+        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"plate","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":591,"delta_kcal":2,"tolerance_kcal":118.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>lunch_dinner_mutton-keema-jowar-roti</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti</v>
       </c>
       <c r="B16" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C16" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="D16" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="E16" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="F16" t="str">
         <v>Indian</v>
       </c>
       <c r="G16">
-        <v>670</v>
+        <v>702</v>
       </c>
       <c r="H16">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="I16">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="J16">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="K16" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1197,42 +1197,42 @@
         <v>1</v>
       </c>
       <c r="O16" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P16" t="str">
-        <v>{"macros_p":34,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":654,"delta_kcal":16,"tolerance_kcal":134},"issues":[]}}</v>
+        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":676,"delta_kcal":26,"tolerance_kcal":140.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
+        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B17" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C17" t="str">
-        <v>Arhar dal + rice + matar paneer</v>
+        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
       </c>
       <c r="D17" t="str">
-        <v>Arhar Dal + Rice + Matar Paneer</v>
+        <v>Salmon + Veg + Aglio Olio</v>
       </c>
       <c r="E17" t="str">
-        <v>Arhar dal + rice + matar paneer</v>
+        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
       </c>
       <c r="F17" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G17">
         <v>669</v>
       </c>
       <c r="H17">
+        <v>46</v>
+      </c>
+      <c r="I17">
+        <v>54</v>
+      </c>
+      <c r="J17">
         <v>32</v>
-      </c>
-      <c r="I17">
-        <v>67</v>
-      </c>
-      <c r="J17">
-        <v>30</v>
       </c>
       <c r="K17" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1247,42 +1247,42 @@
         <v>1</v>
       </c>
       <c r="O17" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"continental","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P17" t="str">
-        <v>{"macros_p":32,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":666,"delta_kcal":3,"tolerance_kcal":133.8},"issues":[]}}</v>
+        <v>{"macros_p":46,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":688,"delta_kcal":19,"tolerance_kcal":133.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
+        <v>lunch_dinner_rajma-chawal-raita</v>
       </c>
       <c r="B18" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C18" t="str">
-        <v>Chicken curry + jowar roti + dal</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="D18" t="str">
-        <v>Chicken Curry + Roti + Dal</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="E18" t="str">
-        <v>Chicken curry + jowar roti + dal</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="F18" t="str">
         <v>Indian</v>
       </c>
       <c r="G18">
-        <v>736</v>
+        <v>482</v>
       </c>
       <c r="H18">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="I18">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J18">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K18" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1297,42 +1297,42 @@
         <v>1</v>
       </c>
       <c r="O18" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P18" t="str">
-        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":709,"delta_kcal":27,"tolerance_kcal":147.2},"issues":[]}}</v>
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":482,"delta_kcal":0,"tolerance_kcal":96.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
+        <v>lunch_dinner_chole-jowar-roti-raita</v>
       </c>
       <c r="B19" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C19" t="str">
-        <v>Grilled fish + pumpkin salad</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="D19" t="str">
-        <v>Grilled Fish + Pumpkin Salad</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="E19" t="str">
-        <v>Grilled fish + pumpkin salad</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="F19" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G19">
-        <v>308</v>
+        <v>726</v>
       </c>
       <c r="H19">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I19">
+        <v>113</v>
+      </c>
+      <c r="J19">
         <v>18</v>
-      </c>
-      <c r="J19">
-        <v>9</v>
       </c>
       <c r="K19" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1347,42 +1347,42 @@
         <v>1</v>
       </c>
       <c r="O19" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P19" t="str">
-        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":305,"delta_kcal":3,"tolerance_kcal":61.6},"issues":[]}}</v>
+        <v>{"macros_p":27,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":722,"delta_kcal":4,"tolerance_kcal":145.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
+        <v>lunch_dinner_vietnamese-chicken-pho</v>
       </c>
       <c r="B20" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C20" t="str">
-        <v>Grilled salmon + sauteed veg + garlic rice</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="D20" t="str">
-        <v>Salmon + Veg + Garlic Rice</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="E20" t="str">
-        <v>Grilled salmon + sauteed veg + garlic rice</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="F20" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G20">
-        <v>514</v>
+        <v>394</v>
       </c>
       <c r="H20">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I20">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J20">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="K20" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1397,42 +1397,42 @@
         <v>1</v>
       </c>
       <c r="O20" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P20" t="str">
-        <v>{"macros_p":40,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":11,"tolerance_kcal":102.8},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":374,"delta_kcal":20,"tolerance_kcal":78.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
+        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
       </c>
       <c r="B21" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C21" t="str">
-        <v>Chicken soup + smoked salmon salad</v>
+        <v>Grilled steak + mixed greens salad</v>
       </c>
       <c r="D21" t="str">
-        <v>Chicken Soup + Salmon Salad</v>
+        <v>Steak + Mixed Greens</v>
       </c>
       <c r="E21" t="str">
-        <v>Chicken soup + smoked salmon salad</v>
+        <v>Grilled steak + mixed greens salad</v>
       </c>
       <c r="F21" t="str">
         <v>Continental</v>
       </c>
       <c r="G21">
-        <v>302</v>
+        <v>480</v>
       </c>
       <c r="H21">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="K21" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1447,42 +1447,42 @@
         <v>1</v>
       </c>
       <c r="O21" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"low","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P21" t="str">
-        <v>{"macros_p":50,"protein_family":"mixed","meal_weight_class":"light","carb_level":"low","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":284,"delta_kcal":18,"tolerance_kcal":60.4},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":477,"delta_kcal":3,"tolerance_kcal":96},"issues":[]}}</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
+        <v>lunch_dinner_thai-pad-krapow-rice</v>
       </c>
       <c r="B22" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C22" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="D22" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="E22" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="F22" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G22">
-        <v>628</v>
+        <v>438</v>
       </c>
       <c r="H22">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="I22">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J22">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K22" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1497,42 +1497,42 @@
         <v>1</v>
       </c>
       <c r="O22" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P22" t="str">
-        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":631,"delta_kcal":3,"tolerance_kcal":125.6},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":422,"delta_kcal":16,"tolerance_kcal":87.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
+        <v>lunch_dinner_mutton-keema-jowar-roti</v>
       </c>
       <c r="B23" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C23" t="str">
-        <v>Pork chop + pumpkin salad</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="D23" t="str">
-        <v>Pork Chop + Pumpkin Salad</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="E23" t="str">
-        <v>Pork chop + pumpkin salad</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="F23" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G23">
-        <v>562</v>
+        <v>670</v>
       </c>
       <c r="H23">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="I23">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J23">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K23" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1547,42 +1547,42 @@
         <v>1</v>
       </c>
       <c r="O23" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P23" t="str">
-        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":13,"tolerance_kcal":112.4},"issues":[]}}</v>
+        <v>{"macros_p":34,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":654,"delta_kcal":16,"tolerance_kcal":134},"issues":[]}}</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
+        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
       </c>
       <c r="B24" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C24" t="str">
-        <v>Pork chop + mixed greens salad</v>
+        <v>Arhar dal + rice + matar paneer</v>
       </c>
       <c r="D24" t="str">
-        <v>Pork Chop + Mixed Greens</v>
+        <v>Arhar Dal + Rice + Matar Paneer</v>
       </c>
       <c r="E24" t="str">
-        <v>Pork chop + mixed greens salad</v>
+        <v>Arhar dal + rice + matar paneer</v>
       </c>
       <c r="F24" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G24">
-        <v>449</v>
+        <v>669</v>
       </c>
       <c r="H24">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="J24">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K24" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1597,42 +1597,42 @@
         <v>1</v>
       </c>
       <c r="O24" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P24" t="str">
-        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":435,"delta_kcal":14,"tolerance_kcal":89.8},"issues":[]}}</v>
+        <v>{"macros_p":32,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":666,"delta_kcal":3,"tolerance_kcal":133.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
       </c>
       <c r="B25" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C25" t="str">
-        <v>Tandoori chicken + smoked chicken + avocado salad</v>
+        <v>Chicken curry + jowar roti + dal</v>
       </c>
       <c r="D25" t="str">
-        <v>Tandoori Chicken + Smoked Chicken Salad</v>
+        <v>Chicken Curry + Roti + Dal</v>
       </c>
       <c r="E25" t="str">
-        <v>Tandoori chicken + smoked chicken + avocado salad</v>
+        <v>Chicken curry + jowar roti + dal</v>
       </c>
       <c r="F25" t="str">
         <v>Indian</v>
       </c>
       <c r="G25">
-        <v>366</v>
+        <v>736</v>
       </c>
       <c r="H25">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="J25">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K25" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1647,42 +1647,42 @@
         <v>1</v>
       </c>
       <c r="O25" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P25" t="str">
-        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":347,"delta_kcal":19,"tolerance_kcal":73.2},"issues":[]}}</v>
+        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":709,"delta_kcal":27,"tolerance_kcal":147.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
       </c>
       <c r="B26" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C26" t="str">
-        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
+        <v>Grilled fish + pumpkin salad</v>
       </c>
       <c r="D26" t="str">
-        <v>Broccoli Soup + Fish + Aglio Olio</v>
+        <v>Grilled Fish + Pumpkin Salad</v>
       </c>
       <c r="E26" t="str">
-        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
+        <v>Grilled fish + pumpkin salad</v>
       </c>
       <c r="F26" t="str">
         <v>Continental</v>
       </c>
       <c r="G26">
-        <v>433</v>
+        <v>308</v>
       </c>
       <c r="H26">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I26">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J26">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K26" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1697,42 +1697,42 @@
         <v>1</v>
       </c>
       <c r="O26" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P26" t="str">
-        <v>{"macros_p":45,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":448,"delta_kcal":15,"tolerance_kcal":86.6},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":305,"delta_kcal":3,"tolerance_kcal":61.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
+        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
       </c>
       <c r="B27" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C27" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Grilled salmon + sauteed veg + garlic rice</v>
       </c>
       <c r="D27" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Salmon + Veg + Garlic Rice</v>
       </c>
       <c r="E27" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Grilled salmon + sauteed veg + garlic rice</v>
       </c>
       <c r="F27" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G27">
-        <v>771</v>
+        <v>514</v>
       </c>
       <c r="H27">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I27">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="J27">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K27" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1747,42 +1747,42 @@
         <v>1</v>
       </c>
       <c r="O27" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P27" t="str">
-        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":755,"delta_kcal":16,"tolerance_kcal":154.2},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":11,"tolerance_kcal":102.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lunch_dinner_kofta-dal-jowar-roti</v>
+        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
       </c>
       <c r="B28" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C28" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Chicken soup + smoked salmon salad</v>
       </c>
       <c r="D28" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Chicken Soup + Salmon Salad</v>
       </c>
       <c r="E28" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Chicken soup + smoked salmon salad</v>
       </c>
       <c r="F28" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G28">
-        <v>769</v>
+        <v>302</v>
       </c>
       <c r="H28">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="I28">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="J28">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K28" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1797,42 +1797,42 @@
         <v>1</v>
       </c>
       <c r="O28" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"low","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P28" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":746,"delta_kcal":23,"tolerance_kcal":153.8},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"mixed","meal_weight_class":"light","carb_level":"low","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":284,"delta_kcal":18,"tolerance_kcal":60.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
+        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
       </c>
       <c r="B29" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C29" t="str">
-        <v>Kababs + dal + gobi + jowar roti</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="D29" t="str">
-        <v>Kababs + Dal + Gobi + Roti</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="E29" t="str">
-        <v>Kababs + dal + gobi + jowar roti</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="F29" t="str">
         <v>Indian</v>
       </c>
       <c r="G29">
-        <v>823</v>
+        <v>628</v>
       </c>
       <c r="H29">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I29">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J29">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K29" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1847,42 +1847,42 @@
         <v>1</v>
       </c>
       <c r="O29" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P29" t="str">
-        <v>{"macros_p":41,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":813,"delta_kcal":10,"tolerance_kcal":164.6},"issues":[]}}</v>
+        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":631,"delta_kcal":3,"tolerance_kcal":125.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>lunch_dinner_fish-curry-rice</v>
+        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
       </c>
       <c r="B30" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C30" t="str">
-        <v>Fish curry + rice</v>
+        <v>Pork chop + pumpkin salad</v>
       </c>
       <c r="D30" t="str">
-        <v>Fish curry + rice</v>
+        <v>Pork Chop + Pumpkin Salad</v>
       </c>
       <c r="E30" t="str">
-        <v>Fish curry + rice</v>
+        <v>Pork chop + pumpkin salad</v>
       </c>
       <c r="F30" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G30">
-        <v>446</v>
+        <v>562</v>
       </c>
       <c r="H30">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I30">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="J30">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K30" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1897,42 +1897,42 @@
         <v>1</v>
       </c>
       <c r="O30" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P30" t="str">
-        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":433,"delta_kcal":13,"tolerance_kcal":89.2},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":13,"tolerance_kcal":112.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
+        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
       </c>
       <c r="B31" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C31" t="str">
-        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
+        <v>Pork chop + mixed greens salad</v>
       </c>
       <c r="D31" t="str">
-        <v>Sweet Potato Curry + Kaala Chanaa + Jowar Roti</v>
+        <v>Pork Chop + Mixed Greens</v>
       </c>
       <c r="E31" t="str">
-        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
+        <v>Pork chop + mixed greens salad</v>
       </c>
       <c r="F31" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G31">
-        <v>731</v>
+        <v>449</v>
       </c>
       <c r="H31">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I31">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K31" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1947,42 +1947,42 @@
         <v>1</v>
       </c>
       <c r="O31" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P31" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":735,"delta_kcal":4,"tolerance_kcal":146.2},"issues":[]}}</v>
+        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":435,"delta_kcal":14,"tolerance_kcal":89.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
+        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
       </c>
       <c r="B32" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C32" t="str">
-        <v>Avocado and smoked salmon salad</v>
+        <v>Tandoori chicken + smoked chicken + avocado salad</v>
       </c>
       <c r="D32" t="str">
-        <v>Avocado &amp; Smoked Salmon Salad</v>
+        <v>Tandoori Chicken + Smoked Chicken Salad</v>
       </c>
       <c r="E32" t="str">
-        <v>Avocado and smoked salmon salad</v>
+        <v>Tandoori chicken + smoked chicken + avocado salad</v>
       </c>
       <c r="F32" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G32">
-        <v>206</v>
+        <v>366</v>
       </c>
       <c r="H32">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K32" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1997,42 +1997,42 @@
         <v>1</v>
       </c>
       <c r="O32" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P32" t="str">
-        <v>{"macros_p":24,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":201,"delta_kcal":5,"tolerance_kcal":41.2},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":347,"delta_kcal":19,"tolerance_kcal":73.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
+        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B33" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C33" t="str">
-        <v>Avocado and smoked chicken salad</v>
+        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
       </c>
       <c r="D33" t="str">
-        <v>Avocado &amp; Smoked Chicken Salad</v>
+        <v>Broccoli Soup + Fish + Aglio Olio</v>
       </c>
       <c r="E33" t="str">
-        <v>Avocado and smoked chicken salad</v>
+        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
       </c>
       <c r="F33" t="str">
         <v>Continental</v>
       </c>
       <c r="G33">
-        <v>244</v>
+        <v>433</v>
       </c>
       <c r="H33">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K33" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2047,42 +2047,42 @@
         <v>1</v>
       </c>
       <c r="O33" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P33" t="str">
-        <v>{"macros_p":33,"protein_family":"chicken","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":237,"delta_kcal":7,"tolerance_kcal":48.8},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":448,"delta_kcal":15,"tolerance_kcal":86.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>lunch_dinner_chicken-red-curry-rice</v>
+        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
       </c>
       <c r="B34" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C34" t="str">
-        <v>Chicken red curry + rice</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="D34" t="str">
-        <v>Chicken Red Curry + Rice</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="E34" t="str">
-        <v>Chicken red curry + rice</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="F34" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G34">
-        <v>504</v>
+        <v>771</v>
       </c>
       <c r="H34">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I34">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="J34">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K34" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2097,48 +2097,48 @@
         <v>1</v>
       </c>
       <c r="O34" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P34" t="str">
-        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":486,"delta_kcal":18,"tolerance_kcal":100.8},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":755,"delta_kcal":16,"tolerance_kcal":154.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>lunch_dinner_kofta-dal-jowar-roti</v>
       </c>
       <c r="B35" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C35" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="D35" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="E35" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="F35" t="str">
-        <v>General</v>
+        <v>Indian</v>
       </c>
       <c r="G35">
-        <v>200</v>
+        <v>769</v>
       </c>
       <c r="H35">
         <v>23</v>
       </c>
       <c r="I35">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="K35" t="str">
-        <v>USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L35" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M35" t="str">
         <v>seed_v1</v>
@@ -2147,48 +2147,48 @@
         <v>1</v>
       </c>
       <c r="O35" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
       </c>
       <c r="P35" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":746,"delta_kcal":23,"tolerance_kcal":153.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
       </c>
       <c r="B36" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C36" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Kababs + dal + gobi + jowar roti</v>
       </c>
       <c r="D36" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Kababs + Dal + Gobi + Roti</v>
       </c>
       <c r="E36" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Kababs + dal + gobi + jowar roti</v>
       </c>
       <c r="F36" t="str">
         <v>Indian</v>
       </c>
       <c r="G36">
-        <v>345</v>
+        <v>823</v>
       </c>
       <c r="H36">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="I36">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J36">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="K36" t="str">
-        <v>IFCT/USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L36" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M36" t="str">
         <v>seed_v1</v>
@@ -2197,42 +2197,42 @@
         <v>1</v>
       </c>
       <c r="O36" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P36" t="str">
-        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":813,"delta_kcal":10,"tolerance_kcal":164.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>lunch_dinner_fish-curry-rice</v>
       </c>
       <c r="B37" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C37" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="D37" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="E37" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="F37" t="str">
-        <v>International</v>
+        <v>Indian</v>
       </c>
       <c r="G37">
-        <v>203</v>
+        <v>446</v>
       </c>
       <c r="H37">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="I37">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K37" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2247,42 +2247,42 @@
         <v>1</v>
       </c>
       <c r="O37" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P37" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":433,"delta_kcal":13,"tolerance_kcal":89.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B38" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C38" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="D38" t="str">
-        <v>Carrot Halwa + Protein Shake</v>
+        <v>Sweet Potato Curry + Kaala Chanaa + Jowar Roti</v>
       </c>
       <c r="E38" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="F38" t="str">
         <v>Indian</v>
       </c>
       <c r="G38">
-        <v>220</v>
+        <v>731</v>
       </c>
       <c r="H38">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I38">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="J38">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K38" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2297,42 +2297,42 @@
         <v>1</v>
       </c>
       <c r="O38" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
       </c>
       <c r="P38" t="str">
-        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":735,"delta_kcal":4,"tolerance_kcal":146.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
       </c>
       <c r="B39" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C39" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Avocado and smoked salmon salad</v>
       </c>
       <c r="D39" t="str">
-        <v>Nuts + Seeds + Protein Shake</v>
+        <v>Avocado &amp; Smoked Salmon Salad</v>
       </c>
       <c r="E39" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Avocado and smoked salmon salad</v>
       </c>
       <c r="F39" t="str">
-        <v>International</v>
+        <v>Continental</v>
       </c>
       <c r="G39">
-        <v>320</v>
+        <v>206</v>
       </c>
       <c r="H39">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I39">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K39" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2347,42 +2347,42 @@
         <v>1</v>
       </c>
       <c r="O39" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P39" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+        <v>{"macros_p":24,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":201,"delta_kcal":5,"tolerance_kcal":41.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
       </c>
       <c r="B40" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C40" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Avocado and smoked chicken salad</v>
       </c>
       <c r="D40" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Avocado &amp; Smoked Chicken Salad</v>
       </c>
       <c r="E40" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Avocado and smoked chicken salad</v>
       </c>
       <c r="F40" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G40">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="I40">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K40" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2397,42 +2397,42 @@
         <v>1</v>
       </c>
       <c r="O40" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P40" t="str">
-        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+        <v>{"macros_p":33,"protein_family":"chicken","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":237,"delta_kcal":7,"tolerance_kcal":48.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>lunch_dinner_chicken-red-curry-rice</v>
       </c>
       <c r="B41" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C41" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Chicken red curry + rice</v>
       </c>
       <c r="D41" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Chicken Red Curry + Rice</v>
       </c>
       <c r="E41" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Chicken red curry + rice</v>
       </c>
       <c r="F41" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G41">
-        <v>246</v>
+        <v>504</v>
       </c>
       <c r="H41">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="I41">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K41" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2447,48 +2447,48 @@
         <v>1</v>
       </c>
       <c r="O41" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P41" t="str">
-        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":486,"delta_kcal":18,"tolerance_kcal":100.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>snack_fruit-almonds-plant-shake</v>
       </c>
       <c r="B42" t="str">
         <v>snack</v>
       </c>
       <c r="C42" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="D42" t="str">
-        <v>Avocado/Cheese Toast</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="E42" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="F42" t="str">
-        <v>Continental</v>
+        <v>General</v>
       </c>
       <c r="G42">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="H42">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I42">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J42">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K42" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+        <v>USDA + custom user specs</v>
       </c>
       <c r="L42" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>v1_custom</v>
       </c>
       <c r="M42" t="str">
         <v>seed_v1</v>
@@ -2497,22 +2497,372 @@
         <v>1</v>
       </c>
       <c r="O42" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P42" t="str">
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>snack_chaat-bhel-protein-shake</v>
+      </c>
+      <c r="B43" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G43">
+        <v>345</v>
+      </c>
+      <c r="H43">
+        <v>26</v>
+      </c>
+      <c r="I43">
+        <v>38</v>
+      </c>
+      <c r="J43">
+        <v>9</v>
+      </c>
+      <c r="K43" t="str">
+        <v>IFCT/USDA + custom user specs</v>
+      </c>
+      <c r="L43" t="str">
+        <v>v1_custom</v>
+      </c>
+      <c r="M43" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
+      </c>
+      <c r="O43" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+      </c>
+      <c r="P43" t="str">
+        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>snack_greek-yogurt-berry-bowl</v>
+      </c>
+      <c r="B44" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="F44" t="str">
+        <v>International</v>
+      </c>
+      <c r="G44">
+        <v>203</v>
+      </c>
+      <c r="H44">
+        <v>21</v>
+      </c>
+      <c r="I44">
+        <v>22</v>
+      </c>
+      <c r="J44">
+        <v>4</v>
+      </c>
+      <c r="K44" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L44" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M44" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P44" t="str">
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+      </c>
+      <c r="B45" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Carrot halwa (sugar-free) + protein shake</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Carrot Halwa + Protein Shake</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Carrot halwa (sugar-free) + protein shake</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G45">
+        <v>220</v>
+      </c>
+      <c r="H45">
+        <v>28</v>
+      </c>
+      <c r="I45">
+        <v>17</v>
+      </c>
+      <c r="J45">
+        <v>5</v>
+      </c>
+      <c r="K45" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L45" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M45" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P45" t="str">
+        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B46" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Nuts + Seeds + Protein Shake</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="F46" t="str">
+        <v>International</v>
+      </c>
+      <c r="G46">
+        <v>320</v>
+      </c>
+      <c r="H46">
+        <v>31</v>
+      </c>
+      <c r="I46">
+        <v>11</v>
+      </c>
+      <c r="J46">
+        <v>17</v>
+      </c>
+      <c r="K46" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L46" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M46" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P46" t="str">
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B47" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G47">
+        <v>135</v>
+      </c>
+      <c r="H47">
+        <v>3</v>
+      </c>
+      <c r="I47">
+        <v>32</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L47" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M47" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N47" t="b">
+        <v>1</v>
+      </c>
+      <c r="O47" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P47" t="str">
+        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B48" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G48">
+        <v>246</v>
+      </c>
+      <c r="H48">
+        <v>13</v>
+      </c>
+      <c r="I48">
+        <v>41</v>
+      </c>
+      <c r="J48">
+        <v>4</v>
+      </c>
+      <c r="K48" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L48" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M48" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N48" t="b">
+        <v>1</v>
+      </c>
+      <c r="O48" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+      </c>
+      <c r="P48" t="str">
+        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B49" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Avocado/Cheese Toast</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G49">
+        <v>193</v>
+      </c>
+      <c r="H49">
+        <v>9</v>
+      </c>
+      <c r="I49">
+        <v>14</v>
+      </c>
+      <c r="J49">
+        <v>12</v>
+      </c>
+      <c r="K49" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L49" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M49" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N49" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49" t="str">
         <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
-      <c r="P42" t="str">
+      <c r="P49" t="str">
         <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":200,"delta_kcal":7,"tolerance_kcal":38.6},"issues":[]}}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P49"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2748,13 +3098,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti</v>
+        <v>breakfast_chicken-keema-bhurji-jowar-roti</v>
       </c>
       <c r="B9" t="str">
-        <v>Chicken breast</v>
+        <v>Chicken keema</v>
       </c>
       <c r="C9">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D9" t="str">
         <v>Jowar roti (millet)</v>
@@ -2763,13 +3113,13 @@
         <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Cauliflower</v>
       </c>
       <c r="G9">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H9" t="str">
-        <v>Curry style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I9" t="str">
         <v>{}</v>
@@ -2777,28 +3127,28 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
+        <v>breakfast_moong-dal-chilla-paneer-hung-curd</v>
       </c>
       <c r="B10" t="str">
-        <v>Grilled salmon</v>
+        <v>Paneer</v>
       </c>
       <c r="C10">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="D10" t="str">
-        <v>Spaghetti aglio e olio (small portion)</v>
+        <v>Moong dal chilla</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>Sautéed broccoli</v>
-      </c>
-      <c r="G10">
-        <v>150</v>
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I10" t="str">
         <v>{}</v>
@@ -2806,28 +3156,28 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>lunch_dinner_rajma-chawal-raita</v>
+        <v>breakfast_oats-whey-porridge-nuts</v>
       </c>
       <c r="B11" t="str">
+        <v>Whey protein + milk</v>
+      </c>
+      <c r="C11">
+        <v>34</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Rolled oats</v>
+      </c>
+      <c r="E11">
+        <v>45</v>
+      </c>
+      <c r="F11" t="str">
         <v/>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Cooked rice</v>
-      </c>
-      <c r="E11">
-        <v>80</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Mixed veg sabzi</v>
-      </c>
-      <c r="G11">
-        <v>150</v>
+      <c r="G11" t="str">
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>Curry style</v>
+        <v>Porridge</v>
       </c>
       <c r="I11" t="str">
         <v>{}</v>
@@ -2835,28 +3185,28 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>lunch_dinner_chole-jowar-roti-raita</v>
+        <v>breakfast_chicken-sausage-scrambled-eggs-toast</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>Chicken sausage + eggs</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="D12" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Whole wheat toast</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
+        <v>Mixed greens</v>
+      </c>
+      <c r="G12">
+        <v>80</v>
       </c>
       <c r="H12" t="str">
-        <v>Curry style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I12" t="str">
         <v>{}</v>
@@ -2864,28 +3214,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>lunch_dinner_vietnamese-chicken-pho</v>
+        <v>breakfast_tofu-spinach-scramble-avocado-toast</v>
       </c>
       <c r="B13" t="str">
-        <v>Chicken breast</v>
+        <v>Firm tofu</v>
       </c>
       <c r="C13">
+        <v>200</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Whole wheat toast</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Spinach + greens</v>
+      </c>
+      <c r="G13">
         <v>150</v>
       </c>
-      <c r="D13" t="str">
-        <v>Rice noodles</v>
-      </c>
-      <c r="E13">
-        <v>120</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Pho greens + side salad</v>
-      </c>
-      <c r="G13">
-        <v>80</v>
-      </c>
       <c r="H13" t="str">
-        <v>Soup style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I13" t="str">
         <v>{}</v>
@@ -2893,28 +3243,28 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
+        <v>breakfast_idli-sambar-masala-egg-bhurji</v>
       </c>
       <c r="B14" t="str">
-        <v>Beef steak</v>
+        <v>Eggs (whole)</v>
       </c>
       <c r="C14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D14" t="str">
-        <v>No carb</v>
+        <v>Idli</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="str">
-        <v>Mixed greens salad</v>
+        <v>Sambar</v>
       </c>
       <c r="G14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H14" t="str">
-        <v>Grilled</v>
+        <v>Steamed</v>
       </c>
       <c r="I14" t="str">
         <v>{}</v>
@@ -2922,25 +3272,25 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>lunch_dinner_thai-pad-krapow-rice</v>
+        <v>breakfast_paneer-paratha-curd</v>
       </c>
       <c r="B15" t="str">
-        <v>Chicken breast</v>
+        <v>Paneer</v>
       </c>
       <c r="C15">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="D15" t="str">
-        <v>Cooked rice</v>
+        <v>Whole wheat paratha</v>
       </c>
       <c r="E15">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>Sautéed peppers + side salad</v>
-      </c>
-      <c r="G15">
-        <v>130</v>
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
       </c>
       <c r="H15" t="str">
         <v>Pan-fried</v>
@@ -2951,10 +3301,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>lunch_dinner_mutton-keema-jowar-roti</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti</v>
       </c>
       <c r="B16" t="str">
-        <v>Mutton keema</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C16">
         <v>150</v>
@@ -2966,10 +3316,10 @@
         <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G16">
+        <v>120</v>
       </c>
       <c r="H16" t="str">
         <v>Curry style</v>
@@ -2980,28 +3330,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
+        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B17" t="str">
-        <v>Paneer</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C17">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D17" t="str">
-        <v>Cooked rice</v>
+        <v>Spaghetti aglio e olio (small portion)</v>
       </c>
       <c r="E17">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F17" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G17">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H17" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I17" t="str">
         <v>{}</v>
@@ -3009,25 +3359,25 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
+        <v>lunch_dinner_rajma-chawal-raita</v>
       </c>
       <c r="B18" t="str">
-        <v>Chicken breast</v>
+        <v/>
       </c>
       <c r="C18">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D18" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="F18" t="str">
         <v>Mixed veg sabzi</v>
       </c>
       <c r="G18">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H18" t="str">
         <v>Curry style</v>
@@ -3038,28 +3388,28 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
+        <v>lunch_dinner_chole-jowar-roti-raita</v>
       </c>
       <c r="B19" t="str">
-        <v>Fish fillet</v>
+        <v/>
       </c>
       <c r="C19">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D19" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>Pumpkin salad</v>
-      </c>
-      <c r="G19">
-        <v>120</v>
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I19" t="str">
         <v>{}</v>
@@ -3067,28 +3417,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
+        <v>lunch_dinner_vietnamese-chicken-pho</v>
       </c>
       <c r="B20" t="str">
-        <v>Grilled salmon</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C20">
         <v>150</v>
       </c>
       <c r="D20" t="str">
-        <v>Garlic rice (small portion)</v>
+        <v>Rice noodles</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F20" t="str">
-        <v>Sautéed broccoli</v>
+        <v>Pho greens + side salad</v>
       </c>
       <c r="G20">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="H20" t="str">
-        <v>Grilled</v>
+        <v>Soup style</v>
       </c>
       <c r="I20" t="str">
         <v>{}</v>
@@ -3096,13 +3446,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
+        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
       </c>
       <c r="B21" t="str">
-        <v>Chicken breast</v>
+        <v>Beef steak</v>
       </c>
       <c r="C21">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D21" t="str">
         <v>No carb</v>
@@ -3111,13 +3461,13 @@
         <v>0</v>
       </c>
       <c r="F21" t="str">
-        <v>Smoked salmon salad</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G21">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H21" t="str">
-        <v>Soup style</v>
+        <v>Grilled</v>
       </c>
       <c r="I21" t="str">
         <v>{}</v>
@@ -3125,28 +3475,28 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
+        <v>lunch_dinner_thai-pad-krapow-rice</v>
       </c>
       <c r="B22" t="str">
-        <v>Paneer</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D22" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F22" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Sautéed peppers + side salad</v>
       </c>
       <c r="G22">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H22" t="str">
-        <v>Curry style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I22" t="str">
         <v>{}</v>
@@ -3154,28 +3504,28 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
+        <v>lunch_dinner_mutton-keema-jowar-roti</v>
       </c>
       <c r="B23" t="str">
-        <v>Pork chop</v>
+        <v>Mutton keema</v>
       </c>
       <c r="C23">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D23" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" t="str">
-        <v>Pumpkin salad</v>
-      </c>
-      <c r="G23">
-        <v>120</v>
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
       </c>
       <c r="H23" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I23" t="str">
         <v>{}</v>
@@ -3183,28 +3533,28 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
+        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
       </c>
       <c r="B24" t="str">
-        <v>Pork chop</v>
+        <v>Paneer</v>
       </c>
       <c r="C24">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="D24" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F24" t="str">
-        <v>Mixed greens salad</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G24">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H24" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I24" t="str">
         <v>{}</v>
@@ -3212,7 +3562,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
       </c>
       <c r="B25" t="str">
         <v>Chicken breast</v>
@@ -3221,19 +3571,19 @@
         <v>150</v>
       </c>
       <c r="D25" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>Smoked chicken + avocado salad</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H25" t="str">
-        <v>Tandoori</v>
+        <v>Curry style</v>
       </c>
       <c r="I25" t="str">
         <v>{}</v>
@@ -3241,7 +3591,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
       </c>
       <c r="B26" t="str">
         <v>Fish fillet</v>
@@ -3250,19 +3600,19 @@
         <v>150</v>
       </c>
       <c r="D26" t="str">
-        <v>Spaghetti aglio e olio (small portion)</v>
+        <v>No carb</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26" t="str">
-        <v>Sautéed broccoli</v>
+        <v>Pumpkin salad</v>
       </c>
       <c r="G26">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H26" t="str">
-        <v>Soup style</v>
+        <v>Grilled</v>
       </c>
       <c r="I26" t="str">
         <v>{}</v>
@@ -3270,28 +3620,28 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
+        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
       </c>
       <c r="B27" t="str">
-        <v>Lamb (seekh kabab)</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C27">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D27" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Garlic rice (small portion)</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F27" t="str">
-        <v>Sautéed spinach</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G27">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H27" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I27" t="str">
         <v>{}</v>
@@ -3299,28 +3649,28 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lunch_dinner_kofta-dal-jowar-roti</v>
+        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
       </c>
       <c r="B28" t="str">
-        <v>Veg kofta</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C28">
         <v>150</v>
       </c>
       <c r="D28" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>No carb</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Smoked salmon salad</v>
       </c>
       <c r="G28">
         <v>120</v>
       </c>
       <c r="H28" t="str">
-        <v>Curry style</v>
+        <v>Soup style</v>
       </c>
       <c r="I28" t="str">
         <v>{}</v>
@@ -3328,28 +3678,28 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
+        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
       </c>
       <c r="B29" t="str">
-        <v>Lamb (seekh kabab)</v>
+        <v>Paneer</v>
       </c>
       <c r="C29">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="D29" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>No carb</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" t="str">
-        <v>Cauliflower</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G29">
         <v>150</v>
       </c>
       <c r="H29" t="str">
-        <v>Tandoori</v>
+        <v>Curry style</v>
       </c>
       <c r="I29" t="str">
         <v>{}</v>
@@ -3357,28 +3707,28 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>lunch_dinner_fish-curry-rice</v>
+        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
       </c>
       <c r="B30" t="str">
-        <v>Fish fillet</v>
+        <v>Pork chop</v>
       </c>
       <c r="C30">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D30" t="str">
-        <v>Cooked rice</v>
+        <v>No carb</v>
       </c>
       <c r="E30">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <v/>
+        <v>Pumpkin salad</v>
+      </c>
+      <c r="G30">
+        <v>120</v>
       </c>
       <c r="H30" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I30" t="str">
         <v>{}</v>
@@ -3386,28 +3736,28 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
+        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
       </c>
       <c r="B31" t="str">
-        <v>Kaala chanaa (black chickpeas)</v>
+        <v>Pork chop</v>
       </c>
       <c r="C31">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D31" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>No carb</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31" t="str">
-        <v>Sweet potato curry</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G31">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H31" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I31" t="str">
         <v>{}</v>
@@ -3415,13 +3765,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
+        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
       </c>
       <c r="B32" t="str">
-        <v>Smoked salmon</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C32">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D32" t="str">
         <v>No carb</v>
@@ -3430,13 +3780,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="str">
-        <v>Avocado &amp; mixed greens</v>
+        <v>Smoked chicken + avocado salad</v>
       </c>
       <c r="G32">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="H32" t="str">
-        <v>Salad</v>
+        <v>Tandoori</v>
       </c>
       <c r="I32" t="str">
         <v>{}</v>
@@ -3444,28 +3794,28 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
+        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B33" t="str">
-        <v>Smoked chicken breast</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C33">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D33" t="str">
-        <v>No carb</v>
+        <v>Spaghetti aglio e olio (small portion)</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33" t="str">
-        <v>Avocado &amp; mixed greens</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G33">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="H33" t="str">
-        <v>Salad</v>
+        <v>Soup style</v>
       </c>
       <c r="I33" t="str">
         <v>{}</v>
@@ -3473,25 +3823,25 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>lunch_dinner_chicken-red-curry-rice</v>
+        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
       </c>
       <c r="B34" t="str">
-        <v>Chicken breast</v>
+        <v>Lamb (seekh kabab)</v>
       </c>
       <c r="C34">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="D34" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E34">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>Red curry vegetables</v>
+        <v>Sautéed spinach</v>
       </c>
       <c r="G34">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H34" t="str">
         <v>Curry style</v>
@@ -3502,28 +3852,28 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>lunch_dinner_kofta-dal-jowar-roti</v>
       </c>
       <c r="B35" t="str">
-        <v>Plant Shake</v>
+        <v>Veg kofta</v>
       </c>
       <c r="C35">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D35" t="str">
-        <v>Mixed Fruit</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E35">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>Almonds</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="H35" t="str">
-        <v>Snack</v>
+        <v>Curry style</v>
       </c>
       <c r="I35" t="str">
         <v>{}</v>
@@ -3531,28 +3881,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
       </c>
       <c r="B36" t="str">
-        <v>Plant Shake</v>
+        <v>Lamb (seekh kabab)</v>
       </c>
       <c r="C36">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="D36" t="str">
-        <v>Chaat &amp; Bhel</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Cauliflower</v>
+      </c>
+      <c r="G36">
         <v>150</v>
       </c>
-      <c r="F36" t="str">
-        <v/>
-      </c>
-      <c r="G36" t="str">
-        <v/>
-      </c>
       <c r="H36" t="str">
-        <v>Street Food Twist</v>
+        <v>Tandoori</v>
       </c>
       <c r="I36" t="str">
         <v>{}</v>
@@ -3560,19 +3910,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>lunch_dinner_fish-curry-rice</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Fish fillet</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D37" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F37" t="str">
         <v/>
@@ -3581,7 +3931,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I37" t="str">
         <v>{}</v>
@@ -3589,28 +3939,28 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Kaala chanaa (black chickpeas)</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="D38" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v/>
-      </c>
-      <c r="G38" t="str">
-        <v/>
+        <v>Sweet potato curry</v>
+      </c>
+      <c r="G38">
+        <v>180</v>
       </c>
       <c r="H38" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I38" t="str">
         <v>{}</v>
@@ -3618,13 +3968,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
       </c>
       <c r="B39" t="str">
-        <v>Mixed nuts &amp; seeds</v>
+        <v>Smoked salmon</v>
       </c>
       <c r="C39">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D39" t="str">
         <v>No carb</v>
@@ -3633,13 +3983,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="str">
-        <v/>
-      </c>
-      <c r="G39" t="str">
-        <v/>
+        <v>Avocado &amp; mixed greens</v>
+      </c>
+      <c r="G39">
+        <v>155</v>
       </c>
       <c r="H39" t="str">
-        <v>Raw</v>
+        <v>Salad</v>
       </c>
       <c r="I39" t="str">
         <v>{}</v>
@@ -3647,28 +3997,28 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Smoked chicken breast</v>
       </c>
       <c r="C40">
+        <v>120</v>
+      </c>
+      <c r="D40" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E40">
         <v>0</v>
       </c>
-      <c r="D40" t="str">
-        <v>Sweet potato</v>
-      </c>
-      <c r="E40">
-        <v>150</v>
-      </c>
       <c r="F40" t="str">
-        <v/>
-      </c>
-      <c r="G40" t="str">
-        <v/>
+        <v>Avocado &amp; mixed greens</v>
+      </c>
+      <c r="G40">
+        <v>155</v>
       </c>
       <c r="H40" t="str">
-        <v>Chaat</v>
+        <v>Salad</v>
       </c>
       <c r="I40" t="str">
         <v>{}</v>
@@ -3676,28 +4026,28 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>lunch_dinner_chicken-red-curry-rice</v>
       </c>
       <c r="B41" t="str">
-        <v>Kaala chana</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C41">
         <v>150</v>
       </c>
       <c r="D41" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F41" t="str">
-        <v/>
-      </c>
-      <c r="G41" t="str">
-        <v/>
+        <v>Red curry vegetables</v>
+      </c>
+      <c r="G41">
+        <v>100</v>
       </c>
       <c r="H41" t="str">
-        <v>Chaat</v>
+        <v>Curry style</v>
       </c>
       <c r="I41" t="str">
         <v>{}</v>
@@ -3705,36 +4055,239 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>snack_fruit-almonds-plant-shake</v>
       </c>
       <c r="B42" t="str">
-        <v/>
+        <v>Plant Shake</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D42" t="str">
-        <v>Whole wheat toast</v>
+        <v>Mixed Fruit</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F42" t="str">
-        <v>Avocado</v>
+        <v>Almonds</v>
       </c>
       <c r="G42">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="H42" t="str">
-        <v>Toast</v>
+        <v>Snack</v>
       </c>
       <c r="I42" t="str">
         <v>{}</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>snack_chaat-bhel-protein-shake</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Plant Shake</v>
+      </c>
+      <c r="C43">
+        <v>25</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Chaat &amp; Bhel</v>
+      </c>
+      <c r="E43">
+        <v>150</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v>Street Food Twist</v>
+      </c>
+      <c r="I43" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>snack_greek-yogurt-berry-bowl</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>Grilled</v>
+      </c>
+      <c r="I44" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>Grilled</v>
+      </c>
+      <c r="I45" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Mixed nuts &amp; seeds</v>
+      </c>
+      <c r="C46">
+        <v>30</v>
+      </c>
+      <c r="D46" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="I46" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Sweet potato</v>
+      </c>
+      <c r="E47">
+        <v>150</v>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I47" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Kaala chana</v>
+      </c>
+      <c r="C48">
+        <v>150</v>
+      </c>
+      <c r="D48" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I48" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Whole wheat toast</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Avocado</v>
+      </c>
+      <c r="G49">
+        <v>50</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Toast</v>
+      </c>
+      <c r="I49" t="str">
+        <v>{}</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I49"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/exports/meal_database_architecture_v1.xlsx
+++ b/exports/meal_database_architecture_v1.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2455,40 +2455,40 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
       </c>
       <c r="B42" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C42" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Korean chicken bibimbap bowl</v>
       </c>
       <c r="D42" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Chicken Bibimbap Bowl</v>
       </c>
       <c r="E42" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Korean chicken bibimbap bowl</v>
       </c>
       <c r="F42" t="str">
-        <v>General</v>
+        <v>Asian</v>
       </c>
       <c r="G42">
-        <v>200</v>
+        <v>471</v>
       </c>
       <c r="H42">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="I42">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K42" t="str">
-        <v>USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L42" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M42" t="str">
         <v>seed_v1</v>
@@ -2497,48 +2497,48 @@
         <v>1</v>
       </c>
       <c r="O42" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P42" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
+        <v>{"macros_p":52,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":452,"delta_kcal":19,"tolerance_kcal":94.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
       </c>
       <c r="B43" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C43" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Salmon teriyaki + soba noodles</v>
       </c>
       <c r="D43" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Salmon Teriyaki + Soba</v>
       </c>
       <c r="E43" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Salmon teriyaki + soba noodles</v>
       </c>
       <c r="F43" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G43">
-        <v>345</v>
+        <v>499</v>
       </c>
       <c r="H43">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I43">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J43">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K43" t="str">
-        <v>IFCT/USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L43" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M43" t="str">
         <v>seed_v1</v>
@@ -2547,48 +2547,48 @@
         <v>1</v>
       </c>
       <c r="O43" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P43" t="str">
-        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
+        <v>{"macros_p":43,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":9,"tolerance_kcal":99.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
       </c>
       <c r="B44" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C44" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Prawn stir-fry + edamame + rice noodles</v>
       </c>
       <c r="D44" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Prawn Stir-fry + Edamame</v>
       </c>
       <c r="E44" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Prawn stir-fry + edamame + rice noodles</v>
       </c>
       <c r="F44" t="str">
-        <v>International</v>
+        <v>Asian</v>
       </c>
       <c r="G44">
-        <v>203</v>
+        <v>472</v>
       </c>
       <c r="H44">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="I44">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J44">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K44" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L44" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M44" t="str">
         <v>seed_v1</v>
@@ -2597,48 +2597,48 @@
         <v>1</v>
       </c>
       <c r="O44" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P44" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
+        <v>{"macros_p":54,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":467,"delta_kcal":5,"tolerance_kcal":94.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>lunch_dinner_miso-chicken-ramen-egg</v>
       </c>
       <c r="B45" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C45" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Miso chicken ramen + egg</v>
       </c>
       <c r="D45" t="str">
-        <v>Carrot Halwa + Protein Shake</v>
+        <v>Miso Chicken Ramen</v>
       </c>
       <c r="E45" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Miso chicken ramen + egg</v>
       </c>
       <c r="F45" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G45">
-        <v>220</v>
+        <v>527</v>
       </c>
       <c r="H45">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="I45">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K45" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L45" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M45" t="str">
         <v>seed_v1</v>
@@ -2647,48 +2647,48 @@
         <v>1</v>
       </c>
       <c r="O45" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P45" t="str">
-        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":515,"delta_kcal":12,"tolerance_kcal":105.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_tofu-edamame-ramen</v>
       </c>
       <c r="B46" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C46" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Tofu &amp; edamame ramen</v>
       </c>
       <c r="D46" t="str">
-        <v>Nuts + Seeds + Protein Shake</v>
+        <v>Tofu &amp; Edamame Ramen</v>
       </c>
       <c r="E46" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Tofu &amp; edamame ramen</v>
       </c>
       <c r="F46" t="str">
-        <v>International</v>
+        <v>Asian</v>
       </c>
       <c r="G46">
-        <v>320</v>
+        <v>565</v>
       </c>
       <c r="H46">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="I46">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="J46">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K46" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L46" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M46" t="str">
         <v>seed_v1</v>
@@ -2697,48 +2697,48 @@
         <v>1</v>
       </c>
       <c r="O46" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P46" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+        <v>{"macros_p":47,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":596,"delta_kcal":31,"tolerance_kcal":113},"issues":[]}}</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>snack_fruit-almonds-plant-shake</v>
       </c>
       <c r="B47" t="str">
         <v>snack</v>
       </c>
       <c r="C47" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="D47" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="E47" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="F47" t="str">
-        <v>Indian</v>
+        <v>General</v>
       </c>
       <c r="G47">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="H47">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I47">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K47" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+        <v>USDA + custom user specs</v>
       </c>
       <c r="L47" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>v1_custom</v>
       </c>
       <c r="M47" t="str">
         <v>seed_v1</v>
@@ -2747,48 +2747,48 @@
         <v>1</v>
       </c>
       <c r="O47" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P47" t="str">
-        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>snack_chaat-bhel-protein-shake</v>
       </c>
       <c r="B48" t="str">
         <v>snack</v>
       </c>
       <c r="C48" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Chaat + Bhel + Protein Shake</v>
       </c>
       <c r="D48" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Chaat + Bhel + Protein Shake</v>
       </c>
       <c r="E48" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Chaat + Bhel + Protein Shake</v>
       </c>
       <c r="F48" t="str">
         <v>Indian</v>
       </c>
       <c r="G48">
-        <v>246</v>
+        <v>345</v>
       </c>
       <c r="H48">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I48">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K48" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+        <v>IFCT/USDA + custom user specs</v>
       </c>
       <c r="L48" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>v1_custom</v>
       </c>
       <c r="M48" t="str">
         <v>seed_v1</v>
@@ -2800,39 +2800,39 @@
         <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P48" t="str">
-        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>snack_greek-yogurt-berry-bowl</v>
       </c>
       <c r="B49" t="str">
         <v>snack</v>
       </c>
       <c r="C49" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Greek yogurt + berry bowl</v>
       </c>
       <c r="D49" t="str">
-        <v>Avocado/Cheese Toast</v>
+        <v>Greek yogurt + berry bowl</v>
       </c>
       <c r="E49" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Greek yogurt + berry bowl</v>
       </c>
       <c r="F49" t="str">
-        <v>Continental</v>
+        <v>International</v>
       </c>
       <c r="G49">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="H49">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I49">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J49">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K49" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2847,22 +2847,272 @@
         <v>1</v>
       </c>
       <c r="O49" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P49" t="str">
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+      </c>
+      <c r="B50" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Carrot halwa (sugar-free) + protein shake</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Carrot Halwa + Protein Shake</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Carrot halwa (sugar-free) + protein shake</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G50">
+        <v>220</v>
+      </c>
+      <c r="H50">
+        <v>28</v>
+      </c>
+      <c r="I50">
+        <v>17</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
+      <c r="K50" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L50" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M50" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N50" t="b">
+        <v>1</v>
+      </c>
+      <c r="O50" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P50" t="str">
+        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B51" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Nuts + Seeds + Protein Shake</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="F51" t="str">
+        <v>International</v>
+      </c>
+      <c r="G51">
+        <v>320</v>
+      </c>
+      <c r="H51">
+        <v>31</v>
+      </c>
+      <c r="I51">
+        <v>11</v>
+      </c>
+      <c r="J51">
+        <v>17</v>
+      </c>
+      <c r="K51" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L51" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M51" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N51" t="b">
+        <v>1</v>
+      </c>
+      <c r="O51" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P51" t="str">
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B52" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G52">
+        <v>135</v>
+      </c>
+      <c r="H52">
+        <v>3</v>
+      </c>
+      <c r="I52">
+        <v>32</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L52" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M52" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N52" t="b">
+        <v>1</v>
+      </c>
+      <c r="O52" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P52" t="str">
+        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B53" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G53">
+        <v>246</v>
+      </c>
+      <c r="H53">
+        <v>13</v>
+      </c>
+      <c r="I53">
+        <v>41</v>
+      </c>
+      <c r="J53">
+        <v>4</v>
+      </c>
+      <c r="K53" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L53" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M53" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N53" t="b">
+        <v>1</v>
+      </c>
+      <c r="O53" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+      </c>
+      <c r="P53" t="str">
+        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B54" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Avocado/Cheese Toast</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G54">
+        <v>193</v>
+      </c>
+      <c r="H54">
+        <v>9</v>
+      </c>
+      <c r="I54">
+        <v>14</v>
+      </c>
+      <c r="J54">
+        <v>12</v>
+      </c>
+      <c r="K54" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L54" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M54" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N54" t="b">
+        <v>1</v>
+      </c>
+      <c r="O54" t="str">
         <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
-      <c r="P49" t="str">
+      <c r="P54" t="str">
         <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":200,"delta_kcal":7,"tolerance_kcal":38.6},"issues":[]}}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P54"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4055,28 +4305,28 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
       </c>
       <c r="B42" t="str">
-        <v>Plant Shake</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C42">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D42" t="str">
-        <v>Mixed Fruit</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E42">
         <v>100</v>
       </c>
       <c r="F42" t="str">
-        <v>Almonds</v>
+        <v>Kimchi + spinach</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="H42" t="str">
-        <v>Snack</v>
+        <v>Bowl</v>
       </c>
       <c r="I42" t="str">
         <v>{}</v>
@@ -4084,28 +4334,28 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
       </c>
       <c r="B43" t="str">
-        <v>Plant Shake</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C43">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D43" t="str">
-        <v>Chaat &amp; Bhel</v>
+        <v>Soba noodles</v>
       </c>
       <c r="E43">
         <v>150</v>
       </c>
       <c r="F43" t="str">
-        <v/>
-      </c>
-      <c r="G43" t="str">
-        <v/>
+        <v>Bok choy</v>
+      </c>
+      <c r="G43">
+        <v>120</v>
       </c>
       <c r="H43" t="str">
-        <v>Street Food Twist</v>
+        <v>Grilled</v>
       </c>
       <c r="I43" t="str">
         <v>{}</v>
@@ -4113,28 +4363,28 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
       </c>
       <c r="B44" t="str">
-        <v/>
+        <v>Prawns</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D44" t="str">
-        <v>No carb</v>
+        <v>Rice noodles</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F44" t="str">
-        <v/>
-      </c>
-      <c r="G44" t="str">
-        <v/>
+        <v>Edamame</v>
+      </c>
+      <c r="G44">
+        <v>80</v>
       </c>
       <c r="H44" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I44" t="str">
         <v>{}</v>
@@ -4142,28 +4392,28 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>lunch_dinner_miso-chicken-ramen-egg</v>
       </c>
       <c r="B45" t="str">
-        <v/>
+        <v>Chicken breast</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D45" t="str">
-        <v>No carb</v>
+        <v>Egg noodles</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F45" t="str">
-        <v/>
-      </c>
-      <c r="G45" t="str">
-        <v/>
+        <v>Bok choy</v>
+      </c>
+      <c r="G45">
+        <v>100</v>
       </c>
       <c r="H45" t="str">
-        <v>Grilled</v>
+        <v>Soup style</v>
       </c>
       <c r="I45" t="str">
         <v>{}</v>
@@ -4171,28 +4421,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_tofu-edamame-ramen</v>
       </c>
       <c r="B46" t="str">
-        <v>Mixed nuts &amp; seeds</v>
+        <v>Firm tofu</v>
       </c>
       <c r="C46">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="D46" t="str">
-        <v>No carb</v>
+        <v>Egg noodles</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F46" t="str">
-        <v/>
-      </c>
-      <c r="G46" t="str">
-        <v/>
+        <v>Bok choy + edamame</v>
+      </c>
+      <c r="G46">
+        <v>180</v>
       </c>
       <c r="H46" t="str">
-        <v>Raw</v>
+        <v>Soup style</v>
       </c>
       <c r="I46" t="str">
         <v>{}</v>
@@ -4200,28 +4450,28 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>snack_fruit-almonds-plant-shake</v>
       </c>
       <c r="B47" t="str">
-        <v/>
+        <v>Plant Shake</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D47" t="str">
-        <v>Sweet potato</v>
+        <v>Mixed Fruit</v>
       </c>
       <c r="E47">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F47" t="str">
-        <v/>
-      </c>
-      <c r="G47" t="str">
-        <v/>
+        <v>Almonds</v>
+      </c>
+      <c r="G47">
+        <v>5</v>
       </c>
       <c r="H47" t="str">
-        <v>Chaat</v>
+        <v>Snack</v>
       </c>
       <c r="I47" t="str">
         <v>{}</v>
@@ -4229,19 +4479,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>snack_chaat-bhel-protein-shake</v>
       </c>
       <c r="B48" t="str">
-        <v>Kaala chana</v>
+        <v>Plant Shake</v>
       </c>
       <c r="C48">
+        <v>25</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Chaat &amp; Bhel</v>
+      </c>
+      <c r="E48">
         <v>150</v>
-      </c>
-      <c r="D48" t="str">
-        <v>No carb</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
       </c>
       <c r="F48" t="str">
         <v/>
@@ -4250,7 +4500,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Chaat</v>
+        <v>Street Food Twist</v>
       </c>
       <c r="I48" t="str">
         <v>{}</v>
@@ -4258,7 +4508,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>snack_greek-yogurt-berry-bowl</v>
       </c>
       <c r="B49" t="str">
         <v/>
@@ -4267,27 +4517,172 @@
         <v>0</v>
       </c>
       <c r="D49" t="str">
-        <v>Whole wheat toast</v>
+        <v>No carb</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="str">
-        <v>Avocado</v>
-      </c>
-      <c r="G49">
-        <v>50</v>
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
       </c>
       <c r="H49" t="str">
-        <v>Toast</v>
+        <v>Grilled</v>
       </c>
       <c r="I49" t="str">
         <v>{}</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+      </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v>Grilled</v>
+      </c>
+      <c r="I50" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Mixed nuts &amp; seeds</v>
+      </c>
+      <c r="C51">
+        <v>30</v>
+      </c>
+      <c r="D51" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="I51" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Sweet potato</v>
+      </c>
+      <c r="E52">
+        <v>150</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I52" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Kaala chana</v>
+      </c>
+      <c r="C53">
+        <v>150</v>
+      </c>
+      <c r="D53" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I53" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Whole wheat toast</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Avocado</v>
+      </c>
+      <c r="G54">
+        <v>50</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Toast</v>
+      </c>
+      <c r="I54" t="str">
+        <v>{}</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/exports/meal_database_architecture_v1.xlsx
+++ b/exports/meal_database_architecture_v1.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2705,40 +2705,40 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>lunch_dinner_butter-chicken-jowar-roti</v>
       </c>
       <c r="B47" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C47" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Butter chicken + jowar roti</v>
       </c>
       <c r="D47" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Butter Chicken + Jowar Roti</v>
       </c>
       <c r="E47" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Butter chicken + jowar roti</v>
       </c>
       <c r="F47" t="str">
-        <v>General</v>
+        <v>Indian</v>
       </c>
       <c r="G47">
-        <v>200</v>
+        <v>635</v>
       </c>
       <c r="H47">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="I47">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J47">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K47" t="str">
-        <v>USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L47" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M47" t="str">
         <v>seed_v1</v>
@@ -2747,48 +2747,48 @@
         <v>1</v>
       </c>
       <c r="O47" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P47" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
+        <v>{"macros_p":54,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":622,"delta_kcal":13,"tolerance_kcal":127},"issues":[]}}</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
       </c>
       <c r="B48" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C48" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Grilled chicken + sweet potato + broccoli</v>
       </c>
       <c r="D48" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Grilled Chicken + Sweet Potato</v>
       </c>
       <c r="E48" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Grilled chicken + sweet potato + broccoli</v>
       </c>
       <c r="F48" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G48">
-        <v>345</v>
+        <v>505</v>
       </c>
       <c r="H48">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="I48">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J48">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K48" t="str">
-        <v>IFCT/USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L48" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M48" t="str">
         <v>seed_v1</v>
@@ -2797,48 +2797,48 @@
         <v>1</v>
       </c>
       <c r="O48" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P48" t="str">
-        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
+        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":3,"tolerance_kcal":101},"issues":[]}}</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
       </c>
       <c r="B49" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C49" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Pepper beef + garlic rice + greens</v>
       </c>
       <c r="D49" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Pepper Beef + Garlic Rice</v>
       </c>
       <c r="E49" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Pepper beef + garlic rice + greens</v>
       </c>
       <c r="F49" t="str">
-        <v>International</v>
+        <v>Asian</v>
       </c>
       <c r="G49">
-        <v>203</v>
+        <v>696</v>
       </c>
       <c r="H49">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="I49">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="K49" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L49" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M49" t="str">
         <v>seed_v1</v>
@@ -2847,48 +2847,48 @@
         <v>1</v>
       </c>
       <c r="O49" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P49" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
+        <v>{"macros_p":53,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":702,"delta_kcal":6,"tolerance_kcal":139.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
       </c>
       <c r="B50" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C50" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Paneer tikka + jowar roti + salad</v>
       </c>
       <c r="D50" t="str">
-        <v>Carrot Halwa + Protein Shake</v>
+        <v>Paneer Tikka + Jowar Roti</v>
       </c>
       <c r="E50" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Paneer tikka + jowar roti + salad</v>
       </c>
       <c r="F50" t="str">
         <v>Indian</v>
       </c>
       <c r="G50">
-        <v>220</v>
+        <v>654</v>
       </c>
       <c r="H50">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I50">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="K50" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L50" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M50" t="str">
         <v>seed_v1</v>
@@ -2897,48 +2897,48 @@
         <v>1</v>
       </c>
       <c r="O50" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P50" t="str">
-        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+        <v>{"macros_p":35,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":647,"delta_kcal":7,"tolerance_kcal":130.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
       </c>
       <c r="B51" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C51" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Grilled salmon + sweet potato + spinach</v>
       </c>
       <c r="D51" t="str">
-        <v>Nuts + Seeds + Protein Shake</v>
+        <v>Salmon + Sweet Potato + Spinach</v>
       </c>
       <c r="E51" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Grilled salmon + sweet potato + spinach</v>
       </c>
       <c r="F51" t="str">
-        <v>International</v>
+        <v>Continental</v>
       </c>
       <c r="G51">
-        <v>320</v>
+        <v>614</v>
       </c>
       <c r="H51">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="I51">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="J51">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K51" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L51" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M51" t="str">
         <v>seed_v1</v>
@@ -2947,48 +2947,48 @@
         <v>1</v>
       </c>
       <c r="O51" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P51" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+        <v>{"macros_p":48,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":614,"delta_kcal":0,"tolerance_kcal":122.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>lunch_dinner_chicken-biryani-raita</v>
       </c>
       <c r="B52" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C52" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="D52" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="E52" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="F52" t="str">
         <v>Indian</v>
       </c>
       <c r="G52">
-        <v>135</v>
+        <v>629</v>
       </c>
       <c r="H52">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="I52">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K52" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L52" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M52" t="str">
         <v>seed_v1</v>
@@ -2997,48 +2997,48 @@
         <v>1</v>
       </c>
       <c r="O52" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P52" t="str">
-        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":607,"delta_kcal":22,"tolerance_kcal":125.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>lunch_dinner_fish-moilee-rice</v>
       </c>
       <c r="B53" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C53" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="D53" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="E53" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="F53" t="str">
         <v>Indian</v>
       </c>
       <c r="G53">
-        <v>246</v>
+        <v>615</v>
       </c>
       <c r="H53">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I53">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K53" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L53" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M53" t="str">
         <v>seed_v1</v>
@@ -3047,72 +3047,872 @@
         <v>1</v>
       </c>
       <c r="O53" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P53" t="str">
-        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+        <v>{"macros_p":53,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":608,"delta_kcal":7,"tolerance_kcal":123},"issues":[]}}</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
+        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
+      </c>
+      <c r="B54" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Egg curry + dal + jowar roti</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Egg Curry + Dal + Roti</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Egg curry + dal + jowar roti</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G54">
+        <v>604</v>
+      </c>
+      <c r="H54">
+        <v>34</v>
+      </c>
+      <c r="I54">
+        <v>47</v>
+      </c>
+      <c r="J54">
+        <v>29</v>
+      </c>
+      <c r="K54" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L54" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M54" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N54" t="b">
+        <v>1</v>
+      </c>
+      <c r="O54" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
+      </c>
+      <c r="P54" t="str">
+        <v>{"macros_p":34,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":585,"delta_kcal":19,"tolerance_kcal":120.8},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>lunch_dinner_chicken-shawarma-bowl</v>
+      </c>
+      <c r="B55" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Chicken shawarma bowl</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Chicken shawarma bowl</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Chicken shawarma bowl</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G55">
+        <v>533</v>
+      </c>
+      <c r="H55">
+        <v>57</v>
+      </c>
+      <c r="I55">
+        <v>38</v>
+      </c>
+      <c r="J55">
+        <v>17</v>
+      </c>
+      <c r="K55" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L55" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M55" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N55" t="b">
+        <v>1</v>
+      </c>
+      <c r="O55" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P55" t="str">
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":533,"delta_kcal":0,"tolerance_kcal":106.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>lunch_dinner_prawn-curry-rice</v>
+      </c>
+      <c r="B56" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Prawn curry + rice</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Prawn curry + rice</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Prawn curry + rice</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G56">
+        <v>552</v>
+      </c>
+      <c r="H56">
+        <v>49</v>
+      </c>
+      <c r="I56">
+        <v>50</v>
+      </c>
+      <c r="J56">
+        <v>17</v>
+      </c>
+      <c r="K56" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L56" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M56" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N56" t="b">
+        <v>1</v>
+      </c>
+      <c r="O56" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P56" t="str">
+        <v>{"macros_p":49,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":3,"tolerance_kcal":110.4},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
+      </c>
+      <c r="B57" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Chicken meatballs + spaghetti + salad</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Chicken Meatballs + Spaghetti</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Chicken meatballs + spaghetti + salad</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G57">
+        <v>649</v>
+      </c>
+      <c r="H57">
+        <v>57</v>
+      </c>
+      <c r="I57">
+        <v>47</v>
+      </c>
+      <c r="J57">
+        <v>27</v>
+      </c>
+      <c r="K57" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L57" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M57" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N57" t="b">
+        <v>1</v>
+      </c>
+      <c r="O57" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P57" t="str">
+        <v>{"macros_p":57,"protein_family":"mixed","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":659,"delta_kcal":10,"tolerance_kcal":129.8},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>lunch_dinner_rajma-paneer-bowl</v>
+      </c>
+      <c r="B58" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Rajma + paneer bowl</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Rajma + Paneer Bowl</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Rajma + paneer bowl</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G58">
+        <v>516</v>
+      </c>
+      <c r="H58">
+        <v>31</v>
+      </c>
+      <c r="I58">
+        <v>48</v>
+      </c>
+      <c r="J58">
+        <v>23</v>
+      </c>
+      <c r="K58" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L58" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M58" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N58" t="b">
+        <v>1</v>
+      </c>
+      <c r="O58" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+      </c>
+      <c r="P58" t="str">
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":523,"delta_kcal":7,"tolerance_kcal":103.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>snack_fruit-almonds-plant-shake</v>
+      </c>
+      <c r="B59" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Fruit + Almonds + Plant Shake</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Fruit + Almonds + Plant Shake</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Fruit + Almonds + Plant Shake</v>
+      </c>
+      <c r="F59" t="str">
+        <v>General</v>
+      </c>
+      <c r="G59">
+        <v>200</v>
+      </c>
+      <c r="H59">
+        <v>23</v>
+      </c>
+      <c r="I59">
+        <v>19</v>
+      </c>
+      <c r="J59">
+        <v>5</v>
+      </c>
+      <c r="K59" t="str">
+        <v>USDA + custom user specs</v>
+      </c>
+      <c r="L59" t="str">
+        <v>v1_custom</v>
+      </c>
+      <c r="M59" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N59" t="b">
+        <v>1</v>
+      </c>
+      <c r="O59" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P59" t="str">
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>snack_chaat-bhel-protein-shake</v>
+      </c>
+      <c r="B60" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G60">
+        <v>345</v>
+      </c>
+      <c r="H60">
+        <v>26</v>
+      </c>
+      <c r="I60">
+        <v>38</v>
+      </c>
+      <c r="J60">
+        <v>9</v>
+      </c>
+      <c r="K60" t="str">
+        <v>IFCT/USDA + custom user specs</v>
+      </c>
+      <c r="L60" t="str">
+        <v>v1_custom</v>
+      </c>
+      <c r="M60" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N60" t="b">
+        <v>1</v>
+      </c>
+      <c r="O60" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+      </c>
+      <c r="P60" t="str">
+        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>snack_greek-yogurt-berry-bowl</v>
+      </c>
+      <c r="B61" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="F61" t="str">
+        <v>International</v>
+      </c>
+      <c r="G61">
+        <v>203</v>
+      </c>
+      <c r="H61">
+        <v>21</v>
+      </c>
+      <c r="I61">
+        <v>22</v>
+      </c>
+      <c r="J61">
+        <v>4</v>
+      </c>
+      <c r="K61" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L61" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M61" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N61" t="b">
+        <v>1</v>
+      </c>
+      <c r="O61" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P61" t="str">
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+      </c>
+      <c r="B62" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Carrot halwa (sugar-free) + protein shake</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Carrot Halwa + Protein Shake</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Carrot halwa (sugar-free) + protein shake</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G62">
+        <v>220</v>
+      </c>
+      <c r="H62">
+        <v>28</v>
+      </c>
+      <c r="I62">
+        <v>17</v>
+      </c>
+      <c r="J62">
+        <v>5</v>
+      </c>
+      <c r="K62" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L62" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M62" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N62" t="b">
+        <v>1</v>
+      </c>
+      <c r="O62" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P62" t="str">
+        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B63" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Nuts + Seeds + Protein Shake</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="F63" t="str">
+        <v>International</v>
+      </c>
+      <c r="G63">
+        <v>320</v>
+      </c>
+      <c r="H63">
+        <v>31</v>
+      </c>
+      <c r="I63">
+        <v>11</v>
+      </c>
+      <c r="J63">
+        <v>17</v>
+      </c>
+      <c r="K63" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L63" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M63" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N63" t="b">
+        <v>1</v>
+      </c>
+      <c r="O63" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P63" t="str">
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B64" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G64">
+        <v>135</v>
+      </c>
+      <c r="H64">
+        <v>3</v>
+      </c>
+      <c r="I64">
+        <v>32</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L64" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M64" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N64" t="b">
+        <v>1</v>
+      </c>
+      <c r="O64" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P64" t="str">
+        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B65" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G65">
+        <v>246</v>
+      </c>
+      <c r="H65">
+        <v>13</v>
+      </c>
+      <c r="I65">
+        <v>41</v>
+      </c>
+      <c r="J65">
+        <v>4</v>
+      </c>
+      <c r="K65" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L65" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M65" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N65" t="b">
+        <v>1</v>
+      </c>
+      <c r="O65" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+      </c>
+      <c r="P65" t="str">
+        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
         <v>snack_avocado-cheese-toast</v>
       </c>
-      <c r="B54" t="str">
+      <c r="B66" t="str">
         <v>snack</v>
       </c>
-      <c r="C54" t="str">
+      <c r="C66" t="str">
         <v>Avocado/cheese toast</v>
       </c>
-      <c r="D54" t="str">
+      <c r="D66" t="str">
         <v>Avocado/Cheese Toast</v>
       </c>
-      <c r="E54" t="str">
+      <c r="E66" t="str">
         <v>Avocado/cheese toast</v>
       </c>
-      <c r="F54" t="str">
+      <c r="F66" t="str">
         <v>Continental</v>
       </c>
-      <c r="G54">
+      <c r="G66">
         <v>193</v>
       </c>
-      <c r="H54">
+      <c r="H66">
         <v>9</v>
       </c>
-      <c r="I54">
+      <c r="I66">
         <v>14</v>
       </c>
-      <c r="J54">
+      <c r="J66">
         <v>12</v>
       </c>
-      <c r="K54" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
-      </c>
-      <c r="L54" t="str">
+      <c r="K66" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L66" t="str">
         <v>assumptions_v2026_02_17</v>
       </c>
-      <c r="M54" t="str">
-        <v>seed_v1</v>
-      </c>
-      <c r="N54" t="b">
-        <v>1</v>
-      </c>
-      <c r="O54" t="str">
+      <c r="M66" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N66" t="b">
+        <v>1</v>
+      </c>
+      <c r="O66" t="str">
         <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
-      <c r="P54" t="str">
+      <c r="P66" t="str">
         <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":200,"delta_kcal":7,"tolerance_kcal":38.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+      </c>
+      <c r="B67" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Boiled eggs + hummus + veg sticks</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Eggs + Hummus + Veg Sticks</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Boiled eggs + hummus + veg sticks</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G67">
+        <v>246</v>
+      </c>
+      <c r="H67">
+        <v>18</v>
+      </c>
+      <c r="I67">
+        <v>12</v>
+      </c>
+      <c r="J67">
+        <v>14</v>
+      </c>
+      <c r="K67" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L67" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M67" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N67" t="b">
+        <v>1</v>
+      </c>
+      <c r="O67" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P67" t="str">
+        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":246,"delta_kcal":0,"tolerance_kcal":49.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>snack_edamame-sea-salt</v>
+      </c>
+      <c r="B68" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Edamame + sea salt</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Edamame + sea salt</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Edamame + sea salt</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G68">
+        <v>183</v>
+      </c>
+      <c r="H68">
+        <v>18</v>
+      </c>
+      <c r="I68">
+        <v>13</v>
+      </c>
+      <c r="J68">
+        <v>8</v>
+      </c>
+      <c r="K68" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L68" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M68" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N68" t="b">
+        <v>1</v>
+      </c>
+      <c r="O68" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"asian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P68" t="str">
+        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":196,"delta_kcal":13,"tolerance_kcal":36.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>snack_paneer-tikka-skewers</v>
+      </c>
+      <c r="B69" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Paneer tikka skewers</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Paneer tikka skewers</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Paneer tikka skewers</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G69">
+        <v>224</v>
+      </c>
+      <c r="H69">
+        <v>15</v>
+      </c>
+      <c r="I69">
+        <v>4</v>
+      </c>
+      <c r="J69">
+        <v>16</v>
+      </c>
+      <c r="K69" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L69" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M69" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N69" t="b">
+        <v>1</v>
+      </c>
+      <c r="O69" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P69" t="str">
+        <v>{"macros_p":15,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":220,"delta_kcal":4,"tolerance_kcal":44.8},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>snack_overnight-oats-whey-bowl</v>
+      </c>
+      <c r="B70" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Overnight oats + whey bowl</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Overnight Oats + Whey</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Overnight oats + whey bowl</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G70">
+        <v>218</v>
+      </c>
+      <c r="H70">
+        <v>9</v>
+      </c>
+      <c r="I70">
+        <v>32</v>
+      </c>
+      <c r="J70">
+        <v>6</v>
+      </c>
+      <c r="K70" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L70" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M70" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N70" t="b">
+        <v>1</v>
+      </c>
+      <c r="O70" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P70" t="str">
+        <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":218,"delta_kcal":0,"tolerance_kcal":43.6},"issues":[]}}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P70"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4450,28 +5250,28 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>lunch_dinner_butter-chicken-jowar-roti</v>
       </c>
       <c r="B47" t="str">
-        <v>Plant Shake</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C47">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D47" t="str">
-        <v>Mixed Fruit</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E47">
+        <v>1.5</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Cauliflower</v>
+      </c>
+      <c r="G47">
         <v>100</v>
       </c>
-      <c r="F47" t="str">
-        <v>Almonds</v>
-      </c>
-      <c r="G47">
-        <v>5</v>
-      </c>
       <c r="H47" t="str">
-        <v>Snack</v>
+        <v>Curry style</v>
       </c>
       <c r="I47" t="str">
         <v>{}</v>
@@ -4479,28 +5279,28 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
       </c>
       <c r="B48" t="str">
-        <v>Plant Shake</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C48">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D48" t="str">
-        <v>Chaat &amp; Bhel</v>
+        <v>Sweet potato</v>
       </c>
       <c r="E48">
         <v>150</v>
       </c>
       <c r="F48" t="str">
-        <v/>
-      </c>
-      <c r="G48" t="str">
-        <v/>
+        <v>Broccoli</v>
+      </c>
+      <c r="G48">
+        <v>150</v>
       </c>
       <c r="H48" t="str">
-        <v>Street Food Twist</v>
+        <v>Grilled</v>
       </c>
       <c r="I48" t="str">
         <v>{}</v>
@@ -4508,28 +5308,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
       </c>
       <c r="B49" t="str">
-        <v/>
+        <v>Beef steak</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D49" t="str">
-        <v>No carb</v>
+        <v>Garlic rice</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F49" t="str">
-        <v/>
-      </c>
-      <c r="G49" t="str">
-        <v/>
+        <v>Bok choy</v>
+      </c>
+      <c r="G49">
+        <v>120</v>
       </c>
       <c r="H49" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I49" t="str">
         <v>{}</v>
@@ -4537,28 +5337,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
       </c>
       <c r="B50" t="str">
-        <v/>
+        <v>Paneer</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D50" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F50" t="str">
-        <v/>
-      </c>
-      <c r="G50" t="str">
-        <v/>
+        <v>Mixed greens salad</v>
+      </c>
+      <c r="G50">
+        <v>100</v>
       </c>
       <c r="H50" t="str">
-        <v>Grilled</v>
+        <v>Tandoori</v>
       </c>
       <c r="I50" t="str">
         <v>{}</v>
@@ -4566,28 +5366,28 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
       </c>
       <c r="B51" t="str">
-        <v>Mixed nuts &amp; seeds</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C51">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="D51" t="str">
-        <v>No carb</v>
+        <v>Sweet potato</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F51" t="str">
-        <v/>
-      </c>
-      <c r="G51" t="str">
-        <v/>
+        <v>Sautéed spinach</v>
+      </c>
+      <c r="G51">
+        <v>120</v>
       </c>
       <c r="H51" t="str">
-        <v>Raw</v>
+        <v>Grilled</v>
       </c>
       <c r="I51" t="str">
         <v>{}</v>
@@ -4595,16 +5395,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>lunch_dinner_chicken-biryani-raita</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>Chicken breast</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D52" t="str">
-        <v>Sweet potato</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E52">
         <v>150</v>
@@ -4616,7 +5416,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Chaat</v>
+        <v>Curry style</v>
       </c>
       <c r="I52" t="str">
         <v>{}</v>
@@ -4624,28 +5424,28 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>lunch_dinner_fish-moilee-rice</v>
       </c>
       <c r="B53" t="str">
-        <v>Kaala chana</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C53">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D53" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F53" t="str">
-        <v/>
-      </c>
-      <c r="G53" t="str">
-        <v/>
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G53">
+        <v>80</v>
       </c>
       <c r="H53" t="str">
-        <v>Chaat</v>
+        <v>Curry style</v>
       </c>
       <c r="I53" t="str">
         <v>{}</v>
@@ -4653,36 +5453,500 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
+        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Eggs (whole)</v>
+      </c>
+      <c r="C54">
+        <v>200</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Jowar roti (millet)</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Dal</v>
+      </c>
+      <c r="G54">
+        <v>80</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Curry style</v>
+      </c>
+      <c r="I54" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>lunch_dinner_chicken-shawarma-bowl</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Chicken breast</v>
+      </c>
+      <c r="C55">
+        <v>140</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Flatbread</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Salad + hummus</v>
+      </c>
+      <c r="G55">
+        <v>180</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Bowl</v>
+      </c>
+      <c r="I55" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>lunch_dinner_prawn-curry-rice</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Prawns</v>
+      </c>
+      <c r="C56">
+        <v>180</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Cooked rice</v>
+      </c>
+      <c r="E56">
+        <v>110</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G56">
+        <v>70</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Curry style</v>
+      </c>
+      <c r="I56" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Chicken keema</v>
+      </c>
+      <c r="C57">
+        <v>180</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Spaghetti</v>
+      </c>
+      <c r="E57">
+        <v>150</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Mixed greens salad</v>
+      </c>
+      <c r="G57">
+        <v>100</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Pan-fried</v>
+      </c>
+      <c r="I57" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>lunch_dinner_rajma-paneer-bowl</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Paneer + rajma</v>
+      </c>
+      <c r="C58">
+        <v>260</v>
+      </c>
+      <c r="D58" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v>Curry style</v>
+      </c>
+      <c r="I58" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>snack_fruit-almonds-plant-shake</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Plant Shake</v>
+      </c>
+      <c r="C59">
+        <v>25</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Mixed Fruit</v>
+      </c>
+      <c r="E59">
+        <v>100</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Almonds</v>
+      </c>
+      <c r="G59">
+        <v>5</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Snack</v>
+      </c>
+      <c r="I59" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>snack_chaat-bhel-protein-shake</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Plant Shake</v>
+      </c>
+      <c r="C60">
+        <v>25</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Chaat &amp; Bhel</v>
+      </c>
+      <c r="E60">
+        <v>150</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v>Street Food Twist</v>
+      </c>
+      <c r="I60" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>snack_greek-yogurt-berry-bowl</v>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v>Grilled</v>
+      </c>
+      <c r="I61" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+      </c>
+      <c r="B62" t="str">
+        <v/>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v>Grilled</v>
+      </c>
+      <c r="I62" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mixed nuts &amp; seeds</v>
+      </c>
+      <c r="C63">
+        <v>30</v>
+      </c>
+      <c r="D63" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="I63" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Sweet potato</v>
+      </c>
+      <c r="E64">
+        <v>150</v>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I64" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Kaala chana</v>
+      </c>
+      <c r="C65">
+        <v>150</v>
+      </c>
+      <c r="D65" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I65" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
         <v>snack_avocado-cheese-toast</v>
       </c>
-      <c r="B54" t="str">
+      <c r="B66" t="str">
         <v/>
       </c>
-      <c r="C54">
+      <c r="C66">
         <v>0</v>
       </c>
-      <c r="D54" t="str">
+      <c r="D66" t="str">
         <v>Whole wheat toast</v>
       </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54" t="str">
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66" t="str">
         <v>Avocado</v>
       </c>
-      <c r="G54">
+      <c r="G66">
         <v>50</v>
       </c>
-      <c r="H54" t="str">
+      <c r="H66" t="str">
         <v>Toast</v>
       </c>
-      <c r="I54" t="str">
+      <c r="I66" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Eggs (whole)</v>
+      </c>
+      <c r="C67">
+        <v>100</v>
+      </c>
+      <c r="D67" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Raw vegetable sticks</v>
+      </c>
+      <c r="G67">
+        <v>100</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Snack</v>
+      </c>
+      <c r="I67" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>snack_edamame-sea-salt</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Edamame</v>
+      </c>
+      <c r="C68">
+        <v>150</v>
+      </c>
+      <c r="D68" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v>Steamed</v>
+      </c>
+      <c r="I68" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>snack_paneer-tikka-skewers</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Paneer</v>
+      </c>
+      <c r="C69">
+        <v>80</v>
+      </c>
+      <c r="D69" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Mixed greens</v>
+      </c>
+      <c r="G69">
+        <v>60</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Tandoori</v>
+      </c>
+      <c r="I69" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>snack_overnight-oats-whey-bowl</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Milk</v>
+      </c>
+      <c r="C70">
+        <v>150</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Rolled oats</v>
+      </c>
+      <c r="E70">
+        <v>25</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Mixed berries</v>
+      </c>
+      <c r="G70">
+        <v>60</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Bowl</v>
+      </c>
+      <c r="I70" t="str">
         <v>{}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I70"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/exports/meal_database_architecture_v1.xlsx
+++ b/exports/meal_database_architecture_v1.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -847,10 +847,10 @@
         <v>1</v>
       </c>
       <c r="O9" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"mixed","carb_level":"high","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P9" t="str">
-        <v>{"macros_p":40,"protein_family":"mixed","meal_weight_class":"medium","carb_level":"high","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":542,"delta_kcal":12,"tolerance_kcal":110.8},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"high","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":542,"delta_kcal":12,"tolerance_kcal":110.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="10">
@@ -1155,40 +1155,40 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti</v>
+        <v>breakfast_paneer-egg-white-bhurji-toast</v>
       </c>
       <c r="B16" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C16" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Paneer &amp; egg-white bhurji + toast</v>
       </c>
       <c r="D16" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Paneer &amp; Egg-White Bhurji</v>
       </c>
       <c r="E16" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Paneer &amp; egg-white bhurji + toast</v>
       </c>
       <c r="F16" t="str">
         <v>Indian</v>
       </c>
       <c r="G16">
-        <v>702</v>
+        <v>556</v>
       </c>
       <c r="H16">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="I16">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="J16">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K16" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L16" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M16" t="str">
         <v>seed_v1</v>
@@ -1197,48 +1197,48 @@
         <v>1</v>
       </c>
       <c r="O16" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"toast","effort":"low","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P16" t="str">
-        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":676,"delta_kcal":26,"tolerance_kcal":140.4},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"low","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":548,"delta_kcal":8,"tolerance_kcal":111.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
+        <v>breakfast_anda-bhurji-toast</v>
       </c>
       <c r="B17" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C17" t="str">
-        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
+        <v>Anda bhurji + toast</v>
       </c>
       <c r="D17" t="str">
-        <v>Salmon + Veg + Aglio Olio</v>
+        <v>Anda bhurji + toast</v>
       </c>
       <c r="E17" t="str">
-        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
+        <v>Anda bhurji + toast</v>
       </c>
       <c r="F17" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G17">
-        <v>669</v>
+        <v>490</v>
       </c>
       <c r="H17">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I17">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="J17">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K17" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L17" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M17" t="str">
         <v>seed_v1</v>
@@ -1247,48 +1247,48 @@
         <v>1</v>
       </c>
       <c r="O17" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"continental","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"toast","effort":"low","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P17" t="str">
-        <v>{"macros_p":46,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":688,"delta_kcal":19,"tolerance_kcal":133.8},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"low","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":474,"delta_kcal":16,"tolerance_kcal":98},"issues":[]}}</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>lunch_dinner_rajma-chawal-raita</v>
+        <v>breakfast_sardines-toast-avocado</v>
       </c>
       <c r="B18" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C18" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Sardines on toast + avocado</v>
       </c>
       <c r="D18" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Sardines on Toast + Avocado</v>
       </c>
       <c r="E18" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Sardines on toast + avocado</v>
       </c>
       <c r="F18" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G18">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="H18">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I18">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="J18">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K18" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L18" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M18" t="str">
         <v>seed_v1</v>
@@ -1297,48 +1297,48 @@
         <v>1</v>
       </c>
       <c r="O18" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P18" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":482,"delta_kcal":0,"tolerance_kcal":96.4},"issues":[]}}</v>
+        <v>{"macros_p":39,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":487,"delta_kcal":7,"tolerance_kcal":98.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>lunch_dinner_chole-jowar-roti-raita</v>
+        <v>breakfast_shakshuka-feta</v>
       </c>
       <c r="B19" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C19" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Shakshuka with feta</v>
       </c>
       <c r="D19" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Shakshuka with feta</v>
       </c>
       <c r="E19" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Shakshuka with feta</v>
       </c>
       <c r="F19" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G19">
-        <v>726</v>
+        <v>504</v>
       </c>
       <c r="H19">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="I19">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="J19">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K19" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L19" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M19" t="str">
         <v>seed_v1</v>
@@ -1347,48 +1347,48 @@
         <v>1</v>
       </c>
       <c r="O19" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P19" t="str">
-        <v>{"macros_p":27,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":722,"delta_kcal":4,"tolerance_kcal":145.2},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":500,"delta_kcal":4,"tolerance_kcal":100.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>lunch_dinner_vietnamese-chicken-pho</v>
+        <v>breakfast_cottage-cheese-smoked-salmon-bowl</v>
       </c>
       <c r="B20" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C20" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Cottage cheese &amp; smoked salmon bowl</v>
       </c>
       <c r="D20" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Cottage Cheese &amp; Smoked Salmon</v>
       </c>
       <c r="E20" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Cottage cheese &amp; smoked salmon bowl</v>
       </c>
       <c r="F20" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G20">
-        <v>394</v>
+        <v>494</v>
       </c>
       <c r="H20">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I20">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J20">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K20" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L20" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M20" t="str">
         <v>seed_v1</v>
@@ -1397,42 +1397,42 @@
         <v>1</v>
       </c>
       <c r="O20" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P20" t="str">
-        <v>{"macros_p":49,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":374,"delta_kcal":20,"tolerance_kcal":78.8},"issues":[]}}</v>
+        <v>{"macros_p":44,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":491,"delta_kcal":3,"tolerance_kcal":98.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti</v>
       </c>
       <c r="B21" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C21" t="str">
-        <v>Grilled steak + mixed greens salad</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="D21" t="str">
-        <v>Steak + Mixed Greens</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="E21" t="str">
-        <v>Grilled steak + mixed greens salad</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="F21" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G21">
-        <v>480</v>
+        <v>702</v>
       </c>
       <c r="H21">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="J21">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K21" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1447,42 +1447,42 @@
         <v>1</v>
       </c>
       <c r="O21" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P21" t="str">
-        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":477,"delta_kcal":3,"tolerance_kcal":96},"issues":[]}}</v>
+        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":676,"delta_kcal":26,"tolerance_kcal":140.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lunch_dinner_thai-pad-krapow-rice</v>
+        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B22" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C22" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
       </c>
       <c r="D22" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Salmon + Veg + Aglio Olio</v>
       </c>
       <c r="E22" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
       </c>
       <c r="F22" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G22">
-        <v>438</v>
+        <v>669</v>
       </c>
       <c r="H22">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I22">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="J22">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K22" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1497,42 +1497,42 @@
         <v>1</v>
       </c>
       <c r="O22" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"continental","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P22" t="str">
-        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":422,"delta_kcal":16,"tolerance_kcal":87.6},"issues":[]}}</v>
+        <v>{"macros_p":46,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":688,"delta_kcal":19,"tolerance_kcal":133.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lunch_dinner_mutton-keema-jowar-roti</v>
+        <v>lunch_dinner_rajma-chawal-raita</v>
       </c>
       <c r="B23" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C23" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="D23" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="E23" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="F23" t="str">
         <v>Indian</v>
       </c>
       <c r="G23">
-        <v>670</v>
+        <v>482</v>
       </c>
       <c r="H23">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I23">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J23">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K23" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1547,42 +1547,42 @@
         <v>1</v>
       </c>
       <c r="O23" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P23" t="str">
-        <v>{"macros_p":34,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":654,"delta_kcal":16,"tolerance_kcal":134},"issues":[]}}</v>
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":482,"delta_kcal":0,"tolerance_kcal":96.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
+        <v>lunch_dinner_chole-jowar-roti-raita</v>
       </c>
       <c r="B24" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C24" t="str">
-        <v>Arhar dal + rice + matar paneer</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="D24" t="str">
-        <v>Arhar Dal + Rice + Matar Paneer</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="E24" t="str">
-        <v>Arhar dal + rice + matar paneer</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="F24" t="str">
         <v>Indian</v>
       </c>
       <c r="G24">
-        <v>669</v>
+        <v>726</v>
       </c>
       <c r="H24">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I24">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="J24">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K24" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1600,39 +1600,39 @@
         <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P24" t="str">
-        <v>{"macros_p":32,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":666,"delta_kcal":3,"tolerance_kcal":133.8},"issues":[]}}</v>
+        <v>{"macros_p":27,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":722,"delta_kcal":4,"tolerance_kcal":145.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
+        <v>lunch_dinner_vietnamese-chicken-pho</v>
       </c>
       <c r="B25" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C25" t="str">
-        <v>Chicken curry + jowar roti + dal</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="D25" t="str">
-        <v>Chicken Curry + Roti + Dal</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="E25" t="str">
-        <v>Chicken curry + jowar roti + dal</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="F25" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G25">
-        <v>736</v>
+        <v>394</v>
       </c>
       <c r="H25">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="I25">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="J25">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K25" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1647,42 +1647,42 @@
         <v>1</v>
       </c>
       <c r="O25" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P25" t="str">
-        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":709,"delta_kcal":27,"tolerance_kcal":147.2},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":374,"delta_kcal":20,"tolerance_kcal":78.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
+        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
       </c>
       <c r="B26" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C26" t="str">
-        <v>Grilled fish + pumpkin salad</v>
+        <v>Grilled steak + mixed greens salad</v>
       </c>
       <c r="D26" t="str">
-        <v>Grilled Fish + Pumpkin Salad</v>
+        <v>Steak + Mixed Greens</v>
       </c>
       <c r="E26" t="str">
-        <v>Grilled fish + pumpkin salad</v>
+        <v>Grilled steak + mixed greens salad</v>
       </c>
       <c r="F26" t="str">
         <v>Continental</v>
       </c>
       <c r="G26">
-        <v>308</v>
+        <v>480</v>
       </c>
       <c r="H26">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I26">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K26" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1697,42 +1697,42 @@
         <v>1</v>
       </c>
       <c r="O26" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P26" t="str">
-        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":305,"delta_kcal":3,"tolerance_kcal":61.6},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":477,"delta_kcal":3,"tolerance_kcal":96},"issues":[]}}</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
+        <v>lunch_dinner_thai-pad-krapow-rice</v>
       </c>
       <c r="B27" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C27" t="str">
-        <v>Grilled salmon + sauteed veg + garlic rice</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="D27" t="str">
-        <v>Salmon + Veg + Garlic Rice</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="E27" t="str">
-        <v>Grilled salmon + sauteed veg + garlic rice</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="F27" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G27">
-        <v>514</v>
+        <v>438</v>
       </c>
       <c r="H27">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I27">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J27">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K27" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1747,42 +1747,42 @@
         <v>1</v>
       </c>
       <c r="O27" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P27" t="str">
-        <v>{"macros_p":40,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":11,"tolerance_kcal":102.8},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":422,"delta_kcal":16,"tolerance_kcal":87.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
+        <v>lunch_dinner_mutton-keema-jowar-roti</v>
       </c>
       <c r="B28" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C28" t="str">
-        <v>Chicken soup + smoked salmon salad</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="D28" t="str">
-        <v>Chicken Soup + Salmon Salad</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="E28" t="str">
-        <v>Chicken soup + smoked salmon salad</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="F28" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G28">
-        <v>302</v>
+        <v>670</v>
       </c>
       <c r="H28">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="J28">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="K28" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1797,42 +1797,42 @@
         <v>1</v>
       </c>
       <c r="O28" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"low","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P28" t="str">
-        <v>{"macros_p":50,"protein_family":"mixed","meal_weight_class":"light","carb_level":"low","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":284,"delta_kcal":18,"tolerance_kcal":60.4},"issues":[]}}</v>
+        <v>{"macros_p":34,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":654,"delta_kcal":16,"tolerance_kcal":134},"issues":[]}}</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
+        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
       </c>
       <c r="B29" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C29" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Arhar dal + rice + matar paneer</v>
       </c>
       <c r="D29" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Arhar Dal + Rice + Matar Paneer</v>
       </c>
       <c r="E29" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Arhar dal + rice + matar paneer</v>
       </c>
       <c r="F29" t="str">
         <v>Indian</v>
       </c>
       <c r="G29">
-        <v>628</v>
+        <v>669</v>
       </c>
       <c r="H29">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I29">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="J29">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K29" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1847,42 +1847,42 @@
         <v>1</v>
       </c>
       <c r="O29" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P29" t="str">
-        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":631,"delta_kcal":3,"tolerance_kcal":125.6},"issues":[]}}</v>
+        <v>{"macros_p":32,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":666,"delta_kcal":3,"tolerance_kcal":133.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
       </c>
       <c r="B30" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C30" t="str">
-        <v>Pork chop + pumpkin salad</v>
+        <v>Chicken curry + jowar roti + dal</v>
       </c>
       <c r="D30" t="str">
-        <v>Pork Chop + Pumpkin Salad</v>
+        <v>Chicken Curry + Roti + Dal</v>
       </c>
       <c r="E30" t="str">
-        <v>Pork chop + pumpkin salad</v>
+        <v>Chicken curry + jowar roti + dal</v>
       </c>
       <c r="F30" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G30">
-        <v>562</v>
+        <v>736</v>
       </c>
       <c r="H30">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I30">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="J30">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="K30" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1897,42 +1897,42 @@
         <v>1</v>
       </c>
       <c r="O30" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P30" t="str">
-        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":13,"tolerance_kcal":112.4},"issues":[]}}</v>
+        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":709,"delta_kcal":27,"tolerance_kcal":147.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
+        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
       </c>
       <c r="B31" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C31" t="str">
-        <v>Pork chop + mixed greens salad</v>
+        <v>Grilled fish + pumpkin salad</v>
       </c>
       <c r="D31" t="str">
-        <v>Pork Chop + Mixed Greens</v>
+        <v>Grilled Fish + Pumpkin Salad</v>
       </c>
       <c r="E31" t="str">
-        <v>Pork chop + mixed greens salad</v>
+        <v>Grilled fish + pumpkin salad</v>
       </c>
       <c r="F31" t="str">
         <v>Continental</v>
       </c>
       <c r="G31">
-        <v>449</v>
+        <v>308</v>
       </c>
       <c r="H31">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J31">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="K31" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1947,42 +1947,42 @@
         <v>1</v>
       </c>
       <c r="O31" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P31" t="str">
-        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":435,"delta_kcal":14,"tolerance_kcal":89.8},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":305,"delta_kcal":3,"tolerance_kcal":61.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
+        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
       </c>
       <c r="B32" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C32" t="str">
-        <v>Tandoori chicken + smoked chicken + avocado salad</v>
+        <v>Grilled salmon + sauteed veg + garlic rice</v>
       </c>
       <c r="D32" t="str">
-        <v>Tandoori Chicken + Smoked Chicken Salad</v>
+        <v>Salmon + Veg + Garlic Rice</v>
       </c>
       <c r="E32" t="str">
-        <v>Tandoori chicken + smoked chicken + avocado salad</v>
+        <v>Grilled salmon + sauteed veg + garlic rice</v>
       </c>
       <c r="F32" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G32">
-        <v>366</v>
+        <v>514</v>
       </c>
       <c r="H32">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="J32">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K32" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1997,42 +1997,42 @@
         <v>1</v>
       </c>
       <c r="O32" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P32" t="str">
-        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":347,"delta_kcal":19,"tolerance_kcal":73.2},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":11,"tolerance_kcal":102.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
       </c>
       <c r="B33" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C33" t="str">
-        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
+        <v>Chicken soup + smoked salmon salad</v>
       </c>
       <c r="D33" t="str">
-        <v>Broccoli Soup + Fish + Aglio Olio</v>
+        <v>Chicken Soup + Salmon Salad</v>
       </c>
       <c r="E33" t="str">
-        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
+        <v>Chicken soup + smoked salmon salad</v>
       </c>
       <c r="F33" t="str">
         <v>Continental</v>
       </c>
       <c r="G33">
-        <v>433</v>
+        <v>302</v>
       </c>
       <c r="H33">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I33">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="J33">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K33" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2047,42 +2047,42 @@
         <v>1</v>
       </c>
       <c r="O33" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"low","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P33" t="str">
-        <v>{"macros_p":45,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":448,"delta_kcal":15,"tolerance_kcal":86.6},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"mixed","meal_weight_class":"light","carb_level":"low","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":284,"delta_kcal":18,"tolerance_kcal":60.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
+        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
       </c>
       <c r="B34" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C34" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="D34" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="E34" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="F34" t="str">
         <v>Indian</v>
       </c>
       <c r="G34">
-        <v>771</v>
+        <v>628</v>
       </c>
       <c r="H34">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I34">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="J34">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K34" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2097,42 +2097,42 @@
         <v>1</v>
       </c>
       <c r="O34" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P34" t="str">
-        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":755,"delta_kcal":16,"tolerance_kcal":154.2},"issues":[]}}</v>
+        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":631,"delta_kcal":3,"tolerance_kcal":125.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>lunch_dinner_kofta-dal-jowar-roti</v>
+        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
       </c>
       <c r="B35" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C35" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Pork chop + pumpkin salad</v>
       </c>
       <c r="D35" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Pork Chop + Pumpkin Salad</v>
       </c>
       <c r="E35" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Pork chop + pumpkin salad</v>
       </c>
       <c r="F35" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G35">
-        <v>769</v>
+        <v>562</v>
       </c>
       <c r="H35">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="I35">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="J35">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K35" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2147,42 +2147,42 @@
         <v>1</v>
       </c>
       <c r="O35" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P35" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":746,"delta_kcal":23,"tolerance_kcal":153.8},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":13,"tolerance_kcal":112.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
+        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
       </c>
       <c r="B36" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C36" t="str">
-        <v>Kababs + dal + gobi + jowar roti</v>
+        <v>Pork chop + mixed greens salad</v>
       </c>
       <c r="D36" t="str">
-        <v>Kababs + Dal + Gobi + Roti</v>
+        <v>Pork Chop + Mixed Greens</v>
       </c>
       <c r="E36" t="str">
-        <v>Kababs + dal + gobi + jowar roti</v>
+        <v>Pork chop + mixed greens salad</v>
       </c>
       <c r="F36" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G36">
-        <v>823</v>
+        <v>449</v>
       </c>
       <c r="H36">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I36">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K36" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2197,42 +2197,42 @@
         <v>1</v>
       </c>
       <c r="O36" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P36" t="str">
-        <v>{"macros_p":41,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":813,"delta_kcal":10,"tolerance_kcal":164.6},"issues":[]}}</v>
+        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":435,"delta_kcal":14,"tolerance_kcal":89.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>lunch_dinner_fish-curry-rice</v>
+        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
       </c>
       <c r="B37" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C37" t="str">
-        <v>Fish curry + rice</v>
+        <v>Tandoori chicken + smoked chicken + avocado salad</v>
       </c>
       <c r="D37" t="str">
-        <v>Fish curry + rice</v>
+        <v>Tandoori Chicken + Smoked Chicken Salad</v>
       </c>
       <c r="E37" t="str">
-        <v>Fish curry + rice</v>
+        <v>Tandoori chicken + smoked chicken + avocado salad</v>
       </c>
       <c r="F37" t="str">
         <v>Indian</v>
       </c>
       <c r="G37">
-        <v>446</v>
+        <v>366</v>
       </c>
       <c r="H37">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I37">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K37" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2247,42 +2247,42 @@
         <v>1</v>
       </c>
       <c r="O37" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P37" t="str">
-        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":433,"delta_kcal":13,"tolerance_kcal":89.2},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":347,"delta_kcal":19,"tolerance_kcal":73.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
+        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B38" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C38" t="str">
-        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
+        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
       </c>
       <c r="D38" t="str">
-        <v>Sweet Potato Curry + Kaala Chanaa + Jowar Roti</v>
+        <v>Broccoli Soup + Fish + Aglio Olio</v>
       </c>
       <c r="E38" t="str">
-        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
+        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
       </c>
       <c r="F38" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G38">
-        <v>731</v>
+        <v>433</v>
       </c>
       <c r="H38">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="I38">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="J38">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K38" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2297,42 +2297,42 @@
         <v>1</v>
       </c>
       <c r="O38" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P38" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":735,"delta_kcal":4,"tolerance_kcal":146.2},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":448,"delta_kcal":15,"tolerance_kcal":86.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
+        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
       </c>
       <c r="B39" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C39" t="str">
-        <v>Avocado and smoked salmon salad</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="D39" t="str">
-        <v>Avocado &amp; Smoked Salmon Salad</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="E39" t="str">
-        <v>Avocado and smoked salmon salad</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="F39" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G39">
-        <v>206</v>
+        <v>771</v>
       </c>
       <c r="H39">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="J39">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="K39" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2347,42 +2347,42 @@
         <v>1</v>
       </c>
       <c r="O39" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P39" t="str">
-        <v>{"macros_p":24,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":201,"delta_kcal":5,"tolerance_kcal":41.2},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":755,"delta_kcal":16,"tolerance_kcal":154.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
+        <v>lunch_dinner_kofta-dal-jowar-roti</v>
       </c>
       <c r="B40" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C40" t="str">
-        <v>Avocado and smoked chicken salad</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="D40" t="str">
-        <v>Avocado &amp; Smoked Chicken Salad</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="E40" t="str">
-        <v>Avocado and smoked chicken salad</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="F40" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G40">
-        <v>244</v>
+        <v>769</v>
       </c>
       <c r="H40">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="J40">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K40" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2397,42 +2397,42 @@
         <v>1</v>
       </c>
       <c r="O40" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
       </c>
       <c r="P40" t="str">
-        <v>{"macros_p":33,"protein_family":"chicken","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":237,"delta_kcal":7,"tolerance_kcal":48.8},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":746,"delta_kcal":23,"tolerance_kcal":153.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>lunch_dinner_chicken-red-curry-rice</v>
+        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
       </c>
       <c r="B41" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C41" t="str">
-        <v>Chicken red curry + rice</v>
+        <v>Kababs + dal + gobi + jowar roti</v>
       </c>
       <c r="D41" t="str">
-        <v>Chicken Red Curry + Rice</v>
+        <v>Kababs + Dal + Gobi + Roti</v>
       </c>
       <c r="E41" t="str">
-        <v>Chicken red curry + rice</v>
+        <v>Kababs + dal + gobi + jowar roti</v>
       </c>
       <c r="F41" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G41">
-        <v>504</v>
+        <v>823</v>
       </c>
       <c r="H41">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="I41">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J41">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="K41" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2447,48 +2447,48 @@
         <v>1</v>
       </c>
       <c r="O41" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P41" t="str">
-        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":486,"delta_kcal":18,"tolerance_kcal":100.8},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":813,"delta_kcal":10,"tolerance_kcal":164.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
+        <v>lunch_dinner_fish-curry-rice</v>
       </c>
       <c r="B42" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C42" t="str">
-        <v>Korean chicken bibimbap bowl</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="D42" t="str">
-        <v>Chicken Bibimbap Bowl</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="E42" t="str">
-        <v>Korean chicken bibimbap bowl</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="F42" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G42">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="H42">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I42">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K42" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L42" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M42" t="str">
         <v>seed_v1</v>
@@ -2497,48 +2497,48 @@
         <v>1</v>
       </c>
       <c r="O42" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P42" t="str">
-        <v>{"macros_p":52,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":452,"delta_kcal":19,"tolerance_kcal":94.2},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":433,"delta_kcal":13,"tolerance_kcal":89.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B43" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C43" t="str">
-        <v>Salmon teriyaki + soba noodles</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="D43" t="str">
-        <v>Salmon Teriyaki + Soba</v>
+        <v>Sweet Potato Curry + Kaala Chanaa + Jowar Roti</v>
       </c>
       <c r="E43" t="str">
-        <v>Salmon teriyaki + soba noodles</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="F43" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G43">
-        <v>499</v>
+        <v>731</v>
       </c>
       <c r="H43">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I43">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="J43">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K43" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L43" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M43" t="str">
         <v>seed_v1</v>
@@ -2547,48 +2547,48 @@
         <v>1</v>
       </c>
       <c r="O43" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
       </c>
       <c r="P43" t="str">
-        <v>{"macros_p":43,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":9,"tolerance_kcal":99.8},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":735,"delta_kcal":4,"tolerance_kcal":146.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
+        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
       </c>
       <c r="B44" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C44" t="str">
-        <v>Prawn stir-fry + edamame + rice noodles</v>
+        <v>Avocado and smoked salmon salad</v>
       </c>
       <c r="D44" t="str">
-        <v>Prawn Stir-fry + Edamame</v>
+        <v>Avocado &amp; Smoked Salmon Salad</v>
       </c>
       <c r="E44" t="str">
-        <v>Prawn stir-fry + edamame + rice noodles</v>
+        <v>Avocado and smoked salmon salad</v>
       </c>
       <c r="F44" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G44">
-        <v>472</v>
+        <v>206</v>
       </c>
       <c r="H44">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="I44">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="J44">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K44" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L44" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M44" t="str">
         <v>seed_v1</v>
@@ -2597,48 +2597,48 @@
         <v>1</v>
       </c>
       <c r="O44" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P44" t="str">
-        <v>{"macros_p":54,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":467,"delta_kcal":5,"tolerance_kcal":94.4},"issues":[]}}</v>
+        <v>{"macros_p":24,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":201,"delta_kcal":5,"tolerance_kcal":41.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>lunch_dinner_miso-chicken-ramen-egg</v>
+        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
       </c>
       <c r="B45" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C45" t="str">
-        <v>Miso chicken ramen + egg</v>
+        <v>Avocado and smoked chicken salad</v>
       </c>
       <c r="D45" t="str">
-        <v>Miso Chicken Ramen</v>
+        <v>Avocado &amp; Smoked Chicken Salad</v>
       </c>
       <c r="E45" t="str">
-        <v>Miso chicken ramen + egg</v>
+        <v>Avocado and smoked chicken salad</v>
       </c>
       <c r="F45" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G45">
-        <v>527</v>
+        <v>244</v>
       </c>
       <c r="H45">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="I45">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J45">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K45" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L45" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M45" t="str">
         <v>seed_v1</v>
@@ -2647,48 +2647,48 @@
         <v>1</v>
       </c>
       <c r="O45" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P45" t="str">
-        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":515,"delta_kcal":12,"tolerance_kcal":105.4},"issues":[]}}</v>
+        <v>{"macros_p":33,"protein_family":"chicken","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":237,"delta_kcal":7,"tolerance_kcal":48.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>lunch_dinner_tofu-edamame-ramen</v>
+        <v>lunch_dinner_chicken-red-curry-rice</v>
       </c>
       <c r="B46" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C46" t="str">
-        <v>Tofu &amp; edamame ramen</v>
+        <v>Chicken red curry + rice</v>
       </c>
       <c r="D46" t="str">
-        <v>Tofu &amp; Edamame Ramen</v>
+        <v>Chicken Red Curry + Rice</v>
       </c>
       <c r="E46" t="str">
-        <v>Tofu &amp; edamame ramen</v>
+        <v>Chicken red curry + rice</v>
       </c>
       <c r="F46" t="str">
         <v>Asian</v>
       </c>
       <c r="G46">
-        <v>565</v>
+        <v>504</v>
       </c>
       <c r="H46">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I46">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J46">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K46" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L46" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M46" t="str">
         <v>seed_v1</v>
@@ -2697,42 +2697,42 @@
         <v>1</v>
       </c>
       <c r="O46" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P46" t="str">
-        <v>{"macros_p":47,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":596,"delta_kcal":31,"tolerance_kcal":113},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":486,"delta_kcal":18,"tolerance_kcal":100.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>lunch_dinner_butter-chicken-jowar-roti</v>
+        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
       </c>
       <c r="B47" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C47" t="str">
-        <v>Butter chicken + jowar roti</v>
+        <v>Korean chicken bibimbap bowl</v>
       </c>
       <c r="D47" t="str">
-        <v>Butter Chicken + Jowar Roti</v>
+        <v>Chicken Bibimbap Bowl</v>
       </c>
       <c r="E47" t="str">
-        <v>Butter chicken + jowar roti</v>
+        <v>Korean chicken bibimbap bowl</v>
       </c>
       <c r="F47" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G47">
-        <v>635</v>
+        <v>471</v>
       </c>
       <c r="H47">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I47">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="J47">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K47" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2747,42 +2747,42 @@
         <v>1</v>
       </c>
       <c r="O47" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P47" t="str">
-        <v>{"macros_p":54,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":622,"delta_kcal":13,"tolerance_kcal":127},"issues":[]}}</v>
+        <v>{"macros_p":52,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":452,"delta_kcal":19,"tolerance_kcal":94.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
+        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
       </c>
       <c r="B48" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C48" t="str">
-        <v>Grilled chicken + sweet potato + broccoli</v>
+        <v>Salmon teriyaki + soba noodles</v>
       </c>
       <c r="D48" t="str">
-        <v>Grilled Chicken + Sweet Potato</v>
+        <v>Salmon Teriyaki + Soba</v>
       </c>
       <c r="E48" t="str">
-        <v>Grilled chicken + sweet potato + broccoli</v>
+        <v>Salmon teriyaki + soba noodles</v>
       </c>
       <c r="F48" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G48">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="H48">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="I48">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J48">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K48" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2797,42 +2797,42 @@
         <v>1</v>
       </c>
       <c r="O48" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P48" t="str">
-        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":3,"tolerance_kcal":101},"issues":[]}}</v>
+        <v>{"macros_p":43,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":9,"tolerance_kcal":99.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
+        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
       </c>
       <c r="B49" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C49" t="str">
-        <v>Pepper beef + garlic rice + greens</v>
+        <v>Prawn stir-fry + edamame + rice noodles</v>
       </c>
       <c r="D49" t="str">
-        <v>Pepper Beef + Garlic Rice</v>
+        <v>Prawn Stir-fry + Edamame</v>
       </c>
       <c r="E49" t="str">
-        <v>Pepper beef + garlic rice + greens</v>
+        <v>Prawn stir-fry + edamame + rice noodles</v>
       </c>
       <c r="F49" t="str">
         <v>Asian</v>
       </c>
       <c r="G49">
-        <v>696</v>
+        <v>472</v>
       </c>
       <c r="H49">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I49">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J49">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="K49" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2847,42 +2847,42 @@
         <v>1</v>
       </c>
       <c r="O49" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P49" t="str">
-        <v>{"macros_p":53,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":702,"delta_kcal":6,"tolerance_kcal":139.2},"issues":[]}}</v>
+        <v>{"macros_p":54,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":467,"delta_kcal":5,"tolerance_kcal":94.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
+        <v>lunch_dinner_miso-chicken-ramen-egg</v>
       </c>
       <c r="B50" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C50" t="str">
-        <v>Paneer tikka + jowar roti + salad</v>
+        <v>Miso chicken ramen + egg</v>
       </c>
       <c r="D50" t="str">
-        <v>Paneer Tikka + Jowar Roti</v>
+        <v>Miso Chicken Ramen</v>
       </c>
       <c r="E50" t="str">
-        <v>Paneer tikka + jowar roti + salad</v>
+        <v>Miso chicken ramen + egg</v>
       </c>
       <c r="F50" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G50">
-        <v>654</v>
+        <v>527</v>
       </c>
       <c r="H50">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="I50">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J50">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="K50" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2897,42 +2897,42 @@
         <v>1</v>
       </c>
       <c r="O50" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P50" t="str">
-        <v>{"macros_p":35,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":647,"delta_kcal":7,"tolerance_kcal":130.8},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":515,"delta_kcal":12,"tolerance_kcal":105.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
+        <v>lunch_dinner_tofu-edamame-ramen</v>
       </c>
       <c r="B51" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C51" t="str">
-        <v>Grilled salmon + sweet potato + spinach</v>
+        <v>Tofu &amp; edamame ramen</v>
       </c>
       <c r="D51" t="str">
-        <v>Salmon + Sweet Potato + Spinach</v>
+        <v>Tofu &amp; Edamame Ramen</v>
       </c>
       <c r="E51" t="str">
-        <v>Grilled salmon + sweet potato + spinach</v>
+        <v>Tofu &amp; edamame ramen</v>
       </c>
       <c r="F51" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G51">
-        <v>614</v>
+        <v>565</v>
       </c>
       <c r="H51">
+        <v>47</v>
+      </c>
+      <c r="I51">
         <v>48</v>
       </c>
-      <c r="I51">
-        <v>38</v>
-      </c>
       <c r="J51">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K51" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2947,42 +2947,42 @@
         <v>1</v>
       </c>
       <c r="O51" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P51" t="str">
-        <v>{"macros_p":48,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":614,"delta_kcal":0,"tolerance_kcal":122.8},"issues":[]}}</v>
+        <v>{"macros_p":47,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":596,"delta_kcal":31,"tolerance_kcal":113},"issues":[]}}</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>lunch_dinner_chicken-biryani-raita</v>
+        <v>lunch_dinner_butter-chicken-jowar-roti</v>
       </c>
       <c r="B52" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C52" t="str">
-        <v>Chicken biryani + raita</v>
+        <v>Butter chicken + jowar roti</v>
       </c>
       <c r="D52" t="str">
-        <v>Chicken biryani + raita</v>
+        <v>Butter Chicken + Jowar Roti</v>
       </c>
       <c r="E52" t="str">
-        <v>Chicken biryani + raita</v>
+        <v>Butter chicken + jowar roti</v>
       </c>
       <c r="F52" t="str">
         <v>Indian</v>
       </c>
       <c r="G52">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="H52">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I52">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J52">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K52" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3000,39 +3000,39 @@
         <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P52" t="str">
-        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":607,"delta_kcal":22,"tolerance_kcal":125.8},"issues":[]}}</v>
+        <v>{"macros_p":54,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":622,"delta_kcal":13,"tolerance_kcal":127},"issues":[]}}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>lunch_dinner_fish-moilee-rice</v>
+        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
       </c>
       <c r="B53" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C53" t="str">
-        <v>Fish moilee + rice</v>
+        <v>Grilled chicken + sweet potato + broccoli</v>
       </c>
       <c r="D53" t="str">
-        <v>Fish moilee + rice</v>
+        <v>Grilled Chicken + Sweet Potato</v>
       </c>
       <c r="E53" t="str">
-        <v>Fish moilee + rice</v>
+        <v>Grilled chicken + sweet potato + broccoli</v>
       </c>
       <c r="F53" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G53">
-        <v>615</v>
+        <v>505</v>
       </c>
       <c r="H53">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I53">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="J53">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K53" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3047,42 +3047,42 @@
         <v>1</v>
       </c>
       <c r="O53" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P53" t="str">
-        <v>{"macros_p":53,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":608,"delta_kcal":7,"tolerance_kcal":123},"issues":[]}}</v>
+        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":3,"tolerance_kcal":101},"issues":[]}}</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
+        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
       </c>
       <c r="B54" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C54" t="str">
-        <v>Egg curry + dal + jowar roti</v>
+        <v>Pepper beef + garlic rice + greens</v>
       </c>
       <c r="D54" t="str">
-        <v>Egg Curry + Dal + Roti</v>
+        <v>Pepper Beef + Garlic Rice</v>
       </c>
       <c r="E54" t="str">
-        <v>Egg curry + dal + jowar roti</v>
+        <v>Pepper beef + garlic rice + greens</v>
       </c>
       <c r="F54" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G54">
-        <v>604</v>
+        <v>696</v>
       </c>
       <c r="H54">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="I54">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J54">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K54" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3097,42 +3097,42 @@
         <v>1</v>
       </c>
       <c r="O54" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P54" t="str">
-        <v>{"macros_p":34,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":585,"delta_kcal":19,"tolerance_kcal":120.8},"issues":[]}}</v>
+        <v>{"macros_p":53,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":702,"delta_kcal":6,"tolerance_kcal":139.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>lunch_dinner_chicken-shawarma-bowl</v>
+        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
       </c>
       <c r="B55" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C55" t="str">
-        <v>Chicken shawarma bowl</v>
+        <v>Paneer tikka + jowar roti + salad</v>
       </c>
       <c r="D55" t="str">
-        <v>Chicken shawarma bowl</v>
+        <v>Paneer Tikka + Jowar Roti</v>
       </c>
       <c r="E55" t="str">
-        <v>Chicken shawarma bowl</v>
+        <v>Paneer tikka + jowar roti + salad</v>
       </c>
       <c r="F55" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G55">
-        <v>533</v>
+        <v>654</v>
       </c>
       <c r="H55">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="I55">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="J55">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K55" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3147,42 +3147,42 @@
         <v>1</v>
       </c>
       <c r="O55" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P55" t="str">
-        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":533,"delta_kcal":0,"tolerance_kcal":106.6},"issues":[]}}</v>
+        <v>{"macros_p":35,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":647,"delta_kcal":7,"tolerance_kcal":130.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>lunch_dinner_prawn-curry-rice</v>
+        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
       </c>
       <c r="B56" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C56" t="str">
-        <v>Prawn curry + rice</v>
+        <v>Grilled salmon + sweet potato + spinach</v>
       </c>
       <c r="D56" t="str">
-        <v>Prawn curry + rice</v>
+        <v>Salmon + Sweet Potato + Spinach</v>
       </c>
       <c r="E56" t="str">
-        <v>Prawn curry + rice</v>
+        <v>Grilled salmon + sweet potato + spinach</v>
       </c>
       <c r="F56" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G56">
-        <v>552</v>
+        <v>614</v>
       </c>
       <c r="H56">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I56">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J56">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K56" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3197,42 +3197,42 @@
         <v>1</v>
       </c>
       <c r="O56" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P56" t="str">
-        <v>{"macros_p":49,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":3,"tolerance_kcal":110.4},"issues":[]}}</v>
+        <v>{"macros_p":48,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":614,"delta_kcal":0,"tolerance_kcal":122.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
+        <v>lunch_dinner_chicken-biryani-raita</v>
       </c>
       <c r="B57" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C57" t="str">
-        <v>Chicken meatballs + spaghetti + salad</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="D57" t="str">
-        <v>Chicken Meatballs + Spaghetti</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="E57" t="str">
-        <v>Chicken meatballs + spaghetti + salad</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="F57" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G57">
-        <v>649</v>
+        <v>629</v>
       </c>
       <c r="H57">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I57">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J57">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K57" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3247,42 +3247,42 @@
         <v>1</v>
       </c>
       <c r="O57" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P57" t="str">
-        <v>{"macros_p":57,"protein_family":"mixed","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":659,"delta_kcal":10,"tolerance_kcal":129.8},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":607,"delta_kcal":22,"tolerance_kcal":125.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>lunch_dinner_rajma-paneer-bowl</v>
+        <v>lunch_dinner_fish-moilee-rice</v>
       </c>
       <c r="B58" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C58" t="str">
-        <v>Rajma + paneer bowl</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="D58" t="str">
-        <v>Rajma + Paneer Bowl</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="E58" t="str">
-        <v>Rajma + paneer bowl</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="F58" t="str">
         <v>Indian</v>
       </c>
       <c r="G58">
-        <v>516</v>
+        <v>615</v>
       </c>
       <c r="H58">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="I58">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J58">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K58" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3297,48 +3297,48 @@
         <v>1</v>
       </c>
       <c r="O58" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P58" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":523,"delta_kcal":7,"tolerance_kcal":103.2},"issues":[]}}</v>
+        <v>{"macros_p":53,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":608,"delta_kcal":7,"tolerance_kcal":123},"issues":[]}}</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
       </c>
       <c r="B59" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C59" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Egg curry + dal + jowar roti</v>
       </c>
       <c r="D59" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Egg Curry + Dal + Roti</v>
       </c>
       <c r="E59" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Egg curry + dal + jowar roti</v>
       </c>
       <c r="F59" t="str">
-        <v>General</v>
+        <v>Indian</v>
       </c>
       <c r="G59">
-        <v>200</v>
+        <v>604</v>
       </c>
       <c r="H59">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="I59">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="J59">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="K59" t="str">
-        <v>USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L59" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M59" t="str">
         <v>seed_v1</v>
@@ -3347,48 +3347,48 @@
         <v>1</v>
       </c>
       <c r="O59" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P59" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
+        <v>{"macros_p":34,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":585,"delta_kcal":19,"tolerance_kcal":120.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>lunch_dinner_chicken-shawarma-bowl</v>
       </c>
       <c r="B60" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C60" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Chicken shawarma bowl</v>
       </c>
       <c r="D60" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Chicken shawarma bowl</v>
       </c>
       <c r="E60" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Chicken shawarma bowl</v>
       </c>
       <c r="F60" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G60">
-        <v>345</v>
+        <v>533</v>
       </c>
       <c r="H60">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="I60">
         <v>38</v>
       </c>
       <c r="J60">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K60" t="str">
-        <v>IFCT/USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L60" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M60" t="str">
         <v>seed_v1</v>
@@ -3397,48 +3397,48 @@
         <v>1</v>
       </c>
       <c r="O60" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P60" t="str">
-        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":533,"delta_kcal":0,"tolerance_kcal":106.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>lunch_dinner_prawn-curry-rice</v>
       </c>
       <c r="B61" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C61" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Prawn curry + rice</v>
       </c>
       <c r="D61" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Prawn curry + rice</v>
       </c>
       <c r="E61" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Prawn curry + rice</v>
       </c>
       <c r="F61" t="str">
-        <v>International</v>
+        <v>Asian</v>
       </c>
       <c r="G61">
-        <v>203</v>
+        <v>552</v>
       </c>
       <c r="H61">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="I61">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K61" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L61" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M61" t="str">
         <v>seed_v1</v>
@@ -3447,48 +3447,48 @@
         <v>1</v>
       </c>
       <c r="O61" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P61" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":3,"tolerance_kcal":110.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
       </c>
       <c r="B62" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C62" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Chicken meatballs + spaghetti + salad</v>
       </c>
       <c r="D62" t="str">
-        <v>Carrot Halwa + Protein Shake</v>
+        <v>Chicken Meatballs + Spaghetti</v>
       </c>
       <c r="E62" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Chicken meatballs + spaghetti + salad</v>
       </c>
       <c r="F62" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G62">
-        <v>220</v>
+        <v>649</v>
       </c>
       <c r="H62">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="I62">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="J62">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="K62" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L62" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M62" t="str">
         <v>seed_v1</v>
@@ -3497,48 +3497,48 @@
         <v>1</v>
       </c>
       <c r="O62" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P62" t="str">
-        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":659,"delta_kcal":10,"tolerance_kcal":129.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_rajma-paneer-bowl</v>
       </c>
       <c r="B63" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C63" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Rajma + paneer bowl</v>
       </c>
       <c r="D63" t="str">
-        <v>Nuts + Seeds + Protein Shake</v>
+        <v>Rajma + Paneer Bowl</v>
       </c>
       <c r="E63" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Rajma + paneer bowl</v>
       </c>
       <c r="F63" t="str">
-        <v>International</v>
+        <v>Indian</v>
       </c>
       <c r="G63">
-        <v>320</v>
+        <v>516</v>
       </c>
       <c r="H63">
         <v>31</v>
       </c>
       <c r="I63">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="J63">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K63" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L63" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M63" t="str">
         <v>seed_v1</v>
@@ -3547,48 +3547,48 @@
         <v>1</v>
       </c>
       <c r="O63" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P63" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":523,"delta_kcal":7,"tolerance_kcal":103.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>lunch_dinner_palak-paneer-jowar-roti</v>
       </c>
       <c r="B64" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C64" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Palak paneer + jowar roti</v>
       </c>
       <c r="D64" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Palak paneer + jowar roti</v>
       </c>
       <c r="E64" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Palak paneer + jowar roti</v>
       </c>
       <c r="F64" t="str">
         <v>Indian</v>
       </c>
       <c r="G64">
-        <v>135</v>
+        <v>734</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I64">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K64" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L64" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M64" t="str">
         <v>seed_v1</v>
@@ -3597,48 +3597,48 @@
         <v>1</v>
       </c>
       <c r="O64" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P64" t="str">
-        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":731,"delta_kcal":3,"tolerance_kcal":146.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>lunch_dinner_achari-paneer-tikka-dal-salad</v>
       </c>
       <c r="B65" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C65" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Achari paneer tikka + dal + salad</v>
       </c>
       <c r="D65" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Achari Paneer Tikka + Dal</v>
       </c>
       <c r="E65" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Achari paneer tikka + dal + salad</v>
       </c>
       <c r="F65" t="str">
         <v>Indian</v>
       </c>
       <c r="G65">
-        <v>246</v>
+        <v>622</v>
       </c>
       <c r="H65">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="I65">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="K65" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L65" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M65" t="str">
         <v>seed_v1</v>
@@ -3647,48 +3647,48 @@
         <v>1</v>
       </c>
       <c r="O65" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P65" t="str">
-        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":621,"delta_kcal":1,"tolerance_kcal":124.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>lunch_dinner_soya-keema-curry-jowar-roti</v>
       </c>
       <c r="B66" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C66" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Soya keema curry + jowar roti</v>
       </c>
       <c r="D66" t="str">
-        <v>Avocado/Cheese Toast</v>
+        <v>Soya Keema + Jowar Roti</v>
       </c>
       <c r="E66" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Soya keema curry + jowar roti</v>
       </c>
       <c r="F66" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G66">
-        <v>193</v>
+        <v>530</v>
       </c>
       <c r="H66">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="I66">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="J66">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K66" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L66" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M66" t="str">
         <v>seed_v1</v>
@@ -3697,48 +3697,48 @@
         <v>1</v>
       </c>
       <c r="O66" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P66" t="str">
-        <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":200,"delta_kcal":7,"tolerance_kcal":38.6},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":5,"tolerance_kcal":106},"issues":[]}}</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+        <v>lunch_dinner_chole-paneer-bowl-salad</v>
       </c>
       <c r="B67" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C67" t="str">
-        <v>Boiled eggs + hummus + veg sticks</v>
+        <v>Chole-paneer bowl + salad</v>
       </c>
       <c r="D67" t="str">
-        <v>Eggs + Hummus + Veg Sticks</v>
+        <v>Chole-Paneer Bowl</v>
       </c>
       <c r="E67" t="str">
-        <v>Boiled eggs + hummus + veg sticks</v>
+        <v>Chole-paneer bowl + salad</v>
       </c>
       <c r="F67" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G67">
-        <v>246</v>
+        <v>659</v>
       </c>
       <c r="H67">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="I67">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="J67">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="K67" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L67" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M67" t="str">
         <v>seed_v1</v>
@@ -3747,48 +3747,48 @@
         <v>1</v>
       </c>
       <c r="O67" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P67" t="str">
-        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":246,"delta_kcal":0,"tolerance_kcal":49.2},"issues":[]}}</v>
+        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":662,"delta_kcal":3,"tolerance_kcal":131.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>snack_edamame-sea-salt</v>
+        <v>lunch_dinner_kadai-chicken-jowar-roti</v>
       </c>
       <c r="B68" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C68" t="str">
-        <v>Edamame + sea salt</v>
+        <v>Kadai chicken + jowar roti</v>
       </c>
       <c r="D68" t="str">
-        <v>Edamame + sea salt</v>
+        <v>Kadai chicken + jowar roti</v>
       </c>
       <c r="E68" t="str">
-        <v>Edamame + sea salt</v>
+        <v>Kadai chicken + jowar roti</v>
       </c>
       <c r="F68" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G68">
-        <v>183</v>
+        <v>586</v>
       </c>
       <c r="H68">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="I68">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="J68">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K68" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L68" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M68" t="str">
         <v>seed_v1</v>
@@ -3797,48 +3797,48 @@
         <v>1</v>
       </c>
       <c r="O68" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"asian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P68" t="str">
-        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":196,"delta_kcal":13,"tolerance_kcal":36.6},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":568,"delta_kcal":18,"tolerance_kcal":117.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>snack_paneer-tikka-skewers</v>
+        <v>lunch_dinner_tandoori-fish-tikka-veg-roti</v>
       </c>
       <c r="B69" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C69" t="str">
-        <v>Paneer tikka skewers</v>
+        <v>Tandoori fish tikka + sauteed veg + roti</v>
       </c>
       <c r="D69" t="str">
-        <v>Paneer tikka skewers</v>
+        <v>Tandoori Fish Tikka + Veg</v>
       </c>
       <c r="E69" t="str">
-        <v>Paneer tikka skewers</v>
+        <v>Tandoori fish tikka + sauteed veg + roti</v>
       </c>
       <c r="F69" t="str">
         <v>Indian</v>
       </c>
       <c r="G69">
-        <v>224</v>
+        <v>477</v>
       </c>
       <c r="H69">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="J69">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K69" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L69" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M69" t="str">
         <v>seed_v1</v>
@@ -3847,72 +3847,1472 @@
         <v>1</v>
       </c>
       <c r="O69" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P69" t="str">
-        <v>{"macros_p":15,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":220,"delta_kcal":4,"tolerance_kcal":44.8},"issues":[]}}</v>
+        <v>{"macros_p":58,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":474,"delta_kcal":3,"tolerance_kcal":95.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
+        <v>lunch_dinner_chicken-keema-matar-jowar-roti</v>
+      </c>
+      <c r="B70" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Chicken keema matar + jowar roti</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Chicken Keema Matar + Roti</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Chicken keema matar + jowar roti</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G70">
+        <v>674</v>
+      </c>
+      <c r="H70">
+        <v>59</v>
+      </c>
+      <c r="I70">
+        <v>37</v>
+      </c>
+      <c r="J70">
+        <v>32</v>
+      </c>
+      <c r="K70" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L70" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M70" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N70" t="b">
+        <v>1</v>
+      </c>
+      <c r="O70" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P70" t="str">
+        <v>{"macros_p":59,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":672,"delta_kcal":2,"tolerance_kcal":134.8},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>lunch_dinner_beef-bulgogi-bowl</v>
+      </c>
+      <c r="B71" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Beef bulgogi bowl</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Beef bulgogi bowl</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Beef bulgogi bowl</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G71">
+        <v>575</v>
+      </c>
+      <c r="H71">
+        <v>46</v>
+      </c>
+      <c r="I71">
+        <v>37</v>
+      </c>
+      <c r="J71">
+        <v>26</v>
+      </c>
+      <c r="K71" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L71" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M71" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N71" t="b">
+        <v>1</v>
+      </c>
+      <c r="O71" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P71" t="str">
+        <v>{"macros_p":46,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":566,"delta_kcal":9,"tolerance_kcal":115},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>lunch_dinner_tofu-veg-bibimbap</v>
+      </c>
+      <c r="B72" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Tofu &amp; vegetable bibimbap</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Tofu &amp; Veg Bibimbap</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Tofu &amp; vegetable bibimbap</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G72">
+        <v>555</v>
+      </c>
+      <c r="H72">
+        <v>44</v>
+      </c>
+      <c r="I72">
+        <v>41</v>
+      </c>
+      <c r="J72">
+        <v>27</v>
+      </c>
+      <c r="K72" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L72" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M72" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N72" t="b">
+        <v>1</v>
+      </c>
+      <c r="O72" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P72" t="str">
+        <v>{"macros_p":44,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":583,"delta_kcal":28,"tolerance_kcal":111},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>lunch_dinner_oyakodon-side-salad</v>
+      </c>
+      <c r="B73" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Oyakodon + side salad</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Oyakodon (chicken &amp; egg)</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Oyakodon + side salad</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G73">
+        <v>568</v>
+      </c>
+      <c r="H73">
+        <v>60</v>
+      </c>
+      <c r="I73">
+        <v>41</v>
+      </c>
+      <c r="J73">
+        <v>15</v>
+      </c>
+      <c r="K73" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L73" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M73" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N73" t="b">
+        <v>1</v>
+      </c>
+      <c r="O73" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P73" t="str">
+        <v>{"macros_p":60,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":539,"delta_kcal":29,"tolerance_kcal":113.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>lunch_dinner_dubu-jorim-rice-kimchi</v>
+      </c>
+      <c r="B74" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Dubu jorim + rice + kimchi</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Dubu Jorim (braised tofu)</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Dubu jorim + rice + kimchi</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G74">
+        <v>480</v>
+      </c>
+      <c r="H74">
+        <v>38</v>
+      </c>
+      <c r="I74">
+        <v>38</v>
+      </c>
+      <c r="J74">
+        <v>23</v>
+      </c>
+      <c r="K74" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L74" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M74" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N74" t="b">
+        <v>1</v>
+      </c>
+      <c r="O74" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
+      </c>
+      <c r="P74" t="str">
+        <v>{"macros_p":38,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":511,"delta_kcal":31,"tolerance_kcal":96},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>lunch_dinner_home-style-tofu-chicken-stir-fry</v>
+      </c>
+      <c r="B75" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Home-style tofu &amp; chicken stir-fry</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Home-Style Tofu &amp; Chicken</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Home-style tofu &amp; chicken stir-fry</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G75">
+        <v>609</v>
+      </c>
+      <c r="H75">
+        <v>64</v>
+      </c>
+      <c r="I75">
+        <v>39</v>
+      </c>
+      <c r="J75">
+        <v>23</v>
+      </c>
+      <c r="K75" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L75" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M75" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N75" t="b">
+        <v>1</v>
+      </c>
+      <c r="O75" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P75" t="str">
+        <v>{"macros_p":64,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":619,"delta_kcal":10,"tolerance_kcal":121.8},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>lunch_dinner_vietnamese-lemongrass-chicken-bowl</v>
+      </c>
+      <c r="B76" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Vietnamese lemongrass chicken bowl</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Lemongrass Chicken Bowl</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Vietnamese lemongrass chicken bowl</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G76">
+        <v>514</v>
+      </c>
+      <c r="H76">
+        <v>59</v>
+      </c>
+      <c r="I76">
+        <v>33</v>
+      </c>
+      <c r="J76">
+        <v>14</v>
+      </c>
+      <c r="K76" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L76" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M76" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N76" t="b">
+        <v>1</v>
+      </c>
+      <c r="O76" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+      </c>
+      <c r="P76" t="str">
+        <v>{"macros_p":59,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":494,"delta_kcal":20,"tolerance_kcal":102.8},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>lunch_dinner_cantonese-steamed-fish-edamame</v>
+      </c>
+      <c r="B77" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Cantonese steamed fish + edamame + rice</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Steamed Fish + Edamame</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Cantonese steamed fish + edamame + rice</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G77">
+        <v>484</v>
+      </c>
+      <c r="H77">
+        <v>60</v>
+      </c>
+      <c r="I77">
+        <v>36</v>
+      </c>
+      <c r="J77">
+        <v>12</v>
+      </c>
+      <c r="K77" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L77" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M77" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N77" t="b">
+        <v>1</v>
+      </c>
+      <c r="O77" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P77" t="str">
+        <v>{"macros_p":60,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":492,"delta_kcal":8,"tolerance_kcal":96.8},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>lunch_dinner_chicken-bulgogi-bowl</v>
+      </c>
+      <c r="B78" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Chicken bulgogi bowl</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Chicken bulgogi bowl</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Chicken bulgogi bowl</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G78">
+        <v>495</v>
+      </c>
+      <c r="H78">
+        <v>61</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>8</v>
+      </c>
+      <c r="K78" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L78" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M78" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N78" t="b">
+        <v>1</v>
+      </c>
+      <c r="O78" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P78" t="str">
+        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":484,"delta_kcal":11,"tolerance_kcal":99},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>lunch_dinner_chicken-souvlaki-tzatziki-greek-salad</v>
+      </c>
+      <c r="B79" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Chicken souvlaki + tzatziki + Greek salad</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Chicken Souvlaki + Greek Salad</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Chicken souvlaki + tzatziki + Greek salad</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G79">
+        <v>544</v>
+      </c>
+      <c r="H79">
+        <v>72</v>
+      </c>
+      <c r="I79">
+        <v>9</v>
+      </c>
+      <c r="J79">
+        <v>23</v>
+      </c>
+      <c r="K79" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L79" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M79" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N79" t="b">
+        <v>1</v>
+      </c>
+      <c r="O79" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+      </c>
+      <c r="P79" t="str">
+        <v>{"macros_p":72,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":531,"delta_kcal":13,"tolerance_kcal":108.8},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>lunch_dinner_baked-feta-chickpea-traybake</v>
+      </c>
+      <c r="B80" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Baked feta &amp; chickpea traybake</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Baked Feta &amp; Chickpea Traybake</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Baked feta &amp; chickpea traybake</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G80">
+        <v>615</v>
+      </c>
+      <c r="H80">
+        <v>36</v>
+      </c>
+      <c r="I80">
+        <v>47</v>
+      </c>
+      <c r="J80">
+        <v>33</v>
+      </c>
+      <c r="K80" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L80" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M80" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N80" t="b">
+        <v>1</v>
+      </c>
+      <c r="O80" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["two_meals"]}</v>
+      </c>
+      <c r="P80" t="str">
+        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":629,"delta_kcal":14,"tolerance_kcal":123},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>lunch_dinner_tuna-nicoise-salad</v>
+      </c>
+      <c r="B81" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Tuna Nicoise salad</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Tuna Nicoise salad</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Tuna Nicoise salad</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G81">
+        <v>524</v>
+      </c>
+      <c r="H81">
+        <v>55</v>
+      </c>
+      <c r="I81">
+        <v>24</v>
+      </c>
+      <c r="J81">
+        <v>22</v>
+      </c>
+      <c r="K81" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L81" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M81" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N81" t="b">
+        <v>1</v>
+      </c>
+      <c r="O81" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+      </c>
+      <c r="P81" t="str">
+        <v>{"macros_p":55,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":514,"delta_kcal":10,"tolerance_kcal":104.8},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>lunch_dinner_halloumi-roasted-veg-quinoa-bowl</v>
+      </c>
+      <c r="B82" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Halloumi &amp; roasted-veg quinoa bowl</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Halloumi &amp; Quinoa Bowl</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Halloumi &amp; roasted-veg quinoa bowl</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G82">
+        <v>601</v>
+      </c>
+      <c r="H82">
+        <v>40</v>
+      </c>
+      <c r="I82">
+        <v>39</v>
+      </c>
+      <c r="J82">
+        <v>33</v>
+      </c>
+      <c r="K82" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L82" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M82" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N82" t="b">
+        <v>1</v>
+      </c>
+      <c r="O82" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P82" t="str">
+        <v>{"macros_p":40,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":613,"delta_kcal":12,"tolerance_kcal":120.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>lunch_dinner_chicken-white-bean-stew</v>
+      </c>
+      <c r="B83" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Chicken &amp; white-bean stew</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Chicken &amp; White-Bean Stew</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Chicken &amp; white-bean stew</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G83">
+        <v>620</v>
+      </c>
+      <c r="H83">
+        <v>65</v>
+      </c>
+      <c r="I83">
+        <v>44</v>
+      </c>
+      <c r="J83">
+        <v>20</v>
+      </c>
+      <c r="K83" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L83" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M83" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O83" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P83" t="str">
+        <v>{"macros_p":65,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":616,"delta_kcal":4,"tolerance_kcal":124},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>lunch_dinner_chickpea-pasta-tuna-tomato</v>
+      </c>
+      <c r="B84" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Chickpea pasta with tuna &amp; tomato</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Chickpea Pasta with Tuna</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Chickpea pasta with tuna &amp; tomato</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G84">
+        <v>496</v>
+      </c>
+      <c r="H84">
+        <v>50</v>
+      </c>
+      <c r="I84">
+        <v>45</v>
+      </c>
+      <c r="J84">
+        <v>16</v>
+      </c>
+      <c r="K84" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L84" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M84" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N84" t="b">
+        <v>1</v>
+      </c>
+      <c r="O84" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P84" t="str">
+        <v>{"macros_p":50,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":524,"delta_kcal":28,"tolerance_kcal":99.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>lunch_dinner_chicken-ricotta-carbonara-style-spaghetti</v>
+      </c>
+      <c r="B85" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Chicken &amp; ricotta carbonara-style spaghetti</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Chicken &amp; Ricotta Spaghetti</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Chicken &amp; ricotta carbonara-style spaghetti</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G85">
+        <v>630</v>
+      </c>
+      <c r="H85">
+        <v>57</v>
+      </c>
+      <c r="I85">
+        <v>47</v>
+      </c>
+      <c r="J85">
+        <v>23</v>
+      </c>
+      <c r="K85" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L85" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M85" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N85" t="b">
+        <v>1</v>
+      </c>
+      <c r="O85" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"]}</v>
+      </c>
+      <c r="P85" t="str">
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":623,"delta_kcal":7,"tolerance_kcal":126},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>lunch_dinner_mackerel-quinoa-salad</v>
+      </c>
+      <c r="B86" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Mackerel &amp; quinoa salad</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Mackerel &amp; Quinoa Salad</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Mackerel &amp; quinoa salad</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G86">
+        <v>463</v>
+      </c>
+      <c r="H86">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>33</v>
+      </c>
+      <c r="J86">
+        <v>21</v>
+      </c>
+      <c r="K86" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L86" t="str">
+        <v>assumptions_v2026_08_03</v>
+      </c>
+      <c r="M86" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N86" t="b">
+        <v>1</v>
+      </c>
+      <c r="O86" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P86" t="str">
+        <v>{"macros_p":35,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":461,"delta_kcal":2,"tolerance_kcal":92.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>snack_fruit-almonds-plant-shake</v>
+      </c>
+      <c r="B87" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Fruit + Almonds + Plant Shake</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Fruit + Almonds + Plant Shake</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Fruit + Almonds + Plant Shake</v>
+      </c>
+      <c r="F87" t="str">
+        <v>General</v>
+      </c>
+      <c r="G87">
+        <v>200</v>
+      </c>
+      <c r="H87">
+        <v>23</v>
+      </c>
+      <c r="I87">
+        <v>19</v>
+      </c>
+      <c r="J87">
+        <v>5</v>
+      </c>
+      <c r="K87" t="str">
+        <v>USDA + custom user specs</v>
+      </c>
+      <c r="L87" t="str">
+        <v>v1_custom</v>
+      </c>
+      <c r="M87" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N87" t="b">
+        <v>1</v>
+      </c>
+      <c r="O87" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P87" t="str">
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>snack_chaat-bhel-protein-shake</v>
+      </c>
+      <c r="B88" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G88">
+        <v>345</v>
+      </c>
+      <c r="H88">
+        <v>26</v>
+      </c>
+      <c r="I88">
+        <v>38</v>
+      </c>
+      <c r="J88">
+        <v>9</v>
+      </c>
+      <c r="K88" t="str">
+        <v>IFCT/USDA + custom user specs</v>
+      </c>
+      <c r="L88" t="str">
+        <v>v1_custom</v>
+      </c>
+      <c r="M88" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N88" t="b">
+        <v>1</v>
+      </c>
+      <c r="O88" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+      </c>
+      <c r="P88" t="str">
+        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>snack_greek-yogurt-berry-bowl</v>
+      </c>
+      <c r="B89" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="F89" t="str">
+        <v>International</v>
+      </c>
+      <c r="G89">
+        <v>203</v>
+      </c>
+      <c r="H89">
+        <v>21</v>
+      </c>
+      <c r="I89">
+        <v>22</v>
+      </c>
+      <c r="J89">
+        <v>4</v>
+      </c>
+      <c r="K89" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L89" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M89" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N89" t="b">
+        <v>1</v>
+      </c>
+      <c r="O89" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P89" t="str">
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+      </c>
+      <c r="B90" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Carrot halwa (sugar-free) + protein shake</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Carrot Halwa + Protein Shake</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Carrot halwa (sugar-free) + protein shake</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G90">
+        <v>220</v>
+      </c>
+      <c r="H90">
+        <v>28</v>
+      </c>
+      <c r="I90">
+        <v>17</v>
+      </c>
+      <c r="J90">
+        <v>5</v>
+      </c>
+      <c r="K90" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L90" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M90" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N90" t="b">
+        <v>1</v>
+      </c>
+      <c r="O90" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P90" t="str">
+        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B91" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Nuts + Seeds + Protein Shake</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="F91" t="str">
+        <v>International</v>
+      </c>
+      <c r="G91">
+        <v>320</v>
+      </c>
+      <c r="H91">
+        <v>31</v>
+      </c>
+      <c r="I91">
+        <v>11</v>
+      </c>
+      <c r="J91">
+        <v>17</v>
+      </c>
+      <c r="K91" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L91" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M91" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N91" t="b">
+        <v>1</v>
+      </c>
+      <c r="O91" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P91" t="str">
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B92" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G92">
+        <v>135</v>
+      </c>
+      <c r="H92">
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <v>32</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L92" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M92" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N92" t="b">
+        <v>1</v>
+      </c>
+      <c r="O92" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P92" t="str">
+        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B93" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G93">
+        <v>246</v>
+      </c>
+      <c r="H93">
+        <v>13</v>
+      </c>
+      <c r="I93">
+        <v>41</v>
+      </c>
+      <c r="J93">
+        <v>4</v>
+      </c>
+      <c r="K93" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L93" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M93" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N93" t="b">
+        <v>1</v>
+      </c>
+      <c r="O93" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+      </c>
+      <c r="P93" t="str">
+        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B94" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Avocado/Cheese Toast</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G94">
+        <v>193</v>
+      </c>
+      <c r="H94">
+        <v>9</v>
+      </c>
+      <c r="I94">
+        <v>14</v>
+      </c>
+      <c r="J94">
+        <v>12</v>
+      </c>
+      <c r="K94" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L94" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M94" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N94" t="b">
+        <v>1</v>
+      </c>
+      <c r="O94" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P94" t="str">
+        <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":200,"delta_kcal":7,"tolerance_kcal":38.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+      </c>
+      <c r="B95" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Boiled eggs + hummus + veg sticks</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Eggs + Hummus + Veg Sticks</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Boiled eggs + hummus + veg sticks</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G95">
+        <v>246</v>
+      </c>
+      <c r="H95">
+        <v>18</v>
+      </c>
+      <c r="I95">
+        <v>12</v>
+      </c>
+      <c r="J95">
+        <v>14</v>
+      </c>
+      <c r="K95" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L95" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M95" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N95" t="b">
+        <v>1</v>
+      </c>
+      <c r="O95" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P95" t="str">
+        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":246,"delta_kcal":0,"tolerance_kcal":49.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>snack_edamame-sea-salt</v>
+      </c>
+      <c r="B96" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Edamame + sea salt</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Edamame + sea salt</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Edamame + sea salt</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G96">
+        <v>183</v>
+      </c>
+      <c r="H96">
+        <v>18</v>
+      </c>
+      <c r="I96">
+        <v>13</v>
+      </c>
+      <c r="J96">
+        <v>8</v>
+      </c>
+      <c r="K96" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L96" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M96" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N96" t="b">
+        <v>1</v>
+      </c>
+      <c r="O96" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"asian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P96" t="str">
+        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":196,"delta_kcal":13,"tolerance_kcal":36.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>snack_paneer-tikka-skewers</v>
+      </c>
+      <c r="B97" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Paneer tikka skewers</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Paneer tikka skewers</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Paneer tikka skewers</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G97">
+        <v>224</v>
+      </c>
+      <c r="H97">
+        <v>15</v>
+      </c>
+      <c r="I97">
+        <v>4</v>
+      </c>
+      <c r="J97">
+        <v>16</v>
+      </c>
+      <c r="K97" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L97" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M97" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N97" t="b">
+        <v>1</v>
+      </c>
+      <c r="O97" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P97" t="str">
+        <v>{"macros_p":15,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":220,"delta_kcal":4,"tolerance_kcal":44.8},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>snack_overnight-oats-whey-bowl</v>
       </c>
-      <c r="B70" t="str">
+      <c r="B98" t="str">
         <v>snack</v>
       </c>
-      <c r="C70" t="str">
+      <c r="C98" t="str">
         <v>Overnight oats + whey bowl</v>
       </c>
-      <c r="D70" t="str">
+      <c r="D98" t="str">
         <v>Overnight Oats + Whey</v>
       </c>
-      <c r="E70" t="str">
+      <c r="E98" t="str">
         <v>Overnight oats + whey bowl</v>
       </c>
-      <c r="F70" t="str">
+      <c r="F98" t="str">
         <v>Continental</v>
       </c>
-      <c r="G70">
+      <c r="G98">
         <v>218</v>
       </c>
-      <c r="H70">
+      <c r="H98">
         <v>9</v>
       </c>
-      <c r="I70">
+      <c r="I98">
         <v>32</v>
       </c>
-      <c r="J70">
+      <c r="J98">
         <v>6</v>
       </c>
-      <c r="K70" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
-      </c>
-      <c r="L70" t="str">
+      <c r="K98" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L98" t="str">
         <v>assumptions_v2026_08_02</v>
       </c>
-      <c r="M70" t="str">
-        <v>seed_v1</v>
-      </c>
-      <c r="N70" t="b">
-        <v>1</v>
-      </c>
-      <c r="O70" t="str">
+      <c r="M98" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N98" t="b">
+        <v>1</v>
+      </c>
+      <c r="O98" t="str">
         <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
-      <c r="P70" t="str">
+      <c r="P98" t="str">
         <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":218,"delta_kcal":0,"tolerance_kcal":43.6},"issues":[]}}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P98"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4351,28 +5751,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti</v>
+        <v>breakfast_paneer-egg-white-bhurji-toast</v>
       </c>
       <c r="B16" t="str">
-        <v>Chicken breast</v>
+        <v>Paneer + egg whites</v>
       </c>
       <c r="C16">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="D16" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Whole wheat toast</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="F16" t="str">
-        <v>Mixed veg sabzi</v>
-      </c>
-      <c r="G16">
-        <v>120</v>
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>Curry style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I16" t="str">
         <v>{}</v>
@@ -4380,28 +5780,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
+        <v>breakfast_anda-bhurji-toast</v>
       </c>
       <c r="B17" t="str">
-        <v>Grilled salmon</v>
+        <v>Eggs (whole + whites)</v>
       </c>
       <c r="C17">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="D17" t="str">
-        <v>Spaghetti aglio e olio (small portion)</v>
+        <v>Whole wheat toast</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F17" t="str">
-        <v>Sautéed broccoli</v>
-      </c>
-      <c r="G17">
-        <v>150</v>
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I17" t="str">
         <v>{}</v>
@@ -4409,28 +5809,28 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>lunch_dinner_rajma-chawal-raita</v>
+        <v>breakfast_sardines-toast-avocado</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Sardines</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D18" t="str">
-        <v>Cooked rice</v>
+        <v>Whole wheat toast</v>
       </c>
       <c r="E18">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F18" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Avocado + greens</v>
       </c>
       <c r="G18">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H18" t="str">
-        <v>Curry style</v>
+        <v>Toast</v>
       </c>
       <c r="I18" t="str">
         <v>{}</v>
@@ -4438,28 +5838,28 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>lunch_dinner_chole-jowar-roti-raita</v>
+        <v>breakfast_shakshuka-feta</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>Eggs + feta</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="D19" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Whole wheat toast</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
+        <v>Tomato, pepper, spinach</v>
+      </c>
+      <c r="G19">
+        <v>120</v>
       </c>
       <c r="H19" t="str">
-        <v>Curry style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I19" t="str">
         <v>{}</v>
@@ -4467,28 +5867,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>lunch_dinner_vietnamese-chicken-pho</v>
+        <v>breakfast_cottage-cheese-smoked-salmon-bowl</v>
       </c>
       <c r="B20" t="str">
-        <v>Chicken breast</v>
+        <v>Cottage cheese + smoked salmon</v>
       </c>
       <c r="C20">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="D20" t="str">
-        <v>Rice noodles</v>
+        <v>Whole wheat toast</v>
       </c>
       <c r="E20">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F20" t="str">
-        <v>Pho greens + side salad</v>
+        <v>Avocado + greens</v>
       </c>
       <c r="G20">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H20" t="str">
-        <v>Soup style</v>
+        <v>Bowl</v>
       </c>
       <c r="I20" t="str">
         <v>{}</v>
@@ -4496,28 +5896,28 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti</v>
       </c>
       <c r="B21" t="str">
-        <v>Beef steak</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C21">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D21" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>Mixed greens salad</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G21">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H21" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I21" t="str">
         <v>{}</v>
@@ -4525,28 +5925,28 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lunch_dinner_thai-pad-krapow-rice</v>
+        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B22" t="str">
-        <v>Chicken breast</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C22">
         <v>150</v>
       </c>
       <c r="D22" t="str">
-        <v>Cooked rice</v>
+        <v>Spaghetti aglio e olio (small portion)</v>
       </c>
       <c r="E22">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F22" t="str">
-        <v>Sautéed peppers + side salad</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G22">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="H22" t="str">
-        <v>Pan-fried</v>
+        <v>Grilled</v>
       </c>
       <c r="I22" t="str">
         <v>{}</v>
@@ -4554,25 +5954,25 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lunch_dinner_mutton-keema-jowar-roti</v>
+        <v>lunch_dinner_rajma-chawal-raita</v>
       </c>
       <c r="B23" t="str">
-        <v>Mutton keema</v>
+        <v/>
       </c>
       <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Cooked rice</v>
+      </c>
+      <c r="E23">
+        <v>80</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G23">
         <v>150</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Jowar roti (millet)</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v/>
       </c>
       <c r="H23" t="str">
         <v>Curry style</v>
@@ -4583,25 +5983,25 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
+        <v>lunch_dinner_chole-jowar-roti-raita</v>
       </c>
       <c r="B24" t="str">
-        <v>Paneer</v>
+        <v/>
       </c>
       <c r="C24">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D24" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E24">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F24" t="str">
-        <v>Mixed veg sabzi</v>
-      </c>
-      <c r="G24">
-        <v>120</v>
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
       </c>
       <c r="H24" t="str">
         <v>Curry style</v>
@@ -4612,7 +6012,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
+        <v>lunch_dinner_vietnamese-chicken-pho</v>
       </c>
       <c r="B25" t="str">
         <v>Chicken breast</v>
@@ -4621,19 +6021,19 @@
         <v>150</v>
       </c>
       <c r="D25" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Rice noodles</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="F25" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Pho greens + side salad</v>
       </c>
       <c r="G25">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H25" t="str">
-        <v>Curry style</v>
+        <v>Soup style</v>
       </c>
       <c r="I25" t="str">
         <v>{}</v>
@@ -4641,13 +6041,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
+        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
       </c>
       <c r="B26" t="str">
-        <v>Fish fillet</v>
+        <v>Beef steak</v>
       </c>
       <c r="C26">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D26" t="str">
         <v>No carb</v>
@@ -4656,10 +6056,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="str">
-        <v>Pumpkin salad</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G26">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H26" t="str">
         <v>Grilled</v>
@@ -4670,28 +6070,28 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
+        <v>lunch_dinner_thai-pad-krapow-rice</v>
       </c>
       <c r="B27" t="str">
-        <v>Grilled salmon</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C27">
         <v>150</v>
       </c>
       <c r="D27" t="str">
-        <v>Garlic rice (small portion)</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F27" t="str">
-        <v>Sautéed broccoli</v>
+        <v>Sautéed peppers + side salad</v>
       </c>
       <c r="G27">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H27" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I27" t="str">
         <v>{}</v>
@@ -4699,28 +6099,28 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
+        <v>lunch_dinner_mutton-keema-jowar-roti</v>
       </c>
       <c r="B28" t="str">
-        <v>Chicken breast</v>
+        <v>Mutton keema</v>
       </c>
       <c r="C28">
         <v>150</v>
       </c>
       <c r="D28" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>Smoked salmon salad</v>
-      </c>
-      <c r="G28">
-        <v>120</v>
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
       </c>
       <c r="H28" t="str">
-        <v>Soup style</v>
+        <v>Curry style</v>
       </c>
       <c r="I28" t="str">
         <v>{}</v>
@@ -4728,25 +6128,25 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
+        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
       </c>
       <c r="B29" t="str">
         <v>Paneer</v>
       </c>
       <c r="C29">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D29" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F29" t="str">
         <v>Mixed veg sabzi</v>
       </c>
       <c r="G29">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H29" t="str">
         <v>Curry style</v>
@@ -4757,28 +6157,28 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
       </c>
       <c r="B30" t="str">
-        <v>Pork chop</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C30">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D30" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" t="str">
-        <v>Pumpkin salad</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H30" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I30" t="str">
         <v>{}</v>
@@ -4786,13 +6186,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
+        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
       </c>
       <c r="B31" t="str">
-        <v>Pork chop</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C31">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D31" t="str">
         <v>No carb</v>
@@ -4801,10 +6201,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="str">
-        <v>Mixed greens salad</v>
+        <v>Pumpkin salad</v>
       </c>
       <c r="G31">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H31" t="str">
         <v>Grilled</v>
@@ -4815,28 +6215,28 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
+        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
       </c>
       <c r="B32" t="str">
-        <v>Chicken breast</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C32">
         <v>150</v>
       </c>
       <c r="D32" t="str">
-        <v>No carb</v>
+        <v>Garlic rice (small portion)</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" t="str">
-        <v>Smoked chicken + avocado salad</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G32">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H32" t="str">
-        <v>Tandoori</v>
+        <v>Grilled</v>
       </c>
       <c r="I32" t="str">
         <v>{}</v>
@@ -4844,25 +6244,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
       </c>
       <c r="B33" t="str">
-        <v>Fish fillet</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C33">
         <v>150</v>
       </c>
       <c r="D33" t="str">
-        <v>Spaghetti aglio e olio (small portion)</v>
+        <v>No carb</v>
       </c>
       <c r="E33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F33" t="str">
-        <v>Sautéed broccoli</v>
+        <v>Smoked salmon salad</v>
       </c>
       <c r="G33">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H33" t="str">
         <v>Soup style</v>
@@ -4873,25 +6273,25 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
+        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
       </c>
       <c r="B34" t="str">
-        <v>Lamb (seekh kabab)</v>
+        <v>Paneer</v>
       </c>
       <c r="C34">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="D34" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>No carb</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" t="str">
-        <v>Sautéed spinach</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G34">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H34" t="str">
         <v>Curry style</v>
@@ -4902,28 +6302,28 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>lunch_dinner_kofta-dal-jowar-roti</v>
+        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
       </c>
       <c r="B35" t="str">
-        <v>Veg kofta</v>
+        <v>Pork chop</v>
       </c>
       <c r="C35">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D35" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>No carb</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Pumpkin salad</v>
       </c>
       <c r="G35">
         <v>120</v>
       </c>
       <c r="H35" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I35" t="str">
         <v>{}</v>
@@ -4931,28 +6331,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
+        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
       </c>
       <c r="B36" t="str">
-        <v>Lamb (seekh kabab)</v>
+        <v>Pork chop</v>
       </c>
       <c r="C36">
         <v>180</v>
       </c>
       <c r="D36" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>No carb</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36" t="str">
-        <v>Cauliflower</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G36">
         <v>150</v>
       </c>
       <c r="H36" t="str">
-        <v>Tandoori</v>
+        <v>Grilled</v>
       </c>
       <c r="I36" t="str">
         <v>{}</v>
@@ -4960,28 +6360,28 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>lunch_dinner_fish-curry-rice</v>
+        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
       </c>
       <c r="B37" t="str">
-        <v>Fish fillet</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C37">
         <v>150</v>
       </c>
       <c r="D37" t="str">
-        <v>Cooked rice</v>
+        <v>No carb</v>
       </c>
       <c r="E37">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F37" t="str">
-        <v/>
-      </c>
-      <c r="G37" t="str">
-        <v/>
+        <v>Smoked chicken + avocado salad</v>
+      </c>
+      <c r="G37">
+        <v>120</v>
       </c>
       <c r="H37" t="str">
-        <v>Curry style</v>
+        <v>Tandoori</v>
       </c>
       <c r="I37" t="str">
         <v>{}</v>
@@ -4989,28 +6389,28 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
+        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B38" t="str">
-        <v>Kaala chanaa (black chickpeas)</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C38">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D38" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Spaghetti aglio e olio (small portion)</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F38" t="str">
-        <v>Sweet potato curry</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G38">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H38" t="str">
-        <v>Curry style</v>
+        <v>Soup style</v>
       </c>
       <c r="I38" t="str">
         <v>{}</v>
@@ -5018,28 +6418,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
+        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
       </c>
       <c r="B39" t="str">
-        <v>Smoked salmon</v>
+        <v>Lamb (seekh kabab)</v>
       </c>
       <c r="C39">
+        <v>170</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Jowar roti (millet)</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Sautéed spinach</v>
+      </c>
+      <c r="G39">
         <v>120</v>
       </c>
-      <c r="D39" t="str">
-        <v>No carb</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39" t="str">
-        <v>Avocado &amp; mixed greens</v>
-      </c>
-      <c r="G39">
-        <v>155</v>
-      </c>
       <c r="H39" t="str">
-        <v>Salad</v>
+        <v>Curry style</v>
       </c>
       <c r="I39" t="str">
         <v>{}</v>
@@ -5047,28 +6447,28 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
+        <v>lunch_dinner_kofta-dal-jowar-roti</v>
       </c>
       <c r="B40" t="str">
-        <v>Smoked chicken breast</v>
+        <v>Veg kofta</v>
       </c>
       <c r="C40">
+        <v>150</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Jowar roti (millet)</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G40">
         <v>120</v>
       </c>
-      <c r="D40" t="str">
-        <v>No carb</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40" t="str">
-        <v>Avocado &amp; mixed greens</v>
-      </c>
-      <c r="G40">
-        <v>155</v>
-      </c>
       <c r="H40" t="str">
-        <v>Salad</v>
+        <v>Curry style</v>
       </c>
       <c r="I40" t="str">
         <v>{}</v>
@@ -5076,28 +6476,28 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>lunch_dinner_chicken-red-curry-rice</v>
+        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
       </c>
       <c r="B41" t="str">
-        <v>Chicken breast</v>
+        <v>Lamb (seekh kabab)</v>
       </c>
       <c r="C41">
+        <v>180</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Jowar roti (millet)</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Cauliflower</v>
+      </c>
+      <c r="G41">
         <v>150</v>
       </c>
-      <c r="D41" t="str">
-        <v>Cooked rice</v>
-      </c>
-      <c r="E41">
-        <v>80</v>
-      </c>
-      <c r="F41" t="str">
-        <v>Red curry vegetables</v>
-      </c>
-      <c r="G41">
-        <v>100</v>
-      </c>
       <c r="H41" t="str">
-        <v>Curry style</v>
+        <v>Tandoori</v>
       </c>
       <c r="I41" t="str">
         <v>{}</v>
@@ -5105,10 +6505,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
+        <v>lunch_dinner_fish-curry-rice</v>
       </c>
       <c r="B42" t="str">
-        <v>Chicken breast</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C42">
         <v>150</v>
@@ -5117,16 +6517,16 @@
         <v>Cooked rice</v>
       </c>
       <c r="E42">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F42" t="str">
-        <v>Kimchi + spinach</v>
-      </c>
-      <c r="G42">
-        <v>140</v>
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
       </c>
       <c r="H42" t="str">
-        <v>Bowl</v>
+        <v>Curry style</v>
       </c>
       <c r="I42" t="str">
         <v>{}</v>
@@ -5134,28 +6534,28 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B43" t="str">
-        <v>Grilled salmon</v>
+        <v>Kaala chanaa (black chickpeas)</v>
       </c>
       <c r="C43">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D43" t="str">
-        <v>Soba noodles</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E43">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>Bok choy</v>
+        <v>Sweet potato curry</v>
       </c>
       <c r="G43">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H43" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I43" t="str">
         <v>{}</v>
@@ -5163,28 +6563,28 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
+        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
       </c>
       <c r="B44" t="str">
-        <v>Prawns</v>
+        <v>Smoked salmon</v>
       </c>
       <c r="C44">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="D44" t="str">
-        <v>Rice noodles</v>
+        <v>No carb</v>
       </c>
       <c r="E44">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F44" t="str">
-        <v>Edamame</v>
+        <v>Avocado &amp; mixed greens</v>
       </c>
       <c r="G44">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="H44" t="str">
-        <v>Pan-fried</v>
+        <v>Salad</v>
       </c>
       <c r="I44" t="str">
         <v>{}</v>
@@ -5192,28 +6592,28 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>lunch_dinner_miso-chicken-ramen-egg</v>
+        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
       </c>
       <c r="B45" t="str">
-        <v>Chicken breast</v>
+        <v>Smoked chicken breast</v>
       </c>
       <c r="C45">
         <v>120</v>
       </c>
       <c r="D45" t="str">
-        <v>Egg noodles</v>
+        <v>No carb</v>
       </c>
       <c r="E45">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F45" t="str">
-        <v>Bok choy</v>
+        <v>Avocado &amp; mixed greens</v>
       </c>
       <c r="G45">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="H45" t="str">
-        <v>Soup style</v>
+        <v>Salad</v>
       </c>
       <c r="I45" t="str">
         <v>{}</v>
@@ -5221,28 +6621,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>lunch_dinner_tofu-edamame-ramen</v>
+        <v>lunch_dinner_chicken-red-curry-rice</v>
       </c>
       <c r="B46" t="str">
-        <v>Firm tofu</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C46">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D46" t="str">
-        <v>Egg noodles</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E46">
+        <v>80</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Red curry vegetables</v>
+      </c>
+      <c r="G46">
         <v>100</v>
       </c>
-      <c r="F46" t="str">
-        <v>Bok choy + edamame</v>
-      </c>
-      <c r="G46">
-        <v>180</v>
-      </c>
       <c r="H46" t="str">
-        <v>Soup style</v>
+        <v>Curry style</v>
       </c>
       <c r="I46" t="str">
         <v>{}</v>
@@ -5250,7 +6650,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>lunch_dinner_butter-chicken-jowar-roti</v>
+        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
       </c>
       <c r="B47" t="str">
         <v>Chicken breast</v>
@@ -5259,19 +6659,19 @@
         <v>150</v>
       </c>
       <c r="D47" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E47">
-        <v>1.5</v>
+        <v>100</v>
       </c>
       <c r="F47" t="str">
-        <v>Cauliflower</v>
+        <v>Kimchi + spinach</v>
       </c>
       <c r="G47">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H47" t="str">
-        <v>Curry style</v>
+        <v>Bowl</v>
       </c>
       <c r="I47" t="str">
         <v>{}</v>
@@ -5279,25 +6679,25 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
+        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
       </c>
       <c r="B48" t="str">
-        <v>Chicken breast</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C48">
         <v>150</v>
       </c>
       <c r="D48" t="str">
-        <v>Sweet potato</v>
+        <v>Soba noodles</v>
       </c>
       <c r="E48">
         <v>150</v>
       </c>
       <c r="F48" t="str">
-        <v>Broccoli</v>
+        <v>Bok choy</v>
       </c>
       <c r="G48">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H48" t="str">
         <v>Grilled</v>
@@ -5308,25 +6708,25 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
+        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
       </c>
       <c r="B49" t="str">
-        <v>Beef steak</v>
+        <v>Prawns</v>
       </c>
       <c r="C49">
         <v>180</v>
       </c>
       <c r="D49" t="str">
-        <v>Garlic rice</v>
+        <v>Rice noodles</v>
       </c>
       <c r="E49">
         <v>120</v>
       </c>
       <c r="F49" t="str">
-        <v>Bok choy</v>
+        <v>Edamame</v>
       </c>
       <c r="G49">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H49" t="str">
         <v>Pan-fried</v>
@@ -5337,28 +6737,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
+        <v>lunch_dinner_miso-chicken-ramen-egg</v>
       </c>
       <c r="B50" t="str">
-        <v>Paneer</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C50">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D50" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Egg noodles</v>
       </c>
       <c r="E50">
-        <v>1.5</v>
+        <v>120</v>
       </c>
       <c r="F50" t="str">
-        <v>Mixed greens salad</v>
+        <v>Bok choy</v>
       </c>
       <c r="G50">
         <v>100</v>
       </c>
       <c r="H50" t="str">
-        <v>Tandoori</v>
+        <v>Soup style</v>
       </c>
       <c r="I50" t="str">
         <v>{}</v>
@@ -5366,28 +6766,28 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
+        <v>lunch_dinner_tofu-edamame-ramen</v>
       </c>
       <c r="B51" t="str">
-        <v>Grilled salmon</v>
+        <v>Firm tofu</v>
       </c>
       <c r="C51">
         <v>180</v>
       </c>
       <c r="D51" t="str">
-        <v>Sweet potato</v>
+        <v>Egg noodles</v>
       </c>
       <c r="E51">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F51" t="str">
-        <v>Sautéed spinach</v>
+        <v>Bok choy + edamame</v>
       </c>
       <c r="G51">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H51" t="str">
-        <v>Grilled</v>
+        <v>Soup style</v>
       </c>
       <c r="I51" t="str">
         <v>{}</v>
@@ -5395,7 +6795,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>lunch_dinner_chicken-biryani-raita</v>
+        <v>lunch_dinner_butter-chicken-jowar-roti</v>
       </c>
       <c r="B52" t="str">
         <v>Chicken breast</v>
@@ -5404,16 +6804,16 @@
         <v>150</v>
       </c>
       <c r="D52" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E52">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="F52" t="str">
-        <v/>
-      </c>
-      <c r="G52" t="str">
-        <v/>
+        <v>Cauliflower</v>
+      </c>
+      <c r="G52">
+        <v>100</v>
       </c>
       <c r="H52" t="str">
         <v>Curry style</v>
@@ -5424,28 +6824,28 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>lunch_dinner_fish-moilee-rice</v>
+        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
       </c>
       <c r="B53" t="str">
-        <v>Fish fillet</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C53">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D53" t="str">
-        <v>Cooked rice</v>
+        <v>Sweet potato</v>
       </c>
       <c r="E53">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F53" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Broccoli</v>
       </c>
       <c r="G53">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="H53" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I53" t="str">
         <v>{}</v>
@@ -5453,28 +6853,28 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
+        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
       </c>
       <c r="B54" t="str">
-        <v>Eggs (whole)</v>
+        <v>Beef steak</v>
       </c>
       <c r="C54">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D54" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Garlic rice</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F54" t="str">
-        <v>Dal</v>
+        <v>Bok choy</v>
       </c>
       <c r="G54">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H54" t="str">
-        <v>Curry style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I54" t="str">
         <v>{}</v>
@@ -5482,28 +6882,28 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>lunch_dinner_chicken-shawarma-bowl</v>
+        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
       </c>
       <c r="B55" t="str">
-        <v>Chicken breast</v>
+        <v>Paneer</v>
       </c>
       <c r="C55">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D55" t="str">
-        <v>Flatbread</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F55" t="str">
-        <v>Salad + hummus</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G55">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="H55" t="str">
-        <v>Bowl</v>
+        <v>Tandoori</v>
       </c>
       <c r="I55" t="str">
         <v>{}</v>
@@ -5511,28 +6911,28 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>lunch_dinner_prawn-curry-rice</v>
+        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
       </c>
       <c r="B56" t="str">
-        <v>Prawns</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C56">
         <v>180</v>
       </c>
       <c r="D56" t="str">
-        <v>Cooked rice</v>
+        <v>Sweet potato</v>
       </c>
       <c r="E56">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="F56" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Sautéed spinach</v>
       </c>
       <c r="G56">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="H56" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I56" t="str">
         <v>{}</v>
@@ -5540,28 +6940,28 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
+        <v>lunch_dinner_chicken-biryani-raita</v>
       </c>
       <c r="B57" t="str">
-        <v>Chicken keema</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C57">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D57" t="str">
-        <v>Spaghetti</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E57">
         <v>150</v>
       </c>
       <c r="F57" t="str">
-        <v>Mixed greens salad</v>
-      </c>
-      <c r="G57">
-        <v>100</v>
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
       </c>
       <c r="H57" t="str">
-        <v>Pan-fried</v>
+        <v>Curry style</v>
       </c>
       <c r="I57" t="str">
         <v>{}</v>
@@ -5569,25 +6969,25 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>lunch_dinner_rajma-paneer-bowl</v>
+        <v>lunch_dinner_fish-moilee-rice</v>
       </c>
       <c r="B58" t="str">
-        <v>Paneer + rajma</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C58">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="D58" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F58" t="str">
-        <v/>
-      </c>
-      <c r="G58" t="str">
-        <v/>
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G58">
+        <v>80</v>
       </c>
       <c r="H58" t="str">
         <v>Curry style</v>
@@ -5598,28 +6998,28 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
       </c>
       <c r="B59" t="str">
-        <v>Plant Shake</v>
+        <v>Eggs (whole)</v>
       </c>
       <c r="C59">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="D59" t="str">
-        <v>Mixed Fruit</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E59">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>Almonds</v>
+        <v>Dal</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="H59" t="str">
-        <v>Snack</v>
+        <v>Curry style</v>
       </c>
       <c r="I59" t="str">
         <v>{}</v>
@@ -5627,28 +7027,28 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>lunch_dinner_chicken-shawarma-bowl</v>
       </c>
       <c r="B60" t="str">
-        <v>Plant Shake</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C60">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="D60" t="str">
-        <v>Chaat &amp; Bhel</v>
+        <v>Flatbread</v>
       </c>
       <c r="E60">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="F60" t="str">
-        <v/>
-      </c>
-      <c r="G60" t="str">
-        <v/>
+        <v>Salad + hummus</v>
+      </c>
+      <c r="G60">
+        <v>180</v>
       </c>
       <c r="H60" t="str">
-        <v>Street Food Twist</v>
+        <v>Bowl</v>
       </c>
       <c r="I60" t="str">
         <v>{}</v>
@@ -5656,28 +7056,28 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>lunch_dinner_prawn-curry-rice</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Prawns</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D61" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F61" t="str">
-        <v/>
-      </c>
-      <c r="G61" t="str">
-        <v/>
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G61">
+        <v>70</v>
       </c>
       <c r="H61" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I61" t="str">
         <v>{}</v>
@@ -5685,28 +7085,28 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Chicken keema</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D62" t="str">
-        <v>No carb</v>
+        <v>Spaghetti</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F62" t="str">
-        <v/>
-      </c>
-      <c r="G62" t="str">
-        <v/>
+        <v>Mixed greens salad</v>
+      </c>
+      <c r="G62">
+        <v>100</v>
       </c>
       <c r="H62" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I62" t="str">
         <v>{}</v>
@@ -5714,13 +7114,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_rajma-paneer-bowl</v>
       </c>
       <c r="B63" t="str">
-        <v>Mixed nuts &amp; seeds</v>
+        <v>Paneer + rajma</v>
       </c>
       <c r="C63">
-        <v>30</v>
+        <v>260</v>
       </c>
       <c r="D63" t="str">
         <v>No carb</v>
@@ -5735,7 +7135,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Raw</v>
+        <v>Curry style</v>
       </c>
       <c r="I63" t="str">
         <v>{}</v>
@@ -5743,28 +7143,28 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>lunch_dinner_palak-paneer-jowar-roti</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Paneer</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D64" t="str">
-        <v>Sweet potato</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E64">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F64" t="str">
-        <v/>
-      </c>
-      <c r="G64" t="str">
-        <v/>
+        <v>Spinach</v>
+      </c>
+      <c r="G64">
+        <v>200</v>
       </c>
       <c r="H64" t="str">
-        <v>Chaat</v>
+        <v>Curry style</v>
       </c>
       <c r="I64" t="str">
         <v>{}</v>
@@ -5772,10 +7172,10 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>lunch_dinner_achari-paneer-tikka-dal-salad</v>
       </c>
       <c r="B65" t="str">
-        <v>Kaala chana</v>
+        <v>Paneer</v>
       </c>
       <c r="C65">
         <v>150</v>
@@ -5787,13 +7187,13 @@
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v/>
-      </c>
-      <c r="G65" t="str">
-        <v/>
+        <v>Dal + salad</v>
+      </c>
+      <c r="G65">
+        <v>250</v>
       </c>
       <c r="H65" t="str">
-        <v>Chaat</v>
+        <v>Tandoori</v>
       </c>
       <c r="I65" t="str">
         <v>{}</v>
@@ -5801,28 +7201,28 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>lunch_dinner_soya-keema-curry-jowar-roti</v>
       </c>
       <c r="B66" t="str">
+        <v>Soya chunks (minced)</v>
+      </c>
+      <c r="C66">
+        <v>70</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Jowar roti (millet)</v>
+      </c>
+      <c r="E66">
+        <v>30</v>
+      </c>
+      <c r="F66" t="str">
         <v/>
       </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66" t="str">
-        <v>Whole wheat toast</v>
-      </c>
-      <c r="E66">
-        <v>1</v>
-      </c>
-      <c r="F66" t="str">
-        <v>Avocado</v>
-      </c>
-      <c r="G66">
-        <v>50</v>
+      <c r="G66" t="str">
+        <v/>
       </c>
       <c r="H66" t="str">
-        <v>Toast</v>
+        <v>Curry style</v>
       </c>
       <c r="I66" t="str">
         <v>{}</v>
@@ -5830,13 +7230,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+        <v>lunch_dinner_chole-paneer-bowl-salad</v>
       </c>
       <c r="B67" t="str">
-        <v>Eggs (whole)</v>
+        <v>Paneer + chole</v>
       </c>
       <c r="C67">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="D67" t="str">
         <v>No carb</v>
@@ -5845,13 +7245,13 @@
         <v>0</v>
       </c>
       <c r="F67" t="str">
-        <v>Raw vegetable sticks</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G67">
         <v>100</v>
       </c>
       <c r="H67" t="str">
-        <v>Snack</v>
+        <v>Bowl</v>
       </c>
       <c r="I67" t="str">
         <v>{}</v>
@@ -5859,28 +7259,28 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>snack_edamame-sea-salt</v>
+        <v>lunch_dinner_kadai-chicken-jowar-roti</v>
       </c>
       <c r="B68" t="str">
-        <v>Edamame</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C68">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D68" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F68" t="str">
-        <v/>
-      </c>
-      <c r="G68" t="str">
-        <v/>
+        <v>Capsicum + salad</v>
+      </c>
+      <c r="G68">
+        <v>80</v>
       </c>
       <c r="H68" t="str">
-        <v>Steamed</v>
+        <v>Curry style</v>
       </c>
       <c r="I68" t="str">
         <v>{}</v>
@@ -5888,25 +7288,25 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>snack_paneer-tikka-skewers</v>
+        <v>lunch_dinner_tandoori-fish-tikka-veg-roti</v>
       </c>
       <c r="B69" t="str">
-        <v>Paneer</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C69">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="D69" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F69" t="str">
-        <v>Mixed greens</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G69">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H69" t="str">
         <v>Tandoori</v>
@@ -5917,36 +7317,848 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>snack_overnight-oats-whey-bowl</v>
+        <v>lunch_dinner_chicken-keema-matar-jowar-roti</v>
       </c>
       <c r="B70" t="str">
-        <v>Milk</v>
+        <v>Chicken keema</v>
       </c>
       <c r="C70">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D70" t="str">
-        <v>Rolled oats</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E70">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F70" t="str">
-        <v>Mixed berries</v>
+        <v>Peas / edamame</v>
       </c>
       <c r="G70">
         <v>60</v>
       </c>
       <c r="H70" t="str">
+        <v>Curry style</v>
+      </c>
+      <c r="I70" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>lunch_dinner_beef-bulgogi-bowl</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Beef steak (lean sirloin)</v>
+      </c>
+      <c r="C71">
+        <v>150</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Cooked rice</v>
+      </c>
+      <c r="E71">
+        <v>100</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Kimchi + spinach</v>
+      </c>
+      <c r="G71">
+        <v>180</v>
+      </c>
+      <c r="H71" t="str">
         <v>Bowl</v>
       </c>
-      <c r="I70" t="str">
+      <c r="I71" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>lunch_dinner_tofu-veg-bibimbap</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Firm tofu + egg</v>
+      </c>
+      <c r="C72">
+        <v>250</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Cooked rice</v>
+      </c>
+      <c r="E72">
+        <v>90</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Kimchi + spinach namul</v>
+      </c>
+      <c r="G72">
+        <v>180</v>
+      </c>
+      <c r="H72" t="str">
+        <v>Bowl</v>
+      </c>
+      <c r="I72" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>lunch_dinner_oyakodon-side-salad</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Chicken breast + egg</v>
+      </c>
+      <c r="C73">
+        <v>240</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Cooked rice</v>
+      </c>
+      <c r="E73">
+        <v>120</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Side salad</v>
+      </c>
+      <c r="G73">
+        <v>80</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Bowl</v>
+      </c>
+      <c r="I73" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>lunch_dinner_dubu-jorim-rice-kimchi</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Firm tofu</v>
+      </c>
+      <c r="C74">
+        <v>220</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Cooked rice</v>
+      </c>
+      <c r="E74">
+        <v>90</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Kimchi</v>
+      </c>
+      <c r="G74">
+        <v>100</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Curry style</v>
+      </c>
+      <c r="I74" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>lunch_dinner_home-style-tofu-chicken-stir-fry</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Chicken breast + tofu</v>
+      </c>
+      <c r="C75">
+        <v>240</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Cooked rice</v>
+      </c>
+      <c r="E75">
+        <v>80</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Broccoli</v>
+      </c>
+      <c r="G75">
+        <v>150</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Pan-fried</v>
+      </c>
+      <c r="I75" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>lunch_dinner_vietnamese-lemongrass-chicken-bowl</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Chicken breast</v>
+      </c>
+      <c r="C76">
+        <v>170</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Rice noodles</v>
+      </c>
+      <c r="E76">
+        <v>100</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Herb salad + pickles</v>
+      </c>
+      <c r="G76">
+        <v>170</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Bowl</v>
+      </c>
+      <c r="I76" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>lunch_dinner_cantonese-steamed-fish-edamame</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Fish fillet</v>
+      </c>
+      <c r="C77">
+        <v>200</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Cooked rice</v>
+      </c>
+      <c r="E77">
+        <v>90</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Bok choy + edamame</v>
+      </c>
+      <c r="G77">
+        <v>230</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Steamed</v>
+      </c>
+      <c r="I77" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>lunch_dinner_chicken-bulgogi-bowl</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Chicken breast</v>
+      </c>
+      <c r="C78">
+        <v>180</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Cooked rice</v>
+      </c>
+      <c r="E78">
+        <v>100</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Kimchi + bok choy</v>
+      </c>
+      <c r="G78">
+        <v>180</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Bowl</v>
+      </c>
+      <c r="I78" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>lunch_dinner_chicken-souvlaki-tzatziki-greek-salad</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Chicken breast</v>
+      </c>
+      <c r="C79">
+        <v>180</v>
+      </c>
+      <c r="D79" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Greek salad + tzatziki</v>
+      </c>
+      <c r="G79">
+        <v>220</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Grilled</v>
+      </c>
+      <c r="I79" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>lunch_dinner_baked-feta-chickpea-traybake</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Feta + chickpeas</v>
+      </c>
+      <c r="C80">
+        <v>220</v>
+      </c>
+      <c r="D80" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Roast vegetables + greens</v>
+      </c>
+      <c r="G80">
+        <v>100</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Plate</v>
+      </c>
+      <c r="I80" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>lunch_dinner_tuna-nicoise-salad</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Tuna + egg</v>
+      </c>
+      <c r="C81">
+        <v>250</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Sweet potato</v>
+      </c>
+      <c r="E81">
+        <v>80</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Salad + olives</v>
+      </c>
+      <c r="G81">
+        <v>180</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Salad</v>
+      </c>
+      <c r="I81" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>lunch_dinner_halloumi-roasted-veg-quinoa-bowl</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Halloumi</v>
+      </c>
+      <c r="C82">
+        <v>100</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Quinoa</v>
+      </c>
+      <c r="E82">
+        <v>120</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Roast broccoli</v>
+      </c>
+      <c r="G82">
+        <v>120</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Bowl</v>
+      </c>
+      <c r="I82" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>lunch_dinner_chicken-white-bean-stew</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Chicken breast + white beans</v>
+      </c>
+      <c r="C83">
+        <v>270</v>
+      </c>
+      <c r="D83" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Spinach + tomato</v>
+      </c>
+      <c r="G83">
+        <v>140</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Soup style</v>
+      </c>
+      <c r="I83" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>lunch_dinner_chickpea-pasta-tuna-tomato</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Tuna</v>
+      </c>
+      <c r="C84">
+        <v>120</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Chickpea pasta</v>
+      </c>
+      <c r="E84">
+        <v>155</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Arrabbiata + side salad</v>
+      </c>
+      <c r="G84">
+        <v>120</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Plate</v>
+      </c>
+      <c r="I84" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>lunch_dinner_chicken-ricotta-carbonara-style-spaghetti</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Chicken breast + ricotta</v>
+      </c>
+      <c r="C85">
+        <v>180</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Spaghetti</v>
+      </c>
+      <c r="E85">
+        <v>150</v>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v>Plate</v>
+      </c>
+      <c r="I85" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>lunch_dinner_mackerel-quinoa-salad</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Mackerel</v>
+      </c>
+      <c r="C86">
+        <v>120</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Quinoa</v>
+      </c>
+      <c r="E86">
+        <v>120</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Salad + avocado</v>
+      </c>
+      <c r="G86">
+        <v>160</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Salad</v>
+      </c>
+      <c r="I86" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>snack_fruit-almonds-plant-shake</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Plant Shake</v>
+      </c>
+      <c r="C87">
+        <v>25</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Mixed Fruit</v>
+      </c>
+      <c r="E87">
+        <v>100</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Almonds</v>
+      </c>
+      <c r="G87">
+        <v>5</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Snack</v>
+      </c>
+      <c r="I87" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>snack_chaat-bhel-protein-shake</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Plant Shake</v>
+      </c>
+      <c r="C88">
+        <v>25</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Chaat &amp; Bhel</v>
+      </c>
+      <c r="E88">
+        <v>150</v>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v>Street Food Twist</v>
+      </c>
+      <c r="I88" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>snack_greek-yogurt-berry-bowl</v>
+      </c>
+      <c r="B89" t="str">
+        <v/>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v>Grilled</v>
+      </c>
+      <c r="I89" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+      </c>
+      <c r="B90" t="str">
+        <v/>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v>Grilled</v>
+      </c>
+      <c r="I90" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Mixed nuts &amp; seeds</v>
+      </c>
+      <c r="C91">
+        <v>30</v>
+      </c>
+      <c r="D91" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="I91" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B92" t="str">
+        <v/>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Sweet potato</v>
+      </c>
+      <c r="E92">
+        <v>150</v>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I92" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Kaala chana</v>
+      </c>
+      <c r="C93">
+        <v>150</v>
+      </c>
+      <c r="D93" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I93" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Whole wheat toast</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Avocado</v>
+      </c>
+      <c r="G94">
+        <v>50</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Toast</v>
+      </c>
+      <c r="I94" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Eggs (whole)</v>
+      </c>
+      <c r="C95">
+        <v>100</v>
+      </c>
+      <c r="D95" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Raw vegetable sticks</v>
+      </c>
+      <c r="G95">
+        <v>100</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Snack</v>
+      </c>
+      <c r="I95" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>snack_edamame-sea-salt</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Edamame</v>
+      </c>
+      <c r="C96">
+        <v>150</v>
+      </c>
+      <c r="D96" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v>Steamed</v>
+      </c>
+      <c r="I96" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>snack_paneer-tikka-skewers</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Paneer</v>
+      </c>
+      <c r="C97">
+        <v>80</v>
+      </c>
+      <c r="D97" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Mixed greens</v>
+      </c>
+      <c r="G97">
+        <v>60</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Tandoori</v>
+      </c>
+      <c r="I97" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>snack_overnight-oats-whey-bowl</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Milk</v>
+      </c>
+      <c r="C98">
+        <v>150</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Rolled oats</v>
+      </c>
+      <c r="E98">
+        <v>25</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Mixed berries</v>
+      </c>
+      <c r="G98">
+        <v>60</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Bowl</v>
+      </c>
+      <c r="I98" t="str">
         <v>{}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I98"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/exports/meal_database_architecture_v1.xlsx
+++ b/exports/meal_database_architecture_v1.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P98"/>
+  <dimension ref="A1:P113"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1155,40 +1155,40 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>breakfast_paneer-egg-white-bhurji-toast</v>
+        <v>breakfast_scrambled-egg-sandwich</v>
       </c>
       <c r="B16" t="str">
         <v>breakfast</v>
       </c>
       <c r="C16" t="str">
-        <v>Paneer &amp; egg-white bhurji + toast</v>
+        <v>Scrambled egg sandwich</v>
       </c>
       <c r="D16" t="str">
-        <v>Paneer &amp; Egg-White Bhurji</v>
+        <v>Scrambled Egg Sandwich</v>
       </c>
       <c r="E16" t="str">
-        <v>Paneer &amp; egg-white bhurji + toast</v>
+        <v>Scrambled egg sandwich</v>
       </c>
       <c r="F16" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G16">
-        <v>556</v>
+        <v>491</v>
       </c>
       <c r="H16">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="I16">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J16">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K16" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L16" t="str">
-        <v>assumptions_v2026_08_03</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M16" t="str">
         <v>seed_v1</v>
@@ -1197,48 +1197,48 @@
         <v>1</v>
       </c>
       <c r="O16" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"toast","effort":"low","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"sandwich","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P16" t="str">
-        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"low","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":548,"delta_kcal":8,"tolerance_kcal":111.2},"issues":[]}}</v>
+        <v>{"macros_p":33,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"sandwich","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":482,"delta_kcal":9,"tolerance_kcal":98.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>breakfast_anda-bhurji-toast</v>
+        <v>breakfast_acai-bowl-protein-boosted</v>
       </c>
       <c r="B17" t="str">
         <v>breakfast</v>
       </c>
       <c r="C17" t="str">
-        <v>Anda bhurji + toast</v>
+        <v>Acai bowl (protein-boosted)</v>
       </c>
       <c r="D17" t="str">
-        <v>Anda bhurji + toast</v>
+        <v>Acai Bowl (Protein-Boosted)</v>
       </c>
       <c r="E17" t="str">
-        <v>Anda bhurji + toast</v>
+        <v>Acai bowl (protein-boosted)</v>
       </c>
       <c r="F17" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G17">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="H17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I17">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J17">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K17" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L17" t="str">
-        <v>assumptions_v2026_08_03</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M17" t="str">
         <v>seed_v1</v>
@@ -1247,42 +1247,42 @@
         <v>1</v>
       </c>
       <c r="O17" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"toast","effort":"low","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"low","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P17" t="str">
-        <v>{"macros_p":38,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"low","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":474,"delta_kcal":16,"tolerance_kcal":98},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":470,"delta_kcal":13,"tolerance_kcal":91.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>breakfast_sardines-toast-avocado</v>
+        <v>breakfast_paneer-egg-white-bhurji-toast</v>
       </c>
       <c r="B18" t="str">
         <v>breakfast</v>
       </c>
       <c r="C18" t="str">
-        <v>Sardines on toast + avocado</v>
+        <v>Paneer &amp; egg-white bhurji + toast</v>
       </c>
       <c r="D18" t="str">
-        <v>Sardines on Toast + Avocado</v>
+        <v>Paneer &amp; Egg-White Bhurji</v>
       </c>
       <c r="E18" t="str">
-        <v>Sardines on toast + avocado</v>
+        <v>Paneer &amp; egg-white bhurji + toast</v>
       </c>
       <c r="F18" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G18">
-        <v>494</v>
+        <v>556</v>
       </c>
       <c r="H18">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I18">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K18" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1297,42 +1297,42 @@
         <v>1</v>
       </c>
       <c r="O18" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"toast","effort":"low","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P18" t="str">
-        <v>{"macros_p":39,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":487,"delta_kcal":7,"tolerance_kcal":98.8},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"low","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":548,"delta_kcal":8,"tolerance_kcal":111.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>breakfast_shakshuka-feta</v>
+        <v>breakfast_anda-bhurji-toast</v>
       </c>
       <c r="B19" t="str">
         <v>breakfast</v>
       </c>
       <c r="C19" t="str">
-        <v>Shakshuka with feta</v>
+        <v>Anda bhurji + toast</v>
       </c>
       <c r="D19" t="str">
-        <v>Shakshuka with feta</v>
+        <v>Anda bhurji + toast</v>
       </c>
       <c r="E19" t="str">
-        <v>Shakshuka with feta</v>
+        <v>Anda bhurji + toast</v>
       </c>
       <c r="F19" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G19">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="H19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I19">
+        <v>31</v>
+      </c>
+      <c r="J19">
         <v>22</v>
-      </c>
-      <c r="J19">
-        <v>28</v>
       </c>
       <c r="K19" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1347,27 +1347,27 @@
         <v>1</v>
       </c>
       <c r="O19" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"toast","effort":"low","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P19" t="str">
-        <v>{"macros_p":40,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":500,"delta_kcal":4,"tolerance_kcal":100.8},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"low","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":474,"delta_kcal":16,"tolerance_kcal":98},"issues":[]}}</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>breakfast_cottage-cheese-smoked-salmon-bowl</v>
+        <v>breakfast_sardines-toast-avocado</v>
       </c>
       <c r="B20" t="str">
         <v>breakfast</v>
       </c>
       <c r="C20" t="str">
-        <v>Cottage cheese &amp; smoked salmon bowl</v>
+        <v>Sardines on toast + avocado</v>
       </c>
       <c r="D20" t="str">
-        <v>Cottage Cheese &amp; Smoked Salmon</v>
+        <v>Sardines on Toast + Avocado</v>
       </c>
       <c r="E20" t="str">
-        <v>Cottage cheese &amp; smoked salmon bowl</v>
+        <v>Sardines on toast + avocado</v>
       </c>
       <c r="F20" t="str">
         <v>Continental</v>
@@ -1376,13 +1376,13 @@
         <v>494</v>
       </c>
       <c r="H20">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I20">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J20">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K20" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1397,48 +1397,48 @@
         <v>1</v>
       </c>
       <c r="O20" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P20" t="str">
-        <v>{"macros_p":44,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":491,"delta_kcal":3,"tolerance_kcal":98.8},"issues":[]}}</v>
+        <v>{"macros_p":39,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":487,"delta_kcal":7,"tolerance_kcal":98.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti</v>
+        <v>breakfast_shakshuka-feta</v>
       </c>
       <c r="B21" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C21" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Shakshuka with feta</v>
       </c>
       <c r="D21" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Shakshuka with feta</v>
       </c>
       <c r="E21" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Shakshuka with feta</v>
       </c>
       <c r="F21" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G21">
-        <v>702</v>
+        <v>504</v>
       </c>
       <c r="H21">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I21">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="J21">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K21" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L21" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M21" t="str">
         <v>seed_v1</v>
@@ -1447,48 +1447,48 @@
         <v>1</v>
       </c>
       <c r="O21" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P21" t="str">
-        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":676,"delta_kcal":26,"tolerance_kcal":140.4},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":500,"delta_kcal":4,"tolerance_kcal":100.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
+        <v>breakfast_cottage-cheese-smoked-salmon-bowl</v>
       </c>
       <c r="B22" t="str">
-        <v>lunch_dinner</v>
+        <v>breakfast</v>
       </c>
       <c r="C22" t="str">
-        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
+        <v>Cottage cheese &amp; smoked salmon bowl</v>
       </c>
       <c r="D22" t="str">
-        <v>Salmon + Veg + Aglio Olio</v>
+        <v>Cottage Cheese &amp; Smoked Salmon</v>
       </c>
       <c r="E22" t="str">
-        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
+        <v>Cottage cheese &amp; smoked salmon bowl</v>
       </c>
       <c r="F22" t="str">
         <v>Continental</v>
       </c>
       <c r="G22">
-        <v>669</v>
+        <v>494</v>
       </c>
       <c r="H22">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I22">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="J22">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K22" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L22" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M22" t="str">
         <v>seed_v1</v>
@@ -1497,42 +1497,42 @@
         <v>1</v>
       </c>
       <c r="O22" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"continental","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P22" t="str">
-        <v>{"macros_p":46,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":688,"delta_kcal":19,"tolerance_kcal":133.8},"issues":[]}}</v>
+        <v>{"macros_p":44,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":491,"delta_kcal":3,"tolerance_kcal":98.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lunch_dinner_rajma-chawal-raita</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti</v>
       </c>
       <c r="B23" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C23" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="D23" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="E23" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="F23" t="str">
         <v>Indian</v>
       </c>
       <c r="G23">
-        <v>482</v>
+        <v>702</v>
       </c>
       <c r="H23">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="I23">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K23" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1547,42 +1547,42 @@
         <v>1</v>
       </c>
       <c r="O23" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P23" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":482,"delta_kcal":0,"tolerance_kcal":96.4},"issues":[]}}</v>
+        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":676,"delta_kcal":26,"tolerance_kcal":140.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lunch_dinner_chole-jowar-roti-raita</v>
+        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B24" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C24" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
       </c>
       <c r="D24" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Salmon + Veg + Aglio Olio</v>
       </c>
       <c r="E24" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
       </c>
       <c r="F24" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G24">
-        <v>726</v>
+        <v>669</v>
       </c>
       <c r="H24">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I24">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="J24">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K24" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1597,42 +1597,42 @@
         <v>1</v>
       </c>
       <c r="O24" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"continental","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P24" t="str">
-        <v>{"macros_p":27,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":722,"delta_kcal":4,"tolerance_kcal":145.2},"issues":[]}}</v>
+        <v>{"macros_p":46,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":688,"delta_kcal":19,"tolerance_kcal":133.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lunch_dinner_vietnamese-chicken-pho</v>
+        <v>lunch_dinner_rajma-chawal-raita</v>
       </c>
       <c r="B25" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C25" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="D25" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="E25" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="F25" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G25">
-        <v>394</v>
+        <v>482</v>
       </c>
       <c r="H25">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="I25">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K25" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1647,42 +1647,42 @@
         <v>1</v>
       </c>
       <c r="O25" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P25" t="str">
-        <v>{"macros_p":49,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":374,"delta_kcal":20,"tolerance_kcal":78.8},"issues":[]}}</v>
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":482,"delta_kcal":0,"tolerance_kcal":96.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
+        <v>lunch_dinner_chole-jowar-roti-raita</v>
       </c>
       <c r="B26" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C26" t="str">
-        <v>Grilled steak + mixed greens salad</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="D26" t="str">
-        <v>Steak + Mixed Greens</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="E26" t="str">
-        <v>Grilled steak + mixed greens salad</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="F26" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G26">
-        <v>480</v>
+        <v>726</v>
       </c>
       <c r="H26">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>113</v>
       </c>
       <c r="J26">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K26" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1697,42 +1697,42 @@
         <v>1</v>
       </c>
       <c r="O26" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P26" t="str">
-        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":477,"delta_kcal":3,"tolerance_kcal":96},"issues":[]}}</v>
+        <v>{"macros_p":27,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":722,"delta_kcal":4,"tolerance_kcal":145.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lunch_dinner_thai-pad-krapow-rice</v>
+        <v>lunch_dinner_vietnamese-chicken-pho</v>
       </c>
       <c r="B27" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C27" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="D27" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="E27" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="F27" t="str">
         <v>Asian</v>
       </c>
       <c r="G27">
-        <v>438</v>
+        <v>394</v>
       </c>
       <c r="H27">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I27">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K27" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1747,42 +1747,42 @@
         <v>1</v>
       </c>
       <c r="O27" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P27" t="str">
-        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":422,"delta_kcal":16,"tolerance_kcal":87.6},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":374,"delta_kcal":20,"tolerance_kcal":78.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lunch_dinner_mutton-keema-jowar-roti</v>
+        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
       </c>
       <c r="B28" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C28" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Grilled steak + mixed greens salad</v>
       </c>
       <c r="D28" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Steak + Mixed Greens</v>
       </c>
       <c r="E28" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Grilled steak + mixed greens salad</v>
       </c>
       <c r="F28" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G28">
-        <v>670</v>
+        <v>480</v>
       </c>
       <c r="H28">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I28">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K28" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1797,42 +1797,42 @@
         <v>1</v>
       </c>
       <c r="O28" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P28" t="str">
-        <v>{"macros_p":34,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":654,"delta_kcal":16,"tolerance_kcal":134},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":477,"delta_kcal":3,"tolerance_kcal":96},"issues":[]}}</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
+        <v>lunch_dinner_thai-pad-krapow-rice</v>
       </c>
       <c r="B29" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C29" t="str">
-        <v>Arhar dal + rice + matar paneer</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="D29" t="str">
-        <v>Arhar Dal + Rice + Matar Paneer</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="E29" t="str">
-        <v>Arhar dal + rice + matar paneer</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="F29" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G29">
-        <v>669</v>
+        <v>438</v>
       </c>
       <c r="H29">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="I29">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="J29">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K29" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1847,42 +1847,42 @@
         <v>1</v>
       </c>
       <c r="O29" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P29" t="str">
-        <v>{"macros_p":32,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":666,"delta_kcal":3,"tolerance_kcal":133.8},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":422,"delta_kcal":16,"tolerance_kcal":87.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
+        <v>lunch_dinner_mutton-keema-jowar-roti</v>
       </c>
       <c r="B30" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C30" t="str">
-        <v>Chicken curry + jowar roti + dal</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="D30" t="str">
-        <v>Chicken Curry + Roti + Dal</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="E30" t="str">
-        <v>Chicken curry + jowar roti + dal</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="F30" t="str">
         <v>Indian</v>
       </c>
       <c r="G30">
-        <v>736</v>
+        <v>670</v>
       </c>
       <c r="H30">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="I30">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="J30">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="K30" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1897,42 +1897,42 @@
         <v>1</v>
       </c>
       <c r="O30" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P30" t="str">
-        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":709,"delta_kcal":27,"tolerance_kcal":147.2},"issues":[]}}</v>
+        <v>{"macros_p":34,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":654,"delta_kcal":16,"tolerance_kcal":134},"issues":[]}}</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
+        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
       </c>
       <c r="B31" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C31" t="str">
-        <v>Grilled fish + pumpkin salad</v>
+        <v>Arhar dal + rice + matar paneer</v>
       </c>
       <c r="D31" t="str">
-        <v>Grilled Fish + Pumpkin Salad</v>
+        <v>Arhar Dal + Rice + Matar Paneer</v>
       </c>
       <c r="E31" t="str">
-        <v>Grilled fish + pumpkin salad</v>
+        <v>Arhar dal + rice + matar paneer</v>
       </c>
       <c r="F31" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G31">
-        <v>308</v>
+        <v>669</v>
       </c>
       <c r="H31">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I31">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="J31">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K31" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1947,42 +1947,42 @@
         <v>1</v>
       </c>
       <c r="O31" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P31" t="str">
-        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":305,"delta_kcal":3,"tolerance_kcal":61.6},"issues":[]}}</v>
+        <v>{"macros_p":32,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":666,"delta_kcal":3,"tolerance_kcal":133.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
       </c>
       <c r="B32" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C32" t="str">
-        <v>Grilled salmon + sauteed veg + garlic rice</v>
+        <v>Chicken curry + jowar roti + dal</v>
       </c>
       <c r="D32" t="str">
-        <v>Salmon + Veg + Garlic Rice</v>
+        <v>Chicken Curry + Roti + Dal</v>
       </c>
       <c r="E32" t="str">
-        <v>Grilled salmon + sauteed veg + garlic rice</v>
+        <v>Chicken curry + jowar roti + dal</v>
       </c>
       <c r="F32" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G32">
-        <v>514</v>
+        <v>736</v>
       </c>
       <c r="H32">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I32">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="J32">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K32" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1997,42 +1997,42 @@
         <v>1</v>
       </c>
       <c r="O32" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P32" t="str">
-        <v>{"macros_p":40,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":11,"tolerance_kcal":102.8},"issues":[]}}</v>
+        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":709,"delta_kcal":27,"tolerance_kcal":147.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
+        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
       </c>
       <c r="B33" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C33" t="str">
-        <v>Chicken soup + smoked salmon salad</v>
+        <v>Grilled fish + pumpkin salad</v>
       </c>
       <c r="D33" t="str">
-        <v>Chicken Soup + Salmon Salad</v>
+        <v>Grilled Fish + Pumpkin Salad</v>
       </c>
       <c r="E33" t="str">
-        <v>Chicken soup + smoked salmon salad</v>
+        <v>Grilled fish + pumpkin salad</v>
       </c>
       <c r="F33" t="str">
         <v>Continental</v>
       </c>
       <c r="G33">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="H33">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K33" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2047,42 +2047,42 @@
         <v>1</v>
       </c>
       <c r="O33" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"low","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P33" t="str">
-        <v>{"macros_p":50,"protein_family":"mixed","meal_weight_class":"light","carb_level":"low","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":284,"delta_kcal":18,"tolerance_kcal":60.4},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":305,"delta_kcal":3,"tolerance_kcal":61.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
+        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
       </c>
       <c r="B34" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C34" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Grilled salmon + sauteed veg + garlic rice</v>
       </c>
       <c r="D34" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Salmon + Veg + Garlic Rice</v>
       </c>
       <c r="E34" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Grilled salmon + sauteed veg + garlic rice</v>
       </c>
       <c r="F34" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G34">
-        <v>628</v>
+        <v>514</v>
       </c>
       <c r="H34">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I34">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J34">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K34" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2097,42 +2097,42 @@
         <v>1</v>
       </c>
       <c r="O34" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P34" t="str">
-        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":631,"delta_kcal":3,"tolerance_kcal":125.6},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":11,"tolerance_kcal":102.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
+        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
       </c>
       <c r="B35" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C35" t="str">
-        <v>Pork chop + pumpkin salad</v>
+        <v>Chicken soup + smoked salmon salad</v>
       </c>
       <c r="D35" t="str">
-        <v>Pork Chop + Pumpkin Salad</v>
+        <v>Chicken Soup + Salmon Salad</v>
       </c>
       <c r="E35" t="str">
-        <v>Pork chop + pumpkin salad</v>
+        <v>Chicken soup + smoked salmon salad</v>
       </c>
       <c r="F35" t="str">
         <v>Continental</v>
       </c>
       <c r="G35">
-        <v>562</v>
+        <v>302</v>
       </c>
       <c r="H35">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I35">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="J35">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="K35" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2147,42 +2147,42 @@
         <v>1</v>
       </c>
       <c r="O35" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"low","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P35" t="str">
-        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":13,"tolerance_kcal":112.4},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"mixed","meal_weight_class":"light","carb_level":"low","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":284,"delta_kcal":18,"tolerance_kcal":60.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
+        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
       </c>
       <c r="B36" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C36" t="str">
-        <v>Pork chop + mixed greens salad</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="D36" t="str">
-        <v>Pork Chop + Mixed Greens</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="E36" t="str">
-        <v>Pork chop + mixed greens salad</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="F36" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G36">
-        <v>449</v>
+        <v>628</v>
       </c>
       <c r="H36">
+        <v>36</v>
+      </c>
+      <c r="I36">
         <v>43</v>
       </c>
-      <c r="I36">
-        <v>5</v>
-      </c>
       <c r="J36">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K36" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2197,42 +2197,42 @@
         <v>1</v>
       </c>
       <c r="O36" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P36" t="str">
-        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":435,"delta_kcal":14,"tolerance_kcal":89.8},"issues":[]}}</v>
+        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":631,"delta_kcal":3,"tolerance_kcal":125.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
+        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
       </c>
       <c r="B37" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C37" t="str">
-        <v>Tandoori chicken + smoked chicken + avocado salad</v>
+        <v>Pork chop + pumpkin salad</v>
       </c>
       <c r="D37" t="str">
-        <v>Tandoori Chicken + Smoked Chicken Salad</v>
+        <v>Pork Chop + Pumpkin Salad</v>
       </c>
       <c r="E37" t="str">
-        <v>Tandoori chicken + smoked chicken + avocado salad</v>
+        <v>Pork chop + pumpkin salad</v>
       </c>
       <c r="F37" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G37">
-        <v>366</v>
+        <v>562</v>
       </c>
       <c r="H37">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J37">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="K37" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2247,42 +2247,42 @@
         <v>1</v>
       </c>
       <c r="O37" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P37" t="str">
-        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":347,"delta_kcal":19,"tolerance_kcal":73.2},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":13,"tolerance_kcal":112.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
       </c>
       <c r="B38" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C38" t="str">
-        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
+        <v>Pork chop + mixed greens salad</v>
       </c>
       <c r="D38" t="str">
-        <v>Broccoli Soup + Fish + Aglio Olio</v>
+        <v>Pork Chop + Mixed Greens</v>
       </c>
       <c r="E38" t="str">
-        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
+        <v>Pork chop + mixed greens salad</v>
       </c>
       <c r="F38" t="str">
         <v>Continental</v>
       </c>
       <c r="G38">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="H38">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I38">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K38" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2297,42 +2297,42 @@
         <v>1</v>
       </c>
       <c r="O38" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P38" t="str">
-        <v>{"macros_p":45,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":448,"delta_kcal":15,"tolerance_kcal":86.6},"issues":[]}}</v>
+        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":435,"delta_kcal":14,"tolerance_kcal":89.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
+        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
       </c>
       <c r="B39" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C39" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Tandoori chicken + smoked chicken + avocado salad</v>
       </c>
       <c r="D39" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Tandoori Chicken + Smoked Chicken Salad</v>
       </c>
       <c r="E39" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Tandoori chicken + smoked chicken + avocado salad</v>
       </c>
       <c r="F39" t="str">
         <v>Indian</v>
       </c>
       <c r="G39">
-        <v>771</v>
+        <v>366</v>
       </c>
       <c r="H39">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="I39">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K39" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2347,42 +2347,42 @@
         <v>1</v>
       </c>
       <c r="O39" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P39" t="str">
-        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":755,"delta_kcal":16,"tolerance_kcal":154.2},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":347,"delta_kcal":19,"tolerance_kcal":73.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>lunch_dinner_kofta-dal-jowar-roti</v>
+        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B40" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C40" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
       </c>
       <c r="D40" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Broccoli Soup + Fish + Aglio Olio</v>
       </c>
       <c r="E40" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
       </c>
       <c r="F40" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G40">
-        <v>769</v>
+        <v>433</v>
       </c>
       <c r="H40">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="I40">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="J40">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K40" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2397,42 +2397,42 @@
         <v>1</v>
       </c>
       <c r="O40" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P40" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":746,"delta_kcal":23,"tolerance_kcal":153.8},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":448,"delta_kcal":15,"tolerance_kcal":86.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
+        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
       </c>
       <c r="B41" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C41" t="str">
-        <v>Kababs + dal + gobi + jowar roti</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="D41" t="str">
-        <v>Kababs + Dal + Gobi + Roti</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="E41" t="str">
-        <v>Kababs + dal + gobi + jowar roti</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="F41" t="str">
         <v>Indian</v>
       </c>
       <c r="G41">
-        <v>823</v>
+        <v>771</v>
       </c>
       <c r="H41">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I41">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J41">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K41" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2447,42 +2447,42 @@
         <v>1</v>
       </c>
       <c r="O41" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P41" t="str">
-        <v>{"macros_p":41,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":813,"delta_kcal":10,"tolerance_kcal":164.6},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":755,"delta_kcal":16,"tolerance_kcal":154.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>lunch_dinner_fish-curry-rice</v>
+        <v>lunch_dinner_kofta-dal-jowar-roti</v>
       </c>
       <c r="B42" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C42" t="str">
-        <v>Fish curry + rice</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="D42" t="str">
-        <v>Fish curry + rice</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="E42" t="str">
-        <v>Fish curry + rice</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="F42" t="str">
         <v>Indian</v>
       </c>
       <c r="G42">
-        <v>446</v>
+        <v>769</v>
       </c>
       <c r="H42">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I42">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="J42">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K42" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2497,42 +2497,42 @@
         <v>1</v>
       </c>
       <c r="O42" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
       </c>
       <c r="P42" t="str">
-        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":433,"delta_kcal":13,"tolerance_kcal":89.2},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":746,"delta_kcal":23,"tolerance_kcal":153.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
+        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
       </c>
       <c r="B43" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C43" t="str">
-        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
+        <v>Kababs + dal + gobi + jowar roti</v>
       </c>
       <c r="D43" t="str">
-        <v>Sweet Potato Curry + Kaala Chanaa + Jowar Roti</v>
+        <v>Kababs + Dal + Gobi + Roti</v>
       </c>
       <c r="E43" t="str">
-        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
+        <v>Kababs + dal + gobi + jowar roti</v>
       </c>
       <c r="F43" t="str">
         <v>Indian</v>
       </c>
       <c r="G43">
-        <v>731</v>
+        <v>823</v>
       </c>
       <c r="H43">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I43">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="J43">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="K43" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2547,42 +2547,42 @@
         <v>1</v>
       </c>
       <c r="O43" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P43" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":735,"delta_kcal":4,"tolerance_kcal":146.2},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":813,"delta_kcal":10,"tolerance_kcal":164.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
+        <v>lunch_dinner_fish-curry-rice</v>
       </c>
       <c r="B44" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C44" t="str">
-        <v>Avocado and smoked salmon salad</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="D44" t="str">
-        <v>Avocado &amp; Smoked Salmon Salad</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="E44" t="str">
-        <v>Avocado and smoked salmon salad</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="F44" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G44">
-        <v>206</v>
+        <v>446</v>
       </c>
       <c r="H44">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I44">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="J44">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K44" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2597,42 +2597,42 @@
         <v>1</v>
       </c>
       <c r="O44" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P44" t="str">
-        <v>{"macros_p":24,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":201,"delta_kcal":5,"tolerance_kcal":41.2},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":433,"delta_kcal":13,"tolerance_kcal":89.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B45" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C45" t="str">
-        <v>Avocado and smoked chicken salad</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="D45" t="str">
-        <v>Avocado &amp; Smoked Chicken Salad</v>
+        <v>Sweet Potato Curry + Kaala Chanaa + Jowar Roti</v>
       </c>
       <c r="E45" t="str">
-        <v>Avocado and smoked chicken salad</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="F45" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G45">
-        <v>244</v>
+        <v>731</v>
       </c>
       <c r="H45">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>127</v>
       </c>
       <c r="J45">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K45" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2647,42 +2647,42 @@
         <v>1</v>
       </c>
       <c r="O45" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
       </c>
       <c r="P45" t="str">
-        <v>{"macros_p":33,"protein_family":"chicken","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":237,"delta_kcal":7,"tolerance_kcal":48.8},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":735,"delta_kcal":4,"tolerance_kcal":146.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>lunch_dinner_chicken-red-curry-rice</v>
+        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
       </c>
       <c r="B46" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C46" t="str">
-        <v>Chicken red curry + rice</v>
+        <v>Avocado and smoked salmon salad</v>
       </c>
       <c r="D46" t="str">
-        <v>Chicken Red Curry + Rice</v>
+        <v>Avocado &amp; Smoked Salmon Salad</v>
       </c>
       <c r="E46" t="str">
-        <v>Chicken red curry + rice</v>
+        <v>Avocado and smoked salmon salad</v>
       </c>
       <c r="F46" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G46">
-        <v>504</v>
+        <v>206</v>
       </c>
       <c r="H46">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="I46">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J46">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K46" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2697,48 +2697,48 @@
         <v>1</v>
       </c>
       <c r="O46" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P46" t="str">
-        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":486,"delta_kcal":18,"tolerance_kcal":100.8},"issues":[]}}</v>
+        <v>{"macros_p":24,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":201,"delta_kcal":5,"tolerance_kcal":41.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
+        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
       </c>
       <c r="B47" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C47" t="str">
-        <v>Korean chicken bibimbap bowl</v>
+        <v>Avocado and smoked chicken salad</v>
       </c>
       <c r="D47" t="str">
-        <v>Chicken Bibimbap Bowl</v>
+        <v>Avocado &amp; Smoked Chicken Salad</v>
       </c>
       <c r="E47" t="str">
-        <v>Korean chicken bibimbap bowl</v>
+        <v>Avocado and smoked chicken salad</v>
       </c>
       <c r="F47" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G47">
-        <v>471</v>
+        <v>244</v>
       </c>
       <c r="H47">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I47">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="J47">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K47" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L47" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M47" t="str">
         <v>seed_v1</v>
@@ -2747,48 +2747,48 @@
         <v>1</v>
       </c>
       <c r="O47" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P47" t="str">
-        <v>{"macros_p":52,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":452,"delta_kcal":19,"tolerance_kcal":94.2},"issues":[]}}</v>
+        <v>{"macros_p":33,"protein_family":"chicken","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":237,"delta_kcal":7,"tolerance_kcal":48.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
+        <v>lunch_dinner_chicken-red-curry-rice</v>
       </c>
       <c r="B48" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C48" t="str">
-        <v>Salmon teriyaki + soba noodles</v>
+        <v>Chicken red curry + rice</v>
       </c>
       <c r="D48" t="str">
-        <v>Salmon Teriyaki + Soba</v>
+        <v>Chicken Red Curry + Rice</v>
       </c>
       <c r="E48" t="str">
-        <v>Salmon teriyaki + soba noodles</v>
+        <v>Chicken red curry + rice</v>
       </c>
       <c r="F48" t="str">
         <v>Asian</v>
       </c>
       <c r="G48">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="H48">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I48">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J48">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K48" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L48" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M48" t="str">
         <v>seed_v1</v>
@@ -2797,42 +2797,42 @@
         <v>1</v>
       </c>
       <c r="O48" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P48" t="str">
-        <v>{"macros_p":43,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":9,"tolerance_kcal":99.8},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":486,"delta_kcal":18,"tolerance_kcal":100.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
+        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
       </c>
       <c r="B49" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C49" t="str">
-        <v>Prawn stir-fry + edamame + rice noodles</v>
+        <v>Korean chicken bibimbap bowl</v>
       </c>
       <c r="D49" t="str">
-        <v>Prawn Stir-fry + Edamame</v>
+        <v>Chicken Bibimbap Bowl</v>
       </c>
       <c r="E49" t="str">
-        <v>Prawn stir-fry + edamame + rice noodles</v>
+        <v>Korean chicken bibimbap bowl</v>
       </c>
       <c r="F49" t="str">
         <v>Asian</v>
       </c>
       <c r="G49">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H49">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I49">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K49" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2847,42 +2847,42 @@
         <v>1</v>
       </c>
       <c r="O49" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P49" t="str">
-        <v>{"macros_p":54,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":467,"delta_kcal":5,"tolerance_kcal":94.4},"issues":[]}}</v>
+        <v>{"macros_p":52,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":452,"delta_kcal":19,"tolerance_kcal":94.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>lunch_dinner_miso-chicken-ramen-egg</v>
+        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
       </c>
       <c r="B50" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C50" t="str">
-        <v>Miso chicken ramen + egg</v>
+        <v>Salmon teriyaki + soba noodles</v>
       </c>
       <c r="D50" t="str">
-        <v>Miso Chicken Ramen</v>
+        <v>Salmon Teriyaki + Soba</v>
       </c>
       <c r="E50" t="str">
-        <v>Miso chicken ramen + egg</v>
+        <v>Salmon teriyaki + soba noodles</v>
       </c>
       <c r="F50" t="str">
         <v>Asian</v>
       </c>
       <c r="G50">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="H50">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="I50">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J50">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K50" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2897,42 +2897,42 @@
         <v>1</v>
       </c>
       <c r="O50" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P50" t="str">
-        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":515,"delta_kcal":12,"tolerance_kcal":105.4},"issues":[]}}</v>
+        <v>{"macros_p":43,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":9,"tolerance_kcal":99.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>lunch_dinner_tofu-edamame-ramen</v>
+        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
       </c>
       <c r="B51" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C51" t="str">
-        <v>Tofu &amp; edamame ramen</v>
+        <v>Prawn stir-fry + edamame + rice noodles</v>
       </c>
       <c r="D51" t="str">
-        <v>Tofu &amp; Edamame Ramen</v>
+        <v>Prawn Stir-fry + Edamame</v>
       </c>
       <c r="E51" t="str">
-        <v>Tofu &amp; edamame ramen</v>
+        <v>Prawn stir-fry + edamame + rice noodles</v>
       </c>
       <c r="F51" t="str">
         <v>Asian</v>
       </c>
       <c r="G51">
-        <v>565</v>
+        <v>472</v>
       </c>
       <c r="H51">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I51">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J51">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K51" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2947,42 +2947,42 @@
         <v>1</v>
       </c>
       <c r="O51" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P51" t="str">
-        <v>{"macros_p":47,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":596,"delta_kcal":31,"tolerance_kcal":113},"issues":[]}}</v>
+        <v>{"macros_p":54,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":467,"delta_kcal":5,"tolerance_kcal":94.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>lunch_dinner_butter-chicken-jowar-roti</v>
+        <v>lunch_dinner_miso-chicken-ramen-egg</v>
       </c>
       <c r="B52" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C52" t="str">
-        <v>Butter chicken + jowar roti</v>
+        <v>Miso chicken ramen + egg</v>
       </c>
       <c r="D52" t="str">
-        <v>Butter Chicken + Jowar Roti</v>
+        <v>Miso Chicken Ramen</v>
       </c>
       <c r="E52" t="str">
-        <v>Butter chicken + jowar roti</v>
+        <v>Miso chicken ramen + egg</v>
       </c>
       <c r="F52" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G52">
-        <v>635</v>
+        <v>527</v>
       </c>
       <c r="H52">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I52">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="J52">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K52" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2997,42 +2997,42 @@
         <v>1</v>
       </c>
       <c r="O52" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P52" t="str">
-        <v>{"macros_p":54,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":622,"delta_kcal":13,"tolerance_kcal":127},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":515,"delta_kcal":12,"tolerance_kcal":105.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
+        <v>lunch_dinner_tofu-edamame-ramen</v>
       </c>
       <c r="B53" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C53" t="str">
-        <v>Grilled chicken + sweet potato + broccoli</v>
+        <v>Tofu &amp; edamame ramen</v>
       </c>
       <c r="D53" t="str">
-        <v>Grilled Chicken + Sweet Potato</v>
+        <v>Tofu &amp; Edamame Ramen</v>
       </c>
       <c r="E53" t="str">
-        <v>Grilled chicken + sweet potato + broccoli</v>
+        <v>Tofu &amp; edamame ramen</v>
       </c>
       <c r="F53" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G53">
-        <v>505</v>
+        <v>565</v>
       </c>
       <c r="H53">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="I53">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J53">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K53" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3047,42 +3047,42 @@
         <v>1</v>
       </c>
       <c r="O53" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P53" t="str">
-        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":3,"tolerance_kcal":101},"issues":[]}}</v>
+        <v>{"macros_p":47,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":596,"delta_kcal":31,"tolerance_kcal":113},"issues":[]}}</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
+        <v>lunch_dinner_butter-chicken-jowar-roti</v>
       </c>
       <c r="B54" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C54" t="str">
-        <v>Pepper beef + garlic rice + greens</v>
+        <v>Butter chicken + jowar roti</v>
       </c>
       <c r="D54" t="str">
-        <v>Pepper Beef + Garlic Rice</v>
+        <v>Butter Chicken + Jowar Roti</v>
       </c>
       <c r="E54" t="str">
-        <v>Pepper beef + garlic rice + greens</v>
+        <v>Butter chicken + jowar roti</v>
       </c>
       <c r="F54" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G54">
-        <v>696</v>
+        <v>635</v>
       </c>
       <c r="H54">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I54">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="J54">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="K54" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3097,42 +3097,42 @@
         <v>1</v>
       </c>
       <c r="O54" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P54" t="str">
-        <v>{"macros_p":53,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":702,"delta_kcal":6,"tolerance_kcal":139.2},"issues":[]}}</v>
+        <v>{"macros_p":54,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":622,"delta_kcal":13,"tolerance_kcal":127},"issues":[]}}</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
+        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
       </c>
       <c r="B55" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C55" t="str">
-        <v>Paneer tikka + jowar roti + salad</v>
+        <v>Grilled chicken + sweet potato + broccoli</v>
       </c>
       <c r="D55" t="str">
-        <v>Paneer Tikka + Jowar Roti</v>
+        <v>Grilled Chicken + Sweet Potato</v>
       </c>
       <c r="E55" t="str">
-        <v>Paneer tikka + jowar roti + salad</v>
+        <v>Grilled chicken + sweet potato + broccoli</v>
       </c>
       <c r="F55" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G55">
-        <v>654</v>
+        <v>505</v>
       </c>
       <c r="H55">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I55">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J55">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K55" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3147,42 +3147,42 @@
         <v>1</v>
       </c>
       <c r="O55" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P55" t="str">
-        <v>{"macros_p":35,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":647,"delta_kcal":7,"tolerance_kcal":130.8},"issues":[]}}</v>
+        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":3,"tolerance_kcal":101},"issues":[]}}</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
+        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
       </c>
       <c r="B56" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C56" t="str">
-        <v>Grilled salmon + sweet potato + spinach</v>
+        <v>Pepper beef + garlic rice + greens</v>
       </c>
       <c r="D56" t="str">
-        <v>Salmon + Sweet Potato + Spinach</v>
+        <v>Pepper Beef + Garlic Rice</v>
       </c>
       <c r="E56" t="str">
-        <v>Grilled salmon + sweet potato + spinach</v>
+        <v>Pepper beef + garlic rice + greens</v>
       </c>
       <c r="F56" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G56">
-        <v>614</v>
+        <v>696</v>
       </c>
       <c r="H56">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I56">
+        <v>37</v>
+      </c>
+      <c r="J56">
         <v>38</v>
-      </c>
-      <c r="J56">
-        <v>30</v>
       </c>
       <c r="K56" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3197,42 +3197,42 @@
         <v>1</v>
       </c>
       <c r="O56" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P56" t="str">
-        <v>{"macros_p":48,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":614,"delta_kcal":0,"tolerance_kcal":122.8},"issues":[]}}</v>
+        <v>{"macros_p":53,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":702,"delta_kcal":6,"tolerance_kcal":139.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>lunch_dinner_chicken-biryani-raita</v>
+        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
       </c>
       <c r="B57" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C57" t="str">
-        <v>Chicken biryani + raita</v>
+        <v>Paneer tikka + jowar roti + salad</v>
       </c>
       <c r="D57" t="str">
-        <v>Chicken biryani + raita</v>
+        <v>Paneer Tikka + Jowar Roti</v>
       </c>
       <c r="E57" t="str">
-        <v>Chicken biryani + raita</v>
+        <v>Paneer tikka + jowar roti + salad</v>
       </c>
       <c r="F57" t="str">
         <v>Indian</v>
       </c>
       <c r="G57">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="H57">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="I57">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J57">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K57" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3247,42 +3247,42 @@
         <v>1</v>
       </c>
       <c r="O57" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P57" t="str">
-        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":607,"delta_kcal":22,"tolerance_kcal":125.8},"issues":[]}}</v>
+        <v>{"macros_p":35,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":647,"delta_kcal":7,"tolerance_kcal":130.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>lunch_dinner_fish-moilee-rice</v>
+        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
       </c>
       <c r="B58" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C58" t="str">
-        <v>Fish moilee + rice</v>
+        <v>Grilled salmon + sweet potato + spinach</v>
       </c>
       <c r="D58" t="str">
-        <v>Fish moilee + rice</v>
+        <v>Salmon + Sweet Potato + Spinach</v>
       </c>
       <c r="E58" t="str">
-        <v>Fish moilee + rice</v>
+        <v>Grilled salmon + sweet potato + spinach</v>
       </c>
       <c r="F58" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G58">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H58">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I58">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="J58">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K58" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3297,42 +3297,42 @@
         <v>1</v>
       </c>
       <c r="O58" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P58" t="str">
-        <v>{"macros_p":53,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":608,"delta_kcal":7,"tolerance_kcal":123},"issues":[]}}</v>
+        <v>{"macros_p":48,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":614,"delta_kcal":0,"tolerance_kcal":122.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
+        <v>lunch_dinner_chicken-biryani-raita</v>
       </c>
       <c r="B59" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C59" t="str">
-        <v>Egg curry + dal + jowar roti</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="D59" t="str">
-        <v>Egg Curry + Dal + Roti</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="E59" t="str">
-        <v>Egg curry + dal + jowar roti</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="F59" t="str">
         <v>Indian</v>
       </c>
       <c r="G59">
-        <v>604</v>
+        <v>629</v>
       </c>
       <c r="H59">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="I59">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J59">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K59" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3347,42 +3347,42 @@
         <v>1</v>
       </c>
       <c r="O59" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P59" t="str">
-        <v>{"macros_p":34,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":585,"delta_kcal":19,"tolerance_kcal":120.8},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":607,"delta_kcal":22,"tolerance_kcal":125.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>lunch_dinner_chicken-shawarma-bowl</v>
+        <v>lunch_dinner_fish-moilee-rice</v>
       </c>
       <c r="B60" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C60" t="str">
-        <v>Chicken shawarma bowl</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="D60" t="str">
-        <v>Chicken shawarma bowl</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="E60" t="str">
-        <v>Chicken shawarma bowl</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="F60" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G60">
-        <v>533</v>
+        <v>615</v>
       </c>
       <c r="H60">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I60">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="J60">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K60" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3397,42 +3397,42 @@
         <v>1</v>
       </c>
       <c r="O60" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P60" t="str">
-        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":533,"delta_kcal":0,"tolerance_kcal":106.6},"issues":[]}}</v>
+        <v>{"macros_p":53,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":608,"delta_kcal":7,"tolerance_kcal":123},"issues":[]}}</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>lunch_dinner_prawn-curry-rice</v>
+        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
       </c>
       <c r="B61" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C61" t="str">
-        <v>Prawn curry + rice</v>
+        <v>Egg curry + dal + jowar roti</v>
       </c>
       <c r="D61" t="str">
-        <v>Prawn curry + rice</v>
+        <v>Egg Curry + Dal + Roti</v>
       </c>
       <c r="E61" t="str">
-        <v>Prawn curry + rice</v>
+        <v>Egg curry + dal + jowar roti</v>
       </c>
       <c r="F61" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G61">
-        <v>552</v>
+        <v>604</v>
       </c>
       <c r="H61">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I61">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J61">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K61" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3447,42 +3447,42 @@
         <v>1</v>
       </c>
       <c r="O61" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P61" t="str">
-        <v>{"macros_p":49,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":3,"tolerance_kcal":110.4},"issues":[]}}</v>
+        <v>{"macros_p":34,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":585,"delta_kcal":19,"tolerance_kcal":120.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
+        <v>lunch_dinner_chicken-shawarma-bowl</v>
       </c>
       <c r="B62" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C62" t="str">
-        <v>Chicken meatballs + spaghetti + salad</v>
+        <v>Chicken shawarma bowl</v>
       </c>
       <c r="D62" t="str">
-        <v>Chicken Meatballs + Spaghetti</v>
+        <v>Chicken shawarma bowl</v>
       </c>
       <c r="E62" t="str">
-        <v>Chicken meatballs + spaghetti + salad</v>
+        <v>Chicken shawarma bowl</v>
       </c>
       <c r="F62" t="str">
         <v>Continental</v>
       </c>
       <c r="G62">
-        <v>649</v>
+        <v>533</v>
       </c>
       <c r="H62">
         <v>57</v>
       </c>
       <c r="I62">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J62">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="K62" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3497,42 +3497,42 @@
         <v>1</v>
       </c>
       <c r="O62" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P62" t="str">
-        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":659,"delta_kcal":10,"tolerance_kcal":129.8},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":533,"delta_kcal":0,"tolerance_kcal":106.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>lunch_dinner_rajma-paneer-bowl</v>
+        <v>lunch_dinner_prawn-curry-rice</v>
       </c>
       <c r="B63" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C63" t="str">
-        <v>Rajma + paneer bowl</v>
+        <v>Prawn curry + rice</v>
       </c>
       <c r="D63" t="str">
-        <v>Rajma + Paneer Bowl</v>
+        <v>Prawn curry + rice</v>
       </c>
       <c r="E63" t="str">
-        <v>Rajma + paneer bowl</v>
+        <v>Prawn curry + rice</v>
       </c>
       <c r="F63" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G63">
-        <v>516</v>
+        <v>552</v>
       </c>
       <c r="H63">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I63">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J63">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K63" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3547,48 +3547,48 @@
         <v>1</v>
       </c>
       <c r="O63" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P63" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":523,"delta_kcal":7,"tolerance_kcal":103.2},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":3,"tolerance_kcal":110.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>lunch_dinner_palak-paneer-jowar-roti</v>
+        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
       </c>
       <c r="B64" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C64" t="str">
-        <v>Palak paneer + jowar roti</v>
+        <v>Chicken meatballs + spaghetti + salad</v>
       </c>
       <c r="D64" t="str">
-        <v>Palak paneer + jowar roti</v>
+        <v>Chicken Meatballs + Spaghetti</v>
       </c>
       <c r="E64" t="str">
-        <v>Palak paneer + jowar roti</v>
+        <v>Chicken meatballs + spaghetti + salad</v>
       </c>
       <c r="F64" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G64">
-        <v>734</v>
+        <v>649</v>
       </c>
       <c r="H64">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="I64">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J64">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="K64" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L64" t="str">
-        <v>assumptions_v2026_08_03</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M64" t="str">
         <v>seed_v1</v>
@@ -3597,48 +3597,48 @@
         <v>1</v>
       </c>
       <c r="O64" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P64" t="str">
-        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":731,"delta_kcal":3,"tolerance_kcal":146.8},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":659,"delta_kcal":10,"tolerance_kcal":129.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>lunch_dinner_achari-paneer-tikka-dal-salad</v>
+        <v>lunch_dinner_rajma-paneer-bowl</v>
       </c>
       <c r="B65" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C65" t="str">
-        <v>Achari paneer tikka + dal + salad</v>
+        <v>Rajma + paneer bowl</v>
       </c>
       <c r="D65" t="str">
-        <v>Achari Paneer Tikka + Dal</v>
+        <v>Rajma + Paneer Bowl</v>
       </c>
       <c r="E65" t="str">
-        <v>Achari paneer tikka + dal + salad</v>
+        <v>Rajma + paneer bowl</v>
       </c>
       <c r="F65" t="str">
         <v>Indian</v>
       </c>
       <c r="G65">
-        <v>622</v>
+        <v>516</v>
       </c>
       <c r="H65">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="I65">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J65">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K65" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L65" t="str">
-        <v>assumptions_v2026_08_03</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M65" t="str">
         <v>seed_v1</v>
@@ -3647,42 +3647,42 @@
         <v>1</v>
       </c>
       <c r="O65" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P65" t="str">
-        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":621,"delta_kcal":1,"tolerance_kcal":124.4},"issues":[]}}</v>
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":523,"delta_kcal":7,"tolerance_kcal":103.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>lunch_dinner_soya-keema-curry-jowar-roti</v>
+        <v>lunch_dinner_palak-paneer-jowar-roti</v>
       </c>
       <c r="B66" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C66" t="str">
-        <v>Soya keema curry + jowar roti</v>
+        <v>Palak paneer + jowar roti</v>
       </c>
       <c r="D66" t="str">
-        <v>Soya Keema + Jowar Roti</v>
+        <v>Palak paneer + jowar roti</v>
       </c>
       <c r="E66" t="str">
-        <v>Soya keema curry + jowar roti</v>
+        <v>Palak paneer + jowar roti</v>
       </c>
       <c r="F66" t="str">
         <v>Indian</v>
       </c>
       <c r="G66">
-        <v>530</v>
+        <v>734</v>
       </c>
       <c r="H66">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I66">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J66">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="K66" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3697,42 +3697,42 @@
         <v>1</v>
       </c>
       <c r="O66" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P66" t="str">
-        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":5,"tolerance_kcal":106},"issues":[]}}</v>
+        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":731,"delta_kcal":3,"tolerance_kcal":146.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>lunch_dinner_chole-paneer-bowl-salad</v>
+        <v>lunch_dinner_achari-paneer-tikka-dal-salad</v>
       </c>
       <c r="B67" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C67" t="str">
-        <v>Chole-paneer bowl + salad</v>
+        <v>Achari paneer tikka + dal + salad</v>
       </c>
       <c r="D67" t="str">
-        <v>Chole-Paneer Bowl</v>
+        <v>Achari Paneer Tikka + Dal</v>
       </c>
       <c r="E67" t="str">
-        <v>Chole-paneer bowl + salad</v>
+        <v>Achari paneer tikka + dal + salad</v>
       </c>
       <c r="F67" t="str">
         <v>Indian</v>
       </c>
       <c r="G67">
-        <v>659</v>
+        <v>622</v>
       </c>
       <c r="H67">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I67">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="J67">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K67" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3747,42 +3747,42 @@
         <v>1</v>
       </c>
       <c r="O67" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P67" t="str">
-        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":662,"delta_kcal":3,"tolerance_kcal":131.8},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":621,"delta_kcal":1,"tolerance_kcal":124.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>lunch_dinner_kadai-chicken-jowar-roti</v>
+        <v>lunch_dinner_soya-keema-curry-jowar-roti</v>
       </c>
       <c r="B68" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C68" t="str">
-        <v>Kadai chicken + jowar roti</v>
+        <v>Soya keema curry + jowar roti</v>
       </c>
       <c r="D68" t="str">
-        <v>Kadai chicken + jowar roti</v>
+        <v>Soya Keema + Jowar Roti</v>
       </c>
       <c r="E68" t="str">
-        <v>Kadai chicken + jowar roti</v>
+        <v>Soya keema curry + jowar roti</v>
       </c>
       <c r="F68" t="str">
         <v>Indian</v>
       </c>
       <c r="G68">
-        <v>586</v>
+        <v>530</v>
       </c>
       <c r="H68">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="I68">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J68">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K68" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3797,42 +3797,42 @@
         <v>1</v>
       </c>
       <c r="O68" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P68" t="str">
-        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":568,"delta_kcal":18,"tolerance_kcal":117.2},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":5,"tolerance_kcal":106},"issues":[]}}</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>lunch_dinner_tandoori-fish-tikka-veg-roti</v>
+        <v>lunch_dinner_chole-paneer-bowl-salad</v>
       </c>
       <c r="B69" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C69" t="str">
-        <v>Tandoori fish tikka + sauteed veg + roti</v>
+        <v>Chole-paneer bowl + salad</v>
       </c>
       <c r="D69" t="str">
-        <v>Tandoori Fish Tikka + Veg</v>
+        <v>Chole-Paneer Bowl</v>
       </c>
       <c r="E69" t="str">
-        <v>Tandoori fish tikka + sauteed veg + roti</v>
+        <v>Chole-paneer bowl + salad</v>
       </c>
       <c r="F69" t="str">
         <v>Indian</v>
       </c>
       <c r="G69">
-        <v>477</v>
+        <v>659</v>
       </c>
       <c r="H69">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="I69">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J69">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="K69" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3847,42 +3847,42 @@
         <v>1</v>
       </c>
       <c r="O69" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P69" t="str">
-        <v>{"macros_p":58,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":474,"delta_kcal":3,"tolerance_kcal":95.4},"issues":[]}}</v>
+        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":662,"delta_kcal":3,"tolerance_kcal":131.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>lunch_dinner_chicken-keema-matar-jowar-roti</v>
+        <v>lunch_dinner_kadai-chicken-jowar-roti</v>
       </c>
       <c r="B70" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C70" t="str">
-        <v>Chicken keema matar + jowar roti</v>
+        <v>Kadai chicken + jowar roti</v>
       </c>
       <c r="D70" t="str">
-        <v>Chicken Keema Matar + Roti</v>
+        <v>Kadai chicken + jowar roti</v>
       </c>
       <c r="E70" t="str">
-        <v>Chicken keema matar + jowar roti</v>
+        <v>Kadai chicken + jowar roti</v>
       </c>
       <c r="F70" t="str">
         <v>Indian</v>
       </c>
       <c r="G70">
-        <v>674</v>
+        <v>586</v>
       </c>
       <c r="H70">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I70">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J70">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K70" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3897,42 +3897,42 @@
         <v>1</v>
       </c>
       <c r="O70" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P70" t="str">
-        <v>{"macros_p":59,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":672,"delta_kcal":2,"tolerance_kcal":134.8},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":568,"delta_kcal":18,"tolerance_kcal":117.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>lunch_dinner_beef-bulgogi-bowl</v>
+        <v>lunch_dinner_tandoori-fish-tikka-veg-roti</v>
       </c>
       <c r="B71" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C71" t="str">
-        <v>Beef bulgogi bowl</v>
+        <v>Tandoori fish tikka + sauteed veg + roti</v>
       </c>
       <c r="D71" t="str">
-        <v>Beef bulgogi bowl</v>
+        <v>Tandoori Fish Tikka + Veg</v>
       </c>
       <c r="E71" t="str">
-        <v>Beef bulgogi bowl</v>
+        <v>Tandoori fish tikka + sauteed veg + roti</v>
       </c>
       <c r="F71" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G71">
-        <v>575</v>
+        <v>477</v>
       </c>
       <c r="H71">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="I71">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J71">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K71" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3947,42 +3947,42 @@
         <v>1</v>
       </c>
       <c r="O71" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P71" t="str">
-        <v>{"macros_p":46,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":566,"delta_kcal":9,"tolerance_kcal":115},"issues":[]}}</v>
+        <v>{"macros_p":58,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":474,"delta_kcal":3,"tolerance_kcal":95.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>lunch_dinner_tofu-veg-bibimbap</v>
+        <v>lunch_dinner_chicken-keema-matar-jowar-roti</v>
       </c>
       <c r="B72" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C72" t="str">
-        <v>Tofu &amp; vegetable bibimbap</v>
+        <v>Chicken keema matar + jowar roti</v>
       </c>
       <c r="D72" t="str">
-        <v>Tofu &amp; Veg Bibimbap</v>
+        <v>Chicken Keema Matar + Roti</v>
       </c>
       <c r="E72" t="str">
-        <v>Tofu &amp; vegetable bibimbap</v>
+        <v>Chicken keema matar + jowar roti</v>
       </c>
       <c r="F72" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G72">
-        <v>555</v>
+        <v>674</v>
       </c>
       <c r="H72">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="I72">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J72">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K72" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3997,42 +3997,42 @@
         <v>1</v>
       </c>
       <c r="O72" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P72" t="str">
-        <v>{"macros_p":44,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":583,"delta_kcal":28,"tolerance_kcal":111},"issues":[]}}</v>
+        <v>{"macros_p":59,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":672,"delta_kcal":2,"tolerance_kcal":134.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>lunch_dinner_oyakodon-side-salad</v>
+        <v>lunch_dinner_beef-bulgogi-bowl</v>
       </c>
       <c r="B73" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C73" t="str">
-        <v>Oyakodon + side salad</v>
+        <v>Beef bulgogi bowl</v>
       </c>
       <c r="D73" t="str">
-        <v>Oyakodon (chicken &amp; egg)</v>
+        <v>Beef bulgogi bowl</v>
       </c>
       <c r="E73" t="str">
-        <v>Oyakodon + side salad</v>
+        <v>Beef bulgogi bowl</v>
       </c>
       <c r="F73" t="str">
         <v>Asian</v>
       </c>
       <c r="G73">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="H73">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I73">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J73">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K73" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4047,42 +4047,42 @@
         <v>1</v>
       </c>
       <c r="O73" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P73" t="str">
-        <v>{"macros_p":60,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":539,"delta_kcal":29,"tolerance_kcal":113.6},"issues":[]}}</v>
+        <v>{"macros_p":46,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":566,"delta_kcal":9,"tolerance_kcal":115},"issues":[]}}</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>lunch_dinner_dubu-jorim-rice-kimchi</v>
+        <v>lunch_dinner_tofu-veg-bibimbap</v>
       </c>
       <c r="B74" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C74" t="str">
-        <v>Dubu jorim + rice + kimchi</v>
+        <v>Tofu &amp; vegetable bibimbap</v>
       </c>
       <c r="D74" t="str">
-        <v>Dubu Jorim (braised tofu)</v>
+        <v>Tofu &amp; Veg Bibimbap</v>
       </c>
       <c r="E74" t="str">
-        <v>Dubu jorim + rice + kimchi</v>
+        <v>Tofu &amp; vegetable bibimbap</v>
       </c>
       <c r="F74" t="str">
         <v>Asian</v>
       </c>
       <c r="G74">
-        <v>480</v>
+        <v>555</v>
       </c>
       <c r="H74">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I74">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J74">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K74" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4097,42 +4097,42 @@
         <v>1</v>
       </c>
       <c r="O74" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P74" t="str">
-        <v>{"macros_p":38,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":511,"delta_kcal":31,"tolerance_kcal":96},"issues":[]}}</v>
+        <v>{"macros_p":44,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":583,"delta_kcal":28,"tolerance_kcal":111},"issues":[]}}</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>lunch_dinner_home-style-tofu-chicken-stir-fry</v>
+        <v>lunch_dinner_oyakodon-side-salad</v>
       </c>
       <c r="B75" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C75" t="str">
-        <v>Home-style tofu &amp; chicken stir-fry</v>
+        <v>Oyakodon + side salad</v>
       </c>
       <c r="D75" t="str">
-        <v>Home-Style Tofu &amp; Chicken</v>
+        <v>Oyakodon (chicken &amp; egg)</v>
       </c>
       <c r="E75" t="str">
-        <v>Home-style tofu &amp; chicken stir-fry</v>
+        <v>Oyakodon + side salad</v>
       </c>
       <c r="F75" t="str">
         <v>Asian</v>
       </c>
       <c r="G75">
-        <v>609</v>
+        <v>568</v>
       </c>
       <c r="H75">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I75">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J75">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K75" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4147,42 +4147,42 @@
         <v>1</v>
       </c>
       <c r="O75" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P75" t="str">
-        <v>{"macros_p":64,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":619,"delta_kcal":10,"tolerance_kcal":121.8},"issues":[]}}</v>
+        <v>{"macros_p":60,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":539,"delta_kcal":29,"tolerance_kcal":113.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>lunch_dinner_vietnamese-lemongrass-chicken-bowl</v>
+        <v>lunch_dinner_dubu-jorim-rice-kimchi</v>
       </c>
       <c r="B76" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C76" t="str">
-        <v>Vietnamese lemongrass chicken bowl</v>
+        <v>Dubu jorim + rice + kimchi</v>
       </c>
       <c r="D76" t="str">
-        <v>Lemongrass Chicken Bowl</v>
+        <v>Dubu Jorim (braised tofu)</v>
       </c>
       <c r="E76" t="str">
-        <v>Vietnamese lemongrass chicken bowl</v>
+        <v>Dubu jorim + rice + kimchi</v>
       </c>
       <c r="F76" t="str">
         <v>Asian</v>
       </c>
       <c r="G76">
-        <v>514</v>
+        <v>480</v>
       </c>
       <c r="H76">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="I76">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J76">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K76" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4197,42 +4197,42 @@
         <v>1</v>
       </c>
       <c r="O76" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P76" t="str">
-        <v>{"macros_p":59,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":494,"delta_kcal":20,"tolerance_kcal":102.8},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":511,"delta_kcal":31,"tolerance_kcal":96},"issues":[]}}</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>lunch_dinner_cantonese-steamed-fish-edamame</v>
+        <v>lunch_dinner_home-style-tofu-chicken-stir-fry</v>
       </c>
       <c r="B77" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C77" t="str">
-        <v>Cantonese steamed fish + edamame + rice</v>
+        <v>Home-style tofu &amp; chicken stir-fry</v>
       </c>
       <c r="D77" t="str">
-        <v>Steamed Fish + Edamame</v>
+        <v>Home-Style Tofu &amp; Chicken</v>
       </c>
       <c r="E77" t="str">
-        <v>Cantonese steamed fish + edamame + rice</v>
+        <v>Home-style tofu &amp; chicken stir-fry</v>
       </c>
       <c r="F77" t="str">
         <v>Asian</v>
       </c>
       <c r="G77">
-        <v>484</v>
+        <v>609</v>
       </c>
       <c r="H77">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I77">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J77">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K77" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4247,42 +4247,42 @@
         <v>1</v>
       </c>
       <c r="O77" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P77" t="str">
-        <v>{"macros_p":60,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":492,"delta_kcal":8,"tolerance_kcal":96.8},"issues":[]}}</v>
+        <v>{"macros_p":64,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":619,"delta_kcal":10,"tolerance_kcal":121.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>lunch_dinner_chicken-bulgogi-bowl</v>
+        <v>lunch_dinner_vietnamese-lemongrass-chicken-bowl</v>
       </c>
       <c r="B78" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C78" t="str">
-        <v>Chicken bulgogi bowl</v>
+        <v>Vietnamese lemongrass chicken bowl</v>
       </c>
       <c r="D78" t="str">
-        <v>Chicken bulgogi bowl</v>
+        <v>Lemongrass Chicken Bowl</v>
       </c>
       <c r="E78" t="str">
-        <v>Chicken bulgogi bowl</v>
+        <v>Vietnamese lemongrass chicken bowl</v>
       </c>
       <c r="F78" t="str">
         <v>Asian</v>
       </c>
       <c r="G78">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="H78">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I78">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="J78">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K78" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4297,42 +4297,42 @@
         <v>1</v>
       </c>
       <c r="O78" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P78" t="str">
-        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":484,"delta_kcal":11,"tolerance_kcal":99},"issues":[]}}</v>
+        <v>{"macros_p":59,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":494,"delta_kcal":20,"tolerance_kcal":102.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>lunch_dinner_chicken-souvlaki-tzatziki-greek-salad</v>
+        <v>lunch_dinner_cantonese-steamed-fish-edamame</v>
       </c>
       <c r="B79" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C79" t="str">
-        <v>Chicken souvlaki + tzatziki + Greek salad</v>
+        <v>Cantonese steamed fish + edamame + rice</v>
       </c>
       <c r="D79" t="str">
-        <v>Chicken Souvlaki + Greek Salad</v>
+        <v>Steamed Fish + Edamame</v>
       </c>
       <c r="E79" t="str">
-        <v>Chicken souvlaki + tzatziki + Greek salad</v>
+        <v>Cantonese steamed fish + edamame + rice</v>
       </c>
       <c r="F79" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G79">
-        <v>544</v>
+        <v>484</v>
       </c>
       <c r="H79">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I79">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="J79">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K79" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4347,42 +4347,42 @@
         <v>1</v>
       </c>
       <c r="O79" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P79" t="str">
-        <v>{"macros_p":72,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":531,"delta_kcal":13,"tolerance_kcal":108.8},"issues":[]}}</v>
+        <v>{"macros_p":60,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":492,"delta_kcal":8,"tolerance_kcal":96.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>lunch_dinner_baked-feta-chickpea-traybake</v>
+        <v>lunch_dinner_chicken-bulgogi-bowl</v>
       </c>
       <c r="B80" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C80" t="str">
-        <v>Baked feta &amp; chickpea traybake</v>
+        <v>Chicken bulgogi bowl</v>
       </c>
       <c r="D80" t="str">
-        <v>Baked Feta &amp; Chickpea Traybake</v>
+        <v>Chicken bulgogi bowl</v>
       </c>
       <c r="E80" t="str">
-        <v>Baked feta &amp; chickpea traybake</v>
+        <v>Chicken bulgogi bowl</v>
       </c>
       <c r="F80" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G80">
-        <v>615</v>
+        <v>495</v>
       </c>
       <c r="H80">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="I80">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J80">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="K80" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4397,42 +4397,42 @@
         <v>1</v>
       </c>
       <c r="O80" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P80" t="str">
-        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":629,"delta_kcal":14,"tolerance_kcal":123},"issues":[]}}</v>
+        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":484,"delta_kcal":11,"tolerance_kcal":99},"issues":[]}}</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>lunch_dinner_tuna-nicoise-salad</v>
+        <v>lunch_dinner_chicken-souvlaki-tzatziki-greek-salad</v>
       </c>
       <c r="B81" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C81" t="str">
-        <v>Tuna Nicoise salad</v>
+        <v>Chicken souvlaki + tzatziki + Greek salad</v>
       </c>
       <c r="D81" t="str">
-        <v>Tuna Nicoise salad</v>
+        <v>Chicken Souvlaki + Greek Salad</v>
       </c>
       <c r="E81" t="str">
-        <v>Tuna Nicoise salad</v>
+        <v>Chicken souvlaki + tzatziki + Greek salad</v>
       </c>
       <c r="F81" t="str">
         <v>Continental</v>
       </c>
       <c r="G81">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="H81">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="I81">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J81">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K81" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4447,39 +4447,39 @@
         <v>1</v>
       </c>
       <c r="O81" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P81" t="str">
-        <v>{"macros_p":55,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":514,"delta_kcal":10,"tolerance_kcal":104.8},"issues":[]}}</v>
+        <v>{"macros_p":72,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":531,"delta_kcal":13,"tolerance_kcal":108.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>lunch_dinner_halloumi-roasted-veg-quinoa-bowl</v>
+        <v>lunch_dinner_baked-feta-chickpea-traybake</v>
       </c>
       <c r="B82" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C82" t="str">
-        <v>Halloumi &amp; roasted-veg quinoa bowl</v>
+        <v>Baked feta &amp; chickpea traybake</v>
       </c>
       <c r="D82" t="str">
-        <v>Halloumi &amp; Quinoa Bowl</v>
+        <v>Baked Feta &amp; Chickpea Traybake</v>
       </c>
       <c r="E82" t="str">
-        <v>Halloumi &amp; roasted-veg quinoa bowl</v>
+        <v>Baked feta &amp; chickpea traybake</v>
       </c>
       <c r="F82" t="str">
         <v>Continental</v>
       </c>
       <c r="G82">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="H82">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I82">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="J82">
         <v>33</v>
@@ -4497,42 +4497,42 @@
         <v>1</v>
       </c>
       <c r="O82" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P82" t="str">
-        <v>{"macros_p":40,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":613,"delta_kcal":12,"tolerance_kcal":120.2},"issues":[]}}</v>
+        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":629,"delta_kcal":14,"tolerance_kcal":123},"issues":[]}}</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>lunch_dinner_chicken-white-bean-stew</v>
+        <v>lunch_dinner_tuna-nicoise-salad</v>
       </c>
       <c r="B83" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C83" t="str">
-        <v>Chicken &amp; white-bean stew</v>
+        <v>Tuna Nicoise salad</v>
       </c>
       <c r="D83" t="str">
-        <v>Chicken &amp; White-Bean Stew</v>
+        <v>Tuna Nicoise salad</v>
       </c>
       <c r="E83" t="str">
-        <v>Chicken &amp; white-bean stew</v>
+        <v>Tuna Nicoise salad</v>
       </c>
       <c r="F83" t="str">
         <v>Continental</v>
       </c>
       <c r="G83">
-        <v>620</v>
+        <v>524</v>
       </c>
       <c r="H83">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I83">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J83">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K83" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4547,42 +4547,42 @@
         <v>1</v>
       </c>
       <c r="O83" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P83" t="str">
-        <v>{"macros_p":65,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":616,"delta_kcal":4,"tolerance_kcal":124},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":514,"delta_kcal":10,"tolerance_kcal":104.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>lunch_dinner_chickpea-pasta-tuna-tomato</v>
+        <v>lunch_dinner_halloumi-roasted-veg-quinoa-bowl</v>
       </c>
       <c r="B84" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C84" t="str">
-        <v>Chickpea pasta with tuna &amp; tomato</v>
+        <v>Halloumi &amp; roasted-veg quinoa bowl</v>
       </c>
       <c r="D84" t="str">
-        <v>Chickpea Pasta with Tuna</v>
+        <v>Halloumi &amp; Quinoa Bowl</v>
       </c>
       <c r="E84" t="str">
-        <v>Chickpea pasta with tuna &amp; tomato</v>
+        <v>Halloumi &amp; roasted-veg quinoa bowl</v>
       </c>
       <c r="F84" t="str">
         <v>Continental</v>
       </c>
       <c r="G84">
-        <v>496</v>
+        <v>601</v>
       </c>
       <c r="H84">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I84">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J84">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K84" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4597,42 +4597,42 @@
         <v>1</v>
       </c>
       <c r="O84" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P84" t="str">
-        <v>{"macros_p":50,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":524,"delta_kcal":28,"tolerance_kcal":99.2},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":613,"delta_kcal":12,"tolerance_kcal":120.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>lunch_dinner_chicken-ricotta-carbonara-style-spaghetti</v>
+        <v>lunch_dinner_chicken-white-bean-stew</v>
       </c>
       <c r="B85" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C85" t="str">
-        <v>Chicken &amp; ricotta carbonara-style spaghetti</v>
+        <v>Chicken &amp; white-bean stew</v>
       </c>
       <c r="D85" t="str">
-        <v>Chicken &amp; Ricotta Spaghetti</v>
+        <v>Chicken &amp; White-Bean Stew</v>
       </c>
       <c r="E85" t="str">
-        <v>Chicken &amp; ricotta carbonara-style spaghetti</v>
+        <v>Chicken &amp; white-bean stew</v>
       </c>
       <c r="F85" t="str">
         <v>Continental</v>
       </c>
       <c r="G85">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="H85">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I85">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J85">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K85" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4647,42 +4647,42 @@
         <v>1</v>
       </c>
       <c r="O85" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P85" t="str">
-        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":623,"delta_kcal":7,"tolerance_kcal":126},"issues":[]}}</v>
+        <v>{"macros_p":65,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":616,"delta_kcal":4,"tolerance_kcal":124},"issues":[]}}</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>lunch_dinner_mackerel-quinoa-salad</v>
+        <v>lunch_dinner_chickpea-pasta-tuna-tomato</v>
       </c>
       <c r="B86" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C86" t="str">
-        <v>Mackerel &amp; quinoa salad</v>
+        <v>Chickpea pasta with tuna &amp; tomato</v>
       </c>
       <c r="D86" t="str">
-        <v>Mackerel &amp; Quinoa Salad</v>
+        <v>Chickpea Pasta with Tuna</v>
       </c>
       <c r="E86" t="str">
-        <v>Mackerel &amp; quinoa salad</v>
+        <v>Chickpea pasta with tuna &amp; tomato</v>
       </c>
       <c r="F86" t="str">
         <v>Continental</v>
       </c>
       <c r="G86">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="H86">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I86">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="J86">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K86" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4697,48 +4697,48 @@
         <v>1</v>
       </c>
       <c r="O86" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P86" t="str">
-        <v>{"macros_p":35,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":461,"delta_kcal":2,"tolerance_kcal":92.6},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":524,"delta_kcal":28,"tolerance_kcal":99.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>lunch_dinner_chicken-ricotta-carbonara-style-spaghetti</v>
       </c>
       <c r="B87" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C87" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Chicken &amp; ricotta carbonara-style spaghetti</v>
       </c>
       <c r="D87" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Chicken &amp; Ricotta Spaghetti</v>
       </c>
       <c r="E87" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Chicken &amp; ricotta carbonara-style spaghetti</v>
       </c>
       <c r="F87" t="str">
-        <v>General</v>
+        <v>Continental</v>
       </c>
       <c r="G87">
-        <v>200</v>
+        <v>630</v>
       </c>
       <c r="H87">
+        <v>57</v>
+      </c>
+      <c r="I87">
+        <v>47</v>
+      </c>
+      <c r="J87">
         <v>23</v>
       </c>
-      <c r="I87">
-        <v>19</v>
-      </c>
-      <c r="J87">
-        <v>5</v>
-      </c>
       <c r="K87" t="str">
-        <v>USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L87" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M87" t="str">
         <v>seed_v1</v>
@@ -4747,48 +4747,48 @@
         <v>1</v>
       </c>
       <c r="O87" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P87" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":623,"delta_kcal":7,"tolerance_kcal":126},"issues":[]}}</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>lunch_dinner_mackerel-quinoa-salad</v>
       </c>
       <c r="B88" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C88" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Mackerel &amp; quinoa salad</v>
       </c>
       <c r="D88" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Mackerel &amp; Quinoa Salad</v>
       </c>
       <c r="E88" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Mackerel &amp; quinoa salad</v>
       </c>
       <c r="F88" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G88">
-        <v>345</v>
+        <v>463</v>
       </c>
       <c r="H88">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I88">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J88">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K88" t="str">
-        <v>IFCT/USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L88" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M88" t="str">
         <v>seed_v1</v>
@@ -4797,48 +4797,48 @@
         <v>1</v>
       </c>
       <c r="O88" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P88" t="str">
-        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
+        <v>{"macros_p":35,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":461,"delta_kcal":2,"tolerance_kcal":92.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>lunch_dinner_grilled-chicken-veg-pasta</v>
       </c>
       <c r="B89" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C89" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Grilled chicken, veg + pasta</v>
       </c>
       <c r="D89" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Grilled Chicken, Veg &amp; Pasta</v>
       </c>
       <c r="E89" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Grilled chicken, veg + pasta</v>
       </c>
       <c r="F89" t="str">
-        <v>International</v>
+        <v>Continental</v>
       </c>
       <c r="G89">
-        <v>203</v>
+        <v>529</v>
       </c>
       <c r="H89">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="I89">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J89">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K89" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L89" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M89" t="str">
         <v>seed_v1</v>
@@ -4847,48 +4847,48 @@
         <v>1</v>
       </c>
       <c r="O89" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P89" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":522,"delta_kcal":7,"tolerance_kcal":105.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>lunch_dinner_chicken-shawarma-plate-garlic-rice</v>
       </c>
       <c r="B90" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C90" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Chicken shawarma plate + garlic rice</v>
       </c>
       <c r="D90" t="str">
-        <v>Carrot Halwa + Protein Shake</v>
+        <v>Chicken Shawarma Plate + Rice</v>
       </c>
       <c r="E90" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Chicken shawarma plate + garlic rice</v>
       </c>
       <c r="F90" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G90">
-        <v>220</v>
+        <v>646</v>
       </c>
       <c r="H90">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="I90">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="J90">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K90" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L90" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M90" t="str">
         <v>seed_v1</v>
@@ -4897,48 +4897,48 @@
         <v>1</v>
       </c>
       <c r="O90" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P90" t="str">
-        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+        <v>{"macros_p":63,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":633,"delta_kcal":13,"tolerance_kcal":129.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_plain-chicken-tikka-plate</v>
       </c>
       <c r="B91" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C91" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Plain chicken tikka plate</v>
       </c>
       <c r="D91" t="str">
-        <v>Nuts + Seeds + Protein Shake</v>
+        <v>Plain Chicken Tikka Plate</v>
       </c>
       <c r="E91" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Plain chicken tikka plate</v>
       </c>
       <c r="F91" t="str">
-        <v>International</v>
+        <v>Indian</v>
       </c>
       <c r="G91">
-        <v>320</v>
+        <v>520</v>
       </c>
       <c r="H91">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="I91">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="J91">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K91" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L91" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M91" t="str">
         <v>seed_v1</v>
@@ -4947,48 +4947,48 @@
         <v>1</v>
       </c>
       <c r="O91" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P91" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":498,"delta_kcal":22,"tolerance_kcal":104},"issues":[]}}</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>lunch_dinner_pesto-millet-pasta-chicken</v>
       </c>
       <c r="B92" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C92" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Pesto millet pasta + chicken</v>
       </c>
       <c r="D92" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Pesto Millet Pasta + Chicken</v>
       </c>
       <c r="E92" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Pesto millet pasta + chicken</v>
       </c>
       <c r="F92" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G92">
-        <v>135</v>
+        <v>561</v>
       </c>
       <c r="H92">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="I92">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K92" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L92" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M92" t="str">
         <v>seed_v1</v>
@@ -4997,48 +4997,48 @@
         <v>1</v>
       </c>
       <c r="O92" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P92" t="str">
-        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+        <v>{"macros_p":47,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"high","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":557,"delta_kcal":4,"tolerance_kcal":112.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>lunch_dinner_aglio-olio-millet-pasta-prawns</v>
       </c>
       <c r="B93" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C93" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Aglio e olio millet pasta + prawns</v>
       </c>
       <c r="D93" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Aglio e Olio Millet Pasta + Prawns</v>
       </c>
       <c r="E93" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Aglio e olio millet pasta + prawns</v>
       </c>
       <c r="F93" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G93">
-        <v>246</v>
+        <v>483</v>
       </c>
       <c r="H93">
+        <v>42</v>
+      </c>
+      <c r="I93">
+        <v>49</v>
+      </c>
+      <c r="J93">
         <v>13</v>
       </c>
-      <c r="I93">
-        <v>41</v>
-      </c>
-      <c r="J93">
-        <v>4</v>
-      </c>
       <c r="K93" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L93" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M93" t="str">
         <v>seed_v1</v>
@@ -5047,48 +5047,48 @@
         <v>1</v>
       </c>
       <c r="O93" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P93" t="str">
-        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+        <v>{"macros_p":42,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":481,"delta_kcal":2,"tolerance_kcal":96.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>lunch_dinner_salmon-avocado-salad-fresh-grilled</v>
       </c>
       <c r="B94" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C94" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Salmon avocado salad (fresh grilled)</v>
       </c>
       <c r="D94" t="str">
-        <v>Avocado/Cheese Toast</v>
+        <v>Fresh Grilled Salmon &amp; Avocado Salad</v>
       </c>
       <c r="E94" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Salmon avocado salad (fresh grilled)</v>
       </c>
       <c r="F94" t="str">
         <v>Continental</v>
       </c>
       <c r="G94">
-        <v>193</v>
+        <v>423</v>
       </c>
       <c r="H94">
+        <v>29</v>
+      </c>
+      <c r="I94">
         <v>9</v>
       </c>
-      <c r="I94">
-        <v>14</v>
-      </c>
       <c r="J94">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K94" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L94" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M94" t="str">
         <v>seed_v1</v>
@@ -5097,48 +5097,48 @@
         <v>1</v>
       </c>
       <c r="O94" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P94" t="str">
-        <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":200,"delta_kcal":7,"tolerance_kcal":38.6},"issues":[]}}</v>
+        <v>{"macros_p":29,"protein_family":"fish","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":431,"delta_kcal":8,"tolerance_kcal":84.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+        <v>lunch_dinner_smoked-chicken-salad-full</v>
       </c>
       <c r="B95" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C95" t="str">
-        <v>Boiled eggs + hummus + veg sticks</v>
+        <v>Smoked chicken salad (full size)</v>
       </c>
       <c r="D95" t="str">
-        <v>Eggs + Hummus + Veg Sticks</v>
+        <v>Smoked Chicken Salad (Full Size)</v>
       </c>
       <c r="E95" t="str">
-        <v>Boiled eggs + hummus + veg sticks</v>
+        <v>Smoked chicken salad (full size)</v>
       </c>
       <c r="F95" t="str">
         <v>Continental</v>
       </c>
       <c r="G95">
-        <v>246</v>
+        <v>386</v>
       </c>
       <c r="H95">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I95">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J95">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K95" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L95" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M95" t="str">
         <v>seed_v1</v>
@@ -5147,48 +5147,48 @@
         <v>1</v>
       </c>
       <c r="O95" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P95" t="str">
-        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":246,"delta_kcal":0,"tolerance_kcal":49.2},"issues":[]}}</v>
+        <v>{"macros_p":42,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":393,"delta_kcal":7,"tolerance_kcal":77.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>snack_edamame-sea-salt</v>
+        <v>lunch_dinner_hummus-salad-protein-boosted</v>
       </c>
       <c r="B96" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C96" t="str">
-        <v>Edamame + sea salt</v>
+        <v>Hummus salad (protein-boosted)</v>
       </c>
       <c r="D96" t="str">
-        <v>Edamame + sea salt</v>
+        <v>Hummus Salad (Protein-Boosted)</v>
       </c>
       <c r="E96" t="str">
-        <v>Edamame + sea salt</v>
+        <v>Hummus salad (protein-boosted)</v>
       </c>
       <c r="F96" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G96">
-        <v>183</v>
+        <v>411</v>
       </c>
       <c r="H96">
+        <v>46</v>
+      </c>
+      <c r="I96">
         <v>18</v>
       </c>
-      <c r="I96">
-        <v>13</v>
-      </c>
       <c r="J96">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K96" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L96" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M96" t="str">
         <v>seed_v1</v>
@@ -5197,48 +5197,48 @@
         <v>1</v>
       </c>
       <c r="O96" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"asian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P96" t="str">
-        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":196,"delta_kcal":13,"tolerance_kcal":36.6},"issues":[]}}</v>
+        <v>{"macros_p":46,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":409,"delta_kcal":2,"tolerance_kcal":82.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>snack_paneer-tikka-skewers</v>
+        <v>lunch_dinner_sweet-potato-kaala-chana-leaner</v>
       </c>
       <c r="B97" t="str">
-        <v>snack</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C97" t="str">
-        <v>Paneer tikka skewers</v>
+        <v>Sweet potato + kaala chana + roti (leaner)</v>
       </c>
       <c r="D97" t="str">
-        <v>Paneer tikka skewers</v>
+        <v>Sweet Potato &amp; Kaala Chana (Leaner)</v>
       </c>
       <c r="E97" t="str">
-        <v>Paneer tikka skewers</v>
+        <v>Sweet potato + kaala chana + roti (leaner)</v>
       </c>
       <c r="F97" t="str">
         <v>Indian</v>
       </c>
       <c r="G97">
-        <v>224</v>
+        <v>526</v>
       </c>
       <c r="H97">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I97">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="J97">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K97" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L97" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M97" t="str">
         <v>seed_v1</v>
@@ -5247,72 +5247,822 @@
         <v>1</v>
       </c>
       <c r="O97" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P97" t="str">
-        <v>{"macros_p":15,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":220,"delta_kcal":4,"tolerance_kcal":44.8},"issues":[]}}</v>
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":526,"delta_kcal":0,"tolerance_kcal":105.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>lunch_dinner_paneer-cutlets-dal-salad</v>
+      </c>
+      <c r="B98" t="str">
+        <v>lunch_dinner</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Paneer cutlets + dal + salad</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Paneer Cutlets + Dal + Salad</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Paneer cutlets + dal + salad</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G98">
+        <v>677</v>
+      </c>
+      <c r="H98">
+        <v>37</v>
+      </c>
+      <c r="I98">
+        <v>56</v>
+      </c>
+      <c r="J98">
+        <v>34</v>
+      </c>
+      <c r="K98" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L98" t="str">
+        <v>assumptions_v2026_08_06</v>
+      </c>
+      <c r="M98" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N98" t="b">
+        <v>1</v>
+      </c>
+      <c r="O98" t="str">
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
+      </c>
+      <c r="P98" t="str">
+        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":678,"delta_kcal":1,"tolerance_kcal":135.4},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>snack_fruit-almonds-plant-shake</v>
+      </c>
+      <c r="B99" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Fruit + Almonds + Plant Shake</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Fruit + Almonds + Plant Shake</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Fruit + Almonds + Plant Shake</v>
+      </c>
+      <c r="F99" t="str">
+        <v>General</v>
+      </c>
+      <c r="G99">
+        <v>200</v>
+      </c>
+      <c r="H99">
+        <v>23</v>
+      </c>
+      <c r="I99">
+        <v>19</v>
+      </c>
+      <c r="J99">
+        <v>5</v>
+      </c>
+      <c r="K99" t="str">
+        <v>USDA + custom user specs</v>
+      </c>
+      <c r="L99" t="str">
+        <v>v1_custom</v>
+      </c>
+      <c r="M99" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N99" t="b">
+        <v>1</v>
+      </c>
+      <c r="O99" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P99" t="str">
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>snack_chaat-bhel-protein-shake</v>
+      </c>
+      <c r="B100" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Chaat + Bhel + Protein Shake</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G100">
+        <v>345</v>
+      </c>
+      <c r="H100">
+        <v>26</v>
+      </c>
+      <c r="I100">
+        <v>38</v>
+      </c>
+      <c r="J100">
+        <v>9</v>
+      </c>
+      <c r="K100" t="str">
+        <v>IFCT/USDA + custom user specs</v>
+      </c>
+      <c r="L100" t="str">
+        <v>v1_custom</v>
+      </c>
+      <c r="M100" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N100" t="b">
+        <v>1</v>
+      </c>
+      <c r="O100" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+      </c>
+      <c r="P100" t="str">
+        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>snack_greek-yogurt-berry-bowl</v>
+      </c>
+      <c r="B101" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Greek yogurt + berry bowl</v>
+      </c>
+      <c r="F101" t="str">
+        <v>International</v>
+      </c>
+      <c r="G101">
+        <v>203</v>
+      </c>
+      <c r="H101">
+        <v>21</v>
+      </c>
+      <c r="I101">
+        <v>22</v>
+      </c>
+      <c r="J101">
+        <v>4</v>
+      </c>
+      <c r="K101" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L101" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M101" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N101" t="b">
+        <v>1</v>
+      </c>
+      <c r="O101" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P101" t="str">
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+      </c>
+      <c r="B102" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Carrot halwa (sugar-free) + protein shake</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Carrot Halwa + Protein Shake</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Carrot halwa (sugar-free) + protein shake</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G102">
+        <v>220</v>
+      </c>
+      <c r="H102">
+        <v>28</v>
+      </c>
+      <c r="I102">
+        <v>17</v>
+      </c>
+      <c r="J102">
+        <v>5</v>
+      </c>
+      <c r="K102" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L102" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M102" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N102" t="b">
+        <v>1</v>
+      </c>
+      <c r="O102" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P102" t="str">
+        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B103" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Nuts + Seeds + Protein Shake</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Nuts, seeds + protein shake</v>
+      </c>
+      <c r="F103" t="str">
+        <v>International</v>
+      </c>
+      <c r="G103">
+        <v>320</v>
+      </c>
+      <c r="H103">
+        <v>31</v>
+      </c>
+      <c r="I103">
+        <v>11</v>
+      </c>
+      <c r="J103">
+        <v>17</v>
+      </c>
+      <c r="K103" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L103" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M103" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N103" t="b">
+        <v>1</v>
+      </c>
+      <c r="O103" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P103" t="str">
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B104" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Sweet potato chaat</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G104">
+        <v>135</v>
+      </c>
+      <c r="H104">
+        <v>3</v>
+      </c>
+      <c r="I104">
+        <v>32</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L104" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M104" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N104" t="b">
+        <v>1</v>
+      </c>
+      <c r="O104" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P104" t="str">
+        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B105" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Kaala chana chaat</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G105">
+        <v>246</v>
+      </c>
+      <c r="H105">
+        <v>13</v>
+      </c>
+      <c r="I105">
+        <v>41</v>
+      </c>
+      <c r="J105">
+        <v>4</v>
+      </c>
+      <c r="K105" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L105" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M105" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N105" t="b">
+        <v>1</v>
+      </c>
+      <c r="O105" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+      </c>
+      <c r="P105" t="str">
+        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B106" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Avocado/Cheese Toast</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Avocado/cheese toast</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G106">
+        <v>193</v>
+      </c>
+      <c r="H106">
+        <v>9</v>
+      </c>
+      <c r="I106">
+        <v>14</v>
+      </c>
+      <c r="J106">
+        <v>12</v>
+      </c>
+      <c r="K106" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L106" t="str">
+        <v>assumptions_v2026_02_17</v>
+      </c>
+      <c r="M106" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N106" t="b">
+        <v>1</v>
+      </c>
+      <c r="O106" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P106" t="str">
+        <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":200,"delta_kcal":7,"tolerance_kcal":38.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+      </c>
+      <c r="B107" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Boiled eggs + hummus + veg sticks</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Eggs + Hummus + Veg Sticks</v>
+      </c>
+      <c r="E107" t="str">
+        <v>Boiled eggs + hummus + veg sticks</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G107">
+        <v>246</v>
+      </c>
+      <c r="H107">
+        <v>18</v>
+      </c>
+      <c r="I107">
+        <v>12</v>
+      </c>
+      <c r="J107">
+        <v>14</v>
+      </c>
+      <c r="K107" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L107" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M107" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N107" t="b">
+        <v>1</v>
+      </c>
+      <c r="O107" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P107" t="str">
+        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":246,"delta_kcal":0,"tolerance_kcal":49.2},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>snack_edamame-sea-salt</v>
+      </c>
+      <c r="B108" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Edamame + sea salt</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Edamame + sea salt</v>
+      </c>
+      <c r="E108" t="str">
+        <v>Edamame + sea salt</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Asian</v>
+      </c>
+      <c r="G108">
+        <v>183</v>
+      </c>
+      <c r="H108">
+        <v>18</v>
+      </c>
+      <c r="I108">
+        <v>13</v>
+      </c>
+      <c r="J108">
+        <v>8</v>
+      </c>
+      <c r="K108" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L108" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M108" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N108" t="b">
+        <v>1</v>
+      </c>
+      <c r="O108" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"asian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P108" t="str">
+        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":196,"delta_kcal":13,"tolerance_kcal":36.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>snack_paneer-tikka-skewers</v>
+      </c>
+      <c r="B109" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Paneer tikka skewers</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Paneer tikka skewers</v>
+      </c>
+      <c r="E109" t="str">
+        <v>Paneer tikka skewers</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G109">
+        <v>224</v>
+      </c>
+      <c r="H109">
+        <v>15</v>
+      </c>
+      <c r="I109">
+        <v>4</v>
+      </c>
+      <c r="J109">
+        <v>16</v>
+      </c>
+      <c r="K109" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L109" t="str">
+        <v>assumptions_v2026_08_02</v>
+      </c>
+      <c r="M109" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N109" t="b">
+        <v>1</v>
+      </c>
+      <c r="O109" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P109" t="str">
+        <v>{"macros_p":15,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":220,"delta_kcal":4,"tolerance_kcal":44.8},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
         <v>snack_overnight-oats-whey-bowl</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B110" t="str">
         <v>snack</v>
       </c>
-      <c r="C98" t="str">
+      <c r="C110" t="str">
         <v>Overnight oats + whey bowl</v>
       </c>
-      <c r="D98" t="str">
+      <c r="D110" t="str">
         <v>Overnight Oats + Whey</v>
       </c>
-      <c r="E98" t="str">
+      <c r="E110" t="str">
         <v>Overnight oats + whey bowl</v>
       </c>
-      <c r="F98" t="str">
+      <c r="F110" t="str">
         <v>Continental</v>
       </c>
-      <c r="G98">
+      <c r="G110">
         <v>218</v>
       </c>
-      <c r="H98">
+      <c r="H110">
         <v>9</v>
       </c>
-      <c r="I98">
+      <c r="I110">
         <v>32</v>
       </c>
-      <c r="J98">
+      <c r="J110">
         <v>6</v>
       </c>
-      <c r="K98" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
-      </c>
-      <c r="L98" t="str">
+      <c r="K110" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L110" t="str">
         <v>assumptions_v2026_08_02</v>
       </c>
-      <c r="M98" t="str">
-        <v>seed_v1</v>
-      </c>
-      <c r="N98" t="b">
-        <v>1</v>
-      </c>
-      <c r="O98" t="str">
+      <c r="M110" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N110" t="b">
+        <v>1</v>
+      </c>
+      <c r="O110" t="str">
         <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
-      <c r="P98" t="str">
+      <c r="P110" t="str">
         <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":218,"delta_kcal":0,"tolerance_kcal":43.6},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>snack_hummus-salad</v>
+      </c>
+      <c r="B111" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Hummus salad</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Hummus Salad</v>
+      </c>
+      <c r="E111" t="str">
+        <v>Hummus salad</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G111">
+        <v>136</v>
+      </c>
+      <c r="H111">
+        <v>7</v>
+      </c>
+      <c r="I111">
+        <v>15</v>
+      </c>
+      <c r="J111">
+        <v>6</v>
+      </c>
+      <c r="K111" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L111" t="str">
+        <v>assumptions_v2026_08_06</v>
+      </c>
+      <c r="M111" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N111" t="b">
+        <v>1</v>
+      </c>
+      <c r="O111" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P111" t="str">
+        <v>{"macros_p":7,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":142,"delta_kcal":6,"tolerance_kcal":35},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>snack_acai-bowl</v>
+      </c>
+      <c r="B112" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Acai bowl</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Acai Bowl</v>
+      </c>
+      <c r="E112" t="str">
+        <v>Acai bowl</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Continental</v>
+      </c>
+      <c r="G112">
+        <v>245</v>
+      </c>
+      <c r="H112">
+        <v>6</v>
+      </c>
+      <c r="I112">
+        <v>28</v>
+      </c>
+      <c r="J112">
+        <v>13</v>
+      </c>
+      <c r="K112" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L112" t="str">
+        <v>assumptions_v2026_08_06</v>
+      </c>
+      <c r="M112" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N112" t="b">
+        <v>1</v>
+      </c>
+      <c r="O112" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P112" t="str">
+        <v>{"macros_p":6,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":253,"delta_kcal":8,"tolerance_kcal":49},"issues":[]}}</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>snack_paneer-cutlets</v>
+      </c>
+      <c r="B113" t="str">
+        <v>snack</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Paneer cutlets</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Paneer Cutlets</v>
+      </c>
+      <c r="E113" t="str">
+        <v>Paneer cutlets</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Indian</v>
+      </c>
+      <c r="G113">
+        <v>250</v>
+      </c>
+      <c r="H113">
+        <v>13</v>
+      </c>
+      <c r="I113">
+        <v>12</v>
+      </c>
+      <c r="J113">
+        <v>17</v>
+      </c>
+      <c r="K113" t="str">
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+      </c>
+      <c r="L113" t="str">
+        <v>assumptions_v2026_08_06</v>
+      </c>
+      <c r="M113" t="str">
+        <v>seed_v1</v>
+      </c>
+      <c r="N113" t="b">
+        <v>1</v>
+      </c>
+      <c r="O113" t="str">
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+      </c>
+      <c r="P113" t="str">
+        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":253,"delta_kcal":3,"tolerance_kcal":50},"issues":[]}}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P113"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I113"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5751,19 +6501,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>breakfast_paneer-egg-white-bhurji-toast</v>
+        <v>breakfast_scrambled-egg-sandwich</v>
       </c>
       <c r="B16" t="str">
-        <v>Paneer + egg whites</v>
+        <v>Eggs (whole)</v>
       </c>
       <c r="C16">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="D16" t="str">
         <v>Whole wheat toast</v>
       </c>
       <c r="E16">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -5780,19 +6530,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>breakfast_anda-bhurji-toast</v>
+        <v>breakfast_acai-bowl-protein-boosted</v>
       </c>
       <c r="B17" t="str">
-        <v>Eggs (whole + whites)</v>
+        <v>Greek yogurt + whey</v>
       </c>
       <c r="C17">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="D17" t="str">
-        <v>Whole wheat toast</v>
+        <v>Acai + fruit</v>
       </c>
       <c r="E17">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -5801,7 +6551,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Pan-fried</v>
+        <v>Bowl</v>
       </c>
       <c r="I17" t="str">
         <v>{}</v>
@@ -5809,13 +6559,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>breakfast_sardines-toast-avocado</v>
+        <v>breakfast_paneer-egg-white-bhurji-toast</v>
       </c>
       <c r="B18" t="str">
-        <v>Sardines</v>
+        <v>Paneer + egg whites</v>
       </c>
       <c r="C18">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="D18" t="str">
         <v>Whole wheat toast</v>
@@ -5824,13 +6574,13 @@
         <v>60</v>
       </c>
       <c r="F18" t="str">
-        <v>Avocado + greens</v>
-      </c>
-      <c r="G18">
-        <v>130</v>
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>Toast</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I18" t="str">
         <v>{}</v>
@@ -5838,25 +6588,25 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>breakfast_shakshuka-feta</v>
+        <v>breakfast_anda-bhurji-toast</v>
       </c>
       <c r="B19" t="str">
-        <v>Eggs + feta</v>
+        <v>Eggs (whole + whites)</v>
       </c>
       <c r="C19">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="D19" t="str">
         <v>Whole wheat toast</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F19" t="str">
-        <v>Tomato, pepper, spinach</v>
-      </c>
-      <c r="G19">
-        <v>120</v>
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
       </c>
       <c r="H19" t="str">
         <v>Pan-fried</v>
@@ -5867,13 +6617,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>breakfast_cottage-cheese-smoked-salmon-bowl</v>
+        <v>breakfast_sardines-toast-avocado</v>
       </c>
       <c r="B20" t="str">
-        <v>Cottage cheese + smoked salmon</v>
+        <v>Sardines</v>
       </c>
       <c r="C20">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="D20" t="str">
         <v>Whole wheat toast</v>
@@ -5885,10 +6635,10 @@
         <v>Avocado + greens</v>
       </c>
       <c r="G20">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H20" t="str">
-        <v>Bowl</v>
+        <v>Toast</v>
       </c>
       <c r="I20" t="str">
         <v>{}</v>
@@ -5896,28 +6646,28 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti</v>
+        <v>breakfast_shakshuka-feta</v>
       </c>
       <c r="B21" t="str">
-        <v>Chicken breast</v>
+        <v>Eggs + feta</v>
       </c>
       <c r="C21">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="D21" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Whole wheat toast</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F21" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Tomato, pepper, spinach</v>
       </c>
       <c r="G21">
         <v>120</v>
       </c>
       <c r="H21" t="str">
-        <v>Curry style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I21" t="str">
         <v>{}</v>
@@ -5925,28 +6675,28 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
+        <v>breakfast_cottage-cheese-smoked-salmon-bowl</v>
       </c>
       <c r="B22" t="str">
-        <v>Grilled salmon</v>
+        <v>Cottage cheese + smoked salmon</v>
       </c>
       <c r="C22">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="D22" t="str">
-        <v>Spaghetti aglio e olio (small portion)</v>
+        <v>Whole wheat toast</v>
       </c>
       <c r="E22">
+        <v>60</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Avocado + greens</v>
+      </c>
+      <c r="G22">
         <v>100</v>
       </c>
-      <c r="F22" t="str">
-        <v>Sautéed broccoli</v>
-      </c>
-      <c r="G22">
-        <v>150</v>
-      </c>
       <c r="H22" t="str">
-        <v>Grilled</v>
+        <v>Bowl</v>
       </c>
       <c r="I22" t="str">
         <v>{}</v>
@@ -5954,25 +6704,25 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lunch_dinner_rajma-chawal-raita</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti</v>
       </c>
       <c r="B23" t="str">
-        <v/>
+        <v>Chicken breast</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D23" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E23">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F23" t="str">
         <v>Mixed veg sabzi</v>
       </c>
       <c r="G23">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H23" t="str">
         <v>Curry style</v>
@@ -5983,28 +6733,28 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lunch_dinner_chole-jowar-roti-raita</v>
+        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B24" t="str">
-        <v/>
+        <v>Grilled salmon</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D24" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Spaghetti aglio e olio (small portion)</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <v/>
+        <v>Sautéed broccoli</v>
+      </c>
+      <c r="G24">
+        <v>150</v>
       </c>
       <c r="H24" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I24" t="str">
         <v>{}</v>
@@ -6012,28 +6762,28 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lunch_dinner_vietnamese-chicken-pho</v>
+        <v>lunch_dinner_rajma-chawal-raita</v>
       </c>
       <c r="B25" t="str">
-        <v>Chicken breast</v>
+        <v/>
       </c>
       <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Cooked rice</v>
+      </c>
+      <c r="E25">
+        <v>80</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G25">
         <v>150</v>
       </c>
-      <c r="D25" t="str">
-        <v>Rice noodles</v>
-      </c>
-      <c r="E25">
-        <v>120</v>
-      </c>
-      <c r="F25" t="str">
-        <v>Pho greens + side salad</v>
-      </c>
-      <c r="G25">
-        <v>80</v>
-      </c>
       <c r="H25" t="str">
-        <v>Soup style</v>
+        <v>Curry style</v>
       </c>
       <c r="I25" t="str">
         <v>{}</v>
@@ -6041,28 +6791,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
+        <v>lunch_dinner_chole-jowar-roti-raita</v>
       </c>
       <c r="B26" t="str">
-        <v>Beef steak</v>
+        <v/>
       </c>
       <c r="C26">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="D26" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" t="str">
-        <v>Mixed greens salad</v>
-      </c>
-      <c r="G26">
-        <v>150</v>
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
       </c>
       <c r="H26" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I26" t="str">
         <v>{}</v>
@@ -6070,7 +6820,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lunch_dinner_thai-pad-krapow-rice</v>
+        <v>lunch_dinner_vietnamese-chicken-pho</v>
       </c>
       <c r="B27" t="str">
         <v>Chicken breast</v>
@@ -6079,19 +6829,19 @@
         <v>150</v>
       </c>
       <c r="D27" t="str">
-        <v>Cooked rice</v>
+        <v>Rice noodles</v>
       </c>
       <c r="E27">
+        <v>120</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Pho greens + side salad</v>
+      </c>
+      <c r="G27">
         <v>80</v>
       </c>
-      <c r="F27" t="str">
-        <v>Sautéed peppers + side salad</v>
-      </c>
-      <c r="G27">
-        <v>130</v>
-      </c>
       <c r="H27" t="str">
-        <v>Pan-fried</v>
+        <v>Soup style</v>
       </c>
       <c r="I27" t="str">
         <v>{}</v>
@@ -6099,28 +6849,28 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lunch_dinner_mutton-keema-jowar-roti</v>
+        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
       </c>
       <c r="B28" t="str">
-        <v>Mutton keema</v>
+        <v>Beef steak</v>
       </c>
       <c r="C28">
+        <v>180</v>
+      </c>
+      <c r="D28" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Mixed greens salad</v>
+      </c>
+      <c r="G28">
         <v>150</v>
       </c>
-      <c r="D28" t="str">
-        <v>Jowar roti (millet)</v>
-      </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
-      <c r="F28" t="str">
-        <v/>
-      </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
       <c r="H28" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I28" t="str">
         <v>{}</v>
@@ -6128,13 +6878,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
+        <v>lunch_dinner_thai-pad-krapow-rice</v>
       </c>
       <c r="B29" t="str">
-        <v>Paneer</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C29">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D29" t="str">
         <v>Cooked rice</v>
@@ -6143,13 +6893,13 @@
         <v>80</v>
       </c>
       <c r="F29" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Sautéed peppers + side salad</v>
       </c>
       <c r="G29">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H29" t="str">
-        <v>Curry style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I29" t="str">
         <v>{}</v>
@@ -6157,10 +6907,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
+        <v>lunch_dinner_mutton-keema-jowar-roti</v>
       </c>
       <c r="B30" t="str">
-        <v>Chicken breast</v>
+        <v>Mutton keema</v>
       </c>
       <c r="C30">
         <v>150</v>
@@ -6172,10 +6922,10 @@
         <v>2</v>
       </c>
       <c r="F30" t="str">
-        <v>Mixed veg sabzi</v>
-      </c>
-      <c r="G30">
-        <v>100</v>
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
       </c>
       <c r="H30" t="str">
         <v>Curry style</v>
@@ -6186,28 +6936,28 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
+        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
       </c>
       <c r="B31" t="str">
-        <v>Fish fillet</v>
+        <v>Paneer</v>
       </c>
       <c r="C31">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D31" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F31" t="str">
-        <v>Pumpkin salad</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G31">
         <v>120</v>
       </c>
       <c r="H31" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I31" t="str">
         <v>{}</v>
@@ -6215,28 +6965,28 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
       </c>
       <c r="B32" t="str">
-        <v>Grilled salmon</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C32">
         <v>150</v>
       </c>
       <c r="D32" t="str">
-        <v>Garlic rice (small portion)</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G32">
         <v>100</v>
       </c>
-      <c r="F32" t="str">
-        <v>Sautéed broccoli</v>
-      </c>
-      <c r="G32">
-        <v>150</v>
-      </c>
       <c r="H32" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I32" t="str">
         <v>{}</v>
@@ -6244,10 +6994,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
+        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
       </c>
       <c r="B33" t="str">
-        <v>Chicken breast</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C33">
         <v>150</v>
@@ -6259,13 +7009,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <v>Smoked salmon salad</v>
+        <v>Pumpkin salad</v>
       </c>
       <c r="G33">
         <v>120</v>
       </c>
       <c r="H33" t="str">
-        <v>Soup style</v>
+        <v>Grilled</v>
       </c>
       <c r="I33" t="str">
         <v>{}</v>
@@ -6273,28 +7023,28 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
+        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
       </c>
       <c r="B34" t="str">
-        <v>Paneer</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C34">
+        <v>150</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Garlic rice (small portion)</v>
+      </c>
+      <c r="E34">
         <v>100</v>
       </c>
-      <c r="D34" t="str">
-        <v>No carb</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
       <c r="F34" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G34">
         <v>150</v>
       </c>
       <c r="H34" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I34" t="str">
         <v>{}</v>
@@ -6302,13 +7052,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
+        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
       </c>
       <c r="B35" t="str">
-        <v>Pork chop</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C35">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D35" t="str">
         <v>No carb</v>
@@ -6317,13 +7067,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="str">
-        <v>Pumpkin salad</v>
+        <v>Smoked salmon salad</v>
       </c>
       <c r="G35">
         <v>120</v>
       </c>
       <c r="H35" t="str">
-        <v>Grilled</v>
+        <v>Soup style</v>
       </c>
       <c r="I35" t="str">
         <v>{}</v>
@@ -6331,13 +7081,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
+        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
       </c>
       <c r="B36" t="str">
-        <v>Pork chop</v>
+        <v>Paneer</v>
       </c>
       <c r="C36">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="D36" t="str">
         <v>No carb</v>
@@ -6346,13 +7096,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="str">
-        <v>Mixed greens salad</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G36">
         <v>150</v>
       </c>
       <c r="H36" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I36" t="str">
         <v>{}</v>
@@ -6360,13 +7110,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
+        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
       </c>
       <c r="B37" t="str">
-        <v>Chicken breast</v>
+        <v>Pork chop</v>
       </c>
       <c r="C37">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D37" t="str">
         <v>No carb</v>
@@ -6375,13 +7125,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <v>Smoked chicken + avocado salad</v>
+        <v>Pumpkin salad</v>
       </c>
       <c r="G37">
         <v>120</v>
       </c>
       <c r="H37" t="str">
-        <v>Tandoori</v>
+        <v>Grilled</v>
       </c>
       <c r="I37" t="str">
         <v>{}</v>
@@ -6389,28 +7139,28 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
       </c>
       <c r="B38" t="str">
-        <v>Fish fillet</v>
+        <v>Pork chop</v>
       </c>
       <c r="C38">
+        <v>180</v>
+      </c>
+      <c r="D38" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Mixed greens salad</v>
+      </c>
+      <c r="G38">
         <v>150</v>
       </c>
-      <c r="D38" t="str">
-        <v>Spaghetti aglio e olio (small portion)</v>
-      </c>
-      <c r="E38">
-        <v>100</v>
-      </c>
-      <c r="F38" t="str">
-        <v>Sautéed broccoli</v>
-      </c>
-      <c r="G38">
-        <v>200</v>
-      </c>
       <c r="H38" t="str">
-        <v>Soup style</v>
+        <v>Grilled</v>
       </c>
       <c r="I38" t="str">
         <v>{}</v>
@@ -6418,28 +7168,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
+        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
       </c>
       <c r="B39" t="str">
-        <v>Lamb (seekh kabab)</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C39">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D39" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>No carb</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39" t="str">
-        <v>Sautéed spinach</v>
+        <v>Smoked chicken + avocado salad</v>
       </c>
       <c r="G39">
         <v>120</v>
       </c>
       <c r="H39" t="str">
-        <v>Curry style</v>
+        <v>Tandoori</v>
       </c>
       <c r="I39" t="str">
         <v>{}</v>
@@ -6447,28 +7197,28 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>lunch_dinner_kofta-dal-jowar-roti</v>
+        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B40" t="str">
-        <v>Veg kofta</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C40">
         <v>150</v>
       </c>
       <c r="D40" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Spaghetti aglio e olio (small portion)</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F40" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G40">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="H40" t="str">
-        <v>Curry style</v>
+        <v>Soup style</v>
       </c>
       <c r="I40" t="str">
         <v>{}</v>
@@ -6476,13 +7226,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
+        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
       </c>
       <c r="B41" t="str">
         <v>Lamb (seekh kabab)</v>
       </c>
       <c r="C41">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D41" t="str">
         <v>Jowar roti (millet)</v>
@@ -6491,13 +7241,13 @@
         <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>Cauliflower</v>
+        <v>Sautéed spinach</v>
       </c>
       <c r="G41">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H41" t="str">
-        <v>Tandoori</v>
+        <v>Curry style</v>
       </c>
       <c r="I41" t="str">
         <v>{}</v>
@@ -6505,25 +7255,25 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>lunch_dinner_fish-curry-rice</v>
+        <v>lunch_dinner_kofta-dal-jowar-roti</v>
       </c>
       <c r="B42" t="str">
-        <v>Fish fillet</v>
+        <v>Veg kofta</v>
       </c>
       <c r="C42">
         <v>150</v>
       </c>
       <c r="D42" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E42">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v/>
-      </c>
-      <c r="G42" t="str">
-        <v/>
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G42">
+        <v>120</v>
       </c>
       <c r="H42" t="str">
         <v>Curry style</v>
@@ -6534,13 +7284,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
+        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
       </c>
       <c r="B43" t="str">
-        <v>Kaala chanaa (black chickpeas)</v>
+        <v>Lamb (seekh kabab)</v>
       </c>
       <c r="C43">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D43" t="str">
         <v>Jowar roti (millet)</v>
@@ -6549,13 +7299,13 @@
         <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>Sweet potato curry</v>
+        <v>Cauliflower</v>
       </c>
       <c r="G43">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H43" t="str">
-        <v>Curry style</v>
+        <v>Tandoori</v>
       </c>
       <c r="I43" t="str">
         <v>{}</v>
@@ -6563,28 +7313,28 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
+        <v>lunch_dinner_fish-curry-rice</v>
       </c>
       <c r="B44" t="str">
-        <v>Smoked salmon</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C44">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D44" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F44" t="str">
-        <v>Avocado &amp; mixed greens</v>
-      </c>
-      <c r="G44">
-        <v>155</v>
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
       </c>
       <c r="H44" t="str">
-        <v>Salad</v>
+        <v>Curry style</v>
       </c>
       <c r="I44" t="str">
         <v>{}</v>
@@ -6592,28 +7342,28 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B45" t="str">
-        <v>Smoked chicken breast</v>
+        <v>Kaala chanaa (black chickpeas)</v>
       </c>
       <c r="C45">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D45" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>Avocado &amp; mixed greens</v>
+        <v>Sweet potato curry</v>
       </c>
       <c r="G45">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="H45" t="str">
-        <v>Salad</v>
+        <v>Curry style</v>
       </c>
       <c r="I45" t="str">
         <v>{}</v>
@@ -6621,28 +7371,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>lunch_dinner_chicken-red-curry-rice</v>
+        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
       </c>
       <c r="B46" t="str">
-        <v>Chicken breast</v>
+        <v>Smoked salmon</v>
       </c>
       <c r="C46">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D46" t="str">
-        <v>Cooked rice</v>
+        <v>No carb</v>
       </c>
       <c r="E46">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F46" t="str">
-        <v>Red curry vegetables</v>
+        <v>Avocado &amp; mixed greens</v>
       </c>
       <c r="G46">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="H46" t="str">
-        <v>Curry style</v>
+        <v>Salad</v>
       </c>
       <c r="I46" t="str">
         <v>{}</v>
@@ -6650,28 +7400,28 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
+        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
       </c>
       <c r="B47" t="str">
-        <v>Chicken breast</v>
+        <v>Smoked chicken breast</v>
       </c>
       <c r="C47">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D47" t="str">
-        <v>Cooked rice</v>
+        <v>No carb</v>
       </c>
       <c r="E47">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F47" t="str">
-        <v>Kimchi + spinach</v>
+        <v>Avocado &amp; mixed greens</v>
       </c>
       <c r="G47">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="H47" t="str">
-        <v>Bowl</v>
+        <v>Salad</v>
       </c>
       <c r="I47" t="str">
         <v>{}</v>
@@ -6679,28 +7429,28 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
+        <v>lunch_dinner_chicken-red-curry-rice</v>
       </c>
       <c r="B48" t="str">
-        <v>Grilled salmon</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C48">
         <v>150</v>
       </c>
       <c r="D48" t="str">
-        <v>Soba noodles</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E48">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="F48" t="str">
-        <v>Bok choy</v>
+        <v>Red curry vegetables</v>
       </c>
       <c r="G48">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H48" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I48" t="str">
         <v>{}</v>
@@ -6708,28 +7458,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
+        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
       </c>
       <c r="B49" t="str">
-        <v>Prawns</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C49">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D49" t="str">
-        <v>Rice noodles</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E49">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F49" t="str">
-        <v>Edamame</v>
+        <v>Kimchi + spinach</v>
       </c>
       <c r="G49">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="H49" t="str">
-        <v>Pan-fried</v>
+        <v>Bowl</v>
       </c>
       <c r="I49" t="str">
         <v>{}</v>
@@ -6737,28 +7487,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>lunch_dinner_miso-chicken-ramen-egg</v>
+        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
       </c>
       <c r="B50" t="str">
-        <v>Chicken breast</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C50">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D50" t="str">
-        <v>Egg noodles</v>
+        <v>Soba noodles</v>
       </c>
       <c r="E50">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F50" t="str">
         <v>Bok choy</v>
       </c>
       <c r="G50">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H50" t="str">
-        <v>Soup style</v>
+        <v>Grilled</v>
       </c>
       <c r="I50" t="str">
         <v>{}</v>
@@ -6766,28 +7516,28 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>lunch_dinner_tofu-edamame-ramen</v>
+        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
       </c>
       <c r="B51" t="str">
-        <v>Firm tofu</v>
+        <v>Prawns</v>
       </c>
       <c r="C51">
         <v>180</v>
       </c>
       <c r="D51" t="str">
-        <v>Egg noodles</v>
+        <v>Rice noodles</v>
       </c>
       <c r="E51">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F51" t="str">
-        <v>Bok choy + edamame</v>
+        <v>Edamame</v>
       </c>
       <c r="G51">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="H51" t="str">
-        <v>Soup style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I51" t="str">
         <v>{}</v>
@@ -6795,28 +7545,28 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>lunch_dinner_butter-chicken-jowar-roti</v>
+        <v>lunch_dinner_miso-chicken-ramen-egg</v>
       </c>
       <c r="B52" t="str">
         <v>Chicken breast</v>
       </c>
       <c r="C52">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D52" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Egg noodles</v>
       </c>
       <c r="E52">
-        <v>1.5</v>
+        <v>120</v>
       </c>
       <c r="F52" t="str">
-        <v>Cauliflower</v>
+        <v>Bok choy</v>
       </c>
       <c r="G52">
         <v>100</v>
       </c>
       <c r="H52" t="str">
-        <v>Curry style</v>
+        <v>Soup style</v>
       </c>
       <c r="I52" t="str">
         <v>{}</v>
@@ -6824,28 +7574,28 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
+        <v>lunch_dinner_tofu-edamame-ramen</v>
       </c>
       <c r="B53" t="str">
-        <v>Chicken breast</v>
+        <v>Firm tofu</v>
       </c>
       <c r="C53">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D53" t="str">
-        <v>Sweet potato</v>
+        <v>Egg noodles</v>
       </c>
       <c r="E53">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F53" t="str">
-        <v>Broccoli</v>
+        <v>Bok choy + edamame</v>
       </c>
       <c r="G53">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="H53" t="str">
-        <v>Grilled</v>
+        <v>Soup style</v>
       </c>
       <c r="I53" t="str">
         <v>{}</v>
@@ -6853,28 +7603,28 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
+        <v>lunch_dinner_butter-chicken-jowar-roti</v>
       </c>
       <c r="B54" t="str">
-        <v>Beef steak</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C54">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D54" t="str">
-        <v>Garlic rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E54">
-        <v>120</v>
+        <v>1.5</v>
       </c>
       <c r="F54" t="str">
-        <v>Bok choy</v>
+        <v>Cauliflower</v>
       </c>
       <c r="G54">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H54" t="str">
-        <v>Pan-fried</v>
+        <v>Curry style</v>
       </c>
       <c r="I54" t="str">
         <v>{}</v>
@@ -6882,28 +7632,28 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
+        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
       </c>
       <c r="B55" t="str">
-        <v>Paneer</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C55">
         <v>150</v>
       </c>
       <c r="D55" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Sweet potato</v>
       </c>
       <c r="E55">
-        <v>1.5</v>
+        <v>150</v>
       </c>
       <c r="F55" t="str">
-        <v>Mixed greens salad</v>
+        <v>Broccoli</v>
       </c>
       <c r="G55">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H55" t="str">
-        <v>Tandoori</v>
+        <v>Grilled</v>
       </c>
       <c r="I55" t="str">
         <v>{}</v>
@@ -6911,28 +7661,28 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
+        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
       </c>
       <c r="B56" t="str">
-        <v>Grilled salmon</v>
+        <v>Beef steak</v>
       </c>
       <c r="C56">
         <v>180</v>
       </c>
       <c r="D56" t="str">
-        <v>Sweet potato</v>
+        <v>Garlic rice</v>
       </c>
       <c r="E56">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F56" t="str">
-        <v>Sautéed spinach</v>
+        <v>Bok choy</v>
       </c>
       <c r="G56">
         <v>120</v>
       </c>
       <c r="H56" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I56" t="str">
         <v>{}</v>
@@ -6940,28 +7690,28 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>lunch_dinner_chicken-biryani-raita</v>
+        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
       </c>
       <c r="B57" t="str">
-        <v>Chicken breast</v>
+        <v>Paneer</v>
       </c>
       <c r="C57">
         <v>150</v>
       </c>
       <c r="D57" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E57">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="F57" t="str">
-        <v/>
-      </c>
-      <c r="G57" t="str">
-        <v/>
+        <v>Mixed greens salad</v>
+      </c>
+      <c r="G57">
+        <v>100</v>
       </c>
       <c r="H57" t="str">
-        <v>Curry style</v>
+        <v>Tandoori</v>
       </c>
       <c r="I57" t="str">
         <v>{}</v>
@@ -6969,28 +7719,28 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>lunch_dinner_fish-moilee-rice</v>
+        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
       </c>
       <c r="B58" t="str">
-        <v>Fish fillet</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C58">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D58" t="str">
-        <v>Cooked rice</v>
+        <v>Sweet potato</v>
       </c>
       <c r="E58">
+        <v>150</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Sautéed spinach</v>
+      </c>
+      <c r="G58">
         <v>120</v>
       </c>
-      <c r="F58" t="str">
-        <v>Mixed veg sabzi</v>
-      </c>
-      <c r="G58">
-        <v>80</v>
-      </c>
       <c r="H58" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I58" t="str">
         <v>{}</v>
@@ -6998,25 +7748,25 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
+        <v>lunch_dinner_chicken-biryani-raita</v>
       </c>
       <c r="B59" t="str">
-        <v>Eggs (whole)</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C59">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D59" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="F59" t="str">
-        <v>Dal</v>
-      </c>
-      <c r="G59">
-        <v>80</v>
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
       </c>
       <c r="H59" t="str">
         <v>Curry style</v>
@@ -7027,28 +7777,28 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>lunch_dinner_chicken-shawarma-bowl</v>
+        <v>lunch_dinner_fish-moilee-rice</v>
       </c>
       <c r="B60" t="str">
-        <v>Chicken breast</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C60">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="D60" t="str">
-        <v>Flatbread</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="F60" t="str">
-        <v>Salad + hummus</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G60">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="H60" t="str">
-        <v>Bowl</v>
+        <v>Curry style</v>
       </c>
       <c r="I60" t="str">
         <v>{}</v>
@@ -7056,25 +7806,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>lunch_dinner_prawn-curry-rice</v>
+        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
       </c>
       <c r="B61" t="str">
-        <v>Prawns</v>
+        <v>Eggs (whole)</v>
       </c>
       <c r="C61">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D61" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E61">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Dal</v>
       </c>
       <c r="G61">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H61" t="str">
         <v>Curry style</v>
@@ -7085,28 +7835,28 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
+        <v>lunch_dinner_chicken-shawarma-bowl</v>
       </c>
       <c r="B62" t="str">
-        <v>Chicken keema</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C62">
+        <v>140</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Flatbread</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Salad + hummus</v>
+      </c>
+      <c r="G62">
         <v>180</v>
       </c>
-      <c r="D62" t="str">
-        <v>Spaghetti</v>
-      </c>
-      <c r="E62">
-        <v>150</v>
-      </c>
-      <c r="F62" t="str">
-        <v>Mixed greens salad</v>
-      </c>
-      <c r="G62">
-        <v>100</v>
-      </c>
       <c r="H62" t="str">
-        <v>Pan-fried</v>
+        <v>Bowl</v>
       </c>
       <c r="I62" t="str">
         <v>{}</v>
@@ -7114,25 +7864,25 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>lunch_dinner_rajma-paneer-bowl</v>
+        <v>lunch_dinner_prawn-curry-rice</v>
       </c>
       <c r="B63" t="str">
-        <v>Paneer + rajma</v>
+        <v>Prawns</v>
       </c>
       <c r="C63">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="D63" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F63" t="str">
-        <v/>
-      </c>
-      <c r="G63" t="str">
-        <v/>
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G63">
+        <v>70</v>
       </c>
       <c r="H63" t="str">
         <v>Curry style</v>
@@ -7143,28 +7893,28 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>lunch_dinner_palak-paneer-jowar-roti</v>
+        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
       </c>
       <c r="B64" t="str">
-        <v>Paneer</v>
+        <v>Chicken keema</v>
       </c>
       <c r="C64">
+        <v>180</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Spaghetti</v>
+      </c>
+      <c r="E64">
         <v>150</v>
       </c>
-      <c r="D64" t="str">
-        <v>Jowar roti (millet)</v>
-      </c>
-      <c r="E64">
-        <v>50</v>
-      </c>
       <c r="F64" t="str">
-        <v>Spinach</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G64">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H64" t="str">
-        <v>Curry style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I64" t="str">
         <v>{}</v>
@@ -7172,13 +7922,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>lunch_dinner_achari-paneer-tikka-dal-salad</v>
+        <v>lunch_dinner_rajma-paneer-bowl</v>
       </c>
       <c r="B65" t="str">
-        <v>Paneer</v>
+        <v>Paneer + rajma</v>
       </c>
       <c r="C65">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="D65" t="str">
         <v>No carb</v>
@@ -7187,13 +7937,13 @@
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v>Dal + salad</v>
-      </c>
-      <c r="G65">
-        <v>250</v>
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
       </c>
       <c r="H65" t="str">
-        <v>Tandoori</v>
+        <v>Curry style</v>
       </c>
       <c r="I65" t="str">
         <v>{}</v>
@@ -7201,25 +7951,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>lunch_dinner_soya-keema-curry-jowar-roti</v>
+        <v>lunch_dinner_palak-paneer-jowar-roti</v>
       </c>
       <c r="B66" t="str">
-        <v>Soya chunks (minced)</v>
+        <v>Paneer</v>
       </c>
       <c r="C66">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="D66" t="str">
         <v>Jowar roti (millet)</v>
       </c>
       <c r="E66">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F66" t="str">
-        <v/>
-      </c>
-      <c r="G66" t="str">
-        <v/>
+        <v>Spinach</v>
+      </c>
+      <c r="G66">
+        <v>200</v>
       </c>
       <c r="H66" t="str">
         <v>Curry style</v>
@@ -7230,13 +7980,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>lunch_dinner_chole-paneer-bowl-salad</v>
+        <v>lunch_dinner_achari-paneer-tikka-dal-salad</v>
       </c>
       <c r="B67" t="str">
-        <v>Paneer + chole</v>
+        <v>Paneer</v>
       </c>
       <c r="C67">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="D67" t="str">
         <v>No carb</v>
@@ -7245,13 +7995,13 @@
         <v>0</v>
       </c>
       <c r="F67" t="str">
-        <v>Mixed greens salad</v>
+        <v>Dal + salad</v>
       </c>
       <c r="G67">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H67" t="str">
-        <v>Bowl</v>
+        <v>Tandoori</v>
       </c>
       <c r="I67" t="str">
         <v>{}</v>
@@ -7259,25 +8009,25 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>lunch_dinner_kadai-chicken-jowar-roti</v>
+        <v>lunch_dinner_soya-keema-curry-jowar-roti</v>
       </c>
       <c r="B68" t="str">
-        <v>Chicken breast</v>
+        <v>Soya chunks (minced)</v>
       </c>
       <c r="C68">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="D68" t="str">
         <v>Jowar roti (millet)</v>
       </c>
       <c r="E68">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F68" t="str">
-        <v>Capsicum + salad</v>
-      </c>
-      <c r="G68">
-        <v>80</v>
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
       </c>
       <c r="H68" t="str">
         <v>Curry style</v>
@@ -7288,28 +8038,28 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>lunch_dinner_tandoori-fish-tikka-veg-roti</v>
+        <v>lunch_dinner_chole-paneer-bowl-salad</v>
       </c>
       <c r="B69" t="str">
-        <v>Fish fillet</v>
+        <v>Paneer + chole</v>
       </c>
       <c r="C69">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="D69" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>No carb</v>
       </c>
       <c r="E69">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F69" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G69">
         <v>100</v>
       </c>
       <c r="H69" t="str">
-        <v>Tandoori</v>
+        <v>Bowl</v>
       </c>
       <c r="I69" t="str">
         <v>{}</v>
@@ -7317,25 +8067,25 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>lunch_dinner_chicken-keema-matar-jowar-roti</v>
+        <v>lunch_dinner_kadai-chicken-jowar-roti</v>
       </c>
       <c r="B70" t="str">
-        <v>Chicken keema</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C70">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D70" t="str">
         <v>Jowar roti (millet)</v>
       </c>
       <c r="E70">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F70" t="str">
-        <v>Peas / edamame</v>
+        <v>Capsicum + salad</v>
       </c>
       <c r="G70">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H70" t="str">
         <v>Curry style</v>
@@ -7346,28 +8096,28 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>lunch_dinner_beef-bulgogi-bowl</v>
+        <v>lunch_dinner_tandoori-fish-tikka-veg-roti</v>
       </c>
       <c r="B71" t="str">
-        <v>Beef steak (lean sirloin)</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C71">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="D71" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E71">
+        <v>40</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G71">
         <v>100</v>
       </c>
-      <c r="F71" t="str">
-        <v>Kimchi + spinach</v>
-      </c>
-      <c r="G71">
-        <v>180</v>
-      </c>
       <c r="H71" t="str">
-        <v>Bowl</v>
+        <v>Tandoori</v>
       </c>
       <c r="I71" t="str">
         <v>{}</v>
@@ -7375,28 +8125,28 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>lunch_dinner_tofu-veg-bibimbap</v>
+        <v>lunch_dinner_chicken-keema-matar-jowar-roti</v>
       </c>
       <c r="B72" t="str">
-        <v>Firm tofu + egg</v>
+        <v>Chicken keema</v>
       </c>
       <c r="C72">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="D72" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E72">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="F72" t="str">
-        <v>Kimchi + spinach namul</v>
+        <v>Peas / edamame</v>
       </c>
       <c r="G72">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H72" t="str">
-        <v>Bowl</v>
+        <v>Curry style</v>
       </c>
       <c r="I72" t="str">
         <v>{}</v>
@@ -7404,25 +8154,25 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>lunch_dinner_oyakodon-side-salad</v>
+        <v>lunch_dinner_beef-bulgogi-bowl</v>
       </c>
       <c r="B73" t="str">
-        <v>Chicken breast + egg</v>
+        <v>Beef steak (lean sirloin)</v>
       </c>
       <c r="C73">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="D73" t="str">
         <v>Cooked rice</v>
       </c>
       <c r="E73">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F73" t="str">
-        <v>Side salad</v>
+        <v>Kimchi + spinach</v>
       </c>
       <c r="G73">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="H73" t="str">
         <v>Bowl</v>
@@ -7433,13 +8183,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>lunch_dinner_dubu-jorim-rice-kimchi</v>
+        <v>lunch_dinner_tofu-veg-bibimbap</v>
       </c>
       <c r="B74" t="str">
-        <v>Firm tofu</v>
+        <v>Firm tofu + egg</v>
       </c>
       <c r="C74">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D74" t="str">
         <v>Cooked rice</v>
@@ -7448,13 +8198,13 @@
         <v>90</v>
       </c>
       <c r="F74" t="str">
-        <v>Kimchi</v>
+        <v>Kimchi + spinach namul</v>
       </c>
       <c r="G74">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="H74" t="str">
-        <v>Curry style</v>
+        <v>Bowl</v>
       </c>
       <c r="I74" t="str">
         <v>{}</v>
@@ -7462,10 +8212,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>lunch_dinner_home-style-tofu-chicken-stir-fry</v>
+        <v>lunch_dinner_oyakodon-side-salad</v>
       </c>
       <c r="B75" t="str">
-        <v>Chicken breast + tofu</v>
+        <v>Chicken breast + egg</v>
       </c>
       <c r="C75">
         <v>240</v>
@@ -7474,16 +8224,16 @@
         <v>Cooked rice</v>
       </c>
       <c r="E75">
+        <v>120</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Side salad</v>
+      </c>
+      <c r="G75">
         <v>80</v>
       </c>
-      <c r="F75" t="str">
-        <v>Broccoli</v>
-      </c>
-      <c r="G75">
-        <v>150</v>
-      </c>
       <c r="H75" t="str">
-        <v>Pan-fried</v>
+        <v>Bowl</v>
       </c>
       <c r="I75" t="str">
         <v>{}</v>
@@ -7491,28 +8241,28 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>lunch_dinner_vietnamese-lemongrass-chicken-bowl</v>
+        <v>lunch_dinner_dubu-jorim-rice-kimchi</v>
       </c>
       <c r="B76" t="str">
-        <v>Chicken breast</v>
+        <v>Firm tofu</v>
       </c>
       <c r="C76">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="D76" t="str">
-        <v>Rice noodles</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E76">
+        <v>90</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Kimchi</v>
+      </c>
+      <c r="G76">
         <v>100</v>
       </c>
-      <c r="F76" t="str">
-        <v>Herb salad + pickles</v>
-      </c>
-      <c r="G76">
-        <v>170</v>
-      </c>
       <c r="H76" t="str">
-        <v>Bowl</v>
+        <v>Curry style</v>
       </c>
       <c r="I76" t="str">
         <v>{}</v>
@@ -7520,28 +8270,28 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>lunch_dinner_cantonese-steamed-fish-edamame</v>
+        <v>lunch_dinner_home-style-tofu-chicken-stir-fry</v>
       </c>
       <c r="B77" t="str">
-        <v>Fish fillet</v>
+        <v>Chicken breast + tofu</v>
       </c>
       <c r="C77">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="D77" t="str">
         <v>Cooked rice</v>
       </c>
       <c r="E77">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F77" t="str">
-        <v>Bok choy + edamame</v>
+        <v>Broccoli</v>
       </c>
       <c r="G77">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="H77" t="str">
-        <v>Steamed</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I77" t="str">
         <v>{}</v>
@@ -7549,25 +8299,25 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>lunch_dinner_chicken-bulgogi-bowl</v>
+        <v>lunch_dinner_vietnamese-lemongrass-chicken-bowl</v>
       </c>
       <c r="B78" t="str">
         <v>Chicken breast</v>
       </c>
       <c r="C78">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D78" t="str">
-        <v>Cooked rice</v>
+        <v>Rice noodles</v>
       </c>
       <c r="E78">
         <v>100</v>
       </c>
       <c r="F78" t="str">
-        <v>Kimchi + bok choy</v>
+        <v>Herb salad + pickles</v>
       </c>
       <c r="G78">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="H78" t="str">
         <v>Bowl</v>
@@ -7578,28 +8328,28 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>lunch_dinner_chicken-souvlaki-tzatziki-greek-salad</v>
+        <v>lunch_dinner_cantonese-steamed-fish-edamame</v>
       </c>
       <c r="B79" t="str">
-        <v>Chicken breast</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C79">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D79" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F79" t="str">
-        <v>Greek salad + tzatziki</v>
+        <v>Bok choy + edamame</v>
       </c>
       <c r="G79">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="H79" t="str">
-        <v>Grilled</v>
+        <v>Steamed</v>
       </c>
       <c r="I79" t="str">
         <v>{}</v>
@@ -7607,28 +8357,28 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>lunch_dinner_baked-feta-chickpea-traybake</v>
+        <v>lunch_dinner_chicken-bulgogi-bowl</v>
       </c>
       <c r="B80" t="str">
-        <v>Feta + chickpeas</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C80">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="D80" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F80" t="str">
-        <v>Roast vegetables + greens</v>
+        <v>Kimchi + bok choy</v>
       </c>
       <c r="G80">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="H80" t="str">
-        <v>Plate</v>
+        <v>Bowl</v>
       </c>
       <c r="I80" t="str">
         <v>{}</v>
@@ -7636,28 +8386,28 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>lunch_dinner_tuna-nicoise-salad</v>
+        <v>lunch_dinner_chicken-souvlaki-tzatziki-greek-salad</v>
       </c>
       <c r="B81" t="str">
-        <v>Tuna + egg</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C81">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="D81" t="str">
-        <v>Sweet potato</v>
+        <v>No carb</v>
       </c>
       <c r="E81">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F81" t="str">
-        <v>Salad + olives</v>
+        <v>Greek salad + tzatziki</v>
       </c>
       <c r="G81">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="H81" t="str">
-        <v>Salad</v>
+        <v>Grilled</v>
       </c>
       <c r="I81" t="str">
         <v>{}</v>
@@ -7665,28 +8415,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>lunch_dinner_halloumi-roasted-veg-quinoa-bowl</v>
+        <v>lunch_dinner_baked-feta-chickpea-traybake</v>
       </c>
       <c r="B82" t="str">
-        <v>Halloumi</v>
+        <v>Feta + chickpeas</v>
       </c>
       <c r="C82">
+        <v>220</v>
+      </c>
+      <c r="D82" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Roast vegetables + greens</v>
+      </c>
+      <c r="G82">
         <v>100</v>
       </c>
-      <c r="D82" t="str">
-        <v>Quinoa</v>
-      </c>
-      <c r="E82">
-        <v>120</v>
-      </c>
-      <c r="F82" t="str">
-        <v>Roast broccoli</v>
-      </c>
-      <c r="G82">
-        <v>120</v>
-      </c>
       <c r="H82" t="str">
-        <v>Bowl</v>
+        <v>Plate</v>
       </c>
       <c r="I82" t="str">
         <v>{}</v>
@@ -7694,28 +8444,28 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>lunch_dinner_chicken-white-bean-stew</v>
+        <v>lunch_dinner_tuna-nicoise-salad</v>
       </c>
       <c r="B83" t="str">
-        <v>Chicken breast + white beans</v>
+        <v>Tuna + egg</v>
       </c>
       <c r="C83">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="D83" t="str">
-        <v>No carb</v>
+        <v>Sweet potato</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F83" t="str">
-        <v>Spinach + tomato</v>
+        <v>Salad + olives</v>
       </c>
       <c r="G83">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="H83" t="str">
-        <v>Soup style</v>
+        <v>Salad</v>
       </c>
       <c r="I83" t="str">
         <v>{}</v>
@@ -7723,28 +8473,28 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>lunch_dinner_chickpea-pasta-tuna-tomato</v>
+        <v>lunch_dinner_halloumi-roasted-veg-quinoa-bowl</v>
       </c>
       <c r="B84" t="str">
-        <v>Tuna</v>
+        <v>Halloumi</v>
       </c>
       <c r="C84">
+        <v>100</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Quinoa</v>
+      </c>
+      <c r="E84">
         <v>120</v>
       </c>
-      <c r="D84" t="str">
-        <v>Chickpea pasta</v>
-      </c>
-      <c r="E84">
-        <v>155</v>
-      </c>
       <c r="F84" t="str">
-        <v>Arrabbiata + side salad</v>
+        <v>Roast broccoli</v>
       </c>
       <c r="G84">
         <v>120</v>
       </c>
       <c r="H84" t="str">
-        <v>Plate</v>
+        <v>Bowl</v>
       </c>
       <c r="I84" t="str">
         <v>{}</v>
@@ -7752,28 +8502,28 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>lunch_dinner_chicken-ricotta-carbonara-style-spaghetti</v>
+        <v>lunch_dinner_chicken-white-bean-stew</v>
       </c>
       <c r="B85" t="str">
-        <v>Chicken breast + ricotta</v>
+        <v>Chicken breast + white beans</v>
       </c>
       <c r="C85">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="D85" t="str">
-        <v>Spaghetti</v>
+        <v>No carb</v>
       </c>
       <c r="E85">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F85" t="str">
-        <v/>
-      </c>
-      <c r="G85" t="str">
-        <v/>
+        <v>Spinach + tomato</v>
+      </c>
+      <c r="G85">
+        <v>140</v>
       </c>
       <c r="H85" t="str">
-        <v>Plate</v>
+        <v>Soup style</v>
       </c>
       <c r="I85" t="str">
         <v>{}</v>
@@ -7781,28 +8531,28 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>lunch_dinner_mackerel-quinoa-salad</v>
+        <v>lunch_dinner_chickpea-pasta-tuna-tomato</v>
       </c>
       <c r="B86" t="str">
-        <v>Mackerel</v>
+        <v>Tuna</v>
       </c>
       <c r="C86">
         <v>120</v>
       </c>
       <c r="D86" t="str">
-        <v>Quinoa</v>
+        <v>Chickpea pasta</v>
       </c>
       <c r="E86">
+        <v>155</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Arrabbiata + side salad</v>
+      </c>
+      <c r="G86">
         <v>120</v>
       </c>
-      <c r="F86" t="str">
-        <v>Salad + avocado</v>
-      </c>
-      <c r="G86">
-        <v>160</v>
-      </c>
       <c r="H86" t="str">
-        <v>Salad</v>
+        <v>Plate</v>
       </c>
       <c r="I86" t="str">
         <v>{}</v>
@@ -7810,28 +8560,28 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>lunch_dinner_chicken-ricotta-carbonara-style-spaghetti</v>
       </c>
       <c r="B87" t="str">
-        <v>Plant Shake</v>
+        <v>Chicken breast + ricotta</v>
       </c>
       <c r="C87">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="D87" t="str">
-        <v>Mixed Fruit</v>
+        <v>Spaghetti</v>
       </c>
       <c r="E87">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F87" t="str">
-        <v>Almonds</v>
-      </c>
-      <c r="G87">
-        <v>5</v>
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
       </c>
       <c r="H87" t="str">
-        <v>Snack</v>
+        <v>Plate</v>
       </c>
       <c r="I87" t="str">
         <v>{}</v>
@@ -7839,28 +8589,28 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>lunch_dinner_mackerel-quinoa-salad</v>
       </c>
       <c r="B88" t="str">
-        <v>Plant Shake</v>
+        <v>Mackerel</v>
       </c>
       <c r="C88">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="D88" t="str">
-        <v>Chaat &amp; Bhel</v>
+        <v>Quinoa</v>
       </c>
       <c r="E88">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F88" t="str">
-        <v/>
-      </c>
-      <c r="G88" t="str">
-        <v/>
+        <v>Salad + avocado</v>
+      </c>
+      <c r="G88">
+        <v>160</v>
       </c>
       <c r="H88" t="str">
-        <v>Street Food Twist</v>
+        <v>Salad</v>
       </c>
       <c r="I88" t="str">
         <v>{}</v>
@@ -7868,25 +8618,25 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>lunch_dinner_grilled-chicken-veg-pasta</v>
       </c>
       <c r="B89" t="str">
-        <v/>
+        <v>Chicken breast</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D89" t="str">
-        <v>No carb</v>
+        <v>Spaghetti</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F89" t="str">
-        <v/>
-      </c>
-      <c r="G89" t="str">
-        <v/>
+        <v>Sabzi + salad</v>
+      </c>
+      <c r="G89">
+        <v>180</v>
       </c>
       <c r="H89" t="str">
         <v>Grilled</v>
@@ -7897,28 +8647,28 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>lunch_dinner_chicken-shawarma-plate-garlic-rice</v>
       </c>
       <c r="B90" t="str">
-        <v/>
+        <v>Chicken breast</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D90" t="str">
-        <v>No carb</v>
+        <v>Garlic rice</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F90" t="str">
-        <v/>
-      </c>
-      <c r="G90" t="str">
-        <v/>
+        <v>Salad + hummus</v>
+      </c>
+      <c r="G90">
+        <v>120</v>
       </c>
       <c r="H90" t="str">
-        <v>Grilled</v>
+        <v>Plate</v>
       </c>
       <c r="I90" t="str">
         <v>{}</v>
@@ -7926,28 +8676,28 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>lunch_dinner_plain-chicken-tikka-plate</v>
       </c>
       <c r="B91" t="str">
-        <v>Mixed nuts &amp; seeds</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C91">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="D91" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F91" t="str">
-        <v/>
-      </c>
-      <c r="G91" t="str">
-        <v/>
+        <v>Mixed greens salad</v>
+      </c>
+      <c r="G91">
+        <v>100</v>
       </c>
       <c r="H91" t="str">
-        <v>Raw</v>
+        <v>Tandoori</v>
       </c>
       <c r="I91" t="str">
         <v>{}</v>
@@ -7955,28 +8705,28 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>lunch_dinner_pesto-millet-pasta-chicken</v>
       </c>
       <c r="B92" t="str">
-        <v/>
+        <v>Chicken breast</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D92" t="str">
-        <v>Sweet potato</v>
+        <v>Millet pasta</v>
       </c>
       <c r="E92">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F92" t="str">
-        <v/>
-      </c>
-      <c r="G92" t="str">
-        <v/>
+        <v>Cherry tomatoes</v>
+      </c>
+      <c r="G92">
+        <v>50</v>
       </c>
       <c r="H92" t="str">
-        <v>Chaat</v>
+        <v>Plate</v>
       </c>
       <c r="I92" t="str">
         <v>{}</v>
@@ -7984,19 +8734,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>lunch_dinner_aglio-olio-millet-pasta-prawns</v>
       </c>
       <c r="B93" t="str">
-        <v>Kaala chana</v>
+        <v>Prawns</v>
       </c>
       <c r="C93">
         <v>150</v>
       </c>
       <c r="D93" t="str">
-        <v>No carb</v>
+        <v>Millet pasta</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F93" t="str">
         <v/>
@@ -8005,7 +8755,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Chaat</v>
+        <v>Plate</v>
       </c>
       <c r="I93" t="str">
         <v>{}</v>
@@ -8013,28 +8763,28 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>lunch_dinner_salmon-avocado-salad-fresh-grilled</v>
       </c>
       <c r="B94" t="str">
-        <v/>
+        <v>Grilled salmon</v>
       </c>
       <c r="C94">
+        <v>120</v>
+      </c>
+      <c r="D94" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E94">
         <v>0</v>
       </c>
-      <c r="D94" t="str">
-        <v>Whole wheat toast</v>
-      </c>
-      <c r="E94">
-        <v>1</v>
-      </c>
       <c r="F94" t="str">
-        <v>Avocado</v>
+        <v>Avocado + greens</v>
       </c>
       <c r="G94">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="H94" t="str">
-        <v>Toast</v>
+        <v>Salad</v>
       </c>
       <c r="I94" t="str">
         <v>{}</v>
@@ -8042,13 +8792,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+        <v>lunch_dinner_smoked-chicken-salad-full</v>
       </c>
       <c r="B95" t="str">
-        <v>Eggs (whole)</v>
+        <v>Smoked chicken breast</v>
       </c>
       <c r="C95">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D95" t="str">
         <v>No carb</v>
@@ -8057,13 +8807,13 @@
         <v>0</v>
       </c>
       <c r="F95" t="str">
-        <v>Raw vegetable sticks</v>
+        <v>Avocado + greens</v>
       </c>
       <c r="G95">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="H95" t="str">
-        <v>Snack</v>
+        <v>Salad</v>
       </c>
       <c r="I95" t="str">
         <v>{}</v>
@@ -8071,13 +8821,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>snack_edamame-sea-salt</v>
+        <v>lunch_dinner_hummus-salad-protein-boosted</v>
       </c>
       <c r="B96" t="str">
-        <v>Edamame</v>
+        <v>Chicken breast + hummus</v>
       </c>
       <c r="C96">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D96" t="str">
         <v>No carb</v>
@@ -8086,13 +8836,13 @@
         <v>0</v>
       </c>
       <c r="F96" t="str">
-        <v/>
-      </c>
-      <c r="G96" t="str">
-        <v/>
+        <v>Salad + raw veg</v>
+      </c>
+      <c r="G96">
+        <v>180</v>
       </c>
       <c r="H96" t="str">
-        <v>Steamed</v>
+        <v>Bowl</v>
       </c>
       <c r="I96" t="str">
         <v>{}</v>
@@ -8100,28 +8850,28 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>snack_paneer-tikka-skewers</v>
+        <v>lunch_dinner_sweet-potato-kaala-chana-leaner</v>
       </c>
       <c r="B97" t="str">
-        <v>Paneer</v>
+        <v>Kaala chanaa (black chickpeas)</v>
       </c>
       <c r="C97">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="D97" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet) + sweet potato</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F97" t="str">
-        <v>Mixed greens</v>
-      </c>
-      <c r="G97">
-        <v>60</v>
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
       </c>
       <c r="H97" t="str">
-        <v>Tandoori</v>
+        <v>Curry style</v>
       </c>
       <c r="I97" t="str">
         <v>{}</v>
@@ -8129,36 +8879,471 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>lunch_dinner_paneer-cutlets-dal-salad</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Paneer cutlets + dal</v>
+      </c>
+      <c r="C98">
+        <v>260</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Besan + breadcrumbs</v>
+      </c>
+      <c r="E98">
+        <v>30</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Mixed greens salad</v>
+      </c>
+      <c r="G98">
+        <v>100</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Pan-fried</v>
+      </c>
+      <c r="I98" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>snack_fruit-almonds-plant-shake</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Plant Shake</v>
+      </c>
+      <c r="C99">
+        <v>25</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Mixed Fruit</v>
+      </c>
+      <c r="E99">
+        <v>100</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Almonds</v>
+      </c>
+      <c r="G99">
+        <v>5</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Snack</v>
+      </c>
+      <c r="I99" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>snack_chaat-bhel-protein-shake</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Plant Shake</v>
+      </c>
+      <c r="C100">
+        <v>25</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Chaat &amp; Bhel</v>
+      </c>
+      <c r="E100">
+        <v>150</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v>Street Food Twist</v>
+      </c>
+      <c r="I100" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>snack_greek-yogurt-berry-bowl</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v>Grilled</v>
+      </c>
+      <c r="I101" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v>Grilled</v>
+      </c>
+      <c r="I102" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>snack_nuts-seeds-protein-shake</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Mixed nuts &amp; seeds</v>
+      </c>
+      <c r="C103">
+        <v>30</v>
+      </c>
+      <c r="D103" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v>Raw</v>
+      </c>
+      <c r="I103" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>snack_sweet-potato-chaat</v>
+      </c>
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Sweet potato</v>
+      </c>
+      <c r="E104">
+        <v>150</v>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I104" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>snack_kaala-chana-chaat</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Kaala chana</v>
+      </c>
+      <c r="C105">
+        <v>150</v>
+      </c>
+      <c r="D105" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v>Chaat</v>
+      </c>
+      <c r="I105" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>snack_avocado-cheese-toast</v>
+      </c>
+      <c r="B106" t="str">
+        <v/>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Whole wheat toast</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Avocado</v>
+      </c>
+      <c r="G106">
+        <v>50</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Toast</v>
+      </c>
+      <c r="I106" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Eggs (whole)</v>
+      </c>
+      <c r="C107">
+        <v>100</v>
+      </c>
+      <c r="D107" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Raw vegetable sticks</v>
+      </c>
+      <c r="G107">
+        <v>100</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Snack</v>
+      </c>
+      <c r="I107" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>snack_edamame-sea-salt</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Edamame</v>
+      </c>
+      <c r="C108">
+        <v>150</v>
+      </c>
+      <c r="D108" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v>Steamed</v>
+      </c>
+      <c r="I108" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>snack_paneer-tikka-skewers</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Paneer</v>
+      </c>
+      <c r="C109">
+        <v>80</v>
+      </c>
+      <c r="D109" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Mixed greens</v>
+      </c>
+      <c r="G109">
+        <v>60</v>
+      </c>
+      <c r="H109" t="str">
+        <v>Tandoori</v>
+      </c>
+      <c r="I109" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
         <v>snack_overnight-oats-whey-bowl</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B110" t="str">
         <v>Milk</v>
       </c>
-      <c r="C98">
+      <c r="C110">
         <v>150</v>
       </c>
-      <c r="D98" t="str">
+      <c r="D110" t="str">
         <v>Rolled oats</v>
       </c>
-      <c r="E98">
+      <c r="E110">
         <v>25</v>
       </c>
-      <c r="F98" t="str">
+      <c r="F110" t="str">
         <v>Mixed berries</v>
       </c>
-      <c r="G98">
+      <c r="G110">
         <v>60</v>
       </c>
-      <c r="H98" t="str">
+      <c r="H110" t="str">
         <v>Bowl</v>
       </c>
-      <c r="I98" t="str">
+      <c r="I110" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>snack_hummus-salad</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Hummus</v>
+      </c>
+      <c r="C111">
+        <v>60</v>
+      </c>
+      <c r="D111" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Salad + raw veg</v>
+      </c>
+      <c r="G111">
+        <v>180</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Snack</v>
+      </c>
+      <c r="I111" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>snack_acai-bowl</v>
+      </c>
+      <c r="B112" t="str">
+        <v/>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Acai + fruit</v>
+      </c>
+      <c r="E112">
+        <v>100</v>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v>Bowl</v>
+      </c>
+      <c r="I112" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>snack_paneer-cutlets</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Paneer</v>
+      </c>
+      <c r="C113">
+        <v>55</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Besan + breadcrumbs</v>
+      </c>
+      <c r="E113">
+        <v>16</v>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v>Pan-fried</v>
+      </c>
+      <c r="I113" t="str">
         <v>{}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I113"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/exports/meal_database_architecture_v1.xlsx
+++ b/exports/meal_database_architecture_v1.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P113"/>
+  <dimension ref="A1:P111"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1255,34 +1255,34 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>breakfast_paneer-egg-white-bhurji-toast</v>
+        <v>breakfast_anda-bhurji-toast</v>
       </c>
       <c r="B18" t="str">
         <v>breakfast</v>
       </c>
       <c r="C18" t="str">
-        <v>Paneer &amp; egg-white bhurji + toast</v>
+        <v>Anda bhurji + toast</v>
       </c>
       <c r="D18" t="str">
-        <v>Paneer &amp; Egg-White Bhurji</v>
+        <v>Anda bhurji + toast</v>
       </c>
       <c r="E18" t="str">
-        <v>Paneer &amp; egg-white bhurji + toast</v>
+        <v>Anda bhurji + toast</v>
       </c>
       <c r="F18" t="str">
         <v>Indian</v>
       </c>
       <c r="G18">
-        <v>556</v>
+        <v>490</v>
       </c>
       <c r="H18">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I18">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J18">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K18" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1297,42 +1297,42 @@
         <v>1</v>
       </c>
       <c r="O18" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"toast","effort":"low","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"toast","effort":"low","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P18" t="str">
-        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"low","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":548,"delta_kcal":8,"tolerance_kcal":111.2},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"low","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":474,"delta_kcal":16,"tolerance_kcal":98},"issues":[]}}</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>breakfast_anda-bhurji-toast</v>
+        <v>breakfast_sardines-toast-avocado</v>
       </c>
       <c r="B19" t="str">
         <v>breakfast</v>
       </c>
       <c r="C19" t="str">
-        <v>Anda bhurji + toast</v>
+        <v>Sardines on toast + avocado</v>
       </c>
       <c r="D19" t="str">
-        <v>Anda bhurji + toast</v>
+        <v>Sardines on Toast + Avocado</v>
       </c>
       <c r="E19" t="str">
-        <v>Anda bhurji + toast</v>
+        <v>Sardines on toast + avocado</v>
       </c>
       <c r="F19" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G19">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="H19">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I19">
         <v>31</v>
       </c>
       <c r="J19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K19" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1347,42 +1347,42 @@
         <v>1</v>
       </c>
       <c r="O19" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"toast","effort":"low","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P19" t="str">
-        <v>{"macros_p":38,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"low","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":474,"delta_kcal":16,"tolerance_kcal":98},"issues":[]}}</v>
+        <v>{"macros_p":39,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":487,"delta_kcal":7,"tolerance_kcal":98.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>breakfast_sardines-toast-avocado</v>
+        <v>breakfast_shakshuka-feta</v>
       </c>
       <c r="B20" t="str">
         <v>breakfast</v>
       </c>
       <c r="C20" t="str">
-        <v>Sardines on toast + avocado</v>
+        <v>Shakshuka with feta</v>
       </c>
       <c r="D20" t="str">
-        <v>Sardines on Toast + Avocado</v>
+        <v>Shakshuka with feta</v>
       </c>
       <c r="E20" t="str">
-        <v>Sardines on toast + avocado</v>
+        <v>Shakshuka with feta</v>
       </c>
       <c r="F20" t="str">
         <v>Continental</v>
       </c>
       <c r="G20">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="H20">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I20">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J20">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K20" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1397,42 +1397,42 @@
         <v>1</v>
       </c>
       <c r="O20" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P20" t="str">
-        <v>{"macros_p":39,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"toast","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":487,"delta_kcal":7,"tolerance_kcal":98.8},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":500,"delta_kcal":4,"tolerance_kcal":100.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>breakfast_shakshuka-feta</v>
+        <v>breakfast_cottage-cheese-smoked-salmon-bowl</v>
       </c>
       <c r="B21" t="str">
         <v>breakfast</v>
       </c>
       <c r="C21" t="str">
-        <v>Shakshuka with feta</v>
+        <v>Cottage cheese &amp; smoked salmon bowl</v>
       </c>
       <c r="D21" t="str">
-        <v>Shakshuka with feta</v>
+        <v>Cottage Cheese &amp; Smoked Salmon</v>
       </c>
       <c r="E21" t="str">
-        <v>Shakshuka with feta</v>
+        <v>Cottage cheese &amp; smoked salmon bowl</v>
       </c>
       <c r="F21" t="str">
         <v>Continental</v>
       </c>
       <c r="G21">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="H21">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I21">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J21">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K21" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1447,48 +1447,48 @@
         <v>1</v>
       </c>
       <c r="O21" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P21" t="str">
-        <v>{"macros_p":40,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":500,"delta_kcal":4,"tolerance_kcal":100.8},"issues":[]}}</v>
+        <v>{"macros_p":44,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":491,"delta_kcal":3,"tolerance_kcal":98.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>breakfast_cottage-cheese-smoked-salmon-bowl</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti</v>
       </c>
       <c r="B22" t="str">
-        <v>breakfast</v>
+        <v>lunch_dinner</v>
       </c>
       <c r="C22" t="str">
-        <v>Cottage cheese &amp; smoked salmon bowl</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="D22" t="str">
-        <v>Cottage Cheese &amp; Smoked Salmon</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="E22" t="str">
-        <v>Cottage cheese &amp; smoked salmon bowl</v>
+        <v>Chicken curry + jowar roti</v>
       </c>
       <c r="F22" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G22">
-        <v>494</v>
+        <v>702</v>
       </c>
       <c r="H22">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="I22">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="J22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K22" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L22" t="str">
-        <v>assumptions_v2026_08_03</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M22" t="str">
         <v>seed_v1</v>
@@ -1497,42 +1497,42 @@
         <v>1</v>
       </c>
       <c r="O22" t="str">
-        <v>{"meal_type":"breakfast","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P22" t="str">
-        <v>{"macros_p":44,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":491,"delta_kcal":3,"tolerance_kcal":98.8},"issues":[]}}</v>
+        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":676,"delta_kcal":26,"tolerance_kcal":140.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti</v>
+        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B23" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C23" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
       </c>
       <c r="D23" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Salmon + Veg + Aglio Olio</v>
       </c>
       <c r="E23" t="str">
-        <v>Chicken curry + jowar roti</v>
+        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
       </c>
       <c r="F23" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G23">
-        <v>702</v>
+        <v>669</v>
       </c>
       <c r="H23">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I23">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="J23">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K23" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1547,42 +1547,42 @@
         <v>1</v>
       </c>
       <c r="O23" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"continental","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P23" t="str">
-        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":676,"delta_kcal":26,"tolerance_kcal":140.4},"issues":[]}}</v>
+        <v>{"macros_p":46,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":688,"delta_kcal":19,"tolerance_kcal":133.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_rajma-chawal-raita</v>
       </c>
       <c r="B24" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C24" t="str">
-        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="D24" t="str">
-        <v>Salmon + Veg + Aglio Olio</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="E24" t="str">
-        <v>Grilled salmon fillet + sauteed veg + spaghetti aglio e olio</v>
+        <v>Rajma chawal + raita</v>
       </c>
       <c r="F24" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G24">
-        <v>669</v>
+        <v>482</v>
       </c>
       <c r="H24">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I24">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="J24">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K24" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1597,42 +1597,42 @@
         <v>1</v>
       </c>
       <c r="O24" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"continental","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P24" t="str">
-        <v>{"macros_p":46,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":688,"delta_kcal":19,"tolerance_kcal":133.8},"issues":[]}}</v>
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":482,"delta_kcal":0,"tolerance_kcal":96.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lunch_dinner_rajma-chawal-raita</v>
+        <v>lunch_dinner_chole-jowar-roti-raita</v>
       </c>
       <c r="B25" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C25" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="D25" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="E25" t="str">
-        <v>Rajma chawal + raita</v>
+        <v>Chole + jowar roti + raita</v>
       </c>
       <c r="F25" t="str">
         <v>Indian</v>
       </c>
       <c r="G25">
-        <v>482</v>
+        <v>726</v>
       </c>
       <c r="H25">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I25">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="J25">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K25" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1647,42 +1647,42 @@
         <v>1</v>
       </c>
       <c r="O25" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P25" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":482,"delta_kcal":0,"tolerance_kcal":96.4},"issues":[]}}</v>
+        <v>{"macros_p":27,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":722,"delta_kcal":4,"tolerance_kcal":145.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lunch_dinner_chole-jowar-roti-raita</v>
+        <v>lunch_dinner_vietnamese-chicken-pho</v>
       </c>
       <c r="B26" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C26" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="D26" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="E26" t="str">
-        <v>Chole + jowar roti + raita</v>
+        <v>Vietnamese chicken pho</v>
       </c>
       <c r="F26" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G26">
-        <v>726</v>
+        <v>394</v>
       </c>
       <c r="H26">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="I26">
-        <v>113</v>
+        <v>31</v>
       </c>
       <c r="J26">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K26" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1697,42 +1697,42 @@
         <v>1</v>
       </c>
       <c r="O26" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P26" t="str">
-        <v>{"macros_p":27,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":722,"delta_kcal":4,"tolerance_kcal":145.2},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":374,"delta_kcal":20,"tolerance_kcal":78.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lunch_dinner_vietnamese-chicken-pho</v>
+        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
       </c>
       <c r="B27" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C27" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Grilled steak + mixed greens salad</v>
       </c>
       <c r="D27" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Steak + Mixed Greens</v>
       </c>
       <c r="E27" t="str">
-        <v>Vietnamese chicken pho</v>
+        <v>Grilled steak + mixed greens salad</v>
       </c>
       <c r="F27" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G27">
-        <v>394</v>
+        <v>480</v>
       </c>
       <c r="H27">
         <v>49</v>
       </c>
       <c r="I27">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="K27" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1747,42 +1747,42 @@
         <v>1</v>
       </c>
       <c r="O27" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P27" t="str">
-        <v>{"macros_p":49,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":374,"delta_kcal":20,"tolerance_kcal":78.8},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":477,"delta_kcal":3,"tolerance_kcal":96},"issues":[]}}</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
+        <v>lunch_dinner_thai-pad-krapow-rice</v>
       </c>
       <c r="B28" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C28" t="str">
-        <v>Grilled steak + mixed greens salad</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="D28" t="str">
-        <v>Steak + Mixed Greens</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="E28" t="str">
-        <v>Grilled steak + mixed greens salad</v>
+        <v>Thai pad krapow + rice</v>
       </c>
       <c r="F28" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G28">
-        <v>480</v>
+        <v>438</v>
       </c>
       <c r="H28">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="J28">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="K28" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1797,42 +1797,42 @@
         <v>1</v>
       </c>
       <c r="O28" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P28" t="str">
-        <v>{"macros_p":49,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":477,"delta_kcal":3,"tolerance_kcal":96},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":422,"delta_kcal":16,"tolerance_kcal":87.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lunch_dinner_thai-pad-krapow-rice</v>
+        <v>lunch_dinner_mutton-keema-jowar-roti</v>
       </c>
       <c r="B29" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C29" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="D29" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="E29" t="str">
-        <v>Thai pad krapow + rice</v>
+        <v>Mutton keema + jowar roti</v>
       </c>
       <c r="F29" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G29">
-        <v>438</v>
+        <v>670</v>
       </c>
       <c r="H29">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I29">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J29">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="K29" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1847,42 +1847,42 @@
         <v>1</v>
       </c>
       <c r="O29" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P29" t="str">
-        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":422,"delta_kcal":16,"tolerance_kcal":87.6},"issues":[]}}</v>
+        <v>{"macros_p":34,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":654,"delta_kcal":16,"tolerance_kcal":134},"issues":[]}}</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>lunch_dinner_mutton-keema-jowar-roti</v>
+        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
       </c>
       <c r="B30" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C30" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Arhar dal + rice + matar paneer</v>
       </c>
       <c r="D30" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Arhar Dal + Rice + Matar Paneer</v>
       </c>
       <c r="E30" t="str">
-        <v>Mutton keema + jowar roti</v>
+        <v>Arhar dal + rice + matar paneer</v>
       </c>
       <c r="F30" t="str">
         <v>Indian</v>
       </c>
       <c r="G30">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I30">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="J30">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K30" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1897,42 +1897,42 @@
         <v>1</v>
       </c>
       <c r="O30" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P30" t="str">
-        <v>{"macros_p":34,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":654,"delta_kcal":16,"tolerance_kcal":134},"issues":[]}}</v>
+        <v>{"macros_p":32,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":666,"delta_kcal":3,"tolerance_kcal":133.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
       </c>
       <c r="B31" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C31" t="str">
-        <v>Arhar dal + rice + matar paneer</v>
+        <v>Chicken curry + jowar roti + dal</v>
       </c>
       <c r="D31" t="str">
-        <v>Arhar Dal + Rice + Matar Paneer</v>
+        <v>Chicken Curry + Roti + Dal</v>
       </c>
       <c r="E31" t="str">
-        <v>Arhar dal + rice + matar paneer</v>
+        <v>Chicken curry + jowar roti + dal</v>
       </c>
       <c r="F31" t="str">
         <v>Indian</v>
       </c>
       <c r="G31">
-        <v>669</v>
+        <v>736</v>
       </c>
       <c r="H31">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="I31">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="J31">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K31" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1947,42 +1947,42 @@
         <v>1</v>
       </c>
       <c r="O31" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P31" t="str">
-        <v>{"macros_p":32,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":666,"delta_kcal":3,"tolerance_kcal":133.8},"issues":[]}}</v>
+        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":709,"delta_kcal":27,"tolerance_kcal":147.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
+        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
       </c>
       <c r="B32" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C32" t="str">
-        <v>Chicken curry + jowar roti + dal</v>
+        <v>Grilled fish + pumpkin salad</v>
       </c>
       <c r="D32" t="str">
-        <v>Chicken Curry + Roti + Dal</v>
+        <v>Grilled Fish + Pumpkin Salad</v>
       </c>
       <c r="E32" t="str">
-        <v>Chicken curry + jowar roti + dal</v>
+        <v>Grilled fish + pumpkin salad</v>
       </c>
       <c r="F32" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G32">
-        <v>736</v>
+        <v>308</v>
       </c>
       <c r="H32">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="I32">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="J32">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K32" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -1997,42 +1997,42 @@
         <v>1</v>
       </c>
       <c r="O32" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P32" t="str">
-        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":709,"delta_kcal":27,"tolerance_kcal":147.2},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":305,"delta_kcal":3,"tolerance_kcal":61.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
+        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
       </c>
       <c r="B33" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C33" t="str">
-        <v>Grilled fish + pumpkin salad</v>
+        <v>Grilled salmon + sauteed veg + garlic rice</v>
       </c>
       <c r="D33" t="str">
-        <v>Grilled Fish + Pumpkin Salad</v>
+        <v>Salmon + Veg + Garlic Rice</v>
       </c>
       <c r="E33" t="str">
-        <v>Grilled fish + pumpkin salad</v>
+        <v>Grilled salmon + sauteed veg + garlic rice</v>
       </c>
       <c r="F33" t="str">
         <v>Continental</v>
       </c>
       <c r="G33">
-        <v>308</v>
+        <v>514</v>
       </c>
       <c r="H33">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I33">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="J33">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K33" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2047,42 +2047,42 @@
         <v>1</v>
       </c>
       <c r="O33" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P33" t="str">
-        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":305,"delta_kcal":3,"tolerance_kcal":61.6},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":11,"tolerance_kcal":102.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
+        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
       </c>
       <c r="B34" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C34" t="str">
-        <v>Grilled salmon + sauteed veg + garlic rice</v>
+        <v>Chicken soup + smoked salmon salad</v>
       </c>
       <c r="D34" t="str">
-        <v>Salmon + Veg + Garlic Rice</v>
+        <v>Chicken Soup + Salmon Salad</v>
       </c>
       <c r="E34" t="str">
-        <v>Grilled salmon + sauteed veg + garlic rice</v>
+        <v>Chicken soup + smoked salmon salad</v>
       </c>
       <c r="F34" t="str">
         <v>Continental</v>
       </c>
       <c r="G34">
-        <v>514</v>
+        <v>302</v>
       </c>
       <c r="H34">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I34">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="J34">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K34" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2097,42 +2097,42 @@
         <v>1</v>
       </c>
       <c r="O34" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"low","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P34" t="str">
-        <v>{"macros_p":40,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":11,"tolerance_kcal":102.8},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"mixed","meal_weight_class":"light","carb_level":"low","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":284,"delta_kcal":18,"tolerance_kcal":60.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
+        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
       </c>
       <c r="B35" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C35" t="str">
-        <v>Chicken soup + smoked salmon salad</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="D35" t="str">
-        <v>Chicken Soup + Salmon Salad</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="E35" t="str">
-        <v>Chicken soup + smoked salmon salad</v>
+        <v>Paneer sabzi + dal + raita</v>
       </c>
       <c r="F35" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G35">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="H35">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="J35">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K35" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2147,42 +2147,42 @@
         <v>1</v>
       </c>
       <c r="O35" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"mixed","carb_level":"low","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P35" t="str">
-        <v>{"macros_p":50,"protein_family":"mixed","meal_weight_class":"light","carb_level":"low","format":"soup","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":284,"delta_kcal":18,"tolerance_kcal":60.4},"issues":[]}}</v>
+        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":631,"delta_kcal":3,"tolerance_kcal":125.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
+        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
       </c>
       <c r="B36" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C36" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Pork chop + pumpkin salad</v>
       </c>
       <c r="D36" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Pork Chop + Pumpkin Salad</v>
       </c>
       <c r="E36" t="str">
-        <v>Paneer sabzi + dal + raita</v>
+        <v>Pork chop + pumpkin salad</v>
       </c>
       <c r="F36" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G36">
-        <v>628</v>
+        <v>562</v>
       </c>
       <c r="H36">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I36">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="J36">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K36" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2197,42 +2197,42 @@
         <v>1</v>
       </c>
       <c r="O36" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P36" t="str">
-        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":631,"delta_kcal":3,"tolerance_kcal":125.6},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":13,"tolerance_kcal":112.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
+        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
       </c>
       <c r="B37" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C37" t="str">
-        <v>Pork chop + pumpkin salad</v>
+        <v>Pork chop + mixed greens salad</v>
       </c>
       <c r="D37" t="str">
-        <v>Pork Chop + Pumpkin Salad</v>
+        <v>Pork Chop + Mixed Greens</v>
       </c>
       <c r="E37" t="str">
-        <v>Pork chop + pumpkin salad</v>
+        <v>Pork chop + mixed greens salad</v>
       </c>
       <c r="F37" t="str">
         <v>Continental</v>
       </c>
       <c r="G37">
-        <v>562</v>
+        <v>449</v>
       </c>
       <c r="H37">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I37">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K37" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2247,42 +2247,42 @@
         <v>1</v>
       </c>
       <c r="O37" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P37" t="str">
-        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":13,"tolerance_kcal":112.4},"issues":[]}}</v>
+        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":435,"delta_kcal":14,"tolerance_kcal":89.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
+        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
       </c>
       <c r="B38" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C38" t="str">
-        <v>Pork chop + mixed greens salad</v>
+        <v>Tandoori chicken + smoked chicken + avocado salad</v>
       </c>
       <c r="D38" t="str">
-        <v>Pork Chop + Mixed Greens</v>
+        <v>Tandoori Chicken + Smoked Chicken Salad</v>
       </c>
       <c r="E38" t="str">
-        <v>Pork chop + mixed greens salad</v>
+        <v>Tandoori chicken + smoked chicken + avocado salad</v>
       </c>
       <c r="F38" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G38">
-        <v>449</v>
+        <v>366</v>
       </c>
       <c r="H38">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I38">
         <v>5</v>
       </c>
       <c r="J38">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="K38" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2297,42 +2297,42 @@
         <v>1</v>
       </c>
       <c r="O38" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P38" t="str">
-        <v>{"macros_p":43,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":435,"delta_kcal":14,"tolerance_kcal":89.8},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":347,"delta_kcal":19,"tolerance_kcal":73.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
+        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B39" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C39" t="str">
-        <v>Tandoori chicken + smoked chicken + avocado salad</v>
+        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
       </c>
       <c r="D39" t="str">
-        <v>Tandoori Chicken + Smoked Chicken Salad</v>
+        <v>Broccoli Soup + Fish + Aglio Olio</v>
       </c>
       <c r="E39" t="str">
-        <v>Tandoori chicken + smoked chicken + avocado salad</v>
+        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
       </c>
       <c r="F39" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G39">
-        <v>366</v>
+        <v>433</v>
       </c>
       <c r="H39">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="J39">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K39" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2347,42 +2347,42 @@
         <v>1</v>
       </c>
       <c r="O39" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P39" t="str">
-        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":347,"delta_kcal":19,"tolerance_kcal":73.2},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":448,"delta_kcal":15,"tolerance_kcal":86.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
       </c>
       <c r="B40" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C40" t="str">
-        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="D40" t="str">
-        <v>Broccoli Soup + Fish + Aglio Olio</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="E40" t="str">
-        <v>Broccoli soup + grilled fish + spaghetti aglio e olio</v>
+        <v>Saag meat + jowar roti + dal</v>
       </c>
       <c r="F40" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G40">
-        <v>433</v>
+        <v>771</v>
       </c>
       <c r="H40">
         <v>45</v>
       </c>
       <c r="I40">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="J40">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K40" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2397,42 +2397,42 @@
         <v>1</v>
       </c>
       <c r="O40" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P40" t="str">
-        <v>{"macros_p":45,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":448,"delta_kcal":15,"tolerance_kcal":86.6},"issues":[]}}</v>
+        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":755,"delta_kcal":16,"tolerance_kcal":154.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
+        <v>lunch_dinner_kofta-dal-jowar-roti</v>
       </c>
       <c r="B41" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C41" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="D41" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="E41" t="str">
-        <v>Saag meat + jowar roti + dal</v>
+        <v>Kofta + dal + jowar roti</v>
       </c>
       <c r="F41" t="str">
         <v>Indian</v>
       </c>
       <c r="G41">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="H41">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="I41">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="J41">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K41" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2447,42 +2447,42 @@
         <v>1</v>
       </c>
       <c r="O41" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
       </c>
       <c r="P41" t="str">
-        <v>{"macros_p":45,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":755,"delta_kcal":16,"tolerance_kcal":154.2},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":746,"delta_kcal":23,"tolerance_kcal":153.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>lunch_dinner_kofta-dal-jowar-roti</v>
+        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
       </c>
       <c r="B42" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C42" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Kababs + dal + gobi + jowar roti</v>
       </c>
       <c r="D42" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Kababs + Dal + Gobi + Roti</v>
       </c>
       <c r="E42" t="str">
-        <v>Kofta + dal + jowar roti</v>
+        <v>Kababs + dal + gobi + jowar roti</v>
       </c>
       <c r="F42" t="str">
         <v>Indian</v>
       </c>
       <c r="G42">
-        <v>769</v>
+        <v>823</v>
       </c>
       <c r="H42">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I42">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="J42">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K42" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2497,42 +2497,42 @@
         <v>1</v>
       </c>
       <c r="O42" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P42" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":746,"delta_kcal":23,"tolerance_kcal":153.8},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":813,"delta_kcal":10,"tolerance_kcal":164.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
+        <v>lunch_dinner_fish-curry-rice</v>
       </c>
       <c r="B43" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C43" t="str">
-        <v>Kababs + dal + gobi + jowar roti</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="D43" t="str">
-        <v>Kababs + Dal + Gobi + Roti</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="E43" t="str">
-        <v>Kababs + dal + gobi + jowar roti</v>
+        <v>Fish curry + rice</v>
       </c>
       <c r="F43" t="str">
         <v>Indian</v>
       </c>
       <c r="G43">
-        <v>823</v>
+        <v>446</v>
       </c>
       <c r="H43">
+        <v>38</v>
+      </c>
+      <c r="I43">
         <v>41</v>
       </c>
-      <c r="I43">
-        <v>79</v>
-      </c>
       <c r="J43">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="K43" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2547,42 +2547,42 @@
         <v>1</v>
       </c>
       <c r="O43" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"high","cuisine":"indian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P43" t="str">
-        <v>{"macros_p":41,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"high","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":813,"delta_kcal":10,"tolerance_kcal":164.6},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":433,"delta_kcal":13,"tolerance_kcal":89.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>lunch_dinner_fish-curry-rice</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B44" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C44" t="str">
-        <v>Fish curry + rice</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="D44" t="str">
-        <v>Fish curry + rice</v>
+        <v>Sweet Potato Curry + Kaala Chanaa + Jowar Roti</v>
       </c>
       <c r="E44" t="str">
-        <v>Fish curry + rice</v>
+        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
       </c>
       <c r="F44" t="str">
         <v>Indian</v>
       </c>
       <c r="G44">
-        <v>446</v>
+        <v>731</v>
       </c>
       <c r="H44">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I44">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="J44">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K44" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2597,42 +2597,42 @@
         <v>1</v>
       </c>
       <c r="O44" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
       </c>
       <c r="P44" t="str">
-        <v>{"macros_p":38,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":433,"delta_kcal":13,"tolerance_kcal":89.2},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":735,"delta_kcal":4,"tolerance_kcal":146.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
+        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
       </c>
       <c r="B45" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C45" t="str">
-        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
+        <v>Avocado and smoked salmon salad</v>
       </c>
       <c r="D45" t="str">
-        <v>Sweet Potato Curry + Kaala Chanaa + Jowar Roti</v>
+        <v>Avocado &amp; Smoked Salmon Salad</v>
       </c>
       <c r="E45" t="str">
-        <v>Sweet potato curry + kaala chanaa sabzi + jowar roti</v>
+        <v>Avocado and smoked salmon salad</v>
       </c>
       <c r="F45" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G45">
-        <v>731</v>
+        <v>206</v>
       </c>
       <c r="H45">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I45">
-        <v>127</v>
+        <v>6</v>
       </c>
       <c r="J45">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K45" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2647,36 +2647,36 @@
         <v>1</v>
       </c>
       <c r="O45" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"high","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P45" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"high","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":735,"delta_kcal":4,"tolerance_kcal":146.2},"issues":[]}}</v>
+        <v>{"macros_p":24,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":201,"delta_kcal":5,"tolerance_kcal":41.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
+        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
       </c>
       <c r="B46" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C46" t="str">
-        <v>Avocado and smoked salmon salad</v>
+        <v>Avocado and smoked chicken salad</v>
       </c>
       <c r="D46" t="str">
-        <v>Avocado &amp; Smoked Salmon Salad</v>
+        <v>Avocado &amp; Smoked Chicken Salad</v>
       </c>
       <c r="E46" t="str">
-        <v>Avocado and smoked salmon salad</v>
+        <v>Avocado and smoked chicken salad</v>
       </c>
       <c r="F46" t="str">
         <v>Continental</v>
       </c>
       <c r="G46">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="H46">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I46">
         <v>6</v>
@@ -2697,42 +2697,42 @@
         <v>1</v>
       </c>
       <c r="O46" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P46" t="str">
-        <v>{"macros_p":24,"protein_family":"fish","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":201,"delta_kcal":5,"tolerance_kcal":41.2},"issues":[]}}</v>
+        <v>{"macros_p":33,"protein_family":"chicken","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":237,"delta_kcal":7,"tolerance_kcal":48.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
+        <v>lunch_dinner_chicken-red-curry-rice</v>
       </c>
       <c r="B47" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C47" t="str">
-        <v>Avocado and smoked chicken salad</v>
+        <v>Chicken red curry + rice</v>
       </c>
       <c r="D47" t="str">
-        <v>Avocado &amp; Smoked Chicken Salad</v>
+        <v>Chicken Red Curry + Rice</v>
       </c>
       <c r="E47" t="str">
-        <v>Avocado and smoked chicken salad</v>
+        <v>Chicken red curry + rice</v>
       </c>
       <c r="F47" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G47">
-        <v>244</v>
+        <v>504</v>
       </c>
       <c r="H47">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="I47">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J47">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K47" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2747,48 +2747,48 @@
         <v>1</v>
       </c>
       <c r="O47" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P47" t="str">
-        <v>{"macros_p":33,"protein_family":"chicken","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":237,"delta_kcal":7,"tolerance_kcal":48.8},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":486,"delta_kcal":18,"tolerance_kcal":100.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>lunch_dinner_chicken-red-curry-rice</v>
+        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
       </c>
       <c r="B48" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C48" t="str">
-        <v>Chicken red curry + rice</v>
+        <v>Korean chicken bibimbap bowl</v>
       </c>
       <c r="D48" t="str">
-        <v>Chicken Red Curry + Rice</v>
+        <v>Chicken Bibimbap Bowl</v>
       </c>
       <c r="E48" t="str">
-        <v>Chicken red curry + rice</v>
+        <v>Korean chicken bibimbap bowl</v>
       </c>
       <c r="F48" t="str">
         <v>Asian</v>
       </c>
       <c r="G48">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="H48">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I48">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J48">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K48" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L48" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M48" t="str">
         <v>seed_v1</v>
@@ -2797,42 +2797,42 @@
         <v>1</v>
       </c>
       <c r="O48" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P48" t="str">
-        <v>{"macros_p":50,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":486,"delta_kcal":18,"tolerance_kcal":100.8},"issues":[]}}</v>
+        <v>{"macros_p":52,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":452,"delta_kcal":19,"tolerance_kcal":94.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
+        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
       </c>
       <c r="B49" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C49" t="str">
-        <v>Korean chicken bibimbap bowl</v>
+        <v>Salmon teriyaki + soba noodles</v>
       </c>
       <c r="D49" t="str">
-        <v>Chicken Bibimbap Bowl</v>
+        <v>Salmon Teriyaki + Soba</v>
       </c>
       <c r="E49" t="str">
-        <v>Korean chicken bibimbap bowl</v>
+        <v>Salmon teriyaki + soba noodles</v>
       </c>
       <c r="F49" t="str">
         <v>Asian</v>
       </c>
       <c r="G49">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="H49">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I49">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J49">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K49" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2847,42 +2847,42 @@
         <v>1</v>
       </c>
       <c r="O49" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P49" t="str">
-        <v>{"macros_p":52,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":452,"delta_kcal":19,"tolerance_kcal":94.2},"issues":[]}}</v>
+        <v>{"macros_p":43,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":9,"tolerance_kcal":99.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
+        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
       </c>
       <c r="B50" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C50" t="str">
-        <v>Salmon teriyaki + soba noodles</v>
+        <v>Prawn stir-fry + edamame + rice noodles</v>
       </c>
       <c r="D50" t="str">
-        <v>Salmon Teriyaki + Soba</v>
+        <v>Prawn Stir-fry + Edamame</v>
       </c>
       <c r="E50" t="str">
-        <v>Salmon teriyaki + soba noodles</v>
+        <v>Prawn stir-fry + edamame + rice noodles</v>
       </c>
       <c r="F50" t="str">
         <v>Asian</v>
       </c>
       <c r="G50">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="H50">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="I50">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J50">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K50" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2900,39 +2900,39 @@
         <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P50" t="str">
-        <v>{"macros_p":43,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":9,"tolerance_kcal":99.8},"issues":[]}}</v>
+        <v>{"macros_p":54,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":467,"delta_kcal":5,"tolerance_kcal":94.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
+        <v>lunch_dinner_miso-chicken-ramen-egg</v>
       </c>
       <c r="B51" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C51" t="str">
-        <v>Prawn stir-fry + edamame + rice noodles</v>
+        <v>Miso chicken ramen + egg</v>
       </c>
       <c r="D51" t="str">
-        <v>Prawn Stir-fry + Edamame</v>
+        <v>Miso Chicken Ramen</v>
       </c>
       <c r="E51" t="str">
-        <v>Prawn stir-fry + edamame + rice noodles</v>
+        <v>Miso chicken ramen + egg</v>
       </c>
       <c r="F51" t="str">
         <v>Asian</v>
       </c>
       <c r="G51">
-        <v>472</v>
+        <v>527</v>
       </c>
       <c r="H51">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I51">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K51" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2947,42 +2947,42 @@
         <v>1</v>
       </c>
       <c r="O51" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P51" t="str">
-        <v>{"macros_p":54,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":467,"delta_kcal":5,"tolerance_kcal":94.4},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":515,"delta_kcal":12,"tolerance_kcal":105.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>lunch_dinner_miso-chicken-ramen-egg</v>
+        <v>lunch_dinner_tofu-edamame-ramen</v>
       </c>
       <c r="B52" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C52" t="str">
-        <v>Miso chicken ramen + egg</v>
+        <v>Tofu &amp; edamame ramen</v>
       </c>
       <c r="D52" t="str">
-        <v>Miso Chicken Ramen</v>
+        <v>Tofu &amp; Edamame Ramen</v>
       </c>
       <c r="E52" t="str">
-        <v>Miso chicken ramen + egg</v>
+        <v>Tofu &amp; edamame ramen</v>
       </c>
       <c r="F52" t="str">
         <v>Asian</v>
       </c>
       <c r="G52">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="H52">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I52">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J52">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K52" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -2997,42 +2997,42 @@
         <v>1</v>
       </c>
       <c r="O52" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P52" t="str">
-        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":515,"delta_kcal":12,"tolerance_kcal":105.4},"issues":[]}}</v>
+        <v>{"macros_p":47,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":596,"delta_kcal":31,"tolerance_kcal":113},"issues":[]}}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>lunch_dinner_tofu-edamame-ramen</v>
+        <v>lunch_dinner_butter-chicken-jowar-roti</v>
       </c>
       <c r="B53" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C53" t="str">
-        <v>Tofu &amp; edamame ramen</v>
+        <v>Butter chicken + jowar roti</v>
       </c>
       <c r="D53" t="str">
-        <v>Tofu &amp; Edamame Ramen</v>
+        <v>Butter Chicken + Jowar Roti</v>
       </c>
       <c r="E53" t="str">
-        <v>Tofu &amp; edamame ramen</v>
+        <v>Butter chicken + jowar roti</v>
       </c>
       <c r="F53" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G53">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="H53">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I53">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J53">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K53" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3047,42 +3047,42 @@
         <v>1</v>
       </c>
       <c r="O53" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P53" t="str">
-        <v>{"macros_p":47,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":596,"delta_kcal":31,"tolerance_kcal":113},"issues":[]}}</v>
+        <v>{"macros_p":54,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":622,"delta_kcal":13,"tolerance_kcal":127},"issues":[]}}</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>lunch_dinner_butter-chicken-jowar-roti</v>
+        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
       </c>
       <c r="B54" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C54" t="str">
-        <v>Butter chicken + jowar roti</v>
+        <v>Grilled chicken + sweet potato + broccoli</v>
       </c>
       <c r="D54" t="str">
-        <v>Butter Chicken + Jowar Roti</v>
+        <v>Grilled Chicken + Sweet Potato</v>
       </c>
       <c r="E54" t="str">
-        <v>Butter chicken + jowar roti</v>
+        <v>Grilled chicken + sweet potato + broccoli</v>
       </c>
       <c r="F54" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G54">
-        <v>635</v>
+        <v>505</v>
       </c>
       <c r="H54">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I54">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J54">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K54" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3097,42 +3097,42 @@
         <v>1</v>
       </c>
       <c r="O54" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P54" t="str">
-        <v>{"macros_p":54,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":622,"delta_kcal":13,"tolerance_kcal":127},"issues":[]}}</v>
+        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":3,"tolerance_kcal":101},"issues":[]}}</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
+        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
       </c>
       <c r="B55" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C55" t="str">
-        <v>Grilled chicken + sweet potato + broccoli</v>
+        <v>Pepper beef + garlic rice + greens</v>
       </c>
       <c r="D55" t="str">
-        <v>Grilled Chicken + Sweet Potato</v>
+        <v>Pepper Beef + Garlic Rice</v>
       </c>
       <c r="E55" t="str">
-        <v>Grilled chicken + sweet potato + broccoli</v>
+        <v>Pepper beef + garlic rice + greens</v>
       </c>
       <c r="F55" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G55">
-        <v>505</v>
+        <v>696</v>
       </c>
       <c r="H55">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I55">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J55">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="K55" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3147,42 +3147,42 @@
         <v>1</v>
       </c>
       <c r="O55" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P55" t="str">
-        <v>{"macros_p":56,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":508,"delta_kcal":3,"tolerance_kcal":101},"issues":[]}}</v>
+        <v>{"macros_p":53,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":702,"delta_kcal":6,"tolerance_kcal":139.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
+        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
       </c>
       <c r="B56" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C56" t="str">
-        <v>Pepper beef + garlic rice + greens</v>
+        <v>Paneer tikka + jowar roti + salad</v>
       </c>
       <c r="D56" t="str">
-        <v>Pepper Beef + Garlic Rice</v>
+        <v>Paneer Tikka + Jowar Roti</v>
       </c>
       <c r="E56" t="str">
-        <v>Pepper beef + garlic rice + greens</v>
+        <v>Paneer tikka + jowar roti + salad</v>
       </c>
       <c r="F56" t="str">
-        <v>Asian</v>
+        <v>Indian</v>
       </c>
       <c r="G56">
-        <v>696</v>
+        <v>654</v>
       </c>
       <c r="H56">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="I56">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J56">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K56" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3197,42 +3197,42 @@
         <v>1</v>
       </c>
       <c r="O56" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P56" t="str">
-        <v>{"macros_p":53,"protein_family":"red_meat","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":702,"delta_kcal":6,"tolerance_kcal":139.2},"issues":[]}}</v>
+        <v>{"macros_p":35,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":647,"delta_kcal":7,"tolerance_kcal":130.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
+        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
       </c>
       <c r="B57" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C57" t="str">
-        <v>Paneer tikka + jowar roti + salad</v>
+        <v>Grilled salmon + sweet potato + spinach</v>
       </c>
       <c r="D57" t="str">
-        <v>Paneer Tikka + Jowar Roti</v>
+        <v>Salmon + Sweet Potato + Spinach</v>
       </c>
       <c r="E57" t="str">
-        <v>Paneer tikka + jowar roti + salad</v>
+        <v>Grilled salmon + sweet potato + spinach</v>
       </c>
       <c r="F57" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G57">
-        <v>654</v>
+        <v>614</v>
       </c>
       <c r="H57">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I57">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J57">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K57" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3247,42 +3247,42 @@
         <v>1</v>
       </c>
       <c r="O57" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P57" t="str">
-        <v>{"macros_p":35,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":647,"delta_kcal":7,"tolerance_kcal":130.8},"issues":[]}}</v>
+        <v>{"macros_p":48,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":614,"delta_kcal":0,"tolerance_kcal":122.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
+        <v>lunch_dinner_chicken-biryani-raita</v>
       </c>
       <c r="B58" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C58" t="str">
-        <v>Grilled salmon + sweet potato + spinach</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="D58" t="str">
-        <v>Salmon + Sweet Potato + Spinach</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="E58" t="str">
-        <v>Grilled salmon + sweet potato + spinach</v>
+        <v>Chicken biryani + raita</v>
       </c>
       <c r="F58" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G58">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="H58">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I58">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="J58">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K58" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3297,42 +3297,42 @@
         <v>1</v>
       </c>
       <c r="O58" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P58" t="str">
-        <v>{"macros_p":48,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":614,"delta_kcal":0,"tolerance_kcal":122.8},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":607,"delta_kcal":22,"tolerance_kcal":125.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>lunch_dinner_chicken-biryani-raita</v>
+        <v>lunch_dinner_fish-moilee-rice</v>
       </c>
       <c r="B59" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C59" t="str">
-        <v>Chicken biryani + raita</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="D59" t="str">
-        <v>Chicken biryani + raita</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="E59" t="str">
-        <v>Chicken biryani + raita</v>
+        <v>Fish moilee + rice</v>
       </c>
       <c r="F59" t="str">
         <v>Indian</v>
       </c>
       <c r="G59">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="H59">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I59">
         <v>54</v>
       </c>
       <c r="J59">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K59" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3347,42 +3347,42 @@
         <v>1</v>
       </c>
       <c r="O59" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P59" t="str">
-        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":607,"delta_kcal":22,"tolerance_kcal":125.8},"issues":[]}}</v>
+        <v>{"macros_p":53,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":608,"delta_kcal":7,"tolerance_kcal":123},"issues":[]}}</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>lunch_dinner_fish-moilee-rice</v>
+        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
       </c>
       <c r="B60" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C60" t="str">
-        <v>Fish moilee + rice</v>
+        <v>Egg curry + dal + jowar roti</v>
       </c>
       <c r="D60" t="str">
-        <v>Fish moilee + rice</v>
+        <v>Egg Curry + Dal + Roti</v>
       </c>
       <c r="E60" t="str">
-        <v>Fish moilee + rice</v>
+        <v>Egg curry + dal + jowar roti</v>
       </c>
       <c r="F60" t="str">
         <v>Indian</v>
       </c>
       <c r="G60">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="H60">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="I60">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="J60">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K60" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3397,42 +3397,42 @@
         <v>1</v>
       </c>
       <c r="O60" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P60" t="str">
-        <v>{"macros_p":53,"protein_family":"fish","meal_weight_class":"heavy","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":608,"delta_kcal":7,"tolerance_kcal":123},"issues":[]}}</v>
+        <v>{"macros_p":34,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":585,"delta_kcal":19,"tolerance_kcal":120.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
+        <v>lunch_dinner_chicken-shawarma-bowl</v>
       </c>
       <c r="B61" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C61" t="str">
-        <v>Egg curry + dal + jowar roti</v>
+        <v>Chicken shawarma bowl</v>
       </c>
       <c r="D61" t="str">
-        <v>Egg Curry + Dal + Roti</v>
+        <v>Chicken shawarma bowl</v>
       </c>
       <c r="E61" t="str">
-        <v>Egg curry + dal + jowar roti</v>
+        <v>Chicken shawarma bowl</v>
       </c>
       <c r="F61" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G61">
-        <v>604</v>
+        <v>533</v>
       </c>
       <c r="H61">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I61">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J61">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K61" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3447,39 +3447,39 @@
         <v>1</v>
       </c>
       <c r="O61" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P61" t="str">
-        <v>{"macros_p":34,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":585,"delta_kcal":19,"tolerance_kcal":120.8},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":533,"delta_kcal":0,"tolerance_kcal":106.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>lunch_dinner_chicken-shawarma-bowl</v>
+        <v>lunch_dinner_prawn-curry-rice</v>
       </c>
       <c r="B62" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C62" t="str">
-        <v>Chicken shawarma bowl</v>
+        <v>Prawn curry + rice</v>
       </c>
       <c r="D62" t="str">
-        <v>Chicken shawarma bowl</v>
+        <v>Prawn curry + rice</v>
       </c>
       <c r="E62" t="str">
-        <v>Chicken shawarma bowl</v>
+        <v>Prawn curry + rice</v>
       </c>
       <c r="F62" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G62">
-        <v>533</v>
+        <v>552</v>
       </c>
       <c r="H62">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I62">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J62">
         <v>17</v>
@@ -3497,42 +3497,42 @@
         <v>1</v>
       </c>
       <c r="O62" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P62" t="str">
-        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":533,"delta_kcal":0,"tolerance_kcal":106.6},"issues":[]}}</v>
+        <v>{"macros_p":49,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":3,"tolerance_kcal":110.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>lunch_dinner_prawn-curry-rice</v>
+        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
       </c>
       <c r="B63" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C63" t="str">
-        <v>Prawn curry + rice</v>
+        <v>Chicken meatballs + spaghetti + salad</v>
       </c>
       <c r="D63" t="str">
-        <v>Prawn curry + rice</v>
+        <v>Chicken Meatballs + Spaghetti</v>
       </c>
       <c r="E63" t="str">
-        <v>Prawn curry + rice</v>
+        <v>Chicken meatballs + spaghetti + salad</v>
       </c>
       <c r="F63" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G63">
-        <v>552</v>
+        <v>649</v>
       </c>
       <c r="H63">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I63">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J63">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K63" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3547,48 +3547,48 @@
         <v>1</v>
       </c>
       <c r="O63" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P63" t="str">
-        <v>{"macros_p":49,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":549,"delta_kcal":3,"tolerance_kcal":110.4},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":659,"delta_kcal":10,"tolerance_kcal":129.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
+        <v>lunch_dinner_palak-paneer-jowar-roti</v>
       </c>
       <c r="B64" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C64" t="str">
-        <v>Chicken meatballs + spaghetti + salad</v>
+        <v>Palak paneer + jowar roti</v>
       </c>
       <c r="D64" t="str">
-        <v>Chicken Meatballs + Spaghetti</v>
+        <v>Palak paneer + jowar roti</v>
       </c>
       <c r="E64" t="str">
-        <v>Chicken meatballs + spaghetti + salad</v>
+        <v>Palak paneer + jowar roti</v>
       </c>
       <c r="F64" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G64">
-        <v>649</v>
+        <v>734</v>
       </c>
       <c r="H64">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="I64">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J64">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K64" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L64" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M64" t="str">
         <v>seed_v1</v>
@@ -3597,48 +3597,48 @@
         <v>1</v>
       </c>
       <c r="O64" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P64" t="str">
-        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":659,"delta_kcal":10,"tolerance_kcal":129.8},"issues":[]}}</v>
+        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":731,"delta_kcal":3,"tolerance_kcal":146.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>lunch_dinner_rajma-paneer-bowl</v>
+        <v>lunch_dinner_achari-paneer-tikka-dal-salad</v>
       </c>
       <c r="B65" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C65" t="str">
-        <v>Rajma + paneer bowl</v>
+        <v>Achari paneer tikka + dal + salad</v>
       </c>
       <c r="D65" t="str">
-        <v>Rajma + Paneer Bowl</v>
+        <v>Achari Paneer Tikka + Dal</v>
       </c>
       <c r="E65" t="str">
-        <v>Rajma + paneer bowl</v>
+        <v>Achari paneer tikka + dal + salad</v>
       </c>
       <c r="F65" t="str">
         <v>Indian</v>
       </c>
       <c r="G65">
-        <v>516</v>
+        <v>622</v>
       </c>
       <c r="H65">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I65">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J65">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="K65" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L65" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_08_03</v>
       </c>
       <c r="M65" t="str">
         <v>seed_v1</v>
@@ -3647,42 +3647,42 @@
         <v>1</v>
       </c>
       <c r="O65" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P65" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":523,"delta_kcal":7,"tolerance_kcal":103.2},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":621,"delta_kcal":1,"tolerance_kcal":124.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>lunch_dinner_palak-paneer-jowar-roti</v>
+        <v>lunch_dinner_soya-keema-curry-jowar-roti</v>
       </c>
       <c r="B66" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C66" t="str">
-        <v>Palak paneer + jowar roti</v>
+        <v>Soya keema curry + jowar roti</v>
       </c>
       <c r="D66" t="str">
-        <v>Palak paneer + jowar roti</v>
+        <v>Soya Keema + Jowar Roti</v>
       </c>
       <c r="E66" t="str">
-        <v>Palak paneer + jowar roti</v>
+        <v>Soya keema curry + jowar roti</v>
       </c>
       <c r="F66" t="str">
         <v>Indian</v>
       </c>
       <c r="G66">
-        <v>734</v>
+        <v>530</v>
       </c>
       <c r="H66">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I66">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J66">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="K66" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3697,42 +3697,42 @@
         <v>1</v>
       </c>
       <c r="O66" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"curry","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P66" t="str">
-        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":731,"delta_kcal":3,"tolerance_kcal":146.8},"issues":[]}}</v>
+        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":5,"tolerance_kcal":106},"issues":[]}}</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>lunch_dinner_achari-paneer-tikka-dal-salad</v>
+        <v>lunch_dinner_chole-paneer-bowl-salad</v>
       </c>
       <c r="B67" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C67" t="str">
-        <v>Achari paneer tikka + dal + salad</v>
+        <v>Chole-paneer bowl + salad</v>
       </c>
       <c r="D67" t="str">
-        <v>Achari Paneer Tikka + Dal</v>
+        <v>Chole-Paneer Bowl</v>
       </c>
       <c r="E67" t="str">
-        <v>Achari paneer tikka + dal + salad</v>
+        <v>Chole-paneer bowl + salad</v>
       </c>
       <c r="F67" t="str">
         <v>Indian</v>
       </c>
       <c r="G67">
-        <v>622</v>
+        <v>659</v>
       </c>
       <c r="H67">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I67">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="J67">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K67" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3747,42 +3747,42 @@
         <v>1</v>
       </c>
       <c r="O67" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P67" t="str">
-        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":621,"delta_kcal":1,"tolerance_kcal":124.4},"issues":[]}}</v>
+        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":662,"delta_kcal":3,"tolerance_kcal":131.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>lunch_dinner_soya-keema-curry-jowar-roti</v>
+        <v>lunch_dinner_kadai-chicken-jowar-roti</v>
       </c>
       <c r="B68" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C68" t="str">
-        <v>Soya keema curry + jowar roti</v>
+        <v>Kadai chicken + jowar roti</v>
       </c>
       <c r="D68" t="str">
-        <v>Soya Keema + Jowar Roti</v>
+        <v>Kadai chicken + jowar roti</v>
       </c>
       <c r="E68" t="str">
-        <v>Soya keema curry + jowar roti</v>
+        <v>Kadai chicken + jowar roti</v>
       </c>
       <c r="F68" t="str">
         <v>Indian</v>
       </c>
       <c r="G68">
-        <v>530</v>
+        <v>586</v>
       </c>
       <c r="H68">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="I68">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="J68">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K68" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3797,42 +3797,42 @@
         <v>1</v>
       </c>
       <c r="O68" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P68" t="str">
-        <v>{"macros_p":41,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":525,"delta_kcal":5,"tolerance_kcal":106},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":568,"delta_kcal":18,"tolerance_kcal":117.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>lunch_dinner_chole-paneer-bowl-salad</v>
+        <v>lunch_dinner_tandoori-fish-tikka-veg-roti</v>
       </c>
       <c r="B69" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C69" t="str">
-        <v>Chole-paneer bowl + salad</v>
+        <v>Tandoori fish tikka + sauteed veg + roti</v>
       </c>
       <c r="D69" t="str">
-        <v>Chole-Paneer Bowl</v>
+        <v>Tandoori Fish Tikka + Veg</v>
       </c>
       <c r="E69" t="str">
-        <v>Chole-paneer bowl + salad</v>
+        <v>Tandoori fish tikka + sauteed veg + roti</v>
       </c>
       <c r="F69" t="str">
         <v>Indian</v>
       </c>
       <c r="G69">
-        <v>659</v>
+        <v>477</v>
       </c>
       <c r="H69">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="I69">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="J69">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K69" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3847,42 +3847,42 @@
         <v>1</v>
       </c>
       <c r="O69" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P69" t="str">
-        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":662,"delta_kcal":3,"tolerance_kcal":131.8},"issues":[]}}</v>
+        <v>{"macros_p":58,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":474,"delta_kcal":3,"tolerance_kcal":95.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>lunch_dinner_kadai-chicken-jowar-roti</v>
+        <v>lunch_dinner_chicken-keema-matar-jowar-roti</v>
       </c>
       <c r="B70" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C70" t="str">
-        <v>Kadai chicken + jowar roti</v>
+        <v>Chicken keema matar + jowar roti</v>
       </c>
       <c r="D70" t="str">
-        <v>Kadai chicken + jowar roti</v>
+        <v>Chicken Keema Matar + Roti</v>
       </c>
       <c r="E70" t="str">
-        <v>Kadai chicken + jowar roti</v>
+        <v>Chicken keema matar + jowar roti</v>
       </c>
       <c r="F70" t="str">
         <v>Indian</v>
       </c>
       <c r="G70">
-        <v>586</v>
+        <v>674</v>
       </c>
       <c r="H70">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I70">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J70">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K70" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3897,42 +3897,42 @@
         <v>1</v>
       </c>
       <c r="O70" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P70" t="str">
-        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":568,"delta_kcal":18,"tolerance_kcal":117.2},"issues":[]}}</v>
+        <v>{"macros_p":59,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":672,"delta_kcal":2,"tolerance_kcal":134.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>lunch_dinner_tandoori-fish-tikka-veg-roti</v>
+        <v>lunch_dinner_beef-bulgogi-bowl</v>
       </c>
       <c r="B71" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C71" t="str">
-        <v>Tandoori fish tikka + sauteed veg + roti</v>
+        <v>Beef bulgogi bowl</v>
       </c>
       <c r="D71" t="str">
-        <v>Tandoori Fish Tikka + Veg</v>
+        <v>Beef bulgogi bowl</v>
       </c>
       <c r="E71" t="str">
-        <v>Tandoori fish tikka + sauteed veg + roti</v>
+        <v>Beef bulgogi bowl</v>
       </c>
       <c r="F71" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G71">
-        <v>477</v>
+        <v>575</v>
       </c>
       <c r="H71">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="I71">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J71">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K71" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3947,42 +3947,42 @@
         <v>1</v>
       </c>
       <c r="O71" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P71" t="str">
-        <v>{"macros_p":58,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":474,"delta_kcal":3,"tolerance_kcal":95.4},"issues":[]}}</v>
+        <v>{"macros_p":46,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":566,"delta_kcal":9,"tolerance_kcal":115},"issues":[]}}</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>lunch_dinner_chicken-keema-matar-jowar-roti</v>
+        <v>lunch_dinner_tofu-veg-bibimbap</v>
       </c>
       <c r="B72" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C72" t="str">
-        <v>Chicken keema matar + jowar roti</v>
+        <v>Tofu &amp; vegetable bibimbap</v>
       </c>
       <c r="D72" t="str">
-        <v>Chicken Keema Matar + Roti</v>
+        <v>Tofu &amp; Veg Bibimbap</v>
       </c>
       <c r="E72" t="str">
-        <v>Chicken keema matar + jowar roti</v>
+        <v>Tofu &amp; vegetable bibimbap</v>
       </c>
       <c r="F72" t="str">
-        <v>Indian</v>
+        <v>Asian</v>
       </c>
       <c r="G72">
-        <v>674</v>
+        <v>555</v>
       </c>
       <c r="H72">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="I72">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J72">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K72" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -3997,42 +3997,42 @@
         <v>1</v>
       </c>
       <c r="O72" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P72" t="str">
-        <v>{"macros_p":59,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"curry","effort":"high","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":672,"delta_kcal":2,"tolerance_kcal":134.8},"issues":[]}}</v>
+        <v>{"macros_p":44,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":583,"delta_kcal":28,"tolerance_kcal":111},"issues":[]}}</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>lunch_dinner_beef-bulgogi-bowl</v>
+        <v>lunch_dinner_oyakodon-side-salad</v>
       </c>
       <c r="B73" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C73" t="str">
-        <v>Beef bulgogi bowl</v>
+        <v>Oyakodon + side salad</v>
       </c>
       <c r="D73" t="str">
-        <v>Beef bulgogi bowl</v>
+        <v>Oyakodon (chicken &amp; egg)</v>
       </c>
       <c r="E73" t="str">
-        <v>Beef bulgogi bowl</v>
+        <v>Oyakodon + side salad</v>
       </c>
       <c r="F73" t="str">
         <v>Asian</v>
       </c>
       <c r="G73">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="H73">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I73">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J73">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K73" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4047,42 +4047,42 @@
         <v>1</v>
       </c>
       <c r="O73" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"red_meat","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P73" t="str">
-        <v>{"macros_p":46,"protein_family":"red_meat","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":566,"delta_kcal":9,"tolerance_kcal":115},"issues":[]}}</v>
+        <v>{"macros_p":60,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":539,"delta_kcal":29,"tolerance_kcal":113.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>lunch_dinner_tofu-veg-bibimbap</v>
+        <v>lunch_dinner_dubu-jorim-rice-kimchi</v>
       </c>
       <c r="B74" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C74" t="str">
-        <v>Tofu &amp; vegetable bibimbap</v>
+        <v>Dubu jorim + rice + kimchi</v>
       </c>
       <c r="D74" t="str">
-        <v>Tofu &amp; Veg Bibimbap</v>
+        <v>Dubu Jorim (braised tofu)</v>
       </c>
       <c r="E74" t="str">
-        <v>Tofu &amp; vegetable bibimbap</v>
+        <v>Dubu jorim + rice + kimchi</v>
       </c>
       <c r="F74" t="str">
         <v>Asian</v>
       </c>
       <c r="G74">
-        <v>555</v>
+        <v>480</v>
       </c>
       <c r="H74">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I74">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J74">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K74" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4097,42 +4097,42 @@
         <v>1</v>
       </c>
       <c r="O74" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
       </c>
       <c r="P74" t="str">
-        <v>{"macros_p":44,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":583,"delta_kcal":28,"tolerance_kcal":111},"issues":[]}}</v>
+        <v>{"macros_p":38,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":511,"delta_kcal":31,"tolerance_kcal":96},"issues":[]}}</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>lunch_dinner_oyakodon-side-salad</v>
+        <v>lunch_dinner_home-style-tofu-chicken-stir-fry</v>
       </c>
       <c r="B75" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C75" t="str">
-        <v>Oyakodon + side salad</v>
+        <v>Home-style tofu &amp; chicken stir-fry</v>
       </c>
       <c r="D75" t="str">
-        <v>Oyakodon (chicken &amp; egg)</v>
+        <v>Home-Style Tofu &amp; Chicken</v>
       </c>
       <c r="E75" t="str">
-        <v>Oyakodon + side salad</v>
+        <v>Home-style tofu &amp; chicken stir-fry</v>
       </c>
       <c r="F75" t="str">
         <v>Asian</v>
       </c>
       <c r="G75">
-        <v>568</v>
+        <v>609</v>
       </c>
       <c r="H75">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I75">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J75">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K75" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4147,42 +4147,42 @@
         <v>1</v>
       </c>
       <c r="O75" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P75" t="str">
-        <v>{"macros_p":60,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":539,"delta_kcal":29,"tolerance_kcal":113.6},"issues":[]}}</v>
+        <v>{"macros_p":64,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":619,"delta_kcal":10,"tolerance_kcal":121.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>lunch_dinner_dubu-jorim-rice-kimchi</v>
+        <v>lunch_dinner_vietnamese-lemongrass-chicken-bowl</v>
       </c>
       <c r="B76" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C76" t="str">
-        <v>Dubu jorim + rice + kimchi</v>
+        <v>Vietnamese lemongrass chicken bowl</v>
       </c>
       <c r="D76" t="str">
-        <v>Dubu Jorim (braised tofu)</v>
+        <v>Lemongrass Chicken Bowl</v>
       </c>
       <c r="E76" t="str">
-        <v>Dubu jorim + rice + kimchi</v>
+        <v>Vietnamese lemongrass chicken bowl</v>
       </c>
       <c r="F76" t="str">
         <v>Asian</v>
       </c>
       <c r="G76">
-        <v>480</v>
+        <v>514</v>
       </c>
       <c r="H76">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="I76">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J76">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K76" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4197,42 +4197,42 @@
         <v>1</v>
       </c>
       <c r="O76" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"asian","format":"curry","effort":"medium","goal_fit":["high_protein"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P76" t="str">
-        <v>{"macros_p":38,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"medium","format":"curry","effort":"medium","goal_fit":["high_protein"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":511,"delta_kcal":31,"tolerance_kcal":96},"issues":[]}}</v>
+        <v>{"macros_p":59,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":494,"delta_kcal":20,"tolerance_kcal":102.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>lunch_dinner_home-style-tofu-chicken-stir-fry</v>
+        <v>lunch_dinner_cantonese-steamed-fish-edamame</v>
       </c>
       <c r="B77" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C77" t="str">
-        <v>Home-style tofu &amp; chicken stir-fry</v>
+        <v>Cantonese steamed fish + edamame + rice</v>
       </c>
       <c r="D77" t="str">
-        <v>Home-Style Tofu &amp; Chicken</v>
+        <v>Steamed Fish + Edamame</v>
       </c>
       <c r="E77" t="str">
-        <v>Home-style tofu &amp; chicken stir-fry</v>
+        <v>Cantonese steamed fish + edamame + rice</v>
       </c>
       <c r="F77" t="str">
         <v>Asian</v>
       </c>
       <c r="G77">
-        <v>609</v>
+        <v>484</v>
       </c>
       <c r="H77">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I77">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J77">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K77" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4247,42 +4247,42 @@
         <v>1</v>
       </c>
       <c r="O77" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P77" t="str">
-        <v>{"macros_p":64,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":619,"delta_kcal":10,"tolerance_kcal":121.8},"issues":[]}}</v>
+        <v>{"macros_p":60,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":492,"delta_kcal":8,"tolerance_kcal":96.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>lunch_dinner_vietnamese-lemongrass-chicken-bowl</v>
+        <v>lunch_dinner_chicken-bulgogi-bowl</v>
       </c>
       <c r="B78" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C78" t="str">
-        <v>Vietnamese lemongrass chicken bowl</v>
+        <v>Chicken bulgogi bowl</v>
       </c>
       <c r="D78" t="str">
-        <v>Lemongrass Chicken Bowl</v>
+        <v>Chicken bulgogi bowl</v>
       </c>
       <c r="E78" t="str">
-        <v>Vietnamese lemongrass chicken bowl</v>
+        <v>Chicken bulgogi bowl</v>
       </c>
       <c r="F78" t="str">
         <v>Asian</v>
       </c>
       <c r="G78">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="H78">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I78">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J78">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K78" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4297,42 +4297,42 @@
         <v>1</v>
       </c>
       <c r="O78" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P78" t="str">
-        <v>{"macros_p":59,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":494,"delta_kcal":20,"tolerance_kcal":102.8},"issues":[]}}</v>
+        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":484,"delta_kcal":11,"tolerance_kcal":99},"issues":[]}}</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>lunch_dinner_cantonese-steamed-fish-edamame</v>
+        <v>lunch_dinner_chicken-souvlaki-tzatziki-greek-salad</v>
       </c>
       <c r="B79" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C79" t="str">
-        <v>Cantonese steamed fish + edamame + rice</v>
+        <v>Chicken souvlaki + tzatziki + Greek salad</v>
       </c>
       <c r="D79" t="str">
-        <v>Steamed Fish + Edamame</v>
+        <v>Chicken Souvlaki + Greek Salad</v>
       </c>
       <c r="E79" t="str">
-        <v>Cantonese steamed fish + edamame + rice</v>
+        <v>Chicken souvlaki + tzatziki + Greek salad</v>
       </c>
       <c r="F79" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G79">
-        <v>484</v>
+        <v>544</v>
       </c>
       <c r="H79">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I79">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="J79">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K79" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4347,42 +4347,42 @@
         <v>1</v>
       </c>
       <c r="O79" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"asian","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P79" t="str">
-        <v>{"macros_p":60,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":492,"delta_kcal":8,"tolerance_kcal":96.8},"issues":[]}}</v>
+        <v>{"macros_p":72,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":531,"delta_kcal":13,"tolerance_kcal":108.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>lunch_dinner_chicken-bulgogi-bowl</v>
+        <v>lunch_dinner_baked-feta-chickpea-traybake</v>
       </c>
       <c r="B80" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C80" t="str">
-        <v>Chicken bulgogi bowl</v>
+        <v>Baked feta &amp; chickpea traybake</v>
       </c>
       <c r="D80" t="str">
-        <v>Chicken bulgogi bowl</v>
+        <v>Baked Feta &amp; Chickpea Traybake</v>
       </c>
       <c r="E80" t="str">
-        <v>Chicken bulgogi bowl</v>
+        <v>Baked feta &amp; chickpea traybake</v>
       </c>
       <c r="F80" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G80">
-        <v>495</v>
+        <v>615</v>
       </c>
       <c r="H80">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="I80">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J80">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="K80" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4397,42 +4397,42 @@
         <v>1</v>
       </c>
       <c r="O80" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"asian","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P80" t="str">
-        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":484,"delta_kcal":11,"tolerance_kcal":99},"issues":[]}}</v>
+        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":629,"delta_kcal":14,"tolerance_kcal":123},"issues":[]}}</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>lunch_dinner_chicken-souvlaki-tzatziki-greek-salad</v>
+        <v>lunch_dinner_tuna-nicoise-salad</v>
       </c>
       <c r="B81" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C81" t="str">
-        <v>Chicken souvlaki + tzatziki + Greek salad</v>
+        <v>Tuna Nicoise salad</v>
       </c>
       <c r="D81" t="str">
-        <v>Chicken Souvlaki + Greek Salad</v>
+        <v>Tuna Nicoise salad</v>
       </c>
       <c r="E81" t="str">
-        <v>Chicken souvlaki + tzatziki + Greek salad</v>
+        <v>Tuna Nicoise salad</v>
       </c>
       <c r="F81" t="str">
         <v>Continental</v>
       </c>
       <c r="G81">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="H81">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I81">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J81">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K81" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4447,39 +4447,39 @@
         <v>1</v>
       </c>
       <c r="O81" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P81" t="str">
-        <v>{"macros_p":72,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":531,"delta_kcal":13,"tolerance_kcal":108.8},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":514,"delta_kcal":10,"tolerance_kcal":104.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>lunch_dinner_baked-feta-chickpea-traybake</v>
+        <v>lunch_dinner_halloumi-roasted-veg-quinoa-bowl</v>
       </c>
       <c r="B82" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C82" t="str">
-        <v>Baked feta &amp; chickpea traybake</v>
+        <v>Halloumi &amp; roasted-veg quinoa bowl</v>
       </c>
       <c r="D82" t="str">
-        <v>Baked Feta &amp; Chickpea Traybake</v>
+        <v>Halloumi &amp; Quinoa Bowl</v>
       </c>
       <c r="E82" t="str">
-        <v>Baked feta &amp; chickpea traybake</v>
+        <v>Halloumi &amp; roasted-veg quinoa bowl</v>
       </c>
       <c r="F82" t="str">
         <v>Continental</v>
       </c>
       <c r="G82">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="H82">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I82">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="J82">
         <v>33</v>
@@ -4497,42 +4497,42 @@
         <v>1</v>
       </c>
       <c r="O82" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P82" t="str">
-        <v>{"macros_p":36,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":629,"delta_kcal":14,"tolerance_kcal":123},"issues":[]}}</v>
+        <v>{"macros_p":40,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":613,"delta_kcal":12,"tolerance_kcal":120.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>lunch_dinner_tuna-nicoise-salad</v>
+        <v>lunch_dinner_chicken-white-bean-stew</v>
       </c>
       <c r="B83" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C83" t="str">
-        <v>Tuna Nicoise salad</v>
+        <v>Chicken &amp; white-bean stew</v>
       </c>
       <c r="D83" t="str">
-        <v>Tuna Nicoise salad</v>
+        <v>Chicken &amp; White-Bean Stew</v>
       </c>
       <c r="E83" t="str">
-        <v>Tuna Nicoise salad</v>
+        <v>Chicken &amp; white-bean stew</v>
       </c>
       <c r="F83" t="str">
         <v>Continental</v>
       </c>
       <c r="G83">
-        <v>524</v>
+        <v>620</v>
       </c>
       <c r="H83">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I83">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="J83">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K83" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4547,42 +4547,42 @@
         <v>1</v>
       </c>
       <c r="O83" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P83" t="str">
-        <v>{"macros_p":55,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":514,"delta_kcal":10,"tolerance_kcal":104.8},"issues":[]}}</v>
+        <v>{"macros_p":65,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":616,"delta_kcal":4,"tolerance_kcal":124},"issues":[]}}</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>lunch_dinner_halloumi-roasted-veg-quinoa-bowl</v>
+        <v>lunch_dinner_chickpea-pasta-tuna-tomato</v>
       </c>
       <c r="B84" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C84" t="str">
-        <v>Halloumi &amp; roasted-veg quinoa bowl</v>
+        <v>Chickpea pasta with tuna &amp; tomato</v>
       </c>
       <c r="D84" t="str">
-        <v>Halloumi &amp; Quinoa Bowl</v>
+        <v>Chickpea Pasta with Tuna</v>
       </c>
       <c r="E84" t="str">
-        <v>Halloumi &amp; roasted-veg quinoa bowl</v>
+        <v>Chickpea pasta with tuna &amp; tomato</v>
       </c>
       <c r="F84" t="str">
         <v>Continental</v>
       </c>
       <c r="G84">
-        <v>601</v>
+        <v>496</v>
       </c>
       <c r="H84">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I84">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J84">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K84" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4597,42 +4597,42 @@
         <v>1</v>
       </c>
       <c r="O84" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P84" t="str">
-        <v>{"macros_p":40,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":613,"delta_kcal":12,"tolerance_kcal":120.2},"issues":[]}}</v>
+        <v>{"macros_p":50,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":524,"delta_kcal":28,"tolerance_kcal":99.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>lunch_dinner_chicken-white-bean-stew</v>
+        <v>lunch_dinner_chicken-ricotta-carbonara-style-spaghetti</v>
       </c>
       <c r="B85" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C85" t="str">
-        <v>Chicken &amp; white-bean stew</v>
+        <v>Chicken &amp; ricotta carbonara-style spaghetti</v>
       </c>
       <c r="D85" t="str">
-        <v>Chicken &amp; White-Bean Stew</v>
+        <v>Chicken &amp; Ricotta Spaghetti</v>
       </c>
       <c r="E85" t="str">
-        <v>Chicken &amp; white-bean stew</v>
+        <v>Chicken &amp; ricotta carbonara-style spaghetti</v>
       </c>
       <c r="F85" t="str">
         <v>Continental</v>
       </c>
       <c r="G85">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="H85">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="I85">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J85">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K85" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4647,42 +4647,42 @@
         <v>1</v>
       </c>
       <c r="O85" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P85" t="str">
-        <v>{"macros_p":65,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"soup","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":616,"delta_kcal":4,"tolerance_kcal":124},"issues":[]}}</v>
+        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":623,"delta_kcal":7,"tolerance_kcal":126},"issues":[]}}</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>lunch_dinner_chickpea-pasta-tuna-tomato</v>
+        <v>lunch_dinner_mackerel-quinoa-salad</v>
       </c>
       <c r="B86" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C86" t="str">
-        <v>Chickpea pasta with tuna &amp; tomato</v>
+        <v>Mackerel &amp; quinoa salad</v>
       </c>
       <c r="D86" t="str">
-        <v>Chickpea Pasta with Tuna</v>
+        <v>Mackerel &amp; Quinoa Salad</v>
       </c>
       <c r="E86" t="str">
-        <v>Chickpea pasta with tuna &amp; tomato</v>
+        <v>Mackerel &amp; quinoa salad</v>
       </c>
       <c r="F86" t="str">
         <v>Continental</v>
       </c>
       <c r="G86">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="H86">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I86">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="J86">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K86" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4697,48 +4697,48 @@
         <v>1</v>
       </c>
       <c r="O86" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P86" t="str">
-        <v>{"macros_p":50,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":524,"delta_kcal":28,"tolerance_kcal":99.2},"issues":[]}}</v>
+        <v>{"macros_p":35,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":461,"delta_kcal":2,"tolerance_kcal":92.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>lunch_dinner_chicken-ricotta-carbonara-style-spaghetti</v>
+        <v>lunch_dinner_grilled-chicken-veg-pasta</v>
       </c>
       <c r="B87" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C87" t="str">
-        <v>Chicken &amp; ricotta carbonara-style spaghetti</v>
+        <v>Grilled chicken, veg + pasta</v>
       </c>
       <c r="D87" t="str">
-        <v>Chicken &amp; Ricotta Spaghetti</v>
+        <v>Grilled Chicken, Veg &amp; Pasta</v>
       </c>
       <c r="E87" t="str">
-        <v>Chicken &amp; ricotta carbonara-style spaghetti</v>
+        <v>Grilled chicken, veg + pasta</v>
       </c>
       <c r="F87" t="str">
         <v>Continental</v>
       </c>
       <c r="G87">
-        <v>630</v>
+        <v>529</v>
       </c>
       <c r="H87">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I87">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J87">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K87" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L87" t="str">
-        <v>assumptions_v2026_08_03</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M87" t="str">
         <v>seed_v1</v>
@@ -4747,39 +4747,39 @@
         <v>1</v>
       </c>
       <c r="O87" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P87" t="str">
-        <v>{"macros_p":57,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":623,"delta_kcal":7,"tolerance_kcal":126},"issues":[]}}</v>
+        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":522,"delta_kcal":7,"tolerance_kcal":105.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>lunch_dinner_mackerel-quinoa-salad</v>
+        <v>lunch_dinner_chicken-shawarma-plate-garlic-rice</v>
       </c>
       <c r="B88" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C88" t="str">
-        <v>Mackerel &amp; quinoa salad</v>
+        <v>Chicken shawarma plate + garlic rice</v>
       </c>
       <c r="D88" t="str">
-        <v>Mackerel &amp; Quinoa Salad</v>
+        <v>Chicken Shawarma Plate + Rice</v>
       </c>
       <c r="E88" t="str">
-        <v>Mackerel &amp; quinoa salad</v>
+        <v>Chicken shawarma plate + garlic rice</v>
       </c>
       <c r="F88" t="str">
         <v>Continental</v>
       </c>
       <c r="G88">
-        <v>463</v>
+        <v>646</v>
       </c>
       <c r="H88">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="I88">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="J88">
         <v>21</v>
@@ -4788,7 +4788,7 @@
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L88" t="str">
-        <v>assumptions_v2026_08_03</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M88" t="str">
         <v>seed_v1</v>
@@ -4797,39 +4797,39 @@
         <v>1</v>
       </c>
       <c r="O88" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P88" t="str">
-        <v>{"macros_p":35,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":461,"delta_kcal":2,"tolerance_kcal":92.6},"issues":[]}}</v>
+        <v>{"macros_p":63,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":633,"delta_kcal":13,"tolerance_kcal":129.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>lunch_dinner_grilled-chicken-veg-pasta</v>
+        <v>lunch_dinner_plain-chicken-tikka-plate</v>
       </c>
       <c r="B89" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C89" t="str">
-        <v>Grilled chicken, veg + pasta</v>
+        <v>Plain chicken tikka plate</v>
       </c>
       <c r="D89" t="str">
-        <v>Grilled Chicken, Veg &amp; Pasta</v>
+        <v>Plain Chicken Tikka Plate</v>
       </c>
       <c r="E89" t="str">
-        <v>Grilled chicken, veg + pasta</v>
+        <v>Plain chicken tikka plate</v>
       </c>
       <c r="F89" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G89">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="H89">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I89">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="J89">
         <v>14</v>
@@ -4847,42 +4847,42 @@
         <v>1</v>
       </c>
       <c r="O89" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
       </c>
       <c r="P89" t="str">
-        <v>{"macros_p":55,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":522,"delta_kcal":7,"tolerance_kcal":105.8},"issues":[]}}</v>
+        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":498,"delta_kcal":22,"tolerance_kcal":104},"issues":[]}}</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>lunch_dinner_chicken-shawarma-plate-garlic-rice</v>
+        <v>lunch_dinner_pesto-millet-pasta-chicken</v>
       </c>
       <c r="B90" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C90" t="str">
-        <v>Chicken shawarma plate + garlic rice</v>
+        <v>Pesto millet pasta + chicken</v>
       </c>
       <c r="D90" t="str">
-        <v>Chicken Shawarma Plate + Rice</v>
+        <v>Pesto Millet Pasta + Chicken</v>
       </c>
       <c r="E90" t="str">
-        <v>Chicken shawarma plate + garlic rice</v>
+        <v>Pesto millet pasta + chicken</v>
       </c>
       <c r="F90" t="str">
         <v>Continental</v>
       </c>
       <c r="G90">
-        <v>646</v>
+        <v>561</v>
       </c>
       <c r="H90">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="I90">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J90">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K90" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4897,42 +4897,42 @@
         <v>1</v>
       </c>
       <c r="O90" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P90" t="str">
-        <v>{"macros_p":63,"protein_family":"chicken","meal_weight_class":"heavy","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":633,"delta_kcal":13,"tolerance_kcal":129.2},"issues":[]}}</v>
+        <v>{"macros_p":47,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"high","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":557,"delta_kcal":4,"tolerance_kcal":112.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>lunch_dinner_plain-chicken-tikka-plate</v>
+        <v>lunch_dinner_aglio-olio-millet-pasta-prawns</v>
       </c>
       <c r="B91" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C91" t="str">
-        <v>Plain chicken tikka plate</v>
+        <v>Aglio e olio millet pasta + prawns</v>
       </c>
       <c r="D91" t="str">
-        <v>Plain Chicken Tikka Plate</v>
+        <v>Aglio e Olio Millet Pasta + Prawns</v>
       </c>
       <c r="E91" t="str">
-        <v>Plain chicken tikka plate</v>
+        <v>Aglio e olio millet pasta + prawns</v>
       </c>
       <c r="F91" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G91">
-        <v>520</v>
+        <v>483</v>
       </c>
       <c r="H91">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="I91">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="J91">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K91" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4947,42 +4947,42 @@
         <v>1</v>
       </c>
       <c r="O91" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"medium","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"]}</v>
       </c>
       <c r="P91" t="str">
-        <v>{"macros_p":61,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"medium","goal_fit":["high_protein","low_carb","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":498,"delta_kcal":22,"tolerance_kcal":104},"issues":[]}}</v>
+        <v>{"macros_p":42,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":481,"delta_kcal":2,"tolerance_kcal":96.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>lunch_dinner_pesto-millet-pasta-chicken</v>
+        <v>lunch_dinner_salmon-avocado-salad-fresh-grilled</v>
       </c>
       <c r="B92" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C92" t="str">
-        <v>Pesto millet pasta + chicken</v>
+        <v>Salmon avocado salad (fresh grilled)</v>
       </c>
       <c r="D92" t="str">
-        <v>Pesto Millet Pasta + Chicken</v>
+        <v>Fresh Grilled Salmon &amp; Avocado Salad</v>
       </c>
       <c r="E92" t="str">
-        <v>Pesto millet pasta + chicken</v>
+        <v>Salmon avocado salad (fresh grilled)</v>
       </c>
       <c r="F92" t="str">
         <v>Continental</v>
       </c>
       <c r="G92">
-        <v>561</v>
+        <v>423</v>
       </c>
       <c r="H92">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="I92">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="J92">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K92" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -4997,42 +4997,42 @@
         <v>1</v>
       </c>
       <c r="O92" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"high","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P92" t="str">
-        <v>{"macros_p":47,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"high","format":"plate","effort":"medium","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":557,"delta_kcal":4,"tolerance_kcal":112.2},"issues":[]}}</v>
+        <v>{"macros_p":29,"protein_family":"fish","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":431,"delta_kcal":8,"tolerance_kcal":84.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>lunch_dinner_aglio-olio-millet-pasta-prawns</v>
+        <v>lunch_dinner_smoked-chicken-salad-full</v>
       </c>
       <c r="B93" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C93" t="str">
-        <v>Aglio e olio millet pasta + prawns</v>
+        <v>Smoked chicken salad (full size)</v>
       </c>
       <c r="D93" t="str">
-        <v>Aglio e Olio Millet Pasta + Prawns</v>
+        <v>Smoked Chicken Salad (Full Size)</v>
       </c>
       <c r="E93" t="str">
-        <v>Aglio e olio millet pasta + prawns</v>
+        <v>Smoked chicken salad (full size)</v>
       </c>
       <c r="F93" t="str">
         <v>Continental</v>
       </c>
       <c r="G93">
-        <v>483</v>
+        <v>386</v>
       </c>
       <c r="H93">
         <v>42</v>
       </c>
       <c r="I93">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="J93">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K93" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -5047,42 +5047,42 @@
         <v>1</v>
       </c>
       <c r="O93" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"medium","cuisine":"continental","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P93" t="str">
-        <v>{"macros_p":42,"protein_family":"fish","meal_weight_class":"medium","carb_level":"medium","format":"plate","effort":"low","goal_fit":["high_protein","two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":481,"delta_kcal":2,"tolerance_kcal":96.6},"issues":[]}}</v>
+        <v>{"macros_p":42,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":393,"delta_kcal":7,"tolerance_kcal":77.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>lunch_dinner_salmon-avocado-salad-fresh-grilled</v>
+        <v>lunch_dinner_hummus-salad-protein-boosted</v>
       </c>
       <c r="B94" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C94" t="str">
-        <v>Salmon avocado salad (fresh grilled)</v>
+        <v>Hummus salad (protein-boosted)</v>
       </c>
       <c r="D94" t="str">
-        <v>Fresh Grilled Salmon &amp; Avocado Salad</v>
+        <v>Hummus Salad (Protein-Boosted)</v>
       </c>
       <c r="E94" t="str">
-        <v>Salmon avocado salad (fresh grilled)</v>
+        <v>Hummus salad (protein-boosted)</v>
       </c>
       <c r="F94" t="str">
         <v>Continental</v>
       </c>
       <c r="G94">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="H94">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="I94">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J94">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K94" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -5097,42 +5097,42 @@
         <v>1</v>
       </c>
       <c r="O94" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"fish","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
       </c>
       <c r="P94" t="str">
-        <v>{"macros_p":29,"protein_family":"fish","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":431,"delta_kcal":8,"tolerance_kcal":84.6},"issues":[]}}</v>
+        <v>{"macros_p":46,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":409,"delta_kcal":2,"tolerance_kcal":82.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>lunch_dinner_smoked-chicken-salad-full</v>
+        <v>lunch_dinner_sweet-potato-kaala-chana-leaner</v>
       </c>
       <c r="B95" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C95" t="str">
-        <v>Smoked chicken salad (full size)</v>
+        <v>Sweet potato + kaala chana + roti (leaner)</v>
       </c>
       <c r="D95" t="str">
-        <v>Smoked Chicken Salad (Full Size)</v>
+        <v>Sweet Potato &amp; Kaala Chana (Leaner)</v>
       </c>
       <c r="E95" t="str">
-        <v>Smoked chicken salad (full size)</v>
+        <v>Sweet potato + kaala chana + roti (leaner)</v>
       </c>
       <c r="F95" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G95">
-        <v>386</v>
+        <v>526</v>
       </c>
       <c r="H95">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="I95">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="J95">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K95" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -5147,42 +5147,42 @@
         <v>1</v>
       </c>
       <c r="O95" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
       </c>
       <c r="P95" t="str">
-        <v>{"macros_p":42,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":393,"delta_kcal":7,"tolerance_kcal":77.2},"issues":[]}}</v>
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":526,"delta_kcal":0,"tolerance_kcal":105.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>lunch_dinner_hummus-salad-protein-boosted</v>
+        <v>lunch_dinner_paneer-cutlets-dal-salad</v>
       </c>
       <c r="B96" t="str">
         <v>lunch_dinner</v>
       </c>
       <c r="C96" t="str">
-        <v>Hummus salad (protein-boosted)</v>
+        <v>Paneer cutlets + dal + salad</v>
       </c>
       <c r="D96" t="str">
-        <v>Hummus Salad (Protein-Boosted)</v>
+        <v>Paneer Cutlets + Dal + Salad</v>
       </c>
       <c r="E96" t="str">
-        <v>Hummus salad (protein-boosted)</v>
+        <v>Paneer cutlets + dal + salad</v>
       </c>
       <c r="F96" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G96">
-        <v>411</v>
+        <v>677</v>
       </c>
       <c r="H96">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I96">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J96">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="K96" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -5197,48 +5197,48 @@
         <v>1</v>
       </c>
       <c r="O96" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"chicken","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"]}</v>
+        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
       </c>
       <c r="P96" t="str">
-        <v>{"macros_p":46,"protein_family":"chicken","meal_weight_class":"medium","carb_level":"low","format":"salad","effort":"medium","goal_fit":["high_protein","low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":409,"delta_kcal":2,"tolerance_kcal":82.2},"issues":[]}}</v>
+        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":678,"delta_kcal":1,"tolerance_kcal":135.4},"issues":[]}}</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>lunch_dinner_sweet-potato-kaala-chana-leaner</v>
+        <v>snack_fruit-almonds-plant-shake</v>
       </c>
       <c r="B97" t="str">
-        <v>lunch_dinner</v>
+        <v>snack</v>
       </c>
       <c r="C97" t="str">
-        <v>Sweet potato + kaala chana + roti (leaner)</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="D97" t="str">
-        <v>Sweet Potato &amp; Kaala Chana (Leaner)</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="E97" t="str">
-        <v>Sweet potato + kaala chana + roti (leaner)</v>
+        <v>Fruit + Almonds + Plant Shake</v>
       </c>
       <c r="F97" t="str">
-        <v>Indian</v>
+        <v>General</v>
       </c>
       <c r="G97">
-        <v>526</v>
+        <v>200</v>
       </c>
       <c r="H97">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I97">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="J97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K97" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+        <v>USDA + custom user specs</v>
       </c>
       <c r="L97" t="str">
-        <v>assumptions_v2026_08_06</v>
+        <v>v1_custom</v>
       </c>
       <c r="M97" t="str">
         <v>seed_v1</v>
@@ -5247,48 +5247,48 @@
         <v>1</v>
       </c>
       <c r="O97" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"curry","effort":"medium","goal_fit":[]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P97" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"medium","carb_level":"high","format":"curry","effort":"medium","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":526,"delta_kcal":0,"tolerance_kcal":105.2},"issues":[]}}</v>
+        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>lunch_dinner_paneer-cutlets-dal-salad</v>
+        <v>snack_chaat-bhel-protein-shake</v>
       </c>
       <c r="B98" t="str">
-        <v>lunch_dinner</v>
+        <v>snack</v>
       </c>
       <c r="C98" t="str">
-        <v>Paneer cutlets + dal + salad</v>
+        <v>Chaat + Bhel + Protein Shake</v>
       </c>
       <c r="D98" t="str">
-        <v>Paneer Cutlets + Dal + Salad</v>
+        <v>Chaat + Bhel + Protein Shake</v>
       </c>
       <c r="E98" t="str">
-        <v>Paneer cutlets + dal + salad</v>
+        <v>Chaat + Bhel + Protein Shake</v>
       </c>
       <c r="F98" t="str">
         <v>Indian</v>
       </c>
       <c r="G98">
-        <v>677</v>
+        <v>345</v>
       </c>
       <c r="H98">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I98">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="J98">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="K98" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
+        <v>IFCT/USDA + custom user specs</v>
       </c>
       <c r="L98" t="str">
-        <v>assumptions_v2026_08_06</v>
+        <v>v1_custom</v>
       </c>
       <c r="M98" t="str">
         <v>seed_v1</v>
@@ -5297,48 +5297,48 @@
         <v>1</v>
       </c>
       <c r="O98" t="str">
-        <v>{"meal_type":"lunch_dinner","protein_family":"vegetarian","carb_level":"high","cuisine":"indian","format":"salad","effort":"high","goal_fit":["two_meals"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P98" t="str">
-        <v>{"macros_p":37,"protein_family":"vegetarian","meal_weight_class":"heavy","carb_level":"high","format":"salad","effort":"high","goal_fit":["two_meals"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":678,"delta_kcal":1,"tolerance_kcal":135.4},"issues":[]}}</v>
+        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>snack_greek-yogurt-berry-bowl</v>
       </c>
       <c r="B99" t="str">
         <v>snack</v>
       </c>
       <c r="C99" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Greek yogurt + berry bowl</v>
       </c>
       <c r="D99" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Greek yogurt + berry bowl</v>
       </c>
       <c r="E99" t="str">
-        <v>Fruit + Almonds + Plant Shake</v>
+        <v>Greek yogurt + berry bowl</v>
       </c>
       <c r="F99" t="str">
-        <v>General</v>
+        <v>International</v>
       </c>
       <c r="G99">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H99">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I99">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J99">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K99" t="str">
-        <v>USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L99" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M99" t="str">
         <v>seed_v1</v>
@@ -5347,48 +5347,48 @@
         <v>1</v>
       </c>
       <c r="O99" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"general","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P99" t="str">
-        <v>{"macros_p":23,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"usda_reference","source_url":"","confidence_score":0.8,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":213,"delta_kcal":13,"tolerance_kcal":40},"issues":[]}}</v>
+        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
       </c>
       <c r="B100" t="str">
         <v>snack</v>
       </c>
       <c r="C100" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Carrot halwa (sugar-free) + protein shake</v>
       </c>
       <c r="D100" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Carrot Halwa + Protein Shake</v>
       </c>
       <c r="E100" t="str">
-        <v>Chaat + Bhel + Protein Shake</v>
+        <v>Carrot halwa (sugar-free) + protein shake</v>
       </c>
       <c r="F100" t="str">
         <v>Indian</v>
       </c>
       <c r="G100">
-        <v>345</v>
+        <v>220</v>
       </c>
       <c r="H100">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I100">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J100">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K100" t="str">
-        <v>IFCT/USDA + custom user specs</v>
+        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L100" t="str">
-        <v>v1_custom</v>
+        <v>assumptions_v2026_02_17</v>
       </c>
       <c r="M100" t="str">
         <v>seed_v1</v>
@@ -5397,42 +5397,42 @@
         <v>1</v>
       </c>
       <c r="O100" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P100" t="str">
-        <v>{"macros_p":26,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.88,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":337,"delta_kcal":8,"tolerance_kcal":69},"issues":[]}}</v>
+        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>snack_nuts-seeds-protein-shake</v>
       </c>
       <c r="B101" t="str">
         <v>snack</v>
       </c>
       <c r="C101" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Nuts, seeds + protein shake</v>
       </c>
       <c r="D101" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Nuts + Seeds + Protein Shake</v>
       </c>
       <c r="E101" t="str">
-        <v>Greek yogurt + berry bowl</v>
+        <v>Nuts, seeds + protein shake</v>
       </c>
       <c r="F101" t="str">
         <v>International</v>
       </c>
       <c r="G101">
-        <v>203</v>
+        <v>320</v>
       </c>
       <c r="H101">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I101">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J101">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K101" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -5447,42 +5447,42 @@
         <v>1</v>
       </c>
       <c r="O101" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"international","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P101" t="str">
-        <v>{"macros_p":21,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":208,"delta_kcal":5,"tolerance_kcal":40.6},"issues":[]}}</v>
+        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>snack_sweet-potato-chaat</v>
       </c>
       <c r="B102" t="str">
         <v>snack</v>
       </c>
       <c r="C102" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Sweet potato chaat</v>
       </c>
       <c r="D102" t="str">
-        <v>Carrot Halwa + Protein Shake</v>
+        <v>Sweet potato chaat</v>
       </c>
       <c r="E102" t="str">
-        <v>Carrot halwa (sugar-free) + protein shake</v>
+        <v>Sweet potato chaat</v>
       </c>
       <c r="F102" t="str">
         <v>Indian</v>
       </c>
       <c r="G102">
-        <v>220</v>
+        <v>135</v>
       </c>
       <c r="H102">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I102">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J102">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K102" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -5497,42 +5497,42 @@
         <v>1</v>
       </c>
       <c r="O102" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P102" t="str">
-        <v>{"macros_p":28,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":225,"delta_kcal":5,"tolerance_kcal":44},"issues":[]}}</v>
+        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>snack_kaala-chana-chaat</v>
       </c>
       <c r="B103" t="str">
         <v>snack</v>
       </c>
       <c r="C103" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Kaala chana chaat</v>
       </c>
       <c r="D103" t="str">
-        <v>Nuts + Seeds + Protein Shake</v>
+        <v>Kaala chana chaat</v>
       </c>
       <c r="E103" t="str">
-        <v>Nuts, seeds + protein shake</v>
+        <v>Kaala chana chaat</v>
       </c>
       <c r="F103" t="str">
-        <v>International</v>
+        <v>Indian</v>
       </c>
       <c r="G103">
-        <v>320</v>
+        <v>246</v>
       </c>
       <c r="H103">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I103">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="J103">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K103" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -5547,42 +5547,42 @@
         <v>1</v>
       </c>
       <c r="O103" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"international","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
       </c>
       <c r="P103" t="str">
-        <v>{"macros_p":31,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":321,"delta_kcal":1,"tolerance_kcal":64},"issues":[]}}</v>
+        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>snack_avocado-cheese-toast</v>
       </c>
       <c r="B104" t="str">
         <v>snack</v>
       </c>
       <c r="C104" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Avocado/cheese toast</v>
       </c>
       <c r="D104" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Avocado/Cheese Toast</v>
       </c>
       <c r="E104" t="str">
-        <v>Sweet potato chaat</v>
+        <v>Avocado/cheese toast</v>
       </c>
       <c r="F104" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G104">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="H104">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I104">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J104">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K104" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -5597,48 +5597,48 @@
         <v>1</v>
       </c>
       <c r="O104" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P104" t="str">
-        <v>{"macros_p":3,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":140,"delta_kcal":5,"tolerance_kcal":35},"issues":[]}}</v>
+        <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":200,"delta_kcal":7,"tolerance_kcal":38.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>snack_boiled-eggs-hummus-veg-sticks</v>
       </c>
       <c r="B105" t="str">
         <v>snack</v>
       </c>
       <c r="C105" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Boiled eggs + hummus + veg sticks</v>
       </c>
       <c r="D105" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Eggs + Hummus + Veg Sticks</v>
       </c>
       <c r="E105" t="str">
-        <v>Kaala chana chaat</v>
+        <v>Boiled eggs + hummus + veg sticks</v>
       </c>
       <c r="F105" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G105">
         <v>246</v>
       </c>
       <c r="H105">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I105">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="J105">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K105" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L105" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M105" t="str">
         <v>seed_v1</v>
@@ -5647,48 +5647,48 @@
         <v>1</v>
       </c>
       <c r="O105" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"indian","format":"chaat","effort":"low","goal_fit":[]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P105" t="str">
-        <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"chaat","effort":"low","goal_fit":[],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":252,"delta_kcal":6,"tolerance_kcal":49.2},"issues":[]}}</v>
+        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":246,"delta_kcal":0,"tolerance_kcal":49.2},"issues":[]}}</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>snack_edamame-sea-salt</v>
       </c>
       <c r="B106" t="str">
         <v>snack</v>
       </c>
       <c r="C106" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Edamame + sea salt</v>
       </c>
       <c r="D106" t="str">
-        <v>Avocado/Cheese Toast</v>
+        <v>Edamame + sea salt</v>
       </c>
       <c r="E106" t="str">
-        <v>Avocado/cheese toast</v>
+        <v>Edamame + sea salt</v>
       </c>
       <c r="F106" t="str">
-        <v>Continental</v>
+        <v>Asian</v>
       </c>
       <c r="G106">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="H106">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I106">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J106">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K106" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L106" t="str">
-        <v>assumptions_v2026_02_17</v>
+        <v>assumptions_v2026_08_02</v>
       </c>
       <c r="M106" t="str">
         <v>seed_v1</v>
@@ -5697,42 +5697,42 @@
         <v>1</v>
       </c>
       <c r="O106" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"toast","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"asian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P106" t="str">
-        <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"toast","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":200,"delta_kcal":7,"tolerance_kcal":38.6},"issues":[]}}</v>
+        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":196,"delta_kcal":13,"tolerance_kcal":36.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+        <v>snack_paneer-tikka-skewers</v>
       </c>
       <c r="B107" t="str">
         <v>snack</v>
       </c>
       <c r="C107" t="str">
-        <v>Boiled eggs + hummus + veg sticks</v>
+        <v>Paneer tikka skewers</v>
       </c>
       <c r="D107" t="str">
-        <v>Eggs + Hummus + Veg Sticks</v>
+        <v>Paneer tikka skewers</v>
       </c>
       <c r="E107" t="str">
-        <v>Boiled eggs + hummus + veg sticks</v>
+        <v>Paneer tikka skewers</v>
       </c>
       <c r="F107" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G107">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="H107">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I107">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J107">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K107" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -5747,42 +5747,42 @@
         <v>1</v>
       </c>
       <c r="O107" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P107" t="str">
-        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":246,"delta_kcal":0,"tolerance_kcal":49.2},"issues":[]}}</v>
+        <v>{"macros_p":15,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":220,"delta_kcal":4,"tolerance_kcal":44.8},"issues":[]}}</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>snack_edamame-sea-salt</v>
+        <v>snack_overnight-oats-whey-bowl</v>
       </c>
       <c r="B108" t="str">
         <v>snack</v>
       </c>
       <c r="C108" t="str">
-        <v>Edamame + sea salt</v>
+        <v>Overnight oats + whey bowl</v>
       </c>
       <c r="D108" t="str">
-        <v>Edamame + sea salt</v>
+        <v>Overnight Oats + Whey</v>
       </c>
       <c r="E108" t="str">
-        <v>Edamame + sea salt</v>
+        <v>Overnight oats + whey bowl</v>
       </c>
       <c r="F108" t="str">
-        <v>Asian</v>
+        <v>Continental</v>
       </c>
       <c r="G108">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="H108">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I108">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="J108">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K108" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -5797,48 +5797,48 @@
         <v>1</v>
       </c>
       <c r="O108" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"asian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P108" t="str">
-        <v>{"macros_p":18,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":196,"delta_kcal":13,"tolerance_kcal":36.6},"issues":[]}}</v>
+        <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":218,"delta_kcal":0,"tolerance_kcal":43.6},"issues":[]}}</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>snack_paneer-tikka-skewers</v>
+        <v>snack_hummus-salad</v>
       </c>
       <c r="B109" t="str">
         <v>snack</v>
       </c>
       <c r="C109" t="str">
-        <v>Paneer tikka skewers</v>
+        <v>Hummus salad</v>
       </c>
       <c r="D109" t="str">
-        <v>Paneer tikka skewers</v>
+        <v>Hummus Salad</v>
       </c>
       <c r="E109" t="str">
-        <v>Paneer tikka skewers</v>
+        <v>Hummus salad</v>
       </c>
       <c r="F109" t="str">
-        <v>Indian</v>
+        <v>Continental</v>
       </c>
       <c r="G109">
-        <v>224</v>
+        <v>136</v>
       </c>
       <c r="H109">
+        <v>7</v>
+      </c>
+      <c r="I109">
         <v>15</v>
       </c>
-      <c r="I109">
-        <v>4</v>
-      </c>
       <c r="J109">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K109" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L109" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M109" t="str">
         <v>seed_v1</v>
@@ -5847,48 +5847,48 @@
         <v>1</v>
       </c>
       <c r="O109" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P109" t="str">
-        <v>{"macros_p":15,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":220,"delta_kcal":4,"tolerance_kcal":44.8},"issues":[]}}</v>
+        <v>{"macros_p":7,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":142,"delta_kcal":6,"tolerance_kcal":35},"issues":[]}}</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>snack_overnight-oats-whey-bowl</v>
+        <v>snack_acai-bowl</v>
       </c>
       <c r="B110" t="str">
         <v>snack</v>
       </c>
       <c r="C110" t="str">
-        <v>Overnight oats + whey bowl</v>
+        <v>Acai bowl</v>
       </c>
       <c r="D110" t="str">
-        <v>Overnight Oats + Whey</v>
+        <v>Acai Bowl</v>
       </c>
       <c r="E110" t="str">
-        <v>Overnight oats + whey bowl</v>
+        <v>Acai bowl</v>
       </c>
       <c r="F110" t="str">
         <v>Continental</v>
       </c>
       <c r="G110">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H110">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I110">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J110">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K110" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
       </c>
       <c r="L110" t="str">
-        <v>assumptions_v2026_08_02</v>
+        <v>assumptions_v2026_08_06</v>
       </c>
       <c r="M110" t="str">
         <v>seed_v1</v>
@@ -5897,42 +5897,42 @@
         <v>1</v>
       </c>
       <c r="O110" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P110" t="str">
-        <v>{"macros_p":9,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":218,"delta_kcal":0,"tolerance_kcal":43.6},"issues":[]}}</v>
+        <v>{"macros_p":6,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":253,"delta_kcal":8,"tolerance_kcal":49},"issues":[]}}</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>snack_hummus-salad</v>
+        <v>snack_paneer-cutlets</v>
       </c>
       <c r="B111" t="str">
         <v>snack</v>
       </c>
       <c r="C111" t="str">
-        <v>Hummus salad</v>
+        <v>Paneer cutlets</v>
       </c>
       <c r="D111" t="str">
-        <v>Hummus Salad</v>
+        <v>Paneer Cutlets</v>
       </c>
       <c r="E111" t="str">
-        <v>Hummus salad</v>
+        <v>Paneer cutlets</v>
       </c>
       <c r="F111" t="str">
-        <v>Continental</v>
+        <v>Indian</v>
       </c>
       <c r="G111">
-        <v>136</v>
+        <v>250</v>
       </c>
       <c r="H111">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I111">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J111">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K111" t="str">
         <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
@@ -5947,122 +5947,22 @@
         <v>1</v>
       </c>
       <c r="O111" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"continental","format":"salad","effort":"medium","goal_fit":["low_carb"]}</v>
+        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
       </c>
       <c r="P111" t="str">
-        <v>{"macros_p":7,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"salad","effort":"medium","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":142,"delta_kcal":6,"tolerance_kcal":35},"issues":[]}}</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>snack_acai-bowl</v>
-      </c>
-      <c r="B112" t="str">
-        <v>snack</v>
-      </c>
-      <c r="C112" t="str">
-        <v>Acai bowl</v>
-      </c>
-      <c r="D112" t="str">
-        <v>Acai Bowl</v>
-      </c>
-      <c r="E112" t="str">
-        <v>Acai bowl</v>
-      </c>
-      <c r="F112" t="str">
-        <v>Continental</v>
-      </c>
-      <c r="G112">
-        <v>245</v>
-      </c>
-      <c r="H112">
-        <v>6</v>
-      </c>
-      <c r="I112">
-        <v>28</v>
-      </c>
-      <c r="J112">
-        <v>13</v>
-      </c>
-      <c r="K112" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
-      </c>
-      <c r="L112" t="str">
-        <v>assumptions_v2026_08_06</v>
-      </c>
-      <c r="M112" t="str">
-        <v>seed_v1</v>
-      </c>
-      <c r="N112" t="b">
-        <v>1</v>
-      </c>
-      <c r="O112" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"medium","cuisine":"continental","format":"bowl","effort":"low","goal_fit":["low_carb"]}</v>
-      </c>
-      <c r="P112" t="str">
-        <v>{"macros_p":6,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"medium","format":"bowl","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":253,"delta_kcal":8,"tolerance_kcal":49},"issues":[]}}</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>snack_paneer-cutlets</v>
-      </c>
-      <c r="B113" t="str">
-        <v>snack</v>
-      </c>
-      <c r="C113" t="str">
-        <v>Paneer cutlets</v>
-      </c>
-      <c r="D113" t="str">
-        <v>Paneer Cutlets</v>
-      </c>
-      <c r="E113" t="str">
-        <v>Paneer cutlets</v>
-      </c>
-      <c r="F113" t="str">
-        <v>Indian</v>
-      </c>
-      <c r="G113">
-        <v>250</v>
-      </c>
-      <c r="H113">
-        <v>13</v>
-      </c>
-      <c r="I113">
-        <v>12</v>
-      </c>
-      <c r="J113">
-        <v>17</v>
-      </c>
-      <c r="K113" t="str">
-        <v>IFCT/ICMR-NIN + USDA references + user assumptions</v>
-      </c>
-      <c r="L113" t="str">
-        <v>assumptions_v2026_08_06</v>
-      </c>
-      <c r="M113" t="str">
-        <v>seed_v1</v>
-      </c>
-      <c r="N113" t="b">
-        <v>1</v>
-      </c>
-      <c r="O113" t="str">
-        <v>{"meal_type":"snack","protein_family":"vegetarian","carb_level":"low","cuisine":"indian","format":"plate","effort":"low","goal_fit":["low_carb"]}</v>
-      </c>
-      <c r="P113" t="str">
         <v>{"macros_p":13,"protein_family":"vegetarian","meal_weight_class":"light","carb_level":"low","format":"plate","effort":"low","goal_fit":["low_carb"],"source_type":"composite_reference","source_url":"","confidence_score":0.83,"needs_review":false,"validation":{"macro_calorie":{"is_consistent":true,"expected_kcal":253,"delta_kcal":3,"tolerance_kcal":50},"issues":[]}}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P113"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P111"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I111"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6559,13 +6459,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>breakfast_paneer-egg-white-bhurji-toast</v>
+        <v>breakfast_anda-bhurji-toast</v>
       </c>
       <c r="B18" t="str">
-        <v>Paneer + egg whites</v>
+        <v>Eggs (whole + whites)</v>
       </c>
       <c r="C18">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="D18" t="str">
         <v>Whole wheat toast</v>
@@ -6588,13 +6488,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>breakfast_anda-bhurji-toast</v>
+        <v>breakfast_sardines-toast-avocado</v>
       </c>
       <c r="B19" t="str">
-        <v>Eggs (whole + whites)</v>
+        <v>Sardines</v>
       </c>
       <c r="C19">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="D19" t="str">
         <v>Whole wheat toast</v>
@@ -6603,13 +6503,13 @@
         <v>60</v>
       </c>
       <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
+        <v>Avocado + greens</v>
+      </c>
+      <c r="G19">
+        <v>130</v>
       </c>
       <c r="H19" t="str">
-        <v>Pan-fried</v>
+        <v>Toast</v>
       </c>
       <c r="I19" t="str">
         <v>{}</v>
@@ -6617,28 +6517,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>breakfast_sardines-toast-avocado</v>
+        <v>breakfast_shakshuka-feta</v>
       </c>
       <c r="B20" t="str">
-        <v>Sardines</v>
+        <v>Eggs + feta</v>
       </c>
       <c r="C20">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="D20" t="str">
         <v>Whole wheat toast</v>
       </c>
       <c r="E20">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F20" t="str">
-        <v>Avocado + greens</v>
+        <v>Tomato, pepper, spinach</v>
       </c>
       <c r="G20">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H20" t="str">
-        <v>Toast</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I20" t="str">
         <v>{}</v>
@@ -6646,28 +6546,28 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>breakfast_shakshuka-feta</v>
+        <v>breakfast_cottage-cheese-smoked-salmon-bowl</v>
       </c>
       <c r="B21" t="str">
-        <v>Eggs + feta</v>
+        <v>Cottage cheese + smoked salmon</v>
       </c>
       <c r="C21">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D21" t="str">
         <v>Whole wheat toast</v>
       </c>
       <c r="E21">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F21" t="str">
-        <v>Tomato, pepper, spinach</v>
+        <v>Avocado + greens</v>
       </c>
       <c r="G21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H21" t="str">
-        <v>Pan-fried</v>
+        <v>Bowl</v>
       </c>
       <c r="I21" t="str">
         <v>{}</v>
@@ -6675,28 +6575,28 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>breakfast_cottage-cheese-smoked-salmon-bowl</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti</v>
       </c>
       <c r="B22" t="str">
-        <v>Cottage cheese + smoked salmon</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C22">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="D22" t="str">
-        <v>Whole wheat toast</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E22">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>Avocado + greens</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G22">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H22" t="str">
-        <v>Bowl</v>
+        <v>Curry style</v>
       </c>
       <c r="I22" t="str">
         <v>{}</v>
@@ -6704,28 +6604,28 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti</v>
+        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B23" t="str">
-        <v>Chicken breast</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C23">
         <v>150</v>
       </c>
       <c r="D23" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Spaghetti aglio e olio (small portion)</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F23" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G23">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H23" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I23" t="str">
         <v>{}</v>
@@ -6733,28 +6633,28 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lunch_dinner_grilled-salmon-fillet-sauteed-veg-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_rajma-chawal-raita</v>
       </c>
       <c r="B24" t="str">
-        <v>Grilled salmon</v>
+        <v/>
       </c>
       <c r="C24">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D24" t="str">
-        <v>Spaghetti aglio e olio (small portion)</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E24">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F24" t="str">
-        <v>Sautéed broccoli</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G24">
         <v>150</v>
       </c>
       <c r="H24" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I24" t="str">
         <v>{}</v>
@@ -6762,7 +6662,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lunch_dinner_rajma-chawal-raita</v>
+        <v>lunch_dinner_chole-jowar-roti-raita</v>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -6771,16 +6671,16 @@
         <v>0</v>
       </c>
       <c r="D25" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E25">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>Mixed veg sabzi</v>
-      </c>
-      <c r="G25">
-        <v>150</v>
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
       </c>
       <c r="H25" t="str">
         <v>Curry style</v>
@@ -6791,28 +6691,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lunch_dinner_chole-jowar-roti-raita</v>
+        <v>lunch_dinner_vietnamese-chicken-pho</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>Chicken breast</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D26" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Rice noodles</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
+        <v>Pho greens + side salad</v>
+      </c>
+      <c r="G26">
+        <v>80</v>
       </c>
       <c r="H26" t="str">
-        <v>Curry style</v>
+        <v>Soup style</v>
       </c>
       <c r="I26" t="str">
         <v>{}</v>
@@ -6820,28 +6720,28 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lunch_dinner_vietnamese-chicken-pho</v>
+        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
       </c>
       <c r="B27" t="str">
-        <v>Chicken breast</v>
+        <v>Beef steak</v>
       </c>
       <c r="C27">
+        <v>180</v>
+      </c>
+      <c r="D27" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Mixed greens salad</v>
+      </c>
+      <c r="G27">
         <v>150</v>
       </c>
-      <c r="D27" t="str">
-        <v>Rice noodles</v>
-      </c>
-      <c r="E27">
-        <v>120</v>
-      </c>
-      <c r="F27" t="str">
-        <v>Pho greens + side salad</v>
-      </c>
-      <c r="G27">
-        <v>80</v>
-      </c>
       <c r="H27" t="str">
-        <v>Soup style</v>
+        <v>Grilled</v>
       </c>
       <c r="I27" t="str">
         <v>{}</v>
@@ -6849,28 +6749,28 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lunch_dinner_grilled-steak-mixed-greens-salad</v>
+        <v>lunch_dinner_thai-pad-krapow-rice</v>
       </c>
       <c r="B28" t="str">
-        <v>Beef steak</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C28">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D28" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F28" t="str">
-        <v>Mixed greens salad</v>
+        <v>Sautéed peppers + side salad</v>
       </c>
       <c r="G28">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H28" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I28" t="str">
         <v>{}</v>
@@ -6878,28 +6778,28 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lunch_dinner_thai-pad-krapow-rice</v>
+        <v>lunch_dinner_mutton-keema-jowar-roti</v>
       </c>
       <c r="B29" t="str">
-        <v>Chicken breast</v>
+        <v>Mutton keema</v>
       </c>
       <c r="C29">
         <v>150</v>
       </c>
       <c r="D29" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E29">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>Sautéed peppers + side salad</v>
-      </c>
-      <c r="G29">
-        <v>130</v>
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
       </c>
       <c r="H29" t="str">
-        <v>Pan-fried</v>
+        <v>Curry style</v>
       </c>
       <c r="I29" t="str">
         <v>{}</v>
@@ -6907,25 +6807,25 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>lunch_dinner_mutton-keema-jowar-roti</v>
+        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
       </c>
       <c r="B30" t="str">
-        <v>Mutton keema</v>
+        <v>Paneer</v>
       </c>
       <c r="C30">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D30" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <v/>
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G30">
+        <v>120</v>
       </c>
       <c r="H30" t="str">
         <v>Curry style</v>
@@ -6936,25 +6836,25 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lunch_dinner_arhar-dal-rice-matar-paneer</v>
+        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
       </c>
       <c r="B31" t="str">
-        <v>Paneer</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C31">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D31" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E31">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F31" t="str">
         <v>Mixed veg sabzi</v>
       </c>
       <c r="G31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H31" t="str">
         <v>Curry style</v>
@@ -6965,28 +6865,28 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lunch_dinner_chicken-curry-jowar-roti-dal</v>
+        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
       </c>
       <c r="B32" t="str">
-        <v>Chicken breast</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C32">
         <v>150</v>
       </c>
       <c r="D32" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>No carb</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F32" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Pumpkin salad</v>
       </c>
       <c r="G32">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H32" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I32" t="str">
         <v>{}</v>
@@ -6994,25 +6894,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lunch_dinner_grilled-fish-pumpkin-salad</v>
+        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
       </c>
       <c r="B33" t="str">
-        <v>Fish fillet</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C33">
         <v>150</v>
       </c>
       <c r="D33" t="str">
-        <v>No carb</v>
+        <v>Garlic rice (small portion)</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33" t="str">
-        <v>Pumpkin salad</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G33">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H33" t="str">
         <v>Grilled</v>
@@ -7023,28 +6923,28 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>lunch_dinner_grilled-salmon-sauteed-veg-garlic-rice</v>
+        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
       </c>
       <c r="B34" t="str">
-        <v>Grilled salmon</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C34">
         <v>150</v>
       </c>
       <c r="D34" t="str">
-        <v>Garlic rice (small portion)</v>
+        <v>No carb</v>
       </c>
       <c r="E34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F34" t="str">
-        <v>Sautéed broccoli</v>
+        <v>Smoked salmon salad</v>
       </c>
       <c r="G34">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H34" t="str">
-        <v>Grilled</v>
+        <v>Soup style</v>
       </c>
       <c r="I34" t="str">
         <v>{}</v>
@@ -7052,13 +6952,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>lunch_dinner_chicken-soup-smoked-salmon-salad</v>
+        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
       </c>
       <c r="B35" t="str">
-        <v>Chicken breast</v>
+        <v>Paneer</v>
       </c>
       <c r="C35">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D35" t="str">
         <v>No carb</v>
@@ -7067,13 +6967,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="str">
-        <v>Smoked salmon salad</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G35">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H35" t="str">
-        <v>Soup style</v>
+        <v>Curry style</v>
       </c>
       <c r="I35" t="str">
         <v>{}</v>
@@ -7081,13 +6981,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>lunch_dinner_paneer-sabzi-dal-raita</v>
+        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
       </c>
       <c r="B36" t="str">
-        <v>Paneer</v>
+        <v>Pork chop</v>
       </c>
       <c r="C36">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="D36" t="str">
         <v>No carb</v>
@@ -7096,13 +6996,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Pumpkin salad</v>
       </c>
       <c r="G36">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H36" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I36" t="str">
         <v>{}</v>
@@ -7110,7 +7010,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>lunch_dinner_pork-chop-pumpkin-salad</v>
+        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
       </c>
       <c r="B37" t="str">
         <v>Pork chop</v>
@@ -7125,10 +7025,10 @@
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <v>Pumpkin salad</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G37">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H37" t="str">
         <v>Grilled</v>
@@ -7139,13 +7039,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>lunch_dinner_pork-chop-mixed-greens-salad</v>
+        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
       </c>
       <c r="B38" t="str">
-        <v>Pork chop</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C38">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D38" t="str">
         <v>No carb</v>
@@ -7154,13 +7054,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <v>Mixed greens salad</v>
+        <v>Smoked chicken + avocado salad</v>
       </c>
       <c r="G38">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H38" t="str">
-        <v>Grilled</v>
+        <v>Tandoori</v>
       </c>
       <c r="I38" t="str">
         <v>{}</v>
@@ -7168,28 +7068,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>lunch_dinner_tandoori-chicken-smoked-chicken-avocado-salad</v>
+        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
       </c>
       <c r="B39" t="str">
-        <v>Chicken breast</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C39">
         <v>150</v>
       </c>
       <c r="D39" t="str">
-        <v>No carb</v>
+        <v>Spaghetti aglio e olio (small portion)</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39" t="str">
-        <v>Smoked chicken + avocado salad</v>
+        <v>Sautéed broccoli</v>
       </c>
       <c r="G39">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="H39" t="str">
-        <v>Tandoori</v>
+        <v>Soup style</v>
       </c>
       <c r="I39" t="str">
         <v>{}</v>
@@ -7197,28 +7097,28 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>lunch_dinner_broccoli-soup-grilled-fish-spaghetti-aglio-e-olio</v>
+        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
       </c>
       <c r="B40" t="str">
-        <v>Fish fillet</v>
+        <v>Lamb (seekh kabab)</v>
       </c>
       <c r="C40">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="D40" t="str">
-        <v>Spaghetti aglio e olio (small portion)</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E40">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>Sautéed broccoli</v>
+        <v>Sautéed spinach</v>
       </c>
       <c r="G40">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H40" t="str">
-        <v>Soup style</v>
+        <v>Curry style</v>
       </c>
       <c r="I40" t="str">
         <v>{}</v>
@@ -7226,13 +7126,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>lunch_dinner_saag-meat-jowar-roti-dal</v>
+        <v>lunch_dinner_kofta-dal-jowar-roti</v>
       </c>
       <c r="B41" t="str">
-        <v>Lamb (seekh kabab)</v>
+        <v>Veg kofta</v>
       </c>
       <c r="C41">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D41" t="str">
         <v>Jowar roti (millet)</v>
@@ -7241,7 +7141,7 @@
         <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>Sautéed spinach</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G41">
         <v>120</v>
@@ -7255,13 +7155,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>lunch_dinner_kofta-dal-jowar-roti</v>
+        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
       </c>
       <c r="B42" t="str">
-        <v>Veg kofta</v>
+        <v>Lamb (seekh kabab)</v>
       </c>
       <c r="C42">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D42" t="str">
         <v>Jowar roti (millet)</v>
@@ -7270,13 +7170,13 @@
         <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Cauliflower</v>
       </c>
       <c r="G42">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H42" t="str">
-        <v>Curry style</v>
+        <v>Tandoori</v>
       </c>
       <c r="I42" t="str">
         <v>{}</v>
@@ -7284,28 +7184,28 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>lunch_dinner_kababs-dal-gobi-jowar-roti</v>
+        <v>lunch_dinner_fish-curry-rice</v>
       </c>
       <c r="B43" t="str">
-        <v>Lamb (seekh kabab)</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C43">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D43" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="F43" t="str">
-        <v>Cauliflower</v>
-      </c>
-      <c r="G43">
-        <v>150</v>
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
       </c>
       <c r="H43" t="str">
-        <v>Tandoori</v>
+        <v>Curry style</v>
       </c>
       <c r="I43" t="str">
         <v>{}</v>
@@ -7313,25 +7213,25 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>lunch_dinner_fish-curry-rice</v>
+        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
       </c>
       <c r="B44" t="str">
-        <v>Fish fillet</v>
+        <v>Kaala chanaa (black chickpeas)</v>
       </c>
       <c r="C44">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D44" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E44">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v/>
-      </c>
-      <c r="G44" t="str">
-        <v/>
+        <v>Sweet potato curry</v>
+      </c>
+      <c r="G44">
+        <v>180</v>
       </c>
       <c r="H44" t="str">
         <v>Curry style</v>
@@ -7342,28 +7242,28 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>lunch_dinner_sweet-potato-curry-kaala-chanaa-sabzi-jowar-roti</v>
+        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
       </c>
       <c r="B45" t="str">
-        <v>Kaala chanaa (black chickpeas)</v>
+        <v>Smoked salmon</v>
       </c>
       <c r="C45">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D45" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>No carb</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" t="str">
-        <v>Sweet potato curry</v>
+        <v>Avocado &amp; mixed greens</v>
       </c>
       <c r="G45">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="H45" t="str">
-        <v>Curry style</v>
+        <v>Salad</v>
       </c>
       <c r="I45" t="str">
         <v>{}</v>
@@ -7371,10 +7271,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>lunch_dinner_avocado-smoked-salmon-salad</v>
+        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
       </c>
       <c r="B46" t="str">
-        <v>Smoked salmon</v>
+        <v>Smoked chicken breast</v>
       </c>
       <c r="C46">
         <v>120</v>
@@ -7400,28 +7300,28 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>lunch_dinner_avocado-smoked-chicken-salad</v>
+        <v>lunch_dinner_chicken-red-curry-rice</v>
       </c>
       <c r="B47" t="str">
-        <v>Smoked chicken breast</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C47">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D47" t="str">
-        <v>No carb</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F47" t="str">
-        <v>Avocado &amp; mixed greens</v>
+        <v>Red curry vegetables</v>
       </c>
       <c r="G47">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="H47" t="str">
-        <v>Salad</v>
+        <v>Curry style</v>
       </c>
       <c r="I47" t="str">
         <v>{}</v>
@@ -7429,7 +7329,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>lunch_dinner_chicken-red-curry-rice</v>
+        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
       </c>
       <c r="B48" t="str">
         <v>Chicken breast</v>
@@ -7441,16 +7341,16 @@
         <v>Cooked rice</v>
       </c>
       <c r="E48">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F48" t="str">
-        <v>Red curry vegetables</v>
+        <v>Kimchi + spinach</v>
       </c>
       <c r="G48">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H48" t="str">
-        <v>Curry style</v>
+        <v>Bowl</v>
       </c>
       <c r="I48" t="str">
         <v>{}</v>
@@ -7458,28 +7358,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>lunch_dinner_korean-chicken-bibimbap-bowl</v>
+        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
       </c>
       <c r="B49" t="str">
-        <v>Chicken breast</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C49">
         <v>150</v>
       </c>
       <c r="D49" t="str">
-        <v>Cooked rice</v>
+        <v>Soba noodles</v>
       </c>
       <c r="E49">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F49" t="str">
-        <v>Kimchi + spinach</v>
+        <v>Bok choy</v>
       </c>
       <c r="G49">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H49" t="str">
-        <v>Bowl</v>
+        <v>Grilled</v>
       </c>
       <c r="I49" t="str">
         <v>{}</v>
@@ -7487,28 +7387,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>lunch_dinner_salmon-teriyaki-soba-noodles</v>
+        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
       </c>
       <c r="B50" t="str">
-        <v>Grilled salmon</v>
+        <v>Prawns</v>
       </c>
       <c r="C50">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D50" t="str">
-        <v>Soba noodles</v>
+        <v>Rice noodles</v>
       </c>
       <c r="E50">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F50" t="str">
-        <v>Bok choy</v>
+        <v>Edamame</v>
       </c>
       <c r="G50">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H50" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I50" t="str">
         <v>{}</v>
@@ -7516,28 +7416,28 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>lunch_dinner_prawn-stir-fry-edamame-rice-noodles</v>
+        <v>lunch_dinner_miso-chicken-ramen-egg</v>
       </c>
       <c r="B51" t="str">
-        <v>Prawns</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C51">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="D51" t="str">
-        <v>Rice noodles</v>
+        <v>Egg noodles</v>
       </c>
       <c r="E51">
         <v>120</v>
       </c>
       <c r="F51" t="str">
-        <v>Edamame</v>
+        <v>Bok choy</v>
       </c>
       <c r="G51">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H51" t="str">
-        <v>Pan-fried</v>
+        <v>Soup style</v>
       </c>
       <c r="I51" t="str">
         <v>{}</v>
@@ -7545,25 +7445,25 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>lunch_dinner_miso-chicken-ramen-egg</v>
+        <v>lunch_dinner_tofu-edamame-ramen</v>
       </c>
       <c r="B52" t="str">
-        <v>Chicken breast</v>
+        <v>Firm tofu</v>
       </c>
       <c r="C52">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="D52" t="str">
         <v>Egg noodles</v>
       </c>
       <c r="E52">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F52" t="str">
-        <v>Bok choy</v>
+        <v>Bok choy + edamame</v>
       </c>
       <c r="G52">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="H52" t="str">
         <v>Soup style</v>
@@ -7574,28 +7474,28 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>lunch_dinner_tofu-edamame-ramen</v>
+        <v>lunch_dinner_butter-chicken-jowar-roti</v>
       </c>
       <c r="B53" t="str">
-        <v>Firm tofu</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C53">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D53" t="str">
-        <v>Egg noodles</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E53">
+        <v>1.5</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Cauliflower</v>
+      </c>
+      <c r="G53">
         <v>100</v>
       </c>
-      <c r="F53" t="str">
-        <v>Bok choy + edamame</v>
-      </c>
-      <c r="G53">
-        <v>180</v>
-      </c>
       <c r="H53" t="str">
-        <v>Soup style</v>
+        <v>Curry style</v>
       </c>
       <c r="I53" t="str">
         <v>{}</v>
@@ -7603,7 +7503,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>lunch_dinner_butter-chicken-jowar-roti</v>
+        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
       </c>
       <c r="B54" t="str">
         <v>Chicken breast</v>
@@ -7612,19 +7512,19 @@
         <v>150</v>
       </c>
       <c r="D54" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Sweet potato</v>
       </c>
       <c r="E54">
-        <v>1.5</v>
+        <v>150</v>
       </c>
       <c r="F54" t="str">
-        <v>Cauliflower</v>
+        <v>Broccoli</v>
       </c>
       <c r="G54">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H54" t="str">
-        <v>Curry style</v>
+        <v>Grilled</v>
       </c>
       <c r="I54" t="str">
         <v>{}</v>
@@ -7632,28 +7532,28 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>lunch_dinner_grilled-chicken-sweet-potato-broccoli</v>
+        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
       </c>
       <c r="B55" t="str">
-        <v>Chicken breast</v>
+        <v>Beef steak</v>
       </c>
       <c r="C55">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D55" t="str">
-        <v>Sweet potato</v>
+        <v>Garlic rice</v>
       </c>
       <c r="E55">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F55" t="str">
-        <v>Broccoli</v>
+        <v>Bok choy</v>
       </c>
       <c r="G55">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H55" t="str">
-        <v>Grilled</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I55" t="str">
         <v>{}</v>
@@ -7661,28 +7561,28 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>lunch_dinner_pepper-beef-garlic-rice-greens</v>
+        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
       </c>
       <c r="B56" t="str">
-        <v>Beef steak</v>
+        <v>Paneer</v>
       </c>
       <c r="C56">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D56" t="str">
-        <v>Garlic rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E56">
-        <v>120</v>
+        <v>1.5</v>
       </c>
       <c r="F56" t="str">
-        <v>Bok choy</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G56">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H56" t="str">
-        <v>Pan-fried</v>
+        <v>Tandoori</v>
       </c>
       <c r="I56" t="str">
         <v>{}</v>
@@ -7690,28 +7590,28 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>lunch_dinner_paneer-tikka-jowar-roti-salad</v>
+        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
       </c>
       <c r="B57" t="str">
-        <v>Paneer</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C57">
+        <v>180</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Sweet potato</v>
+      </c>
+      <c r="E57">
         <v>150</v>
       </c>
-      <c r="D57" t="str">
-        <v>Jowar roti (millet)</v>
-      </c>
-      <c r="E57">
-        <v>1.5</v>
-      </c>
       <c r="F57" t="str">
-        <v>Mixed greens salad</v>
+        <v>Sautéed spinach</v>
       </c>
       <c r="G57">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H57" t="str">
-        <v>Tandoori</v>
+        <v>Grilled</v>
       </c>
       <c r="I57" t="str">
         <v>{}</v>
@@ -7719,28 +7619,28 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>lunch_dinner_grilled-salmon-sweet-potato-spinach</v>
+        <v>lunch_dinner_chicken-biryani-raita</v>
       </c>
       <c r="B58" t="str">
-        <v>Grilled salmon</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C58">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D58" t="str">
-        <v>Sweet potato</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E58">
         <v>150</v>
       </c>
       <c r="F58" t="str">
-        <v>Sautéed spinach</v>
-      </c>
-      <c r="G58">
-        <v>120</v>
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
       </c>
       <c r="H58" t="str">
-        <v>Grilled</v>
+        <v>Curry style</v>
       </c>
       <c r="I58" t="str">
         <v>{}</v>
@@ -7748,25 +7648,25 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>lunch_dinner_chicken-biryani-raita</v>
+        <v>lunch_dinner_fish-moilee-rice</v>
       </c>
       <c r="B59" t="str">
-        <v>Chicken breast</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C59">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D59" t="str">
         <v>Cooked rice</v>
       </c>
       <c r="E59">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F59" t="str">
-        <v/>
-      </c>
-      <c r="G59" t="str">
-        <v/>
+        <v>Mixed veg sabzi</v>
+      </c>
+      <c r="G59">
+        <v>80</v>
       </c>
       <c r="H59" t="str">
         <v>Curry style</v>
@@ -7777,22 +7677,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>lunch_dinner_fish-moilee-rice</v>
+        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
       </c>
       <c r="B60" t="str">
-        <v>Fish fillet</v>
+        <v>Eggs (whole)</v>
       </c>
       <c r="C60">
         <v>200</v>
       </c>
       <c r="D60" t="str">
-        <v>Cooked rice</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E60">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Dal</v>
       </c>
       <c r="G60">
         <v>80</v>
@@ -7806,28 +7706,28 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>lunch_dinner_egg-curry-dal-jowar-roti</v>
+        <v>lunch_dinner_chicken-shawarma-bowl</v>
       </c>
       <c r="B61" t="str">
-        <v>Eggs (whole)</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C61">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="D61" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Flatbread</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="str">
-        <v>Dal</v>
+        <v>Salad + hummus</v>
       </c>
       <c r="G61">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="H61" t="str">
-        <v>Curry style</v>
+        <v>Bowl</v>
       </c>
       <c r="I61" t="str">
         <v>{}</v>
@@ -7835,28 +7735,28 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>lunch_dinner_chicken-shawarma-bowl</v>
+        <v>lunch_dinner_prawn-curry-rice</v>
       </c>
       <c r="B62" t="str">
-        <v>Chicken breast</v>
+        <v>Prawns</v>
       </c>
       <c r="C62">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="D62" t="str">
-        <v>Flatbread</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="F62" t="str">
-        <v>Salad + hummus</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G62">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="H62" t="str">
-        <v>Bowl</v>
+        <v>Curry style</v>
       </c>
       <c r="I62" t="str">
         <v>{}</v>
@@ -7864,28 +7764,28 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>lunch_dinner_prawn-curry-rice</v>
+        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
       </c>
       <c r="B63" t="str">
-        <v>Prawns</v>
+        <v>Chicken keema</v>
       </c>
       <c r="C63">
         <v>180</v>
       </c>
       <c r="D63" t="str">
-        <v>Cooked rice</v>
+        <v>Spaghetti</v>
       </c>
       <c r="E63">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="F63" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G63">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H63" t="str">
-        <v>Curry style</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I63" t="str">
         <v>{}</v>
@@ -7893,28 +7793,28 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>lunch_dinner_chicken-meatballs-spaghetti-salad</v>
+        <v>lunch_dinner_palak-paneer-jowar-roti</v>
       </c>
       <c r="B64" t="str">
-        <v>Chicken keema</v>
+        <v>Paneer</v>
       </c>
       <c r="C64">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D64" t="str">
-        <v>Spaghetti</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E64">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F64" t="str">
-        <v>Mixed greens salad</v>
+        <v>Spinach</v>
       </c>
       <c r="G64">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H64" t="str">
-        <v>Pan-fried</v>
+        <v>Curry style</v>
       </c>
       <c r="I64" t="str">
         <v>{}</v>
@@ -7922,13 +7822,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>lunch_dinner_rajma-paneer-bowl</v>
+        <v>lunch_dinner_achari-paneer-tikka-dal-salad</v>
       </c>
       <c r="B65" t="str">
-        <v>Paneer + rajma</v>
+        <v>Paneer</v>
       </c>
       <c r="C65">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="D65" t="str">
         <v>No carb</v>
@@ -7937,13 +7837,13 @@
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v/>
-      </c>
-      <c r="G65" t="str">
-        <v/>
+        <v>Dal + salad</v>
+      </c>
+      <c r="G65">
+        <v>250</v>
       </c>
       <c r="H65" t="str">
-        <v>Curry style</v>
+        <v>Tandoori</v>
       </c>
       <c r="I65" t="str">
         <v>{}</v>
@@ -7951,25 +7851,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>lunch_dinner_palak-paneer-jowar-roti</v>
+        <v>lunch_dinner_soya-keema-curry-jowar-roti</v>
       </c>
       <c r="B66" t="str">
-        <v>Paneer</v>
+        <v>Soya chunks (minced)</v>
       </c>
       <c r="C66">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="D66" t="str">
         <v>Jowar roti (millet)</v>
       </c>
       <c r="E66">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F66" t="str">
-        <v>Spinach</v>
-      </c>
-      <c r="G66">
-        <v>200</v>
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
       </c>
       <c r="H66" t="str">
         <v>Curry style</v>
@@ -7980,13 +7880,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>lunch_dinner_achari-paneer-tikka-dal-salad</v>
+        <v>lunch_dinner_chole-paneer-bowl-salad</v>
       </c>
       <c r="B67" t="str">
-        <v>Paneer</v>
+        <v>Paneer + chole</v>
       </c>
       <c r="C67">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="D67" t="str">
         <v>No carb</v>
@@ -7995,13 +7895,13 @@
         <v>0</v>
       </c>
       <c r="F67" t="str">
-        <v>Dal + salad</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G67">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H67" t="str">
-        <v>Tandoori</v>
+        <v>Bowl</v>
       </c>
       <c r="I67" t="str">
         <v>{}</v>
@@ -8009,25 +7909,25 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>lunch_dinner_soya-keema-curry-jowar-roti</v>
+        <v>lunch_dinner_kadai-chicken-jowar-roti</v>
       </c>
       <c r="B68" t="str">
-        <v>Soya chunks (minced)</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C68">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="D68" t="str">
         <v>Jowar roti (millet)</v>
       </c>
       <c r="E68">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F68" t="str">
-        <v/>
-      </c>
-      <c r="G68" t="str">
-        <v/>
+        <v>Capsicum + salad</v>
+      </c>
+      <c r="G68">
+        <v>80</v>
       </c>
       <c r="H68" t="str">
         <v>Curry style</v>
@@ -8038,28 +7938,28 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>lunch_dinner_chole-paneer-bowl-salad</v>
+        <v>lunch_dinner_tandoori-fish-tikka-veg-roti</v>
       </c>
       <c r="B69" t="str">
-        <v>Paneer + chole</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C69">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="D69" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F69" t="str">
-        <v>Mixed greens salad</v>
+        <v>Mixed veg sabzi</v>
       </c>
       <c r="G69">
         <v>100</v>
       </c>
       <c r="H69" t="str">
-        <v>Bowl</v>
+        <v>Tandoori</v>
       </c>
       <c r="I69" t="str">
         <v>{}</v>
@@ -8067,25 +7967,25 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>lunch_dinner_kadai-chicken-jowar-roti</v>
+        <v>lunch_dinner_chicken-keema-matar-jowar-roti</v>
       </c>
       <c r="B70" t="str">
-        <v>Chicken breast</v>
+        <v>Chicken keema</v>
       </c>
       <c r="C70">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D70" t="str">
         <v>Jowar roti (millet)</v>
       </c>
       <c r="E70">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F70" t="str">
-        <v>Capsicum + salad</v>
+        <v>Peas / edamame</v>
       </c>
       <c r="G70">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H70" t="str">
         <v>Curry style</v>
@@ -8096,28 +7996,28 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>lunch_dinner_tandoori-fish-tikka-veg-roti</v>
+        <v>lunch_dinner_beef-bulgogi-bowl</v>
       </c>
       <c r="B71" t="str">
-        <v>Fish fillet</v>
+        <v>Beef steak (lean sirloin)</v>
       </c>
       <c r="C71">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="D71" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E71">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F71" t="str">
-        <v>Mixed veg sabzi</v>
+        <v>Kimchi + spinach</v>
       </c>
       <c r="G71">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="H71" t="str">
-        <v>Tandoori</v>
+        <v>Bowl</v>
       </c>
       <c r="I71" t="str">
         <v>{}</v>
@@ -8125,28 +8025,28 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>lunch_dinner_chicken-keema-matar-jowar-roti</v>
+        <v>lunch_dinner_tofu-veg-bibimbap</v>
       </c>
       <c r="B72" t="str">
-        <v>Chicken keema</v>
+        <v>Firm tofu + egg</v>
       </c>
       <c r="C72">
+        <v>250</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Cooked rice</v>
+      </c>
+      <c r="E72">
+        <v>90</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Kimchi + spinach namul</v>
+      </c>
+      <c r="G72">
         <v>180</v>
       </c>
-      <c r="D72" t="str">
-        <v>Jowar roti (millet)</v>
-      </c>
-      <c r="E72">
-        <v>40</v>
-      </c>
-      <c r="F72" t="str">
-        <v>Peas / edamame</v>
-      </c>
-      <c r="G72">
-        <v>60</v>
-      </c>
       <c r="H72" t="str">
-        <v>Curry style</v>
+        <v>Bowl</v>
       </c>
       <c r="I72" t="str">
         <v>{}</v>
@@ -8154,25 +8054,25 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>lunch_dinner_beef-bulgogi-bowl</v>
+        <v>lunch_dinner_oyakodon-side-salad</v>
       </c>
       <c r="B73" t="str">
-        <v>Beef steak (lean sirloin)</v>
+        <v>Chicken breast + egg</v>
       </c>
       <c r="C73">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="D73" t="str">
         <v>Cooked rice</v>
       </c>
       <c r="E73">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F73" t="str">
-        <v>Kimchi + spinach</v>
+        <v>Side salad</v>
       </c>
       <c r="G73">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="H73" t="str">
         <v>Bowl</v>
@@ -8183,13 +8083,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>lunch_dinner_tofu-veg-bibimbap</v>
+        <v>lunch_dinner_dubu-jorim-rice-kimchi</v>
       </c>
       <c r="B74" t="str">
-        <v>Firm tofu + egg</v>
+        <v>Firm tofu</v>
       </c>
       <c r="C74">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="D74" t="str">
         <v>Cooked rice</v>
@@ -8198,13 +8098,13 @@
         <v>90</v>
       </c>
       <c r="F74" t="str">
-        <v>Kimchi + spinach namul</v>
+        <v>Kimchi</v>
       </c>
       <c r="G74">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="H74" t="str">
-        <v>Bowl</v>
+        <v>Curry style</v>
       </c>
       <c r="I74" t="str">
         <v>{}</v>
@@ -8212,10 +8112,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>lunch_dinner_oyakodon-side-salad</v>
+        <v>lunch_dinner_home-style-tofu-chicken-stir-fry</v>
       </c>
       <c r="B75" t="str">
-        <v>Chicken breast + egg</v>
+        <v>Chicken breast + tofu</v>
       </c>
       <c r="C75">
         <v>240</v>
@@ -8224,16 +8124,16 @@
         <v>Cooked rice</v>
       </c>
       <c r="E75">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F75" t="str">
-        <v>Side salad</v>
+        <v>Broccoli</v>
       </c>
       <c r="G75">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="H75" t="str">
-        <v>Bowl</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I75" t="str">
         <v>{}</v>
@@ -8241,28 +8141,28 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>lunch_dinner_dubu-jorim-rice-kimchi</v>
+        <v>lunch_dinner_vietnamese-lemongrass-chicken-bowl</v>
       </c>
       <c r="B76" t="str">
-        <v>Firm tofu</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C76">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="D76" t="str">
-        <v>Cooked rice</v>
+        <v>Rice noodles</v>
       </c>
       <c r="E76">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F76" t="str">
-        <v>Kimchi</v>
+        <v>Herb salad + pickles</v>
       </c>
       <c r="G76">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="H76" t="str">
-        <v>Curry style</v>
+        <v>Bowl</v>
       </c>
       <c r="I76" t="str">
         <v>{}</v>
@@ -8270,28 +8170,28 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>lunch_dinner_home-style-tofu-chicken-stir-fry</v>
+        <v>lunch_dinner_cantonese-steamed-fish-edamame</v>
       </c>
       <c r="B77" t="str">
-        <v>Chicken breast + tofu</v>
+        <v>Fish fillet</v>
       </c>
       <c r="C77">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="D77" t="str">
         <v>Cooked rice</v>
       </c>
       <c r="E77">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F77" t="str">
-        <v>Broccoli</v>
+        <v>Bok choy + edamame</v>
       </c>
       <c r="G77">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="H77" t="str">
-        <v>Pan-fried</v>
+        <v>Steamed</v>
       </c>
       <c r="I77" t="str">
         <v>{}</v>
@@ -8299,25 +8199,25 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>lunch_dinner_vietnamese-lemongrass-chicken-bowl</v>
+        <v>lunch_dinner_chicken-bulgogi-bowl</v>
       </c>
       <c r="B78" t="str">
         <v>Chicken breast</v>
       </c>
       <c r="C78">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D78" t="str">
-        <v>Rice noodles</v>
+        <v>Cooked rice</v>
       </c>
       <c r="E78">
         <v>100</v>
       </c>
       <c r="F78" t="str">
-        <v>Herb salad + pickles</v>
+        <v>Kimchi + bok choy</v>
       </c>
       <c r="G78">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H78" t="str">
         <v>Bowl</v>
@@ -8328,28 +8228,28 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>lunch_dinner_cantonese-steamed-fish-edamame</v>
+        <v>lunch_dinner_chicken-souvlaki-tzatziki-greek-salad</v>
       </c>
       <c r="B79" t="str">
-        <v>Fish fillet</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C79">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D79" t="str">
-        <v>Cooked rice</v>
+        <v>No carb</v>
       </c>
       <c r="E79">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F79" t="str">
-        <v>Bok choy + edamame</v>
+        <v>Greek salad + tzatziki</v>
       </c>
       <c r="G79">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="H79" t="str">
-        <v>Steamed</v>
+        <v>Grilled</v>
       </c>
       <c r="I79" t="str">
         <v>{}</v>
@@ -8357,28 +8257,28 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>lunch_dinner_chicken-bulgogi-bowl</v>
+        <v>lunch_dinner_baked-feta-chickpea-traybake</v>
       </c>
       <c r="B80" t="str">
-        <v>Chicken breast</v>
+        <v>Feta + chickpeas</v>
       </c>
       <c r="C80">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="D80" t="str">
-        <v>Cooked rice</v>
+        <v>No carb</v>
       </c>
       <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Roast vegetables + greens</v>
+      </c>
+      <c r="G80">
         <v>100</v>
       </c>
-      <c r="F80" t="str">
-        <v>Kimchi + bok choy</v>
-      </c>
-      <c r="G80">
-        <v>180</v>
-      </c>
       <c r="H80" t="str">
-        <v>Bowl</v>
+        <v>Plate</v>
       </c>
       <c r="I80" t="str">
         <v>{}</v>
@@ -8386,28 +8286,28 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>lunch_dinner_chicken-souvlaki-tzatziki-greek-salad</v>
+        <v>lunch_dinner_tuna-nicoise-salad</v>
       </c>
       <c r="B81" t="str">
-        <v>Chicken breast</v>
+        <v>Tuna + egg</v>
       </c>
       <c r="C81">
+        <v>250</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Sweet potato</v>
+      </c>
+      <c r="E81">
+        <v>80</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Salad + olives</v>
+      </c>
+      <c r="G81">
         <v>180</v>
       </c>
-      <c r="D81" t="str">
-        <v>No carb</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81" t="str">
-        <v>Greek salad + tzatziki</v>
-      </c>
-      <c r="G81">
-        <v>220</v>
-      </c>
       <c r="H81" t="str">
-        <v>Grilled</v>
+        <v>Salad</v>
       </c>
       <c r="I81" t="str">
         <v>{}</v>
@@ -8415,28 +8315,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>lunch_dinner_baked-feta-chickpea-traybake</v>
+        <v>lunch_dinner_halloumi-roasted-veg-quinoa-bowl</v>
       </c>
       <c r="B82" t="str">
-        <v>Feta + chickpeas</v>
+        <v>Halloumi</v>
       </c>
       <c r="C82">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="D82" t="str">
-        <v>No carb</v>
+        <v>Quinoa</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F82" t="str">
-        <v>Roast vegetables + greens</v>
+        <v>Roast broccoli</v>
       </c>
       <c r="G82">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H82" t="str">
-        <v>Plate</v>
+        <v>Bowl</v>
       </c>
       <c r="I82" t="str">
         <v>{}</v>
@@ -8444,28 +8344,28 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>lunch_dinner_tuna-nicoise-salad</v>
+        <v>lunch_dinner_chicken-white-bean-stew</v>
       </c>
       <c r="B83" t="str">
-        <v>Tuna + egg</v>
+        <v>Chicken breast + white beans</v>
       </c>
       <c r="C83">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="D83" t="str">
-        <v>Sweet potato</v>
+        <v>No carb</v>
       </c>
       <c r="E83">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F83" t="str">
-        <v>Salad + olives</v>
+        <v>Spinach + tomato</v>
       </c>
       <c r="G83">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="H83" t="str">
-        <v>Salad</v>
+        <v>Soup style</v>
       </c>
       <c r="I83" t="str">
         <v>{}</v>
@@ -8473,28 +8373,28 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>lunch_dinner_halloumi-roasted-veg-quinoa-bowl</v>
+        <v>lunch_dinner_chickpea-pasta-tuna-tomato</v>
       </c>
       <c r="B84" t="str">
-        <v>Halloumi</v>
+        <v>Tuna</v>
       </c>
       <c r="C84">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D84" t="str">
-        <v>Quinoa</v>
+        <v>Chickpea pasta</v>
       </c>
       <c r="E84">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="F84" t="str">
-        <v>Roast broccoli</v>
+        <v>Arrabbiata + side salad</v>
       </c>
       <c r="G84">
         <v>120</v>
       </c>
       <c r="H84" t="str">
-        <v>Bowl</v>
+        <v>Plate</v>
       </c>
       <c r="I84" t="str">
         <v>{}</v>
@@ -8502,28 +8402,28 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>lunch_dinner_chicken-white-bean-stew</v>
+        <v>lunch_dinner_chicken-ricotta-carbonara-style-spaghetti</v>
       </c>
       <c r="B85" t="str">
-        <v>Chicken breast + white beans</v>
+        <v>Chicken breast + ricotta</v>
       </c>
       <c r="C85">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="D85" t="str">
-        <v>No carb</v>
+        <v>Spaghetti</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F85" t="str">
-        <v>Spinach + tomato</v>
-      </c>
-      <c r="G85">
-        <v>140</v>
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
       </c>
       <c r="H85" t="str">
-        <v>Soup style</v>
+        <v>Plate</v>
       </c>
       <c r="I85" t="str">
         <v>{}</v>
@@ -8531,28 +8431,28 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>lunch_dinner_chickpea-pasta-tuna-tomato</v>
+        <v>lunch_dinner_mackerel-quinoa-salad</v>
       </c>
       <c r="B86" t="str">
-        <v>Tuna</v>
+        <v>Mackerel</v>
       </c>
       <c r="C86">
         <v>120</v>
       </c>
       <c r="D86" t="str">
-        <v>Chickpea pasta</v>
+        <v>Quinoa</v>
       </c>
       <c r="E86">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="F86" t="str">
-        <v>Arrabbiata + side salad</v>
+        <v>Salad + avocado</v>
       </c>
       <c r="G86">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H86" t="str">
-        <v>Plate</v>
+        <v>Salad</v>
       </c>
       <c r="I86" t="str">
         <v>{}</v>
@@ -8560,28 +8460,28 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>lunch_dinner_chicken-ricotta-carbonara-style-spaghetti</v>
+        <v>lunch_dinner_grilled-chicken-veg-pasta</v>
       </c>
       <c r="B87" t="str">
-        <v>Chicken breast + ricotta</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C87">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D87" t="str">
         <v>Spaghetti</v>
       </c>
       <c r="E87">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F87" t="str">
-        <v/>
-      </c>
-      <c r="G87" t="str">
-        <v/>
+        <v>Sabzi + salad</v>
+      </c>
+      <c r="G87">
+        <v>180</v>
       </c>
       <c r="H87" t="str">
-        <v>Plate</v>
+        <v>Grilled</v>
       </c>
       <c r="I87" t="str">
         <v>{}</v>
@@ -8589,28 +8489,28 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>lunch_dinner_mackerel-quinoa-salad</v>
+        <v>lunch_dinner_chicken-shawarma-plate-garlic-rice</v>
       </c>
       <c r="B88" t="str">
-        <v>Mackerel</v>
+        <v>Chicken breast</v>
       </c>
       <c r="C88">
+        <v>180</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Garlic rice</v>
+      </c>
+      <c r="E88">
+        <v>150</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Salad + hummus</v>
+      </c>
+      <c r="G88">
         <v>120</v>
       </c>
-      <c r="D88" t="str">
-        <v>Quinoa</v>
-      </c>
-      <c r="E88">
-        <v>120</v>
-      </c>
-      <c r="F88" t="str">
-        <v>Salad + avocado</v>
-      </c>
-      <c r="G88">
-        <v>160</v>
-      </c>
       <c r="H88" t="str">
-        <v>Salad</v>
+        <v>Plate</v>
       </c>
       <c r="I88" t="str">
         <v>{}</v>
@@ -8618,28 +8518,28 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>lunch_dinner_grilled-chicken-veg-pasta</v>
+        <v>lunch_dinner_plain-chicken-tikka-plate</v>
       </c>
       <c r="B89" t="str">
         <v>Chicken breast</v>
       </c>
       <c r="C89">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D89" t="str">
-        <v>Spaghetti</v>
+        <v>Jowar roti (millet)</v>
       </c>
       <c r="E89">
+        <v>45</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Mixed greens salad</v>
+      </c>
+      <c r="G89">
         <v>100</v>
       </c>
-      <c r="F89" t="str">
-        <v>Sabzi + salad</v>
-      </c>
-      <c r="G89">
-        <v>180</v>
-      </c>
       <c r="H89" t="str">
-        <v>Grilled</v>
+        <v>Tandoori</v>
       </c>
       <c r="I89" t="str">
         <v>{}</v>
@@ -8647,25 +8547,25 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>lunch_dinner_chicken-shawarma-plate-garlic-rice</v>
+        <v>lunch_dinner_pesto-millet-pasta-chicken</v>
       </c>
       <c r="B90" t="str">
         <v>Chicken breast</v>
       </c>
       <c r="C90">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="D90" t="str">
-        <v>Garlic rice</v>
+        <v>Millet pasta</v>
       </c>
       <c r="E90">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F90" t="str">
-        <v>Salad + hummus</v>
+        <v>Cherry tomatoes</v>
       </c>
       <c r="G90">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H90" t="str">
         <v>Plate</v>
@@ -8676,28 +8576,28 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>lunch_dinner_plain-chicken-tikka-plate</v>
+        <v>lunch_dinner_aglio-olio-millet-pasta-prawns</v>
       </c>
       <c r="B91" t="str">
-        <v>Chicken breast</v>
+        <v>Prawns</v>
       </c>
       <c r="C91">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D91" t="str">
-        <v>Jowar roti (millet)</v>
+        <v>Millet pasta</v>
       </c>
       <c r="E91">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F91" t="str">
-        <v>Mixed greens salad</v>
-      </c>
-      <c r="G91">
-        <v>100</v>
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
       </c>
       <c r="H91" t="str">
-        <v>Tandoori</v>
+        <v>Plate</v>
       </c>
       <c r="I91" t="str">
         <v>{}</v>
@@ -8705,28 +8605,28 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>lunch_dinner_pesto-millet-pasta-chicken</v>
+        <v>lunch_dinner_salmon-avocado-salad-fresh-grilled</v>
       </c>
       <c r="B92" t="str">
-        <v>Chicken breast</v>
+        <v>Grilled salmon</v>
       </c>
       <c r="C92">
         <v>120</v>
       </c>
       <c r="D92" t="str">
-        <v>Millet pasta</v>
+        <v>No carb</v>
       </c>
       <c r="E92">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F92" t="str">
-        <v>Cherry tomatoes</v>
+        <v>Avocado + greens</v>
       </c>
       <c r="G92">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="H92" t="str">
-        <v>Plate</v>
+        <v>Salad</v>
       </c>
       <c r="I92" t="str">
         <v>{}</v>
@@ -8734,28 +8634,28 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>lunch_dinner_aglio-olio-millet-pasta-prawns</v>
+        <v>lunch_dinner_smoked-chicken-salad-full</v>
       </c>
       <c r="B93" t="str">
-        <v>Prawns</v>
+        <v>Smoked chicken breast</v>
       </c>
       <c r="C93">
         <v>150</v>
       </c>
       <c r="D93" t="str">
-        <v>Millet pasta</v>
+        <v>No carb</v>
       </c>
       <c r="E93">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F93" t="str">
-        <v/>
-      </c>
-      <c r="G93" t="str">
-        <v/>
+        <v>Avocado + greens</v>
+      </c>
+      <c r="G93">
+        <v>180</v>
       </c>
       <c r="H93" t="str">
-        <v>Plate</v>
+        <v>Salad</v>
       </c>
       <c r="I93" t="str">
         <v>{}</v>
@@ -8763,13 +8663,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>lunch_dinner_salmon-avocado-salad-fresh-grilled</v>
+        <v>lunch_dinner_hummus-salad-protein-boosted</v>
       </c>
       <c r="B94" t="str">
-        <v>Grilled salmon</v>
+        <v>Chicken breast + hummus</v>
       </c>
       <c r="C94">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="D94" t="str">
         <v>No carb</v>
@@ -8778,13 +8678,13 @@
         <v>0</v>
       </c>
       <c r="F94" t="str">
-        <v>Avocado + greens</v>
+        <v>Salad + raw veg</v>
       </c>
       <c r="G94">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H94" t="str">
-        <v>Salad</v>
+        <v>Bowl</v>
       </c>
       <c r="I94" t="str">
         <v>{}</v>
@@ -8792,28 +8692,28 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>lunch_dinner_smoked-chicken-salad-full</v>
+        <v>lunch_dinner_sweet-potato-kaala-chana-leaner</v>
       </c>
       <c r="B95" t="str">
-        <v>Smoked chicken breast</v>
+        <v>Kaala chanaa (black chickpeas)</v>
       </c>
       <c r="C95">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D95" t="str">
-        <v>No carb</v>
+        <v>Jowar roti (millet) + sweet potato</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F95" t="str">
-        <v>Avocado + greens</v>
-      </c>
-      <c r="G95">
-        <v>180</v>
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
       </c>
       <c r="H95" t="str">
-        <v>Salad</v>
+        <v>Curry style</v>
       </c>
       <c r="I95" t="str">
         <v>{}</v>
@@ -8821,28 +8721,28 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>lunch_dinner_hummus-salad-protein-boosted</v>
+        <v>lunch_dinner_paneer-cutlets-dal-salad</v>
       </c>
       <c r="B96" t="str">
-        <v>Chicken breast + hummus</v>
+        <v>Paneer cutlets + dal</v>
       </c>
       <c r="C96">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="D96" t="str">
-        <v>No carb</v>
+        <v>Besan + breadcrumbs</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F96" t="str">
-        <v>Salad + raw veg</v>
+        <v>Mixed greens salad</v>
       </c>
       <c r="G96">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="H96" t="str">
-        <v>Bowl</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I96" t="str">
         <v>{}</v>
@@ -8850,28 +8750,28 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>lunch_dinner_sweet-potato-kaala-chana-leaner</v>
+        <v>snack_fruit-almonds-plant-shake</v>
       </c>
       <c r="B97" t="str">
-        <v>Kaala chanaa (black chickpeas)</v>
+        <v>Plant Shake</v>
       </c>
       <c r="C97">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="D97" t="str">
-        <v>Jowar roti (millet) + sweet potato</v>
+        <v>Mixed Fruit</v>
       </c>
       <c r="E97">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="F97" t="str">
-        <v/>
-      </c>
-      <c r="G97" t="str">
-        <v/>
+        <v>Almonds</v>
+      </c>
+      <c r="G97">
+        <v>5</v>
       </c>
       <c r="H97" t="str">
-        <v>Curry style</v>
+        <v>Snack</v>
       </c>
       <c r="I97" t="str">
         <v>{}</v>
@@ -8879,28 +8779,28 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>lunch_dinner_paneer-cutlets-dal-salad</v>
+        <v>snack_chaat-bhel-protein-shake</v>
       </c>
       <c r="B98" t="str">
-        <v>Paneer cutlets + dal</v>
+        <v>Plant Shake</v>
       </c>
       <c r="C98">
-        <v>260</v>
+        <v>25</v>
       </c>
       <c r="D98" t="str">
-        <v>Besan + breadcrumbs</v>
+        <v>Chaat &amp; Bhel</v>
       </c>
       <c r="E98">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="F98" t="str">
-        <v>Mixed greens salad</v>
-      </c>
-      <c r="G98">
-        <v>100</v>
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
       </c>
       <c r="H98" t="str">
-        <v>Pan-fried</v>
+        <v>Street Food Twist</v>
       </c>
       <c r="I98" t="str">
         <v>{}</v>
@@ -8908,28 +8808,28 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>snack_fruit-almonds-plant-shake</v>
+        <v>snack_greek-yogurt-berry-bowl</v>
       </c>
       <c r="B99" t="str">
-        <v>Plant Shake</v>
+        <v/>
       </c>
       <c r="C99">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D99" t="str">
-        <v>Mixed Fruit</v>
+        <v>No carb</v>
       </c>
       <c r="E99">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F99" t="str">
-        <v>Almonds</v>
-      </c>
-      <c r="G99">
-        <v>5</v>
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
       </c>
       <c r="H99" t="str">
-        <v>Snack</v>
+        <v>Grilled</v>
       </c>
       <c r="I99" t="str">
         <v>{}</v>
@@ -8937,19 +8837,19 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>snack_chaat-bhel-protein-shake</v>
+        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
       </c>
       <c r="B100" t="str">
-        <v>Plant Shake</v>
+        <v/>
       </c>
       <c r="C100">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D100" t="str">
-        <v>Chaat &amp; Bhel</v>
+        <v>No carb</v>
       </c>
       <c r="E100">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F100" t="str">
         <v/>
@@ -8958,7 +8858,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Street Food Twist</v>
+        <v>Grilled</v>
       </c>
       <c r="I100" t="str">
         <v>{}</v>
@@ -8966,13 +8866,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>snack_greek-yogurt-berry-bowl</v>
+        <v>snack_nuts-seeds-protein-shake</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>Mixed nuts &amp; seeds</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D101" t="str">
         <v>No carb</v>
@@ -8987,7 +8887,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Grilled</v>
+        <v>Raw</v>
       </c>
       <c r="I101" t="str">
         <v>{}</v>
@@ -8995,7 +8895,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>snack_carrot-halwa-sugar-free-protein-shake</v>
+        <v>snack_sweet-potato-chaat</v>
       </c>
       <c r="B102" t="str">
         <v/>
@@ -9004,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="D102" t="str">
-        <v>No carb</v>
+        <v>Sweet potato</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F102" t="str">
         <v/>
@@ -9016,7 +8916,7 @@
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Grilled</v>
+        <v>Chaat</v>
       </c>
       <c r="I102" t="str">
         <v>{}</v>
@@ -9024,13 +8924,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>snack_nuts-seeds-protein-shake</v>
+        <v>snack_kaala-chana-chaat</v>
       </c>
       <c r="B103" t="str">
-        <v>Mixed nuts &amp; seeds</v>
+        <v>Kaala chana</v>
       </c>
       <c r="C103">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="D103" t="str">
         <v>No carb</v>
@@ -9045,7 +8945,7 @@
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>Raw</v>
+        <v>Chaat</v>
       </c>
       <c r="I103" t="str">
         <v>{}</v>
@@ -9053,7 +8953,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>snack_sweet-potato-chaat</v>
+        <v>snack_avocado-cheese-toast</v>
       </c>
       <c r="B104" t="str">
         <v/>
@@ -9062,19 +8962,19 @@
         <v>0</v>
       </c>
       <c r="D104" t="str">
-        <v>Sweet potato</v>
+        <v>Whole wheat toast</v>
       </c>
       <c r="E104">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="F104" t="str">
-        <v/>
-      </c>
-      <c r="G104" t="str">
-        <v/>
+        <v>Avocado</v>
+      </c>
+      <c r="G104">
+        <v>50</v>
       </c>
       <c r="H104" t="str">
-        <v>Chaat</v>
+        <v>Toast</v>
       </c>
       <c r="I104" t="str">
         <v>{}</v>
@@ -9082,13 +8982,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>snack_kaala-chana-chaat</v>
+        <v>snack_boiled-eggs-hummus-veg-sticks</v>
       </c>
       <c r="B105" t="str">
-        <v>Kaala chana</v>
+        <v>Eggs (whole)</v>
       </c>
       <c r="C105">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D105" t="str">
         <v>No carb</v>
@@ -9097,13 +8997,13 @@
         <v>0</v>
       </c>
       <c r="F105" t="str">
-        <v/>
-      </c>
-      <c r="G105" t="str">
-        <v/>
+        <v>Raw vegetable sticks</v>
+      </c>
+      <c r="G105">
+        <v>100</v>
       </c>
       <c r="H105" t="str">
-        <v>Chaat</v>
+        <v>Snack</v>
       </c>
       <c r="I105" t="str">
         <v>{}</v>
@@ -9111,28 +9011,28 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>snack_avocado-cheese-toast</v>
+        <v>snack_edamame-sea-salt</v>
       </c>
       <c r="B106" t="str">
+        <v>Edamame</v>
+      </c>
+      <c r="C106">
+        <v>150</v>
+      </c>
+      <c r="D106" t="str">
+        <v>No carb</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106" t="str">
         <v/>
       </c>
-      <c r="C106">
-        <v>0</v>
-      </c>
-      <c r="D106" t="str">
-        <v>Whole wheat toast</v>
-      </c>
-      <c r="E106">
-        <v>1</v>
-      </c>
-      <c r="F106" t="str">
-        <v>Avocado</v>
-      </c>
-      <c r="G106">
-        <v>50</v>
+      <c r="G106" t="str">
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>Toast</v>
+        <v>Steamed</v>
       </c>
       <c r="I106" t="str">
         <v>{}</v>
@@ -9140,13 +9040,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>snack_boiled-eggs-hummus-veg-sticks</v>
+        <v>snack_paneer-tikka-skewers</v>
       </c>
       <c r="B107" t="str">
-        <v>Eggs (whole)</v>
+        <v>Paneer</v>
       </c>
       <c r="C107">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D107" t="str">
         <v>No carb</v>
@@ -9155,13 +9055,13 @@
         <v>0</v>
       </c>
       <c r="F107" t="str">
-        <v>Raw vegetable sticks</v>
+        <v>Mixed greens</v>
       </c>
       <c r="G107">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H107" t="str">
-        <v>Snack</v>
+        <v>Tandoori</v>
       </c>
       <c r="I107" t="str">
         <v>{}</v>
@@ -9169,28 +9069,28 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>snack_edamame-sea-salt</v>
+        <v>snack_overnight-oats-whey-bowl</v>
       </c>
       <c r="B108" t="str">
-        <v>Edamame</v>
+        <v>Milk</v>
       </c>
       <c r="C108">
         <v>150</v>
       </c>
       <c r="D108" t="str">
-        <v>No carb</v>
+        <v>Rolled oats</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F108" t="str">
-        <v/>
-      </c>
-      <c r="G108" t="str">
-        <v/>
+        <v>Mixed berries</v>
+      </c>
+      <c r="G108">
+        <v>60</v>
       </c>
       <c r="H108" t="str">
-        <v>Steamed</v>
+        <v>Bowl</v>
       </c>
       <c r="I108" t="str">
         <v>{}</v>
@@ -9198,13 +9098,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>snack_paneer-tikka-skewers</v>
+        <v>snack_hummus-salad</v>
       </c>
       <c r="B109" t="str">
-        <v>Paneer</v>
+        <v>Hummus</v>
       </c>
       <c r="C109">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D109" t="str">
         <v>No carb</v>
@@ -9213,13 +9113,13 @@
         <v>0</v>
       </c>
       <c r="F109" t="str">
-        <v>Mixed greens</v>
+        <v>Salad + raw veg</v>
       </c>
       <c r="G109">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="H109" t="str">
-        <v>Tandoori</v>
+        <v>Snack</v>
       </c>
       <c r="I109" t="str">
         <v>{}</v>
@@ -9227,25 +9127,25 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>snack_overnight-oats-whey-bowl</v>
+        <v>snack_acai-bowl</v>
       </c>
       <c r="B110" t="str">
-        <v>Milk</v>
+        <v/>
       </c>
       <c r="C110">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D110" t="str">
-        <v>Rolled oats</v>
+        <v>Acai + fruit</v>
       </c>
       <c r="E110">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F110" t="str">
-        <v>Mixed berries</v>
-      </c>
-      <c r="G110">
-        <v>60</v>
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
       </c>
       <c r="H110" t="str">
         <v>Bowl</v>
@@ -9256,94 +9156,36 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>snack_hummus-salad</v>
+        <v>snack_paneer-cutlets</v>
       </c>
       <c r="B111" t="str">
-        <v>Hummus</v>
+        <v>Paneer</v>
       </c>
       <c r="C111">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D111" t="str">
-        <v>No carb</v>
+        <v>Besan + breadcrumbs</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F111" t="str">
-        <v>Salad + raw veg</v>
-      </c>
-      <c r="G111">
-        <v>180</v>
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
       </c>
       <c r="H111" t="str">
-        <v>Snack</v>
+        <v>Pan-fried</v>
       </c>
       <c r="I111" t="str">
-        <v>{}</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>snack_acai-bowl</v>
-      </c>
-      <c r="B112" t="str">
-        <v/>
-      </c>
-      <c r="C112">
-        <v>0</v>
-      </c>
-      <c r="D112" t="str">
-        <v>Acai + fruit</v>
-      </c>
-      <c r="E112">
-        <v>100</v>
-      </c>
-      <c r="F112" t="str">
-        <v/>
-      </c>
-      <c r="G112" t="str">
-        <v/>
-      </c>
-      <c r="H112" t="str">
-        <v>Bowl</v>
-      </c>
-      <c r="I112" t="str">
-        <v>{}</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>snack_paneer-cutlets</v>
-      </c>
-      <c r="B113" t="str">
-        <v>Paneer</v>
-      </c>
-      <c r="C113">
-        <v>55</v>
-      </c>
-      <c r="D113" t="str">
-        <v>Besan + breadcrumbs</v>
-      </c>
-      <c r="E113">
-        <v>16</v>
-      </c>
-      <c r="F113" t="str">
-        <v/>
-      </c>
-      <c r="G113" t="str">
-        <v/>
-      </c>
-      <c r="H113" t="str">
-        <v>Pan-fried</v>
-      </c>
-      <c r="I113" t="str">
         <v>{}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I113"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I111"/>
   </ignoredErrors>
 </worksheet>
 </file>
